--- a/engine/phar_study/EIPICO_Valuation_Model_09082026.xlsx
+++ b/engine/phar_study/EIPICO_Valuation_Model_09082026.xlsx
@@ -819,7 +819,7 @@
         <v>1045.230507</v>
       </c>
       <c r="D2" s="13">
-        <f>Assumptions!$C$62</f>
+        <f>Assumptions!$C$63</f>
         <v/>
       </c>
       <c r="E2" s="13">
@@ -856,7 +856,7 @@
         <v>5693.566382</v>
       </c>
       <c r="D3" s="13">
-        <f>Assumptions!$C$63</f>
+        <f>Assumptions!$C$64</f>
         <v/>
       </c>
       <c r="E3" s="13">
@@ -929,7 +929,7 @@
         <v>3584.699946</v>
       </c>
       <c r="D5" s="13">
-        <f>Assumptions!$C$64</f>
+        <f>Assumptions!$C$65</f>
         <v/>
       </c>
       <c r="E5" s="13">
@@ -966,7 +966,7 @@
         <v>3049.275231</v>
       </c>
       <c r="D6" s="13">
-        <f>Assumptions!$C$65</f>
+        <f>Assumptions!$C$66</f>
         <v/>
       </c>
       <c r="E6" s="13">
@@ -1003,27 +1003,27 @@
         <v>185.584353</v>
       </c>
       <c r="D7" s="13">
-        <f>Assumptions!$C$66</f>
+        <f>Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="E7" s="13">
-        <f>'Income Statement'!E2/9441.379305*Assumptions!$C$66</f>
+        <f>'Income Statement'!E2/9441.379305*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="F7" s="13">
-        <f>'Income Statement'!F2/9441.379305*Assumptions!$C$66</f>
+        <f>'Income Statement'!F2/9441.379305*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="G7" s="13">
-        <f>'Income Statement'!G2/9441.379305*Assumptions!$C$66</f>
+        <f>'Income Statement'!G2/9441.379305*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="H7" s="13">
-        <f>'Income Statement'!H2/9441.379305*Assumptions!$C$66</f>
+        <f>'Income Statement'!H2/9441.379305*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="I7" s="13">
-        <f>'Income Statement'!I2/9441.379305*Assumptions!$C$66</f>
+        <f>'Income Statement'!I2/9441.379305*Assumptions!$C$67</f>
         <v/>
       </c>
     </row>
@@ -1040,27 +1040,27 @@
         <v>1295.38686</v>
       </c>
       <c r="D8" s="13">
-        <f>Assumptions!$C$69</f>
+        <f>Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="E8" s="13">
-        <f>Assumptions!$C$69</f>
+        <f>Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="F8" s="13">
-        <f>Assumptions!$C$69</f>
+        <f>Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="G8" s="13">
-        <f>Assumptions!$C$69</f>
+        <f>Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="H8" s="13">
-        <f>Assumptions!$C$69</f>
+        <f>Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="I8" s="13">
-        <f>Assumptions!$C$69</f>
+        <f>Assumptions!$C$70</f>
         <v/>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
         <v>410.391619</v>
       </c>
       <c r="D10" s="13">
-        <f>Assumptions!$C$67</f>
+        <f>Assumptions!$C$68</f>
         <v/>
       </c>
       <c r="E10" s="13">
@@ -1153,27 +1153,27 @@
         <v>367.42118</v>
       </c>
       <c r="D11" s="13">
-        <f>Assumptions!$C$68</f>
+        <f>Assumptions!$C$69</f>
         <v/>
       </c>
       <c r="E11" s="13">
-        <f>'Income Statement'!E2/9441.379305*Assumptions!$C$68</f>
+        <f>'Income Statement'!E2/9441.379305*Assumptions!$C$69</f>
         <v/>
       </c>
       <c r="F11" s="13">
-        <f>'Income Statement'!F2/9441.379305*Assumptions!$C$68</f>
+        <f>'Income Statement'!F2/9441.379305*Assumptions!$C$69</f>
         <v/>
       </c>
       <c r="G11" s="13">
-        <f>'Income Statement'!G2/9441.379305*Assumptions!$C$68</f>
+        <f>'Income Statement'!G2/9441.379305*Assumptions!$C$69</f>
         <v/>
       </c>
       <c r="H11" s="13">
-        <f>'Income Statement'!H2/9441.379305*Assumptions!$C$68</f>
+        <f>'Income Statement'!H2/9441.379305*Assumptions!$C$69</f>
         <v/>
       </c>
       <c r="I11" s="13">
-        <f>'Income Statement'!I2/9441.379305*Assumptions!$C$68</f>
+        <f>'Income Statement'!I2/9441.379305*Assumptions!$C$69</f>
         <v/>
       </c>
     </row>
@@ -1226,27 +1226,27 @@
         <v>9200.032863</v>
       </c>
       <c r="D13" s="13">
-        <f>Assumptions!$C$70</f>
+        <f>Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="E13" s="13">
-        <f>Assumptions!$C$70</f>
+        <f>Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="F13" s="13">
-        <f>Assumptions!$C$70</f>
+        <f>Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="G13" s="13">
-        <f>Assumptions!$C$70</f>
+        <f>Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="H13" s="13">
-        <f>Assumptions!$C$70</f>
+        <f>Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="I13" s="13">
-        <f>Assumptions!$C$70</f>
+        <f>Assumptions!$C$71</f>
         <v/>
       </c>
     </row>
@@ -1263,27 +1263,27 @@
         <v>4653.769234</v>
       </c>
       <c r="D14" s="13">
-        <f>Assumptions!$C$71</f>
+        <f>Assumptions!$C$72</f>
         <v/>
       </c>
       <c r="E14" s="26">
-        <f>Assumptions!$C$71+'Income Statement'!E25*(1-Assumptions!$C$38)</f>
+        <f>Assumptions!$C$72+'Income Statement'!E26*(1-Assumptions!$C$38)</f>
         <v/>
       </c>
       <c r="F14" s="26">
-        <f>E14+'Income Statement'!F25*(1-Assumptions!$C$38)</f>
+        <f>E14+'Income Statement'!F26*(1-Assumptions!$C$38)</f>
         <v/>
       </c>
       <c r="G14" s="26">
-        <f>F14+'Income Statement'!G25*(1-Assumptions!$C$38)</f>
+        <f>F14+'Income Statement'!G26*(1-Assumptions!$C$38)</f>
         <v/>
       </c>
       <c r="H14" s="26">
-        <f>G14+'Income Statement'!H25*(1-Assumptions!$C$38)</f>
+        <f>G14+'Income Statement'!H26*(1-Assumptions!$C$38)</f>
         <v/>
       </c>
       <c r="I14" s="26">
-        <f>H14+'Income Statement'!I25*(1-Assumptions!$C$38)</f>
+        <f>H14+'Income Statement'!I26*(1-Assumptions!$C$38)</f>
         <v/>
       </c>
     </row>
@@ -1299,27 +1299,28 @@
       <c r="C15" s="20" t="n">
         <v>3.816172</v>
       </c>
-      <c r="D15" s="20" t="n">
-        <v>288.704605</v>
+      <c r="D15" s="13">
+        <f>Assumptions!$C$73</f>
+        <v/>
       </c>
       <c r="E15" s="13">
-        <f>Assumptions!$C$72</f>
+        <f>Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="F15" s="13">
-        <f>Assumptions!$C$72</f>
+        <f>Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="G15" s="13">
-        <f>Assumptions!$C$72</f>
+        <f>Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="H15" s="13">
-        <f>Assumptions!$C$72</f>
+        <f>Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="I15" s="13">
-        <f>Assumptions!$C$72</f>
+        <f>Assumptions!$C$74</f>
         <v/>
       </c>
     </row>
@@ -2037,35 +2038,35 @@
         </is>
       </c>
       <c r="B6" s="13">
-        <f>'Income Statement'!B21</f>
+        <f>'Income Statement'!B22</f>
         <v/>
       </c>
       <c r="C6" s="13">
-        <f>'Income Statement'!C21</f>
+        <f>'Income Statement'!C22</f>
         <v/>
       </c>
       <c r="D6" s="13">
-        <f>'Income Statement'!D21</f>
+        <f>'Income Statement'!D22</f>
         <v/>
       </c>
       <c r="E6" s="13">
-        <f>'Income Statement'!E21</f>
+        <f>'Income Statement'!E22</f>
         <v/>
       </c>
       <c r="F6" s="13">
-        <f>'Income Statement'!F21</f>
+        <f>'Income Statement'!F22</f>
         <v/>
       </c>
       <c r="G6" s="13">
-        <f>'Income Statement'!G21</f>
+        <f>'Income Statement'!G22</f>
         <v/>
       </c>
       <c r="H6" s="13">
-        <f>'Income Statement'!H21</f>
+        <f>'Income Statement'!H22</f>
         <v/>
       </c>
       <c r="I6" s="13">
-        <f>'Income Statement'!I21</f>
+        <f>'Income Statement'!I22</f>
         <v/>
       </c>
     </row>
@@ -2076,35 +2077,35 @@
         </is>
       </c>
       <c r="B7" s="13">
-        <f>'Income Statement'!B25</f>
+        <f>'Income Statement'!B26</f>
         <v/>
       </c>
       <c r="C7" s="13">
-        <f>'Income Statement'!C25</f>
+        <f>'Income Statement'!C26</f>
         <v/>
       </c>
       <c r="D7" s="13">
-        <f>'Income Statement'!D25</f>
+        <f>'Income Statement'!D26</f>
         <v/>
       </c>
       <c r="E7" s="13">
-        <f>'Income Statement'!E25</f>
+        <f>'Income Statement'!E26</f>
         <v/>
       </c>
       <c r="F7" s="13">
-        <f>'Income Statement'!F25</f>
+        <f>'Income Statement'!F26</f>
         <v/>
       </c>
       <c r="G7" s="13">
-        <f>'Income Statement'!G25</f>
+        <f>'Income Statement'!G26</f>
         <v/>
       </c>
       <c r="H7" s="13">
-        <f>'Income Statement'!H25</f>
+        <f>'Income Statement'!H26</f>
         <v/>
       </c>
       <c r="I7" s="13">
-        <f>'Income Statement'!I25</f>
+        <f>'Income Statement'!I26</f>
         <v/>
       </c>
     </row>
@@ -2232,35 +2233,35 @@
         </is>
       </c>
       <c r="B11" s="6">
-        <f>'Income Statement'!B25/'Income Statement'!B2</f>
+        <f>'Income Statement'!B26/'Income Statement'!B2</f>
         <v/>
       </c>
       <c r="C11" s="6">
-        <f>'Income Statement'!C25/'Income Statement'!C2</f>
+        <f>'Income Statement'!C26/'Income Statement'!C2</f>
         <v/>
       </c>
       <c r="D11" s="6">
-        <f>'Income Statement'!D25/'Income Statement'!D2</f>
+        <f>'Income Statement'!D26/'Income Statement'!D2</f>
         <v/>
       </c>
       <c r="E11" s="6">
-        <f>'Income Statement'!E25/'Income Statement'!E2</f>
+        <f>'Income Statement'!E26/'Income Statement'!E2</f>
         <v/>
       </c>
       <c r="F11" s="6">
-        <f>'Income Statement'!F25/'Income Statement'!F2</f>
+        <f>'Income Statement'!F26/'Income Statement'!F2</f>
         <v/>
       </c>
       <c r="G11" s="6">
-        <f>'Income Statement'!G25/'Income Statement'!G2</f>
+        <f>'Income Statement'!G26/'Income Statement'!G2</f>
         <v/>
       </c>
       <c r="H11" s="6">
-        <f>'Income Statement'!H25/'Income Statement'!H2</f>
+        <f>'Income Statement'!H26/'Income Statement'!H2</f>
         <v/>
       </c>
       <c r="I11" s="6">
-        <f>'Income Statement'!I25/'Income Statement'!I2</f>
+        <f>'Income Statement'!I26/'Income Statement'!I2</f>
         <v/>
       </c>
     </row>
@@ -2660,19 +2661,19 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>112.3685437671707</v>
+        <v>89.84813331120365</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>97.89340304297896</v>
+        <v>77.40004473614924</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>86.05575046125719</v>
+        <v>67.22333140666257</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>76.19815884150698</v>
+        <v>58.75172925757619</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>67.86482990687243</v>
+        <v>51.59264778644084</v>
       </c>
     </row>
     <row r="7">
@@ -2704,19 +2705,19 @@
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>78.37907531217829</v>
+        <v>60.61098456535337</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>81.87396424224464</v>
+        <v>63.62132658565152</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>86.05575046125719</v>
+        <v>67.22333140666257</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>91.18745877647113</v>
+        <v>71.64355690919623</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>97.68605139720472</v>
+        <v>77.24115581160892</v>
       </c>
     </row>
     <row r="10">
@@ -2748,19 +2749,19 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>102.0606672501618</v>
+        <v>80.97758075566436</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>92.64040190393456</v>
+        <v>72.88120797264808</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>86.05575046125719</v>
+        <v>67.22333140666257</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>77.1779440718923</v>
+        <v>59.59720934796569</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>67.81579138834998</v>
+        <v>51.55825479216958</v>
       </c>
     </row>
     <row r="13">
@@ -2792,19 +2793,19 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>100.8271558310703</v>
+        <v>80.96631184285123</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>95.45573569659282</v>
+        <v>75.9688644115099</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>86.05575046125719</v>
+        <v>67.22333140666257</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>79.3414752931603</v>
+        <v>60.97652211748589</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>71.28434509144404</v>
+        <v>53.48035097047391</v>
       </c>
     </row>
     <row r="16">
@@ -2836,19 +2837,19 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>94.9934319338922</v>
+        <v>75.77915145840042</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>90.52459119757468</v>
+        <v>71.50124143253151</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>86.05575046125719</v>
+        <v>67.22333140666257</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>81.58690972493966</v>
+        <v>62.94542138079377</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>77.11806898862218</v>
+        <v>58.66751135492491</v>
       </c>
     </row>
     <row r="19">
@@ -2880,19 +2881,19 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>81.38726261721223</v>
+        <v>64.48888551420453</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>83.63278129869779</v>
+        <v>65.79955269637973</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>86.05575046125719</v>
+        <v>67.22333140666257</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>88.66630890383252</v>
+        <v>68.76686082035675</v>
       </c>
       <c r="F20" s="16" t="n">
-        <v>91.47497496279347</v>
+        <v>70.43703306905046</v>
       </c>
     </row>
     <row r="22">
@@ -2924,19 +2925,19 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>87.56085253778264</v>
+        <v>68.74251908404773</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>86.64847962314892</v>
+        <v>67.82143868221461</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>86.05575046125719</v>
+        <v>67.22333140666257</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>85.42298698916217</v>
+        <v>66.5851120616971</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>84.69653601029211</v>
+        <v>65.85282935351343</v>
       </c>
     </row>
     <row r="25">
@@ -2968,19 +2969,19 @@
         </is>
       </c>
       <c r="B26" s="16" t="n">
-        <v>98.5400198648115</v>
+        <v>77.93685732648191</v>
       </c>
       <c r="C26" s="16" t="n">
-        <v>104.6744028487575</v>
+        <v>83.22074223232461</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>112.3685437671707</v>
+        <v>89.84813331120365</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>122.3729767894262</v>
+        <v>98.4655073447705</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>136.0117549147244</v>
+        <v>110.2133447489563</v>
       </c>
     </row>
     <row r="27">
@@ -2990,19 +2991,19 @@
         </is>
       </c>
       <c r="B27" s="16" t="n">
-        <v>87.64132994285646</v>
+        <v>68.56936454400906</v>
       </c>
       <c r="C27" s="16" t="n">
-        <v>92.25269102586633</v>
+        <v>72.54138606364246</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>97.89340304297896</v>
+        <v>77.40004473614924</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>105.0024471190708</v>
+        <v>83.52345939528244</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>114.3097809194257</v>
+        <v>91.54038313643774</v>
       </c>
     </row>
     <row r="28">
@@ -3012,19 +3013,19 @@
         </is>
       </c>
       <c r="B28" s="16" t="n">
-        <v>78.37907531217829</v>
+        <v>60.61098456535337</v>
       </c>
       <c r="C28" s="16" t="n">
-        <v>81.87396424224464</v>
+        <v>63.62132658565152</v>
       </c>
       <c r="D28" s="16" t="n">
-        <v>86.05575046125719</v>
+        <v>67.22333140666257</v>
       </c>
       <c r="E28" s="16" t="n">
-        <v>91.18745877647113</v>
+        <v>71.64355690919623</v>
       </c>
       <c r="F28" s="16" t="n">
-        <v>97.68605139720472</v>
+        <v>77.24115581160892</v>
       </c>
     </row>
     <row r="29">
@@ -3034,19 +3035,19 @@
         </is>
       </c>
       <c r="B29" s="16" t="n">
-        <v>70.41477127303929</v>
+        <v>53.77017620527427</v>
       </c>
       <c r="C29" s="16" t="n">
-        <v>73.07646792451291</v>
+        <v>56.06284342175879</v>
       </c>
       <c r="D29" s="16" t="n">
-        <v>76.19815884150698</v>
+        <v>58.75172925757619</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>79.9396643036937</v>
+        <v>61.9744957996253</v>
       </c>
       <c r="F29" s="16" t="n">
-        <v>84.54453940947913</v>
+        <v>65.94093058669804</v>
       </c>
     </row>
     <row r="30">
@@ -3056,19 +3057,19 @@
         </is>
       </c>
       <c r="B30" s="16" t="n">
-        <v>63.49707970369555</v>
+        <v>47.83046185324169</v>
       </c>
       <c r="C30" s="16" t="n">
-        <v>65.52769835728633</v>
+        <v>49.57954652586658</v>
       </c>
       <c r="D30" s="16" t="n">
-        <v>67.86482990687243</v>
+        <v>51.59264778644084</v>
       </c>
       <c r="E30" s="16" t="n">
-        <v>70.60593895464605</v>
+        <v>53.95371731221135</v>
       </c>
       <c r="F30" s="16" t="n">
-        <v>73.89471147795089</v>
+        <v>56.78651981901907</v>
       </c>
     </row>
     <row r="32">
@@ -3085,7 +3086,7 @@
         </is>
       </c>
       <c r="B33" s="20" t="n">
-        <v>4650.989132292205</v>
+        <v>6641.916975726794</v>
       </c>
     </row>
     <row r="34">
@@ -3095,7 +3096,7 @@
         </is>
       </c>
       <c r="B34" s="17" t="n">
-        <v>0.1990281904989722</v>
+        <v>0.2762141296512998</v>
       </c>
     </row>
     <row r="35">
@@ -3105,7 +3106,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>80.60639744007287</v>
+        <v>115.1112127508976</v>
       </c>
     </row>
     <row r="36">
@@ -3115,7 +3116,7 @@
         </is>
       </c>
       <c r="B36" s="35" t="n">
-        <v>0.8060639744007287</v>
+        <v>1.151112127508976</v>
       </c>
     </row>
   </sheetData>
@@ -3196,35 +3197,35 @@
         </is>
       </c>
       <c r="B2" s="5">
-        <f>'Income Statement'!B26</f>
+        <f>'Income Statement'!B27</f>
         <v/>
       </c>
       <c r="C2" s="5">
-        <f>'Income Statement'!C26</f>
+        <f>'Income Statement'!C27</f>
         <v/>
       </c>
       <c r="D2" s="5">
-        <f>'Income Statement'!D26</f>
+        <f>'Income Statement'!D27</f>
         <v/>
       </c>
       <c r="E2" s="5">
-        <f>'Income Statement'!E26</f>
+        <f>'Income Statement'!E27</f>
         <v/>
       </c>
       <c r="F2" s="5">
-        <f>'Income Statement'!F26</f>
+        <f>'Income Statement'!F27</f>
         <v/>
       </c>
       <c r="G2" s="5">
-        <f>'Income Statement'!G26</f>
+        <f>'Income Statement'!G27</f>
         <v/>
       </c>
       <c r="H2" s="5">
-        <f>'Income Statement'!H26</f>
+        <f>'Income Statement'!H27</f>
         <v/>
       </c>
       <c r="I2" s="5">
-        <f>'Income Statement'!I26</f>
+        <f>'Income Statement'!I27</f>
         <v/>
       </c>
     </row>
@@ -3283,23 +3284,23 @@
         <v>3.5</v>
       </c>
       <c r="E4" s="5">
-        <f>'Income Statement'!E26*Assumptions!$C$38</f>
+        <f>'Income Statement'!E27*Assumptions!$C$38</f>
         <v/>
       </c>
       <c r="F4" s="5">
-        <f>'Income Statement'!F26*Assumptions!$C$38</f>
+        <f>'Income Statement'!F27*Assumptions!$C$38</f>
         <v/>
       </c>
       <c r="G4" s="5">
-        <f>'Income Statement'!G26*Assumptions!$C$38</f>
+        <f>'Income Statement'!G27*Assumptions!$C$38</f>
         <v/>
       </c>
       <c r="H4" s="5">
-        <f>'Income Statement'!H26*Assumptions!$C$38</f>
+        <f>'Income Statement'!H27*Assumptions!$C$38</f>
         <v/>
       </c>
       <c r="I4" s="5">
-        <f>'Income Statement'!I26*Assumptions!$C$38</f>
+        <f>'Income Statement'!I27*Assumptions!$C$38</f>
         <v/>
       </c>
     </row>
@@ -3310,23 +3311,23 @@
         </is>
       </c>
       <c r="E5" s="6">
-        <f>'Income Statement'!E25/(('Balance Sheet'!D14+'Balance Sheet'!E14)/2)</f>
+        <f>'Income Statement'!E26/(('Balance Sheet'!D14+'Balance Sheet'!E14)/2)</f>
         <v/>
       </c>
       <c r="F5" s="6">
-        <f>'Income Statement'!F25/(('Balance Sheet'!E14+'Balance Sheet'!F14)/2)</f>
+        <f>'Income Statement'!F26/(('Balance Sheet'!E14+'Balance Sheet'!F14)/2)</f>
         <v/>
       </c>
       <c r="G5" s="6">
-        <f>'Income Statement'!G25/(('Balance Sheet'!F14+'Balance Sheet'!G14)/2)</f>
+        <f>'Income Statement'!G26/(('Balance Sheet'!F14+'Balance Sheet'!G14)/2)</f>
         <v/>
       </c>
       <c r="H5" s="6">
-        <f>'Income Statement'!H25/(('Balance Sheet'!G14+'Balance Sheet'!H14)/2)</f>
+        <f>'Income Statement'!H26/(('Balance Sheet'!G14+'Balance Sheet'!H14)/2)</f>
         <v/>
       </c>
       <c r="I5" s="6">
-        <f>'Income Statement'!I25/(('Balance Sheet'!H14+'Balance Sheet'!I14)/2)</f>
+        <f>'Income Statement'!I26/(('Balance Sheet'!H14+'Balance Sheet'!I14)/2)</f>
         <v/>
       </c>
     </row>
@@ -3337,23 +3338,23 @@
         </is>
       </c>
       <c r="E6" s="34">
-        <f>('Balance Sheet'!E13-Assumptions!$C$69)/'Income Statement'!E17</f>
+        <f>('Balance Sheet'!E13-Assumptions!$C$70)/'Income Statement'!E17</f>
         <v/>
       </c>
       <c r="F6" s="34">
-        <f>('Balance Sheet'!F13-Assumptions!$C$69)/'Income Statement'!F17</f>
+        <f>('Balance Sheet'!F13-Assumptions!$C$70)/'Income Statement'!F17</f>
         <v/>
       </c>
       <c r="G6" s="34">
-        <f>('Balance Sheet'!G13-Assumptions!$C$69)/'Income Statement'!G17</f>
+        <f>('Balance Sheet'!G13-Assumptions!$C$70)/'Income Statement'!G17</f>
         <v/>
       </c>
       <c r="H6" s="34">
-        <f>('Balance Sheet'!H13-Assumptions!$C$69)/'Income Statement'!H17</f>
+        <f>('Balance Sheet'!H13-Assumptions!$C$70)/'Income Statement'!H17</f>
         <v/>
       </c>
       <c r="I6" s="34">
-        <f>('Balance Sheet'!I13-Assumptions!$C$69)/'Income Statement'!I17</f>
+        <f>('Balance Sheet'!I13-Assumptions!$C$70)/'Income Statement'!I17</f>
         <v/>
       </c>
     </row>
@@ -3472,23 +3473,23 @@
         </is>
       </c>
       <c r="E11" s="6">
-        <f>('Income Statement'!E15*(1-Assumptions!$C$5))/('Balance Sheet'!E2+'Balance Sheet'!E3+'Balance Sheet'!E17+Assumptions!$C$74)</f>
+        <f>('Income Statement'!E15*(1-Assumptions!$C$5))/('Balance Sheet'!E2+'Balance Sheet'!E3+'Balance Sheet'!E17+Assumptions!$C$77)</f>
         <v/>
       </c>
       <c r="F11" s="6">
-        <f>('Income Statement'!F15*(1-Assumptions!$C$5))/('Balance Sheet'!F2+'Balance Sheet'!F3+'Balance Sheet'!F17+Assumptions!$C$74)</f>
+        <f>('Income Statement'!F15*(1-Assumptions!$C$5))/('Balance Sheet'!F2+'Balance Sheet'!F3+'Balance Sheet'!F17+Assumptions!$C$77)</f>
         <v/>
       </c>
       <c r="G11" s="6">
-        <f>('Income Statement'!G15*(1-Assumptions!$C$5))/('Balance Sheet'!G2+'Balance Sheet'!G3+'Balance Sheet'!G17+Assumptions!$C$74)</f>
+        <f>('Income Statement'!G15*(1-Assumptions!$C$5))/('Balance Sheet'!G2+'Balance Sheet'!G3+'Balance Sheet'!G17+Assumptions!$C$77)</f>
         <v/>
       </c>
       <c r="H11" s="6">
-        <f>('Income Statement'!H15*(1-Assumptions!$C$5))/('Balance Sheet'!H2+'Balance Sheet'!H3+'Balance Sheet'!H17+Assumptions!$C$74)</f>
+        <f>('Income Statement'!H15*(1-Assumptions!$C$5))/('Balance Sheet'!H2+'Balance Sheet'!H3+'Balance Sheet'!H17+Assumptions!$C$77)</f>
         <v/>
       </c>
       <c r="I11" s="6">
-        <f>('Income Statement'!I15*(1-Assumptions!$C$5))/('Balance Sheet'!I2+'Balance Sheet'!I3+'Balance Sheet'!I17+Assumptions!$C$74)</f>
+        <f>('Income Statement'!I15*(1-Assumptions!$C$5))/('Balance Sheet'!I2+'Balance Sheet'!I3+'Balance Sheet'!I17+Assumptions!$C$77)</f>
         <v/>
       </c>
     </row>
@@ -3611,7 +3612,7 @@
         </is>
       </c>
       <c r="B6" s="49">
-        <f>Assumptions!$C$3/('Income Statement'!D25/Assumptions!$C$4)</f>
+        <f>Assumptions!$C$3/('Income Statement'!D26/Assumptions!$C$4)</f>
         <v/>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -3793,7 +3794,7 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>Terminal value 74% of core enterprise value</t>
+          <t>Terminal value 76% of core enterprise value</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3814,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Terminal value 74% of core enterprise value</t>
+          <t>Terminal value 75% of core enterprise value</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3834,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Justified 1.98 times book</t>
+          <t>Justified 1.71 times book</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3938,7 @@
         </is>
       </c>
       <c r="B12" s="13">
-        <f>Assumptions!$C$93</f>
+        <f>Assumptions!$C$96</f>
         <v/>
       </c>
     </row>
@@ -3948,7 +3949,7 @@
         </is>
       </c>
       <c r="B13" s="13">
-        <f>Assumptions!$C$94</f>
+        <f>Assumptions!$C$97</f>
         <v/>
       </c>
     </row>
@@ -3959,7 +3960,7 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>Assumptions!$C$93+Assumptions!$C$94+Assumptions!$C$72</f>
+        <f>Assumptions!$C$96+Assumptions!$C$97+Assumptions!$C$74</f>
         <v/>
       </c>
     </row>
@@ -3992,7 +3993,7 @@
         </is>
       </c>
       <c r="B17" s="13">
-        <f>'Income Statement'!D25</f>
+        <f>'Income Statement'!D26</f>
         <v/>
       </c>
     </row>
@@ -4003,7 +4004,7 @@
         </is>
       </c>
       <c r="B18" s="14">
-        <f>Assumptions!$C$3/('Income Statement'!D25/Assumptions!$C$4)</f>
+        <f>Assumptions!$C$3/('Income Statement'!D26/Assumptions!$C$4)</f>
         <v/>
       </c>
     </row>
@@ -4014,7 +4015,7 @@
         </is>
       </c>
       <c r="B19" s="14">
-        <f>(Assumptions!$C$93+Assumptions!$C$94+Assumptions!$C$72)/'Income Statement'!D17</f>
+        <f>(Assumptions!$C$96+Assumptions!$C$97+Assumptions!$C$74)/'Income Statement'!D17</f>
         <v/>
       </c>
     </row>
@@ -4025,7 +4026,7 @@
         </is>
       </c>
       <c r="B20" s="15">
-        <f>Assumptions!$C$88</f>
+        <f>Assumptions!$C$91</f>
         <v/>
       </c>
     </row>
@@ -4036,7 +4037,7 @@
         </is>
       </c>
       <c r="B21" s="15">
-        <f>Assumptions!$C$97</f>
+        <f>Assumptions!$C$100</f>
         <v/>
       </c>
     </row>
@@ -4047,7 +4048,7 @@
         </is>
       </c>
       <c r="B22" s="15">
-        <f>Assumptions!$C$103</f>
+        <f>Assumptions!$C$106</f>
         <v/>
       </c>
     </row>
@@ -4132,7 +4133,7 @@
         </is>
       </c>
       <c r="B2" s="12">
-        <f>('SOTP Bridge'!B10)/Assumptions!$C$4</f>
+        <f>('SOTP Bridge'!B11)/Assumptions!$C$4</f>
         <v/>
       </c>
       <c r="C2" s="17" t="n">
@@ -4170,7 +4171,7 @@
         </is>
       </c>
       <c r="B4" s="12">
-        <f>('Balance Sheet'!G18)*0+1.975831*'Balance Sheet'!D18</f>
+        <f>('Balance Sheet'!G18)*0+1.706200*'Balance Sheet'!D18</f>
         <v/>
       </c>
       <c r="C4" s="17" t="n">
@@ -4295,7 +4296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -4430,10 +4431,10 @@
         </is>
       </c>
       <c r="C8" s="17" t="n">
-        <v>0.1</v>
+        <v>0.055</v>
       </c>
       <c r="D8" s="17" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E8" s="17" t="n">
         <v>0.075</v>
@@ -4457,7 +4458,7 @@
         </is>
       </c>
       <c r="C9" s="17" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="D9" s="17" t="n">
         <v>0.09</v>
@@ -4484,10 +4485,10 @@
         </is>
       </c>
       <c r="C10" s="17" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E10" s="17" t="n">
         <v>0.075</v>
@@ -4942,7 +4943,7 @@
         </is>
       </c>
       <c r="C32" s="17" t="n">
-        <v>0.075</v>
+        <v>0.125</v>
       </c>
       <c r="D32" s="17" t="n">
         <v>0.045</v>
@@ -4969,10 +4970,10 @@
         </is>
       </c>
       <c r="C33" s="20" t="n">
-        <v>3200</v>
+        <v>3400</v>
       </c>
       <c r="D33" s="20" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="E33" s="20" t="n">
         <v>400</v>
@@ -5282,314 +5283,326 @@
     <row r="51" ht="26" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Terminal risk-free rate</t>
+          <t>Finance cost charged to profit (EGP mn)</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>5% inflation target plus a 5.5-point real convention</t>
-        </is>
-      </c>
-      <c r="C51" s="19" t="n">
-        <v>0.105</v>
+          <t>What the profit and loss account actually bears — NOT the marginal cost of debt above. Calibrated to the first quarter of 2026</t>
+        </is>
+      </c>
+      <c r="C51" s="20" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D51" s="20" t="n">
+        <v>1210</v>
+      </c>
+      <c r="E51" s="20" t="n">
+        <v>1150</v>
+      </c>
+      <c r="F51" s="20" t="n">
+        <v>1090</v>
+      </c>
+      <c r="G51" s="20" t="n">
+        <v>1030</v>
       </c>
     </row>
     <row r="52" ht="26" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Terminal equity risk premium</t>
+          <t>Terminal risk-free rate</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Normalised toward the rating-class norm</t>
+          <t>5% inflation target plus a 5.5-point real convention</t>
         </is>
       </c>
       <c r="C52" s="19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="53" ht="26" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Terminal local-currency borrowing rate</t>
+          <t>Terminal equity risk premium</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Long-run Egyptian norm</t>
+          <t>Normalised toward the rating-class norm</t>
         </is>
       </c>
       <c r="C53" s="19" t="n">
-        <v>0.15</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="54" ht="26" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Terminal hard-currency coupon</t>
+          <t>Terminal local-currency borrowing rate</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>Long-run norm</t>
+          <t>Long-run Egyptian norm</t>
         </is>
       </c>
       <c r="C54" s="19" t="n">
-        <v>0.065</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="55" ht="26" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Terminal debt weight</t>
+          <t>Terminal hard-currency coupon</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>Reconciled to the model's own forecast balance sheet</t>
-        </is>
-      </c>
-      <c r="C55" s="17" t="n">
-        <v>0.2</v>
+          <t>Long-run norm</t>
+        </is>
+      </c>
+      <c r="C55" s="19" t="n">
+        <v>0.065</v>
       </c>
     </row>
     <row r="56" ht="26" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Terminal growth</t>
+          <t>Terminal debt weight</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>Pound-nominal, against a 5% terminal inflation rate — about zero in real terms</t>
+          <t>Reconciled to the model's own forecast balance sheet</t>
         </is>
       </c>
       <c r="C56" s="17" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="57" ht="26" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Terminal return on invested capital</t>
+          <t>Terminal growth</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>Sets terminal reinvestment as growth over return</t>
+          <t>Pound-nominal, against a 5% terminal inflation rate — about zero in real terms</t>
         </is>
       </c>
       <c r="C57" s="17" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="58" ht="26" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Normalised associate contribution (EGP mn)</t>
+          <t>Terminal return on invested capital</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>Three disclosed years: 74.5, 147.1, 495.5</t>
-        </is>
-      </c>
-      <c r="C58" s="20" t="n">
-        <v>320</v>
+          <t>Sets terminal reinvestment as growth over return</t>
+        </is>
+      </c>
+      <c r="C58" s="17" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="59" ht="26" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Associate earnings multiple</t>
+          <t>Normalised associate contribution (EGP mn)</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>Below the Gulf listed range for a minority, unlisted, non-controlled stake</t>
-        </is>
-      </c>
-      <c r="C59" s="22" t="n">
-        <v>11</v>
+          <t>Three disclosed years: 74.5, 147.1, 495.5</t>
+        </is>
+      </c>
+      <c r="C59" s="20" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="60" ht="26" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
+          <t>Associate earnings multiple</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>Below the Gulf listed range for a minority, unlisted, non-controlled stake</t>
+        </is>
+      </c>
+      <c r="C60" s="22" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" ht="26" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
           <t>Regional peer median price-earnings multiple</t>
         </is>
       </c>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>MARKET DATA, cross-check layer</t>
         </is>
       </c>
-      <c r="C60" s="22" t="n">
+      <c r="C61" s="22" t="n">
         <v>19.5</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="8" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
         <is>
           <t>OPENING BALANCE SHEET (AUDITED, 31 DECEMBER 2025)</t>
         </is>
-      </c>
-    </row>
-    <row r="62" ht="26" customHeight="1">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>Property, plant and equipment, net</t>
-        </is>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>Note (4)</t>
-        </is>
-      </c>
-      <c r="C62" s="20" t="n">
-        <v>3069.747924</v>
       </c>
     </row>
     <row r="63" ht="26" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Projects under construction</t>
+          <t>Property, plant and equipment, net</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>Note (6)</t>
+          <t>Note (4)</t>
         </is>
       </c>
       <c r="C63" s="20" t="n">
-        <v>4901.223806</v>
+        <v>3069.747924</v>
       </c>
     </row>
     <row r="64" ht="26" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Inventories, net</t>
+          <t>Projects under construction</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>Note (9)</t>
+          <t>Note (6)</t>
         </is>
       </c>
       <c r="C64" s="20" t="n">
-        <v>3887.077629</v>
+        <v>4901.223806</v>
       </c>
     </row>
     <row r="65" ht="26" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Trade and notes receivable, net</t>
+          <t>Inventories, net</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>Note (10)</t>
+          <t>Note (9)</t>
         </is>
       </c>
       <c r="C65" s="20" t="n">
-        <v>3325.044117</v>
+        <v>3887.077629</v>
       </c>
     </row>
     <row r="66" ht="26" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Other debtors</t>
+          <t>Trade and notes receivable, net</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>Note (11)</t>
+          <t>Note (10)</t>
         </is>
       </c>
       <c r="C66" s="20" t="n">
-        <v>356.786958</v>
+        <v>3325.044117</v>
       </c>
     </row>
     <row r="67" ht="26" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Trade and notes payable</t>
+          <t>Other debtors</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>Note (22)</t>
+          <t>Note (11)</t>
         </is>
       </c>
       <c r="C67" s="20" t="n">
-        <v>780.416969</v>
+        <v>356.786958</v>
       </c>
     </row>
     <row r="68" ht="26" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>Other creditors</t>
+          <t>Trade and notes payable</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>Note (23)</t>
+          <t>Note (22)</t>
         </is>
       </c>
       <c r="C68" s="20" t="n">
-        <v>1044.832275</v>
+        <v>780.416969</v>
       </c>
     </row>
     <row r="69" ht="26" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Cash and bank balances</t>
+          <t>Other creditors</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Note (12)</t>
+          <t>Note (23)</t>
         </is>
       </c>
       <c r="C69" s="20" t="n">
-        <v>1433.426902</v>
+        <v>1044.832275</v>
       </c>
     </row>
     <row r="70" ht="26" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Gross borrowings including leases</t>
+          <t>Cash and bank balances</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Notes (17), (18) and (21)</t>
+          <t>Note (12)</t>
         </is>
       </c>
       <c r="C70" s="20" t="n">
-        <v>8797.725640000001</v>
+        <v>1433.426902</v>
       </c>
     </row>
     <row r="71" ht="26" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Equity attributable to the holding company</t>
+          <t>Gross borrowings including leases</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>Audited</t>
+          <t>Notes (17), (18) and (21)</t>
         </is>
       </c>
       <c r="C71" s="20" t="n">
-        <v>6243.131482</v>
+        <v>8797.725640000001</v>
       </c>
     </row>
     <row r="72" ht="26" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>Non-controlling interests</t>
+          <t>Equity attributable to the holding company</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
@@ -5598,148 +5611,148 @@
         </is>
       </c>
       <c r="C72" s="20" t="n">
-        <v>288.704605</v>
+        <v>6243.131482</v>
       </c>
     </row>
     <row r="73" ht="26" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Assets held for sale</t>
+          <t>Non-controlling interests, audited 31 December 2025</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>Note (8/1)</t>
+          <t>disclosure — the audited December figure, shown so the reader can see both. It is SUPERSEDED for valuation by the March figure below, because almost all of it was the active-ingredient company and that company was deconsolidated in the first quarter of 2026. This row drives the balance sheet history only</t>
         </is>
       </c>
       <c r="C73" s="20" t="n">
-        <v>12.33</v>
+        <v>288.704605</v>
       </c>
     </row>
     <row r="74" ht="26" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Intangible assets, net</t>
+          <t>Non-controlling interests deducted in the bridge</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>Note (7)</t>
+          <t>Post-deconsolidation, from the reviewed 31 March 2026 interim</t>
         </is>
       </c>
       <c r="C74" s="20" t="n">
-        <v>40.142171</v>
+        <v>3.999807</v>
       </c>
     </row>
     <row r="75" ht="26" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Right-of-use and intangible amortisation run-rate</t>
+          <t>Active-ingredient company at carrying cost (EGP mn)</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>Audited FY2025 cash-flow statement</t>
-        </is>
-      </c>
-      <c r="C75" s="23" t="n">
-        <v>8.269948999999997</v>
+          <t>Pre-revenue, so cost not an earnings multiple; the Q1-2026 movement in investments in associates</t>
+        </is>
+      </c>
+      <c r="C75" s="20" t="n">
+        <v>228.4864180000001</v>
       </c>
     </row>
     <row r="76" ht="26" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Share of depreciation charged to cost of sales</t>
+          <t>Assets held for sale</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>Cost of sales note (26): 93.498 of 117.725</t>
-        </is>
-      </c>
-      <c r="C76" s="17" t="n">
-        <v>0.7942005773538676</v>
+          <t>Note (8/1)</t>
+        </is>
+      </c>
+      <c r="C76" s="20" t="n">
+        <v>12.33</v>
       </c>
     </row>
     <row r="77" ht="26" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>FY2025 cash cost per pack sold (EGP)</t>
+          <t>Intangible assets, net</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>Cost of sales less its depreciation line, over packs sold</t>
-        </is>
-      </c>
-      <c r="C77" s="16" t="n">
-        <v>14.53600902055724</v>
+          <t>Note (7)</t>
+        </is>
+      </c>
+      <c r="C77" s="20" t="n">
+        <v>40.142171</v>
       </c>
     </row>
     <row r="78" ht="26" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>Consolidated-to-separate revenue factor</t>
+          <t>Right-of-use and intangible amortisation run-rate</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>MEASURED: audited consolidated revenue over the separate-company channel total</t>
-        </is>
-      </c>
-      <c r="C78" s="24" t="n">
-        <v>1.014932591450432</v>
+          <t>Audited FY2025 cash-flow statement</t>
+        </is>
+      </c>
+      <c r="C78" s="23" t="n">
+        <v>8.269948999999997</v>
       </c>
     </row>
     <row r="79" ht="26" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>FY2025 domestic packs (million)</t>
+          <t>Share of depreciation charged to cost of sales</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>Unit build</t>
-        </is>
-      </c>
-      <c r="C79" s="16" t="n">
-        <v>291.81</v>
+          <t>Cost of sales note (26): 93.498 of 117.725</t>
+        </is>
+      </c>
+      <c r="C79" s="17" t="n">
+        <v>0.7942005773538676</v>
       </c>
     </row>
     <row r="80" ht="26" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>FY2025 export packs (million)</t>
+          <t>FY2025 cash cost per pack sold (EGP)</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>Investor presentation</t>
+          <t>Cost of sales less its depreciation line, over packs sold</t>
         </is>
       </c>
       <c r="C80" s="16" t="n">
-        <v>60</v>
+        <v>14.53600902055724</v>
       </c>
     </row>
     <row r="81" ht="26" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>FY2025 domestic price per pack (EGP)</t>
+          <t>Consolidated-to-separate revenue factor</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>Unit build</t>
-        </is>
-      </c>
-      <c r="C81" s="16" t="n">
-        <v>21.54012212741167</v>
+          <t>MEASURED: audited consolidated revenue over the separate-company channel total</t>
+        </is>
+      </c>
+      <c r="C81" s="24" t="n">
+        <v>1.014932591450432</v>
       </c>
     </row>
     <row r="82" ht="26" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>FY2025 export price per pack (USD)</t>
+          <t>FY2025 domestic packs (million)</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
@@ -5748,113 +5761,110 @@
         </is>
       </c>
       <c r="C82" s="16" t="n">
-        <v>0.9995553449205068</v>
+        <v>291.81</v>
       </c>
     </row>
     <row r="83" ht="26" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>FY2025 contract-manufacturing packs (million)</t>
+          <t>FY2025 export packs (million)</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>Board report</t>
+          <t>Investor presentation</t>
         </is>
       </c>
       <c r="C83" s="16" t="n">
-        <v>5.485</v>
+        <v>60</v>
       </c>
     </row>
     <row r="84" ht="26" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>FY2025 contract-manufacturing revenue (EGP mn)</t>
+          <t>FY2025 domestic price per pack (EGP)</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>Revenue note (25)</t>
-        </is>
-      </c>
-      <c r="C84" s="23" t="n">
-        <v>49.366365</v>
+          <t>Unit build</t>
+        </is>
+      </c>
+      <c r="C84" s="16" t="n">
+        <v>21.54012212741167</v>
       </c>
     </row>
     <row r="85" ht="26" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
+          <t>FY2025 export price per pack (USD)</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>Unit build</t>
+        </is>
+      </c>
+      <c r="C85" s="16" t="n">
+        <v>0.9995553449205068</v>
+      </c>
+    </row>
+    <row r="86" ht="26" customHeight="1">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 contract-manufacturing packs (million)</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>Board report</t>
+        </is>
+      </c>
+      <c r="C86" s="16" t="n">
+        <v>5.485</v>
+      </c>
+    </row>
+    <row r="87" ht="26" customHeight="1">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 contract-manufacturing revenue (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>Revenue note (25)</t>
+        </is>
+      </c>
+      <c r="C87" s="23" t="n">
+        <v>49.366365</v>
+      </c>
+    </row>
+    <row r="88" ht="26" customHeight="1">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
           <t>FY2025 average exchange rate</t>
         </is>
       </c>
-      <c r="B85" s="7" t="inlineStr">
+      <c r="B88" s="7" t="inlineStr">
         <is>
           <t>Note (36)</t>
         </is>
       </c>
-      <c r="C85" s="16" t="n">
+      <c r="C88" s="16" t="n">
         <v>49.48</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="8" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
         <is>
           <t>DERIVED IN THIS SHEET (formulas, not inputs)</t>
         </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="4" t="inlineStr">
-        <is>
-          <t>Normalised risk-free rate = yield less sovereign spread</t>
-        </is>
-      </c>
-      <c r="B87" s="7" t="inlineStr">
-        <is>
-          <t>calculated</t>
-        </is>
-      </c>
-      <c r="C87" s="25">
-        <f>$C$40-$C$41</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="4" t="inlineStr">
-        <is>
-          <t>Cost of equity = normalised risk-free + beta x premium</t>
-        </is>
-      </c>
-      <c r="B88" s="7" t="inlineStr">
-        <is>
-          <t>calculated</t>
-        </is>
-      </c>
-      <c r="C88" s="25">
-        <f>$C$87+$C$45*$C$42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="4" t="inlineStr">
-        <is>
-          <t>Cost of equity, rating basis (published alternative)</t>
-        </is>
-      </c>
-      <c r="B89" s="7" t="inlineStr">
-        <is>
-          <t>calculated</t>
-        </is>
-      </c>
-      <c r="C89" s="25">
-        <f>($C$40-$C$43)+$C$45*$C$44</f>
-        <v/>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>Hard-currency debt at LOCAL-EQUIVALENT cost</t>
+          <t>Normalised risk-free rate = yield less sovereign spread</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
@@ -5863,14 +5873,14 @@
         </is>
       </c>
       <c r="C90" s="25">
-        <f>(1+$C$47)*(1+$C$48)-1</f>
+        <f>$C$40-$C$41</f>
         <v/>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Blended marginal cost of debt</t>
+          <t>Cost of equity = normalised risk-free + beta x premium</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
@@ -5879,14 +5889,14 @@
         </is>
       </c>
       <c r="C91" s="25">
-        <f>(1-$C$49)*$C$46+$C$49*$C$90</f>
+        <f>$C$90+$C$45*$C$42</f>
         <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>Cost of debt after tax</t>
+          <t>Cost of equity, rating basis (published alternative)</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
@@ -5895,14 +5905,14 @@
         </is>
       </c>
       <c r="C92" s="25">
-        <f>$C$91*(1-$C$5)</f>
+        <f>($C$40-$C$43)+$C$45*$C$44</f>
         <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Market capitalisation (EGP mn)</t>
+          <t>Hard-currency debt at LOCAL-EQUIVALENT cost</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
@@ -5910,15 +5920,15 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C93" s="26">
-        <f>$C$3*$C$4</f>
+      <c r="C93" s="25">
+        <f>(1+$C$47)*(1+$C$48)-1</f>
         <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>Net debt (EGP mn)</t>
+          <t>Blended marginal cost of debt</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
@@ -5926,15 +5936,15 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C94" s="26">
-        <f>$C$70-$C$69</f>
+      <c r="C94" s="25">
+        <f>(1-$C$49)*$C$46+$C$49*$C$93</f>
         <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Equity weight (net basis)</t>
+          <t>Cost of debt after tax</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
@@ -5942,15 +5952,15 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C95" s="27">
-        <f>$C$93/($C$93+$C$94)</f>
+      <c r="C95" s="25">
+        <f>$C$94*(1-$C$5)</f>
         <v/>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>Debt weight (net basis)</t>
+          <t>Market capitalisation (EGP mn)</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
@@ -5958,15 +5968,15 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C96" s="27">
-        <f>1-$C$95</f>
+      <c r="C96" s="26">
+        <f>$C$3*$C$4</f>
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>Weighted average cost of capital, year one</t>
+          <t>Net debt (EGP mn)</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
@@ -5974,15 +5984,15 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C97" s="25">
-        <f>$C$95*$C$88+$C$96*$C$92</f>
+      <c r="C97" s="26">
+        <f>$C$71-$C$70</f>
         <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>Debt weight (gross basis)</t>
+          <t>Equity weight (net basis)</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
@@ -5991,14 +6001,14 @@
         </is>
       </c>
       <c r="C98" s="27">
-        <f>$C$70/($C$93+$C$70)</f>
+        <f>$C$96/($C$96+$C$97)</f>
         <v/>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>Weighted average cost of capital, gross-debt basis</t>
+          <t>Debt weight (net basis)</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
@@ -6006,15 +6016,15 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C99" s="25">
-        <f>(1-$C$98)*$C$88+$C$98*$C$92</f>
+      <c r="C99" s="27">
+        <f>1-$C$98</f>
         <v/>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>Terminal cost of equity</t>
+          <t>Weighted average cost of capital, year one</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
@@ -6023,14 +6033,14 @@
         </is>
       </c>
       <c r="C100" s="25">
-        <f>$C$51+$C$45*$C$52</f>
+        <f>$C$98*$C$91+$C$99*$C$95</f>
         <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>Terminal cost of debt</t>
+          <t>Debt weight (gross basis)</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
@@ -6038,15 +6048,15 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C101" s="25">
-        <f>(1-$C$49)*$C$53+$C$49*((1+$C$54)*1.03-1)</f>
+      <c r="C101" s="27">
+        <f>$C$71/($C$96+$C$71)</f>
         <v/>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>Terminal cost of debt after tax</t>
+          <t>Weighted average cost of capital, gross-debt basis</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
@@ -6055,14 +6065,14 @@
         </is>
       </c>
       <c r="C102" s="25">
-        <f>$C$101*(1-$C$5)</f>
+        <f>(1-$C$101)*$C$91+$C$101*$C$95</f>
         <v/>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>Terminal weighted average cost of capital</t>
+          <t>Terminal cost of equity</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
@@ -6071,119 +6081,167 @@
         </is>
       </c>
       <c r="C103" s="25">
-        <f>(1-$C$55)*$C$100+$C$55*$C$102</f>
+        <f>$C$52+$C$45*$C$53</f>
         <v/>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
+          <t>Terminal cost of debt</t>
+        </is>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="C104" s="25">
+        <f>(1-$C$49)*$C$54+$C$49*((1+$C$55)*1.03-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>Terminal cost of debt after tax</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="C105" s="25">
+        <f>$C$104*(1-$C$5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>Terminal weighted average cost of capital</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="C106" s="25">
+        <f>(1-$C$56)*$C$103+$C$56*$C$105</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
           <t>Terminal reinvestment rate = growth / return on capital</t>
         </is>
       </c>
-      <c r="B104" s="7" t="inlineStr">
+      <c r="B107" s="7" t="inlineStr">
         <is>
           <t>calculated</t>
         </is>
       </c>
-      <c r="C104" s="27">
-        <f>$C$56/$C$57</f>
-        <v/>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="11" t="inlineStr">
+      <c r="C107" s="27">
+        <f>$C$57/$C$58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="11" t="inlineStr">
         <is>
           <t>Glide fraction (derived from the cost-of-debt path)</t>
         </is>
       </c>
-      <c r="B105" s="7" t="inlineStr">
+      <c r="B108" s="7" t="inlineStr">
         <is>
           <t>calculated: (this year's cost of debt less the last year's) over (the first year's less the last year's)</t>
         </is>
       </c>
-      <c r="C105" s="28">
+      <c r="C108" s="28">
         <f>(C$50-$G$50)/($C$50-$G$50)</f>
         <v/>
       </c>
-      <c r="D105" s="28">
+      <c r="D108" s="28">
         <f>(D$50-$G$50)/($C$50-$G$50)</f>
         <v/>
       </c>
-      <c r="E105" s="28">
+      <c r="E108" s="28">
         <f>(E$50-$G$50)/($C$50-$G$50)</f>
         <v/>
       </c>
-      <c r="F105" s="28">
+      <c r="F108" s="28">
         <f>(F$50-$G$50)/($C$50-$G$50)</f>
         <v/>
       </c>
-      <c r="G105" s="28">
+      <c r="G108" s="28">
         <f>(G$50-$G$50)/($C$50-$G$50)</f>
         <v/>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="11" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="11" t="inlineStr">
         <is>
           <t>Discount rate</t>
         </is>
       </c>
-      <c r="B106" s="7" t="inlineStr">
+      <c r="B109" s="7" t="inlineStr">
         <is>
           <t>calculated: terminal rate plus the glide fraction of the gap to year one</t>
         </is>
       </c>
-      <c r="C106" s="15">
-        <f>$C$103+($C$97-$C$103)*C$105</f>
-        <v/>
-      </c>
-      <c r="D106" s="15">
-        <f>$C$103+($C$97-$C$103)*D$105</f>
-        <v/>
-      </c>
-      <c r="E106" s="15">
-        <f>$C$103+($C$97-$C$103)*E$105</f>
-        <v/>
-      </c>
-      <c r="F106" s="15">
-        <f>$C$103+($C$97-$C$103)*F$105</f>
-        <v/>
-      </c>
-      <c r="G106" s="15">
-        <f>$C$103+($C$97-$C$103)*G$105</f>
-        <v/>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="11" t="inlineStr">
+      <c r="C109" s="15">
+        <f>$C$106+($C$100-$C$106)*C$108</f>
+        <v/>
+      </c>
+      <c r="D109" s="15">
+        <f>$C$106+($C$100-$C$106)*D$108</f>
+        <v/>
+      </c>
+      <c r="E109" s="15">
+        <f>$C$106+($C$100-$C$106)*E$108</f>
+        <v/>
+      </c>
+      <c r="F109" s="15">
+        <f>$C$106+($C$100-$C$106)*F$108</f>
+        <v/>
+      </c>
+      <c r="G109" s="15">
+        <f>$C$106+($C$100-$C$106)*G$108</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="11" t="inlineStr">
         <is>
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B107" s="7" t="inlineStr">
+      <c r="B110" s="7" t="inlineStr">
         <is>
           <t>calculated: the previous factor divided by one plus this year's rate — the factors compound</t>
         </is>
       </c>
-      <c r="C107" s="29">
-        <f>1/(1+C$106)</f>
-        <v/>
-      </c>
-      <c r="D107" s="29">
-        <f>C107/(1+D$106)</f>
-        <v/>
-      </c>
-      <c r="E107" s="29">
-        <f>D107/(1+E$106)</f>
-        <v/>
-      </c>
-      <c r="F107" s="29">
-        <f>E107/(1+F$106)</f>
-        <v/>
-      </c>
-      <c r="G107" s="29">
-        <f>F107/(1+G$106)</f>
+      <c r="C110" s="29">
+        <f>1/(1+C$109)</f>
+        <v/>
+      </c>
+      <c r="D110" s="29">
+        <f>C110/(1+D$109)</f>
+        <v/>
+      </c>
+      <c r="E110" s="29">
+        <f>D110/(1+E$109)</f>
+        <v/>
+      </c>
+      <c r="F110" s="29">
+        <f>E110/(1+F$109)</f>
+        <v/>
+      </c>
+      <c r="G110" s="29">
+        <f>F110/(1+G$109)</f>
         <v/>
       </c>
     </row>
@@ -6198,7 +6256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -6267,11 +6325,11 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Add: equity-accounted associates at normalised earnings x the multiple</t>
+          <t>Add: earning associates at normalised earnings x the multiple</t>
         </is>
       </c>
       <c r="B5" s="13">
-        <f>Assumptions!$C$58*Assumptions!$C$59</f>
+        <f>Assumptions!$C$59*Assumptions!$C$60</f>
         <v/>
       </c>
       <c r="C5" s="5">
@@ -6282,11 +6340,11 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Add: assets held for sale</t>
+          <t>Add: the pre-revenue active-ingredient company at carrying cost</t>
         </is>
       </c>
       <c r="B6" s="13">
-        <f>Assumptions!$C$73</f>
+        <f>Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="C6" s="5">
@@ -6295,31 +6353,31 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Add: assets held for sale</t>
+        </is>
+      </c>
+      <c r="B7" s="13">
+        <f>Assumptions!$C$76</f>
+        <v/>
+      </c>
+      <c r="C7" s="5">
+        <f>B7/Assumptions!$C$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>TOTAL ENTERPRISE VALUE</t>
         </is>
       </c>
-      <c r="B7" s="30">
-        <f>B2+B5+B6</f>
-        <v/>
-      </c>
-      <c r="C7" s="9">
-        <f>B7/Assumptions!$C$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Less: net debt</t>
-        </is>
-      </c>
-      <c r="B8" s="13">
-        <f>-Assumptions!$C$94</f>
-        <v/>
-      </c>
-      <c r="C8" s="5">
+      <c r="B8" s="30">
+        <f>B2+B5+B6+B7</f>
+        <v/>
+      </c>
+      <c r="C8" s="9">
         <f>B8/Assumptions!$C$4</f>
         <v/>
       </c>
@@ -6327,11 +6385,11 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Less: non-controlling interests</t>
+          <t>Less: net debt</t>
         </is>
       </c>
       <c r="B9" s="13">
-        <f>-Assumptions!$C$72</f>
+        <f>-Assumptions!$C$97</f>
         <v/>
       </c>
       <c r="C9" s="5">
@@ -6340,32 +6398,47 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Less: non-controlling interests, post-deconsolidation</t>
+        </is>
+      </c>
+      <c r="B10" s="13">
+        <f>-Assumptions!$C$74</f>
+        <v/>
+      </c>
+      <c r="C10" s="5">
+        <f>B10/Assumptions!$C$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>EQUITY VALUE</t>
         </is>
       </c>
-      <c r="B10" s="30">
-        <f>B7+B8+B9</f>
-        <v/>
-      </c>
-      <c r="C10" s="9">
-        <f>B10/Assumptions!$C$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="B11" s="30">
+        <f>B8+B9+B10</f>
+        <v/>
+      </c>
+      <c r="C11" s="9">
+        <f>B11/Assumptions!$C$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Value per share — Frame A</t>
         </is>
       </c>
-      <c r="B12" s="30">
-        <f>B10</f>
-        <v/>
-      </c>
-      <c r="C12" s="9">
-        <f>B12/Assumptions!$C$4</f>
+      <c r="B13" s="30">
+        <f>B11</f>
+        <v/>
+      </c>
+      <c r="C13" s="9">
+        <f>B13/Assumptions!$C$4</f>
         <v/>
       </c>
     </row>
@@ -6448,7 +6521,7 @@
         <v>291.81</v>
       </c>
       <c r="D2" s="5">
-        <f>Assumptions!$C$79*(1+Assumptions!C$8)</f>
+        <f>Assumptions!$C$82*(1+Assumptions!C$8)</f>
         <v/>
       </c>
       <c r="E2" s="5">
@@ -6481,7 +6554,7 @@
         <v>60</v>
       </c>
       <c r="D3" s="5">
-        <f>Assumptions!$C$80*(1+Assumptions!C$9)</f>
+        <f>Assumptions!$C$83*(1+Assumptions!C$9)</f>
         <v/>
       </c>
       <c r="E3" s="5">
@@ -6514,7 +6587,7 @@
         <v>21.54012212741167</v>
       </c>
       <c r="D4" s="5">
-        <f>Assumptions!$C$81*(1+Assumptions!C$10)</f>
+        <f>Assumptions!$C$84*(1+Assumptions!C$10)</f>
         <v/>
       </c>
       <c r="E4" s="5">
@@ -6547,7 +6620,7 @@
         <v>0.9995553449205068</v>
       </c>
       <c r="D5" s="5">
-        <f>Assumptions!$C$82*(1+Assumptions!C$11)</f>
+        <f>Assumptions!$C$85*(1+Assumptions!C$11)</f>
         <v/>
       </c>
       <c r="E5" s="5">
@@ -6679,7 +6752,7 @@
         <v>49.366365</v>
       </c>
       <c r="D9" s="32">
-        <f>Assumptions!$C$84*(1+Assumptions!C$12)</f>
+        <f>Assumptions!$C$87*(1+Assumptions!C$12)</f>
         <v/>
       </c>
       <c r="E9" s="32">
@@ -6712,23 +6785,23 @@
         <v>357.295</v>
       </c>
       <c r="D10" s="5">
-        <f>D2+D3+Assumptions!$C$83</f>
+        <f>D2+D3+Assumptions!$C$86</f>
         <v/>
       </c>
       <c r="E10" s="5">
-        <f>E2+E3+Assumptions!$C$83</f>
+        <f>E2+E3+Assumptions!$C$86</f>
         <v/>
       </c>
       <c r="F10" s="5">
-        <f>F2+F3+Assumptions!$C$83</f>
+        <f>F2+F3+Assumptions!$C$86</f>
         <v/>
       </c>
       <c r="G10" s="5">
-        <f>G2+G3+Assumptions!$C$83</f>
+        <f>G2+G3+Assumptions!$C$86</f>
         <v/>
       </c>
       <c r="H10" s="5">
-        <f>H2+H3+Assumptions!$C$83</f>
+        <f>H2+H3+Assumptions!$C$86</f>
         <v/>
       </c>
     </row>
@@ -6745,23 +6818,23 @@
         <v>9441.379305</v>
       </c>
       <c r="D11" s="30">
-        <f>(D7+D8+D9)*Assumptions!$C$78</f>
+        <f>(D7+D8+D9)*Assumptions!$C$81</f>
         <v/>
       </c>
       <c r="E11" s="30">
-        <f>(E7+E8+E9)*Assumptions!$C$78</f>
+        <f>(E7+E8+E9)*Assumptions!$C$81</f>
         <v/>
       </c>
       <c r="F11" s="30">
-        <f>(F7+F8+F9)*Assumptions!$C$78</f>
+        <f>(F7+F8+F9)*Assumptions!$C$81</f>
         <v/>
       </c>
       <c r="G11" s="30">
-        <f>(G7+G8+G9)*Assumptions!$C$78</f>
+        <f>(G7+G8+G9)*Assumptions!$C$81</f>
         <v/>
       </c>
       <c r="H11" s="30">
-        <f>(H7+H8+H9)*Assumptions!$C$78</f>
+        <f>(H7+H8+H9)*Assumptions!$C$81</f>
         <v/>
       </c>
     </row>
@@ -6868,7 +6941,7 @@
         </is>
       </c>
       <c r="D22" s="29">
-        <f>((1+Assumptions!$C$21)*(Segments!D6/Assumptions!$C$85))</f>
+        <f>((1+Assumptions!$C$21)*(Segments!D6/Assumptions!$C$88))</f>
         <v/>
       </c>
       <c r="E22" s="29">
@@ -6895,7 +6968,7 @@
         </is>
       </c>
       <c r="D23" s="29">
-        <f>(Assumptions!$C$22*(1+Assumptions!$C$21)*(Segments!D6/Assumptions!$C$85)+(1-Assumptions!$C$22)*(1+Assumptions!C$25))</f>
+        <f>(Assumptions!$C$22*(1+Assumptions!$C$21)*(Segments!D6/Assumptions!$C$88)+(1-Assumptions!$C$22)*(1+Assumptions!C$25))</f>
         <v/>
       </c>
       <c r="E23" s="29">
@@ -7030,23 +7103,23 @@
         </is>
       </c>
       <c r="D28" s="12">
-        <f>Assumptions!$C$77*D27</f>
+        <f>Assumptions!$C$80*D27</f>
         <v/>
       </c>
       <c r="E28" s="12">
-        <f>Assumptions!$C$77*E27</f>
+        <f>Assumptions!$C$80*E27</f>
         <v/>
       </c>
       <c r="F28" s="12">
-        <f>Assumptions!$C$77*F27</f>
+        <f>Assumptions!$C$80*F27</f>
         <v/>
       </c>
       <c r="G28" s="12">
-        <f>Assumptions!$C$77*G27</f>
+        <f>Assumptions!$C$80*G27</f>
         <v/>
       </c>
       <c r="H28" s="12">
-        <f>Assumptions!$C$77*H27</f>
+        <f>Assumptions!$C$80*H27</f>
         <v/>
       </c>
     </row>
@@ -7064,7 +7137,7 @@
         </is>
       </c>
       <c r="D31" s="13">
-        <f>Assumptions!$C$62</f>
+        <f>Assumptions!$C$63</f>
         <v/>
       </c>
       <c r="E31" s="13">
@@ -7145,23 +7218,23 @@
         </is>
       </c>
       <c r="D34" s="32">
-        <f>-Assumptions!$C$75</f>
+        <f>-Assumptions!$C$78</f>
         <v/>
       </c>
       <c r="E34" s="32">
-        <f>-Assumptions!$C$75</f>
+        <f>-Assumptions!$C$78</f>
         <v/>
       </c>
       <c r="F34" s="32">
-        <f>-Assumptions!$C$75</f>
+        <f>-Assumptions!$C$78</f>
         <v/>
       </c>
       <c r="G34" s="32">
-        <f>-Assumptions!$C$75</f>
+        <f>-Assumptions!$C$78</f>
         <v/>
       </c>
       <c r="H34" s="32">
-        <f>-Assumptions!$C$75</f>
+        <f>-Assumptions!$C$78</f>
         <v/>
       </c>
     </row>
@@ -7253,7 +7326,7 @@
         </is>
       </c>
       <c r="D38" s="13">
-        <f>Assumptions!$C$63</f>
+        <f>Assumptions!$C$64</f>
         <v/>
       </c>
       <c r="E38" s="13">
@@ -7376,7 +7449,7 @@
         </is>
       </c>
       <c r="B2" s="5">
-        <f>'Income Statement'!E26</f>
+        <f>'Income Statement'!E27</f>
         <v/>
       </c>
     </row>
@@ -7387,7 +7460,7 @@
         </is>
       </c>
       <c r="B3" s="5">
-        <f>((DCF!B31-(Assumptions!C$50*Assumptions!$C$70-0.08*Assumptions!$C$69))*(1-Assumptions!$C$6)+Assumptions!$C$58-18.0)/Assumptions!$C$4</f>
+        <f>((DCF!B31-Assumptions!C$51)*(1-Assumptions!$C$6)+Assumptions!$C$59-18.0)/Assumptions!$C$4</f>
         <v/>
       </c>
     </row>
@@ -7409,7 +7482,7 @@
         </is>
       </c>
       <c r="B5" s="34">
-        <f>(1-Assumptions!$C$56/0.24566655)/(Assumptions!$C$100-Assumptions!$C$56)</f>
+        <f>(1-Assumptions!$C$57/0.21896499)/(Assumptions!$C$103-Assumptions!$C$57)</f>
         <v/>
       </c>
       <c r="C5" s="5">
@@ -7448,7 +7521,7 @@
         </is>
       </c>
       <c r="B7" s="34">
-        <f>Assumptions!$C$60*(0.10-Assumptions!$C$56)/(Assumptions!$C$100-Assumptions!$C$56)</f>
+        <f>Assumptions!$C$61*(0.10-Assumptions!$C$57)/(Assumptions!$C$103-Assumptions!$C$57)</f>
         <v/>
       </c>
       <c r="C7" s="5">
@@ -7595,7 +7668,7 @@
         <v/>
       </c>
       <c r="C17" s="5">
-        <f>'Income Statement'!D26*162.016024/Assumptions!$C$4</f>
+        <f>'Income Statement'!D27*162.016024/Assumptions!$C$4</f>
         <v/>
       </c>
       <c r="D17" s="39">
@@ -7650,7 +7723,7 @@
         </is>
       </c>
       <c r="B23" s="5">
-        <f>((B22-2.0-(Assumptions!D$50*Assumptions!$C$70-0.08*Assumptions!$C$69))*(1-Assumptions!$C$6)+Assumptions!$C$58-18.0)/Assumptions!$C$4</f>
+        <f>((B22-2.0-Assumptions!D$51)*(1-Assumptions!$C$6)+Assumptions!$C$59-18.0)/Assumptions!$C$4</f>
         <v/>
       </c>
     </row>
@@ -7661,7 +7734,7 @@
         </is>
       </c>
       <c r="B24" s="6">
-        <f>1-Assumptions!$C$56/0.24566655</f>
+        <f>1-Assumptions!$C$57/0.21896499</f>
         <v/>
       </c>
     </row>
@@ -7672,7 +7745,7 @@
         </is>
       </c>
       <c r="B25" s="9">
-        <f>B23*B24/(Assumptions!$C$100-Assumptions!$C$56)</f>
+        <f>B23*B24/(Assumptions!$C$103-Assumptions!$C$57)</f>
         <v/>
       </c>
     </row>
@@ -8040,23 +8113,23 @@
         </is>
       </c>
       <c r="B13" s="15">
-        <f>Assumptions!C$106</f>
+        <f>Assumptions!C$109</f>
         <v/>
       </c>
       <c r="C13" s="15">
-        <f>Assumptions!D$106</f>
+        <f>Assumptions!D$109</f>
         <v/>
       </c>
       <c r="D13" s="15">
-        <f>Assumptions!E$106</f>
+        <f>Assumptions!E$109</f>
         <v/>
       </c>
       <c r="E13" s="15">
-        <f>Assumptions!F$106</f>
+        <f>Assumptions!F$109</f>
         <v/>
       </c>
       <c r="F13" s="15">
-        <f>Assumptions!G$106</f>
+        <f>Assumptions!G$109</f>
         <v/>
       </c>
     </row>
@@ -8067,23 +8140,23 @@
         </is>
       </c>
       <c r="B14" s="29">
-        <f>Assumptions!C$107</f>
+        <f>Assumptions!C$110</f>
         <v/>
       </c>
       <c r="C14" s="29">
-        <f>Assumptions!D$107</f>
+        <f>Assumptions!D$110</f>
         <v/>
       </c>
       <c r="D14" s="29">
-        <f>Assumptions!E$107</f>
+        <f>Assumptions!E$110</f>
         <v/>
       </c>
       <c r="E14" s="29">
-        <f>Assumptions!F$107</f>
+        <f>Assumptions!F$110</f>
         <v/>
       </c>
       <c r="F14" s="29">
-        <f>Assumptions!G$107</f>
+        <f>Assumptions!G$110</f>
         <v/>
       </c>
     </row>
@@ -8128,7 +8201,7 @@
         </is>
       </c>
       <c r="B18" s="13">
-        <f>F8*(1+Assumptions!$C$56)</f>
+        <f>F8*(1+Assumptions!$C$57)</f>
         <v/>
       </c>
     </row>
@@ -8139,7 +8212,7 @@
         </is>
       </c>
       <c r="B19" s="6">
-        <f>Assumptions!$C$56/Assumptions!$C$57</f>
+        <f>Assumptions!$C$57/Assumptions!$C$58</f>
         <v/>
       </c>
     </row>
@@ -8161,7 +8234,7 @@
         </is>
       </c>
       <c r="B21" s="15">
-        <f>Assumptions!$C$103</f>
+        <f>Assumptions!$C$106</f>
         <v/>
       </c>
     </row>
@@ -8172,7 +8245,7 @@
         </is>
       </c>
       <c r="B22" s="6">
-        <f>Assumptions!$C$56</f>
+        <f>Assumptions!$C$57</f>
         <v/>
       </c>
     </row>
@@ -8353,7 +8426,7 @@
         </is>
       </c>
       <c r="B35" s="13">
-        <f>F32*(1+Assumptions!$C$56)*(1-B19)/(B21-B22)</f>
+        <f>F32*(1+Assumptions!$C$57)*(1-B19)/(B21-B22)</f>
         <v/>
       </c>
     </row>
@@ -8375,7 +8448,7 @@
         </is>
       </c>
       <c r="B37" s="9">
-        <f>(B36+Assumptions!$C$58*Assumptions!$C$59+Assumptions!$C$73-Assumptions!$C$94-Assumptions!$C$72)/Assumptions!$C$4</f>
+        <f>(B36+Assumptions!$C$59*Assumptions!$C$60+Assumptions!$C$75+Assumptions!$C$76-Assumptions!$C$97-Assumptions!$C$74)/Assumptions!$C$4</f>
         <v/>
       </c>
     </row>
@@ -8390,7 +8463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8539,23 +8612,23 @@
         <v>5193.643343000001</v>
       </c>
       <c r="E4" s="13">
-        <f>Segments!D10*Assumptions!$C$77*Segments!D$27</f>
+        <f>Segments!D10*Assumptions!$C$80*Segments!D$27</f>
         <v/>
       </c>
       <c r="F4" s="13">
-        <f>Segments!E10*Assumptions!$C$77*Segments!E$27</f>
+        <f>Segments!E10*Assumptions!$C$80*Segments!E$27</f>
         <v/>
       </c>
       <c r="G4" s="13">
-        <f>Segments!F10*Assumptions!$C$77*Segments!F$27</f>
+        <f>Segments!F10*Assumptions!$C$80*Segments!F$27</f>
         <v/>
       </c>
       <c r="H4" s="13">
-        <f>Segments!G10*Assumptions!$C$77*Segments!G$27</f>
+        <f>Segments!G10*Assumptions!$C$80*Segments!G$27</f>
         <v/>
       </c>
       <c r="I4" s="13">
-        <f>Segments!H10*Assumptions!$C$77*Segments!H$27</f>
+        <f>Segments!H10*Assumptions!$C$80*Segments!H$27</f>
         <v/>
       </c>
     </row>
@@ -8575,23 +8648,23 @@
         <v>93.49755999999999</v>
       </c>
       <c r="E5" s="13">
-        <f>Segments!D$37*Assumptions!$C$76</f>
+        <f>Segments!D$37*Assumptions!$C$79</f>
         <v/>
       </c>
       <c r="F5" s="13">
-        <f>Segments!E$37*Assumptions!$C$76</f>
+        <f>Segments!E$37*Assumptions!$C$79</f>
         <v/>
       </c>
       <c r="G5" s="13">
-        <f>Segments!F$37*Assumptions!$C$76</f>
+        <f>Segments!F$37*Assumptions!$C$79</f>
         <v/>
       </c>
       <c r="H5" s="13">
-        <f>Segments!G$37*Assumptions!$C$76</f>
+        <f>Segments!G$37*Assumptions!$C$79</f>
         <v/>
       </c>
       <c r="I5" s="13">
-        <f>Segments!H$37*Assumptions!$C$76</f>
+        <f>Segments!H$37*Assumptions!$C$79</f>
         <v/>
       </c>
     </row>
@@ -8752,7 +8825,7 @@
         </is>
       </c>
       <c r="B10" s="20" t="n">
-        <v>-151.584727</v>
+        <v>-147.460991</v>
       </c>
       <c r="C10" s="20" t="n">
         <v>-188.492929</v>
@@ -8900,23 +8973,23 @@
         <v>0</v>
       </c>
       <c r="E14" s="32">
-        <f>-Segments!D37*(1-Assumptions!$C$76)</f>
+        <f>-Segments!D37*(1-Assumptions!$C$79)</f>
         <v/>
       </c>
       <c r="F14" s="32">
-        <f>-Segments!E37*(1-Assumptions!$C$76)</f>
+        <f>-Segments!E37*(1-Assumptions!$C$79)</f>
         <v/>
       </c>
       <c r="G14" s="32">
-        <f>-Segments!F37*(1-Assumptions!$C$76)</f>
+        <f>-Segments!F37*(1-Assumptions!$C$79)</f>
         <v/>
       </c>
       <c r="H14" s="32">
-        <f>-Segments!G37*(1-Assumptions!$C$76)</f>
+        <f>-Segments!G37*(1-Assumptions!$C$79)</f>
         <v/>
       </c>
       <c r="I14" s="32">
-        <f>-Segments!H37*(1-Assumptions!$C$76)</f>
+        <f>-Segments!H37*(1-Assumptions!$C$79)</f>
         <v/>
       </c>
     </row>
@@ -9050,23 +9123,23 @@
         <v>-1332.946559</v>
       </c>
       <c r="E18" s="13">
-        <f>-(Assumptions!C$50*Assumptions!$C$70-0.08*Assumptions!$C$69)</f>
+        <f>-Assumptions!C$51</f>
         <v/>
       </c>
       <c r="F18" s="13">
-        <f>-(Assumptions!D$50*Assumptions!$C$70-0.08*Assumptions!$C$69)</f>
+        <f>-Assumptions!D$51</f>
         <v/>
       </c>
       <c r="G18" s="13">
-        <f>-(Assumptions!E$50*Assumptions!$C$70-0.08*Assumptions!$C$69)</f>
+        <f>-Assumptions!E$51</f>
         <v/>
       </c>
       <c r="H18" s="13">
-        <f>-(Assumptions!F$50*Assumptions!$C$70-0.08*Assumptions!$C$69)</f>
+        <f>-Assumptions!F$51</f>
         <v/>
       </c>
       <c r="I18" s="13">
-        <f>-(Assumptions!G$50*Assumptions!$C$70-0.08*Assumptions!$C$69)</f>
+        <f>-Assumptions!G$51</f>
         <v/>
       </c>
     </row>
@@ -9080,283 +9153,314 @@
         <v>74.508447</v>
       </c>
       <c r="C19" s="20" t="n">
-        <v>147.111993</v>
+        <v>151.580926</v>
       </c>
       <c r="D19" s="20" t="n">
-        <v>495.499218</v>
+        <v>512.084638</v>
       </c>
       <c r="E19" s="13">
-        <f>Assumptions!$C$58</f>
+        <f>Assumptions!$C$59</f>
         <v/>
       </c>
       <c r="F19" s="13">
-        <f>Assumptions!$C$58</f>
+        <f>Assumptions!$C$59</f>
         <v/>
       </c>
       <c r="G19" s="13">
-        <f>Assumptions!$C$58</f>
+        <f>Assumptions!$C$59</f>
         <v/>
       </c>
       <c r="H19" s="13">
-        <f>Assumptions!$C$58</f>
+        <f>Assumptions!$C$59</f>
         <v/>
       </c>
       <c r="I19" s="13">
-        <f>Assumptions!$C$58</f>
+        <f>Assumptions!$C$59</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
+          <t>Dividend distribution tax</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="n">
+        <v>-4.123733</v>
+      </c>
+      <c r="C20" s="23" t="n">
+        <v>-4.468933</v>
+      </c>
+      <c r="D20" s="23" t="n">
+        <v>-16.58542</v>
+      </c>
+      <c r="E20" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
           <t>Interest income, exchange differences and other income</t>
         </is>
       </c>
-      <c r="B20" s="20" t="n">
+      <c r="B21" s="20" t="n">
         <v>191.254269</v>
       </c>
-      <c r="C20" s="20" t="n">
+      <c r="C21" s="20" t="n">
         <v>814.782229</v>
       </c>
-      <c r="D20" s="20" t="n">
+      <c r="D21" s="20" t="n">
         <v>267.358836</v>
       </c>
-      <c r="E20" s="20" t="n">
+      <c r="E21" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="F20" s="20" t="n">
+      <c r="F21" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="20" t="n">
+      <c r="G21" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="20" t="n">
+      <c r="H21" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="20" t="n">
+      <c r="I21" s="20" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Profit before tax</t>
         </is>
       </c>
-      <c r="B21" s="30">
-        <f>B15+B18+B19+B20</f>
-        <v/>
-      </c>
-      <c r="C21" s="30">
-        <f>C15+C18+C19+C20</f>
-        <v/>
-      </c>
-      <c r="D21" s="30">
-        <f>D15+D18+D19+D20</f>
-        <v/>
-      </c>
-      <c r="E21" s="30">
-        <f>E15+E18+E19+E20</f>
-        <v/>
-      </c>
-      <c r="F21" s="30">
-        <f>F15+F18+F19+F20</f>
-        <v/>
-      </c>
-      <c r="G21" s="30">
-        <f>G15+G18+G19+G20</f>
-        <v/>
-      </c>
-      <c r="H21" s="30">
-        <f>H15+H18+H19+H20</f>
-        <v/>
-      </c>
-      <c r="I21" s="30">
-        <f>I15+I18+I19+I20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="B22" s="30">
+        <f>B15+B18+B19+B21+B20</f>
+        <v/>
+      </c>
+      <c r="C22" s="30">
+        <f>C15+C18+C19+C21+C20</f>
+        <v/>
+      </c>
+      <c r="D22" s="30">
+        <f>D15+D18+D19+D21+D20</f>
+        <v/>
+      </c>
+      <c r="E22" s="30">
+        <f>E15+E18+E19+E21+E20</f>
+        <v/>
+      </c>
+      <c r="F22" s="30">
+        <f>F15+F18+F19+F21+F20</f>
+        <v/>
+      </c>
+      <c r="G22" s="30">
+        <f>G15+G18+G19+G21+G20</f>
+        <v/>
+      </c>
+      <c r="H22" s="30">
+        <f>H15+H18+H19+H21+H20</f>
+        <v/>
+      </c>
+      <c r="I22" s="30">
+        <f>I15+I18+I19+I21+I20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Income tax and the statutory solidarity contribution</t>
         </is>
       </c>
-      <c r="B22" s="20" t="n">
+      <c r="B23" s="20" t="n">
         <v>-259.949154</v>
       </c>
-      <c r="C22" s="20" t="n">
+      <c r="C23" s="20" t="n">
         <v>-433.446496</v>
       </c>
-      <c r="D22" s="20" t="n">
+      <c r="D23" s="20" t="n">
         <v>-338.008843</v>
       </c>
-      <c r="E22" s="13">
-        <f>-(E21-E19)*Assumptions!$C$6</f>
-        <v/>
-      </c>
-      <c r="F22" s="13">
-        <f>-(F21-F19)*Assumptions!$C$6</f>
-        <v/>
-      </c>
-      <c r="G22" s="13">
-        <f>-(G21-G19)*Assumptions!$C$6</f>
-        <v/>
-      </c>
-      <c r="H22" s="13">
-        <f>-(H21-H19)*Assumptions!$C$6</f>
-        <v/>
-      </c>
-      <c r="I22" s="13">
-        <f>-(I21-I19)*Assumptions!$C$6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="E23" s="13">
+        <f>-(E22-E19)*Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="F23" s="13">
+        <f>-(F22-F19)*Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="G23" s="13">
+        <f>-(G22-G19)*Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="H23" s="13">
+        <f>-(H22-H19)*Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="I23" s="13">
+        <f>-(I22-I19)*Assumptions!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>Profit for the year</t>
         </is>
       </c>
-      <c r="B23" s="30">
-        <f>B21+B22</f>
-        <v/>
-      </c>
-      <c r="C23" s="30">
-        <f>C21+C22</f>
-        <v/>
-      </c>
-      <c r="D23" s="30">
-        <f>D21+D22</f>
-        <v/>
-      </c>
-      <c r="E23" s="30">
-        <f>E21+E22</f>
-        <v/>
-      </c>
-      <c r="F23" s="30">
-        <f>F21+F22</f>
-        <v/>
-      </c>
-      <c r="G23" s="30">
-        <f>G21+G22</f>
-        <v/>
-      </c>
-      <c r="H23" s="30">
-        <f>H21+H22</f>
-        <v/>
-      </c>
-      <c r="I23" s="30">
-        <f>I21+I22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="B24" s="30">
+        <f>B22+B23</f>
+        <v/>
+      </c>
+      <c r="C24" s="30">
+        <f>C22+C23</f>
+        <v/>
+      </c>
+      <c r="D24" s="30">
+        <f>D22+D23</f>
+        <v/>
+      </c>
+      <c r="E24" s="30">
+        <f>E22+E23</f>
+        <v/>
+      </c>
+      <c r="F24" s="30">
+        <f>F22+F23</f>
+        <v/>
+      </c>
+      <c r="G24" s="30">
+        <f>G22+G23</f>
+        <v/>
+      </c>
+      <c r="H24" s="30">
+        <f>H22+H23</f>
+        <v/>
+      </c>
+      <c r="I24" s="30">
+        <f>I22+I23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Less non-controlling interests</t>
         </is>
       </c>
-      <c r="B24" s="23" t="n">
+      <c r="B25" s="23" t="n">
         <v>-0.9886149999999816</v>
       </c>
-      <c r="C24" s="23" t="n">
+      <c r="C25" s="23" t="n">
         <v>-1.206525000000056</v>
       </c>
-      <c r="D24" s="23" t="n">
+      <c r="D25" s="23" t="n">
         <v>-16.23531500000013</v>
       </c>
-      <c r="E24" s="23" t="n">
+      <c r="E25" s="23" t="n">
         <v>-18</v>
       </c>
-      <c r="F24" s="23" t="n">
+      <c r="F25" s="23" t="n">
         <v>-18</v>
       </c>
-      <c r="G24" s="23" t="n">
+      <c r="G25" s="23" t="n">
         <v>-18</v>
       </c>
-      <c r="H24" s="23" t="n">
+      <c r="H25" s="23" t="n">
         <v>-18</v>
       </c>
-      <c r="I24" s="23" t="n">
+      <c r="I25" s="23" t="n">
         <v>-18</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>Profit attributable to the holding company</t>
         </is>
       </c>
-      <c r="B25" s="30">
-        <f>B23+B24</f>
-        <v/>
-      </c>
-      <c r="C25" s="30">
-        <f>C23+C24</f>
-        <v/>
-      </c>
-      <c r="D25" s="30">
-        <f>D23+D24</f>
-        <v/>
-      </c>
-      <c r="E25" s="30">
-        <f>E23+E24</f>
-        <v/>
-      </c>
-      <c r="F25" s="30">
-        <f>F23+F24</f>
-        <v/>
-      </c>
-      <c r="G25" s="30">
-        <f>G23+G24</f>
-        <v/>
-      </c>
-      <c r="H25" s="30">
-        <f>H23+H24</f>
-        <v/>
-      </c>
-      <c r="I25" s="30">
-        <f>I23+I24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="B26" s="30">
+        <f>B24+B25</f>
+        <v/>
+      </c>
+      <c r="C26" s="30">
+        <f>C24+C25</f>
+        <v/>
+      </c>
+      <c r="D26" s="30">
+        <f>D24+D25</f>
+        <v/>
+      </c>
+      <c r="E26" s="30">
+        <f>E24+E25</f>
+        <v/>
+      </c>
+      <c r="F26" s="30">
+        <f>F24+F25</f>
+        <v/>
+      </c>
+      <c r="G26" s="30">
+        <f>G24+G25</f>
+        <v/>
+      </c>
+      <c r="H26" s="30">
+        <f>H24+H25</f>
+        <v/>
+      </c>
+      <c r="I26" s="30">
+        <f>I24+I25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Earnings per share (EGP)</t>
         </is>
       </c>
-      <c r="B26" s="12">
-        <f>B25/148.75575</f>
-        <v/>
-      </c>
-      <c r="C26" s="12">
-        <f>C25/148.75575</f>
-        <v/>
-      </c>
-      <c r="D26" s="12">
-        <f>D25/162.016024</f>
-        <v/>
-      </c>
-      <c r="E26" s="12">
-        <f>E25/Assumptions!$C$4</f>
-        <v/>
-      </c>
-      <c r="F26" s="12">
-        <f>F25/Assumptions!$C$4</f>
-        <v/>
-      </c>
-      <c r="G26" s="12">
-        <f>G25/Assumptions!$C$4</f>
-        <v/>
-      </c>
-      <c r="H26" s="12">
-        <f>H25/Assumptions!$C$4</f>
-        <v/>
-      </c>
-      <c r="I26" s="12">
-        <f>I25/Assumptions!$C$4</f>
+      <c r="B27" s="12">
+        <f>B26/148.75575</f>
+        <v/>
+      </c>
+      <c r="C27" s="12">
+        <f>C26/148.75575</f>
+        <v/>
+      </c>
+      <c r="D27" s="12">
+        <f>D26/162.016024</f>
+        <v/>
+      </c>
+      <c r="E27" s="12">
+        <f>E26/Assumptions!$C$4</f>
+        <v/>
+      </c>
+      <c r="F27" s="12">
+        <f>F26/Assumptions!$C$4</f>
+        <v/>
+      </c>
+      <c r="G27" s="12">
+        <f>G26/Assumptions!$C$4</f>
+        <v/>
+      </c>
+      <c r="H27" s="12">
+        <f>H26/Assumptions!$C$4</f>
+        <v/>
+      </c>
+      <c r="I27" s="12">
+        <f>I26/Assumptions!$C$4</f>
         <v/>
       </c>
     </row>

--- a/engine/phar_study/EIPICO_Valuation_Model_09082026.xlsx
+++ b/engine/phar_study/EIPICO_Valuation_Model_09082026.xlsx
@@ -36,9 +36,9 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="0.0&quot;x&quot;"/>
-    <numFmt numFmtId="168" formatCode="#,##0.0"/>
-    <numFmt numFmtId="169" formatCode="0.0000"/>
-    <numFmt numFmtId="170" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="168" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0"/>
+    <numFmt numFmtId="170" formatCode="0.0000"/>
     <numFmt numFmtId="171" formatCode="+0.0000;-0.0000"/>
     <numFmt numFmtId="172" formatCode="+0&quot;bp&quot;;-0&quot;bp&quot;"/>
     <numFmt numFmtId="173" formatCode="+0.0%;-0.0%"/>
@@ -173,7 +173,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -213,18 +213,19 @@
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -232,6 +233,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -745,7 +747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1070,35 +1072,35 @@
           <t>TOTAL ASSETS</t>
         </is>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="31">
         <f>SUM(B2:B8)</f>
         <v/>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <f>SUM(C2:C8)</f>
         <v/>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <f>SUM(D2:D8)</f>
         <v/>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <f>SUM(E2:E8)</f>
         <v/>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <f>SUM(F2:F8)</f>
         <v/>
       </c>
-      <c r="G9" s="30">
+      <c r="G9" s="31">
         <f>SUM(G2:G8)</f>
         <v/>
       </c>
-      <c r="H9" s="30">
+      <c r="H9" s="31">
         <f>SUM(H2:H8)</f>
         <v/>
       </c>
-      <c r="I9" s="30">
+      <c r="I9" s="31">
         <f>SUM(I2:I8)</f>
         <v/>
       </c>
@@ -1230,23 +1232,23 @@
         <v/>
       </c>
       <c r="E13" s="13">
-        <f>Assumptions!$C$71</f>
+        <f>E9-E10-E11-E12-E14-E15</f>
         <v/>
       </c>
       <c r="F13" s="13">
-        <f>Assumptions!$C$71</f>
+        <f>F9-F10-F11-F12-F14-F15</f>
         <v/>
       </c>
       <c r="G13" s="13">
-        <f>Assumptions!$C$71</f>
+        <f>G9-G10-G11-G12-G14-G15</f>
         <v/>
       </c>
       <c r="H13" s="13">
-        <f>Assumptions!$C$71</f>
+        <f>H9-H10-H11-H12-H14-H15</f>
         <v/>
       </c>
       <c r="I13" s="13">
-        <f>Assumptions!$C$71</f>
+        <f>I9-I10-I11-I12-I14-I15</f>
         <v/>
       </c>
     </row>
@@ -1263,26 +1265,26 @@
         <v>4653.769234</v>
       </c>
       <c r="D14" s="13">
-        <f>Assumptions!$C$72</f>
-        <v/>
-      </c>
-      <c r="E14" s="26">
-        <f>Assumptions!$C$72+'Income Statement'!E26*(1-Assumptions!$C$38)</f>
-        <v/>
-      </c>
-      <c r="F14" s="26">
+        <f>Assumptions!$C$73</f>
+        <v/>
+      </c>
+      <c r="E14" s="27">
+        <f>Assumptions!$C$73+'Income Statement'!E26*(1-Assumptions!$C$38)</f>
+        <v/>
+      </c>
+      <c r="F14" s="27">
         <f>E14+'Income Statement'!F26*(1-Assumptions!$C$38)</f>
         <v/>
       </c>
-      <c r="G14" s="26">
+      <c r="G14" s="27">
         <f>F14+'Income Statement'!G26*(1-Assumptions!$C$38)</f>
         <v/>
       </c>
-      <c r="H14" s="26">
+      <c r="H14" s="27">
         <f>G14+'Income Statement'!H26*(1-Assumptions!$C$38)</f>
         <v/>
       </c>
-      <c r="I14" s="26">
+      <c r="I14" s="27">
         <f>H14+'Income Statement'!I26*(1-Assumptions!$C$38)</f>
         <v/>
       </c>
@@ -1300,123 +1302,226 @@
         <v>3.816172</v>
       </c>
       <c r="D15" s="13">
-        <f>Assumptions!$C$73</f>
+        <f>Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="E15" s="13">
-        <f>Assumptions!$C$74</f>
+        <f>Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="F15" s="13">
-        <f>Assumptions!$C$74</f>
+        <f>Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="G15" s="13">
-        <f>Assumptions!$C$74</f>
+        <f>Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="H15" s="13">
-        <f>Assumptions!$C$74</f>
+        <f>Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="I15" s="13">
-        <f>Assumptions!$C$74</f>
+        <f>Assumptions!$C$75</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>NET DEBT</t>
-        </is>
-      </c>
-      <c r="B16" s="30">
-        <f>B13-B8</f>
-        <v/>
-      </c>
-      <c r="C16" s="30">
-        <f>C13-C8</f>
-        <v/>
-      </c>
-      <c r="D16" s="30">
-        <f>D13-D8</f>
+          <t>TOTAL LIABILITIES AND EQUITY</t>
+        </is>
+      </c>
+      <c r="B16" s="31">
+        <f>B10+B11+B12+B13+B14+B15</f>
+        <v/>
+      </c>
+      <c r="C16" s="31">
+        <f>C10+C11+C12+C13+C14+C15</f>
+        <v/>
+      </c>
+      <c r="D16" s="31">
+        <f>D10+D11+D12+D13+D14+D15</f>
+        <v/>
+      </c>
+      <c r="E16" s="31">
+        <f>E10+E11+E12+E13+E14+E15</f>
+        <v/>
+      </c>
+      <c r="F16" s="31">
+        <f>F10+F11+F12+F13+F14+F15</f>
+        <v/>
+      </c>
+      <c r="G16" s="31">
+        <f>G10+G11+G12+G13+G14+G15</f>
+        <v/>
+      </c>
+      <c r="H16" s="31">
+        <f>H10+H11+H12+H13+H14+H15</f>
+        <v/>
+      </c>
+      <c r="I16" s="31">
+        <f>I10+I11+I12+I13+I14+I15</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
+          <t>BALANCE CHECK — total assets less total liabilities and equity</t>
+        </is>
+      </c>
+      <c r="B17" s="27">
+        <f>B9-B16</f>
+        <v/>
+      </c>
+      <c r="C17" s="27">
+        <f>C9-C16</f>
+        <v/>
+      </c>
+      <c r="D17" s="27">
+        <f>D9-D16</f>
+        <v/>
+      </c>
+      <c r="E17" s="27">
+        <f>E9-E16</f>
+        <v/>
+      </c>
+      <c r="F17" s="27">
+        <f>F9-F16</f>
+        <v/>
+      </c>
+      <c r="G17" s="27">
+        <f>G9-G16</f>
+        <v/>
+      </c>
+      <c r="H17" s="27">
+        <f>H9-H16</f>
+        <v/>
+      </c>
+      <c r="I17" s="27">
+        <f>I9-I16</f>
+        <v/>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>ZERO IN EVERY FORECAST COLUMN, BY CONSTRUCTION — gross borrowings are the funding plug. The earlier edition never computed this row at all and its forecast columns were out by up to 6.6% of total assets. The three audited columns carry small residuals (-4.1, +0.2, +0.4 on assets of 10.0bn to 18.3bn, under 0.05%) from grouping the filed statement into these line captions; they are shown rather than suppressed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>NET DEBT</t>
+        </is>
+      </c>
+      <c r="B18" s="31">
+        <f>B13-B8</f>
+        <v/>
+      </c>
+      <c r="C18" s="31">
+        <f>C13-C8</f>
+        <v/>
+      </c>
+      <c r="D18" s="31">
+        <f>D13-D8</f>
+        <v/>
+      </c>
+      <c r="E18" s="31">
+        <f>E13-E8</f>
+        <v/>
+      </c>
+      <c r="F18" s="31">
+        <f>F13-F8</f>
+        <v/>
+      </c>
+      <c r="G18" s="31">
+        <f>G13-G8</f>
+        <v/>
+      </c>
+      <c r="H18" s="31">
+        <f>H13-H8</f>
+        <v/>
+      </c>
+      <c r="I18" s="31">
+        <f>I13-I8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
           <t>Net working capital</t>
         </is>
       </c>
-      <c r="B17" s="26">
+      <c r="B19" s="27">
         <f>B5+B6+B7-B10-B11</f>
         <v/>
       </c>
-      <c r="C17" s="26">
+      <c r="C19" s="27">
         <f>C5+C6+C7-C10-C11</f>
         <v/>
       </c>
-      <c r="D17" s="26">
+      <c r="D19" s="27">
         <f>D5+D6+D7-D10-D11</f>
         <v/>
       </c>
-      <c r="E17" s="26">
+      <c r="E19" s="27">
         <f>E5+E6+E7-E10-E11</f>
         <v/>
       </c>
-      <c r="F17" s="26">
+      <c r="F19" s="27">
         <f>F5+F6+F7-F10-F11</f>
         <v/>
       </c>
-      <c r="G17" s="26">
+      <c r="G19" s="27">
         <f>G5+G6+G7-G10-G11</f>
         <v/>
       </c>
-      <c r="H17" s="26">
+      <c r="H19" s="27">
         <f>H5+H6+H7-H10-H11</f>
         <v/>
       </c>
-      <c r="I17" s="26">
+      <c r="I19" s="27">
         <f>I5+I6+I7-I10-I11</f>
         <v/>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Book value per share (EGP)</t>
         </is>
       </c>
-      <c r="B18" s="12">
+      <c r="B20" s="12">
         <f>B14/148.75575</f>
         <v/>
       </c>
-      <c r="C18" s="12">
+      <c r="C20" s="12">
         <f>C14/148.75575</f>
         <v/>
       </c>
-      <c r="D18" s="12">
+      <c r="D20" s="12">
         <f>D14/168.75575</f>
         <v/>
       </c>
-      <c r="E18" s="12">
+      <c r="E20" s="12">
         <f>E14/Assumptions!$C$4</f>
         <v/>
       </c>
-      <c r="F18" s="12">
+      <c r="F20" s="12">
         <f>F14/Assumptions!$C$4</f>
         <v/>
       </c>
-      <c r="G18" s="12">
+      <c r="G20" s="12">
         <f>G14/Assumptions!$C$4</f>
         <v/>
       </c>
-      <c r="H18" s="12">
+      <c r="H20" s="12">
         <f>H14/Assumptions!$C$4</f>
         <v/>
       </c>
-      <c r="I18" s="12">
+      <c r="I20" s="12">
         <f>I14/Assumptions!$C$4</f>
         <v/>
       </c>
@@ -1535,39 +1640,39 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Tax on operating profit at the statutory rate</t>
+          <t>Tax on operating profit at the EFFECTIVE rate the business bears</t>
         </is>
       </c>
       <c r="B3" s="13">
-        <f>-B2*Assumptions!$C$5</f>
+        <f>-B2*Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="C3" s="13">
-        <f>-C2*Assumptions!$C$5</f>
+        <f>-C2*Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="D3" s="13">
-        <f>-D2*Assumptions!$C$5</f>
+        <f>-D2*Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="E3" s="13">
-        <f>-E2*Assumptions!$C$5</f>
+        <f>-E2*Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="F3" s="13">
-        <f>-F2*Assumptions!$C$5</f>
+        <f>-F2*Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="G3" s="13">
-        <f>-G2*Assumptions!$C$5</f>
+        <f>-G2*Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="H3" s="13">
-        <f>-H2*Assumptions!$C$5</f>
+        <f>-H2*Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="I3" s="13">
-        <f>-I2*Assumptions!$C$5</f>
+        <f>-I2*Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -1577,35 +1682,35 @@
           <t>Operating profit after tax (NOPAT)</t>
         </is>
       </c>
-      <c r="B4" s="30">
+      <c r="B4" s="31">
         <f>B2+B3</f>
         <v/>
       </c>
-      <c r="C4" s="30">
+      <c r="C4" s="31">
         <f>C2+C3</f>
         <v/>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="31">
         <f>D2+D3</f>
         <v/>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="31">
         <f>E2+E3</f>
         <v/>
       </c>
-      <c r="F4" s="30">
+      <c r="F4" s="31">
         <f>F2+F3</f>
         <v/>
       </c>
-      <c r="G4" s="30">
+      <c r="G4" s="31">
         <f>G2+G3</f>
         <v/>
       </c>
-      <c r="H4" s="30">
+      <c r="H4" s="31">
         <f>H2+H3</f>
         <v/>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="31">
         <f>I2+I3</f>
         <v/>
       </c>
@@ -1701,23 +1806,23 @@
         <v>-428.2194999999999</v>
       </c>
       <c r="E7" s="13">
-        <f>-('Balance Sheet'!E17-'Balance Sheet'!D17)</f>
+        <f>-('Balance Sheet'!E19-'Balance Sheet'!D19)</f>
         <v/>
       </c>
       <c r="F7" s="13">
-        <f>-('Balance Sheet'!F17-'Balance Sheet'!E17)</f>
+        <f>-('Balance Sheet'!F19-'Balance Sheet'!E19)</f>
         <v/>
       </c>
       <c r="G7" s="13">
-        <f>-('Balance Sheet'!G17-'Balance Sheet'!F17)</f>
+        <f>-('Balance Sheet'!G19-'Balance Sheet'!F19)</f>
         <v/>
       </c>
       <c r="H7" s="13">
-        <f>-('Balance Sheet'!H17-'Balance Sheet'!G17)</f>
+        <f>-('Balance Sheet'!H19-'Balance Sheet'!G19)</f>
         <v/>
       </c>
       <c r="I7" s="13">
-        <f>-('Balance Sheet'!I17-'Balance Sheet'!H17)</f>
+        <f>-('Balance Sheet'!I19-'Balance Sheet'!H19)</f>
         <v/>
       </c>
     </row>
@@ -1727,23 +1832,23 @@
           <t>FREE CASH FLOW TO THE FIRM</t>
         </is>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <f>E4+E5+E6+E7</f>
         <v/>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <f>F4+F5+F6+F7</f>
         <v/>
       </c>
-      <c r="G8" s="30">
+      <c r="G8" s="31">
         <f>G4+G5+G6+G7</f>
         <v/>
       </c>
-      <c r="H8" s="30">
+      <c r="H8" s="31">
         <f>H4+H5+H6+H7</f>
         <v/>
       </c>
-      <c r="I8" s="30">
+      <c r="I8" s="31">
         <f>I4+I5+I6+I7</f>
         <v/>
       </c>
@@ -2313,9 +2418,9 @@
           <t>THESE CELLS ARE A WHOLE-MODEL RE-RUN — 50,000 simulated price paths each. They do NOT redraw when a driver on the Assumptions sheet changes.</t>
         </is>
       </c>
-      <c r="B2" s="42" t="n"/>
-      <c r="C2" s="42" t="n"/>
-      <c r="D2" s="43" t="n"/>
+      <c r="B2" s="44" t="n"/>
+      <c r="C2" s="44" t="n"/>
+      <c r="D2" s="45" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -2341,12 +2446,12 @@
           <t>Check date</t>
         </is>
       </c>
-      <c r="B4" s="44" t="inlineStr">
+      <c r="B4" s="46" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="C4" s="44" t="inlineStr">
+      <c r="C4" s="46" t="inlineStr">
         <is>
           <t>2026-11-08</t>
         </is>
@@ -2508,22 +2613,22 @@
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="37" t="inlineStr">
+      <c r="A18" s="38" t="inlineStr">
         <is>
           <t>Window set</t>
         </is>
       </c>
-      <c r="B18" s="38" t="inlineStr">
+      <c r="B18" s="39" t="inlineStr">
         <is>
           <t>Windows</t>
         </is>
       </c>
-      <c r="C18" s="38" t="inlineStr">
+      <c r="C18" s="39" t="inlineStr">
         <is>
           <t>Skill against the benchmark</t>
         </is>
       </c>
-      <c r="D18" s="38" t="inlineStr">
+      <c r="D18" s="39" t="inlineStr">
         <is>
           <t>Probability-transform uniformity</t>
         </is>
@@ -2538,7 +2643,7 @@
       <c r="B19" s="20" t="n">
         <v>56</v>
       </c>
-      <c r="C19" s="45" t="n">
+      <c r="C19" s="47" t="n">
         <v>-0.01771436655010961</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -2556,7 +2661,7 @@
       <c r="B20" s="20" t="n">
         <v>19</v>
       </c>
-      <c r="C20" s="45" t="n">
+      <c r="C20" s="47" t="n">
         <v>0.002147922911274858</v>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -2574,7 +2679,7 @@
       <c r="B21" s="20" t="n">
         <v>16</v>
       </c>
-      <c r="C21" s="45" t="n">
+      <c r="C21" s="47" t="n">
         <v>-0.01085817085606799</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -2626,11 +2731,11 @@
           <t>THESE GRIDS ARE WHOLE-MODEL RE-RUNS. Each cell re-runs the entire model at a different input. They do NOT redraw when a driver on the Assumptions sheet changes.</t>
         </is>
       </c>
-      <c r="B2" s="42" t="n"/>
-      <c r="C2" s="42" t="n"/>
-      <c r="D2" s="42" t="n"/>
-      <c r="E2" s="42" t="n"/>
-      <c r="F2" s="43" t="n"/>
+      <c r="B2" s="44" t="n"/>
+      <c r="C2" s="44" t="n"/>
+      <c r="D2" s="44" t="n"/>
+      <c r="E2" s="44" t="n"/>
+      <c r="F2" s="45" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -2638,19 +2743,19 @@
           <t>Shift in the cost of equity (basis points)</t>
         </is>
       </c>
-      <c r="B4" s="46" t="n">
+      <c r="B4" s="48" t="n">
         <v>-200</v>
       </c>
-      <c r="C4" s="46" t="n">
+      <c r="C4" s="48" t="n">
         <v>-100</v>
       </c>
-      <c r="D4" s="46" t="n">
+      <c r="D4" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="46" t="n">
+      <c r="E4" s="48" t="n">
         <v>100</v>
       </c>
-      <c r="F4" s="46" t="n">
+      <c r="F4" s="48" t="n">
         <v>200</v>
       </c>
     </row>
@@ -2661,19 +2766,19 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>89.84813331120365</v>
+        <v>78.31243222697051</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>77.40004473614924</v>
+        <v>67.66927140208438</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>67.22333140666257</v>
+        <v>58.89505972579192</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>58.75172925757619</v>
+        <v>51.53879625116383</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>51.59264778644084</v>
+        <v>45.28376888412894</v>
       </c>
     </row>
     <row r="7">
@@ -2705,19 +2810,19 @@
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>60.61098456535337</v>
+        <v>54.91909695306187</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>63.62132658565152</v>
+        <v>56.7496401224546</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>67.22333140666257</v>
+        <v>58.89505972579192</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>71.64355690919623</v>
+        <v>61.48029305778895</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>77.24115581160892</v>
+        <v>64.70644908483796</v>
       </c>
     </row>
     <row r="10">
@@ -2726,19 +2831,19 @@
           <t>Beta</t>
         </is>
       </c>
-      <c r="B10" s="47" t="n">
+      <c r="B10" s="49" t="n">
         <v>0.45</v>
       </c>
-      <c r="C10" s="47" t="n">
+      <c r="C10" s="49" t="n">
         <v>0.55</v>
       </c>
-      <c r="D10" s="47" t="n">
+      <c r="D10" s="49" t="n">
         <v>0.629</v>
       </c>
-      <c r="E10" s="47" t="n">
+      <c r="E10" s="49" t="n">
         <v>0.75</v>
       </c>
-      <c r="F10" s="47" t="n">
+      <c r="F10" s="49" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -2749,19 +2854,19 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>80.97758075566436</v>
+        <v>70.79426033337107</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>72.88120797264808</v>
+        <v>63.80394773089595</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>67.22333140666257</v>
+        <v>58.89505972579192</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>59.59720934796569</v>
+        <v>52.24641505345505</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>51.55825479216958</v>
+        <v>45.19664792628173</v>
       </c>
     </row>
     <row r="13">
@@ -2793,19 +2898,19 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>80.96631184285123</v>
+        <v>75.44108799206906</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>75.9688644115099</v>
+        <v>69.42057921447211</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>67.22333140666257</v>
+        <v>58.89505972579192</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>60.97652211748589</v>
+        <v>51.38643553893024</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>53.48035097047391</v>
+        <v>42.38906083457892</v>
       </c>
     </row>
     <row r="16">
@@ -2814,19 +2919,19 @@
           <t>Exchange-rate path, scaled</t>
         </is>
       </c>
-      <c r="B16" s="35" t="n">
+      <c r="B16" s="23" t="n">
         <v>0.9</v>
       </c>
-      <c r="C16" s="35" t="n">
+      <c r="C16" s="23" t="n">
         <v>0.95</v>
       </c>
-      <c r="D16" s="35" t="n">
+      <c r="D16" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="35" t="n">
+      <c r="E16" s="23" t="n">
         <v>1.05</v>
       </c>
-      <c r="F16" s="35" t="n">
+      <c r="F16" s="23" t="n">
         <v>1.1</v>
       </c>
     </row>
@@ -2837,19 +2942,19 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>75.77915145840042</v>
+        <v>69.63797562069173</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>71.50124143253151</v>
+        <v>64.26420965733911</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>67.22333140666257</v>
+        <v>58.89505972579192</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>62.94542138079377</v>
+        <v>53.53091600504677</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>58.66751135492491</v>
+        <v>48.17221392319875</v>
       </c>
     </row>
     <row r="19">
@@ -2858,19 +2963,19 @@
           <t>Shift in domestic volume growth</t>
         </is>
       </c>
-      <c r="B19" s="48" t="n">
+      <c r="B19" s="50" t="n">
         <v>-0.04</v>
       </c>
-      <c r="C19" s="48" t="n">
+      <c r="C19" s="50" t="n">
         <v>-0.02</v>
       </c>
-      <c r="D19" s="48" t="n">
+      <c r="D19" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="E19" s="48" t="n">
+      <c r="E19" s="50" t="n">
         <v>0.02</v>
       </c>
-      <c r="F19" s="48" t="n">
+      <c r="F19" s="50" t="n">
         <v>0.04</v>
       </c>
     </row>
@@ -2881,19 +2986,19 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>64.48888551420453</v>
+        <v>56.64350538610749</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>65.79955269637973</v>
+        <v>57.7177306936283</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>67.22333140666257</v>
+        <v>58.89505972579192</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>68.76686082035675</v>
+        <v>60.18174317376977</v>
       </c>
       <c r="F20" s="16" t="n">
-        <v>70.43703306905046</v>
+        <v>61.58427576254385</v>
       </c>
     </row>
     <row r="22">
@@ -2925,19 +3030,19 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>68.74251908404773</v>
+        <v>61.06862787034969</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>67.82143868221461</v>
+        <v>59.75834853177898</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>67.22333140666257</v>
+        <v>58.89505972579192</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>66.5851120616971</v>
+        <v>57.96049310852472</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>65.85282935351343</v>
+        <v>56.86697608562417</v>
       </c>
     </row>
     <row r="25">
@@ -2969,19 +3074,19 @@
         </is>
       </c>
       <c r="B26" s="16" t="n">
-        <v>77.93685732648191</v>
+        <v>70.22746456102367</v>
       </c>
       <c r="C26" s="16" t="n">
-        <v>83.22074223232461</v>
+        <v>73.83242923979699</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>89.84813331120365</v>
+        <v>78.31243222697051</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>98.4655073447705</v>
+        <v>84.10042351180795</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>110.2133447489563</v>
+        <v>91.97138153249236</v>
       </c>
     </row>
     <row r="27">
@@ -2991,19 +3096,19 @@
         </is>
       </c>
       <c r="B27" s="16" t="n">
-        <v>68.56936454400906</v>
+        <v>61.97903730199961</v>
       </c>
       <c r="C27" s="16" t="n">
-        <v>72.54138606364246</v>
+        <v>64.55784487355071</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>77.40004473614924</v>
+        <v>67.66927140208438</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>83.52345939528244</v>
+        <v>71.54787934213813</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>91.54038313643774</v>
+        <v>76.58966229449742</v>
       </c>
     </row>
     <row r="28">
@@ -3013,19 +3118,19 @@
         </is>
       </c>
       <c r="B28" s="16" t="n">
-        <v>60.61098456535337</v>
+        <v>54.91909695306187</v>
       </c>
       <c r="C28" s="16" t="n">
-        <v>63.62132658565152</v>
+        <v>56.7496401224546</v>
       </c>
       <c r="D28" s="16" t="n">
-        <v>67.22333140666257</v>
+        <v>58.89505972579192</v>
       </c>
       <c r="E28" s="16" t="n">
-        <v>71.64355690919623</v>
+        <v>61.48029305778895</v>
       </c>
       <c r="F28" s="16" t="n">
-        <v>77.24115581160892</v>
+        <v>64.70644908483796</v>
       </c>
     </row>
     <row r="29">
@@ -3035,19 +3140,19 @@
         </is>
       </c>
       <c r="B29" s="16" t="n">
-        <v>53.77017620527427</v>
+        <v>48.81103139736771</v>
       </c>
       <c r="C29" s="16" t="n">
-        <v>56.06284342175879</v>
+        <v>50.08798575638645</v>
       </c>
       <c r="D29" s="16" t="n">
-        <v>58.75172925757619</v>
+        <v>51.53879625116383</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>61.9744957996253</v>
+        <v>53.22623000061837</v>
       </c>
       <c r="F29" s="16" t="n">
-        <v>65.94093058669804</v>
+        <v>55.24740198900633</v>
       </c>
     </row>
     <row r="30">
@@ -3057,19 +3162,19 @@
         </is>
       </c>
       <c r="B30" s="16" t="n">
-        <v>47.83046185324169</v>
+        <v>43.47701854793333</v>
       </c>
       <c r="C30" s="16" t="n">
-        <v>49.57954652586658</v>
+        <v>44.33968449095657</v>
       </c>
       <c r="D30" s="16" t="n">
-        <v>51.59264778644084</v>
+        <v>45.28376888412894</v>
       </c>
       <c r="E30" s="16" t="n">
-        <v>53.95371731221135</v>
+        <v>46.33623644020645</v>
       </c>
       <c r="F30" s="16" t="n">
-        <v>56.78651981901907</v>
+        <v>47.53743663148617</v>
       </c>
     </row>
     <row r="32">
@@ -3086,7 +3191,7 @@
         </is>
       </c>
       <c r="B33" s="20" t="n">
-        <v>6641.916975726794</v>
+        <v>6848.505570056388</v>
       </c>
     </row>
     <row r="34">
@@ -3096,7 +3201,7 @@
         </is>
       </c>
       <c r="B34" s="17" t="n">
-        <v>0.2762141296512998</v>
+        <v>0.2823794219690113</v>
       </c>
     </row>
     <row r="35">
@@ -3106,7 +3211,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>115.1112127508976</v>
+        <v>118.6916043337329</v>
       </c>
     </row>
     <row r="36">
@@ -3115,8 +3220,8 @@
           <t xml:space="preserve">   as a multiple of the plant's stated USD 100 million cost</t>
         </is>
       </c>
-      <c r="B36" s="35" t="n">
-        <v>1.151112127508976</v>
+      <c r="B36" s="23" t="n">
+        <v>1.186916043337329</v>
       </c>
     </row>
   </sheetData>
@@ -3236,35 +3341,35 @@
         </is>
       </c>
       <c r="B3" s="5">
-        <f>'Balance Sheet'!B18</f>
+        <f>'Balance Sheet'!B20</f>
         <v/>
       </c>
       <c r="C3" s="5">
-        <f>'Balance Sheet'!C18</f>
+        <f>'Balance Sheet'!C20</f>
         <v/>
       </c>
       <c r="D3" s="5">
-        <f>'Balance Sheet'!D18</f>
+        <f>'Balance Sheet'!D20</f>
         <v/>
       </c>
       <c r="E3" s="5">
-        <f>'Balance Sheet'!E18</f>
+        <f>'Balance Sheet'!E20</f>
         <v/>
       </c>
       <c r="F3" s="5">
-        <f>'Balance Sheet'!F18</f>
+        <f>'Balance Sheet'!F20</f>
         <v/>
       </c>
       <c r="G3" s="5">
-        <f>'Balance Sheet'!G18</f>
+        <f>'Balance Sheet'!G20</f>
         <v/>
       </c>
       <c r="H3" s="5">
-        <f>'Balance Sheet'!H18</f>
+        <f>'Balance Sheet'!H20</f>
         <v/>
       </c>
       <c r="I3" s="5">
-        <f>'Balance Sheet'!I18</f>
+        <f>'Balance Sheet'!I20</f>
         <v/>
       </c>
     </row>
@@ -3337,23 +3442,23 @@
           <t>Net debt / EBITDA</t>
         </is>
       </c>
-      <c r="E6" s="34">
+      <c r="E6" s="36">
         <f>('Balance Sheet'!E13-Assumptions!$C$70)/'Income Statement'!E17</f>
         <v/>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="36">
         <f>('Balance Sheet'!F13-Assumptions!$C$70)/'Income Statement'!F17</f>
         <v/>
       </c>
-      <c r="G6" s="34">
+      <c r="G6" s="36">
         <f>('Balance Sheet'!G13-Assumptions!$C$70)/'Income Statement'!G17</f>
         <v/>
       </c>
-      <c r="H6" s="34">
+      <c r="H6" s="36">
         <f>('Balance Sheet'!H13-Assumptions!$C$70)/'Income Statement'!H17</f>
         <v/>
       </c>
-      <c r="I6" s="34">
+      <c r="I6" s="36">
         <f>('Balance Sheet'!I13-Assumptions!$C$70)/'Income Statement'!I17</f>
         <v/>
       </c>
@@ -3445,23 +3550,23 @@
           <t>Cash conversion cycle (days)</t>
         </is>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="27">
         <f>E7+E8-E9</f>
         <v/>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="27">
         <f>F7+F8-F9</f>
         <v/>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="27">
         <f>G7+G8-G9</f>
         <v/>
       </c>
-      <c r="H10" s="26">
+      <c r="H10" s="27">
         <f>H7+H8-H9</f>
         <v/>
       </c>
-      <c r="I10" s="26">
+      <c r="I10" s="27">
         <f>I7+I8-I9</f>
         <v/>
       </c>
@@ -3473,23 +3578,23 @@
         </is>
       </c>
       <c r="E11" s="6">
-        <f>('Income Statement'!E15*(1-Assumptions!$C$5))/('Balance Sheet'!E2+'Balance Sheet'!E3+'Balance Sheet'!E17+Assumptions!$C$77)</f>
+        <f>('Income Statement'!E15*(1-Assumptions!$C$6))/('Balance Sheet'!E2+'Balance Sheet'!E3+'Balance Sheet'!E19+Assumptions!$C$78)</f>
         <v/>
       </c>
       <c r="F11" s="6">
-        <f>('Income Statement'!F15*(1-Assumptions!$C$5))/('Balance Sheet'!F2+'Balance Sheet'!F3+'Balance Sheet'!F17+Assumptions!$C$77)</f>
+        <f>('Income Statement'!F15*(1-Assumptions!$C$6))/('Balance Sheet'!F2+'Balance Sheet'!F3+'Balance Sheet'!F19+Assumptions!$C$78)</f>
         <v/>
       </c>
       <c r="G11" s="6">
-        <f>('Income Statement'!G15*(1-Assumptions!$C$5))/('Balance Sheet'!G2+'Balance Sheet'!G3+'Balance Sheet'!G17+Assumptions!$C$77)</f>
+        <f>('Income Statement'!G15*(1-Assumptions!$C$6))/('Balance Sheet'!G2+'Balance Sheet'!G3+'Balance Sheet'!G19+Assumptions!$C$78)</f>
         <v/>
       </c>
       <c r="H11" s="6">
-        <f>('Income Statement'!H15*(1-Assumptions!$C$5))/('Balance Sheet'!H2+'Balance Sheet'!H3+'Balance Sheet'!H17+Assumptions!$C$77)</f>
+        <f>('Income Statement'!H15*(1-Assumptions!$C$6))/('Balance Sheet'!H2+'Balance Sheet'!H3+'Balance Sheet'!H19+Assumptions!$C$78)</f>
         <v/>
       </c>
       <c r="I11" s="6">
-        <f>('Income Statement'!I15*(1-Assumptions!$C$5))/('Balance Sheet'!I2+'Balance Sheet'!I3+'Balance Sheet'!I17+Assumptions!$C$77)</f>
+        <f>('Income Statement'!I15*(1-Assumptions!$C$6))/('Balance Sheet'!I2+'Balance Sheet'!I3+'Balance Sheet'!I19+Assumptions!$C$78)</f>
         <v/>
       </c>
     </row>
@@ -3541,9 +3646,9 @@
           <t>Peer multiples are MARKET DATA and sit in the cross-check layer. No peer figure is used to build any historical number for the subject company.</t>
         </is>
       </c>
-      <c r="B2" s="42" t="n"/>
-      <c r="C2" s="42" t="n"/>
-      <c r="D2" s="43" t="n"/>
+      <c r="B2" s="44" t="n"/>
+      <c r="C2" s="44" t="n"/>
+      <c r="D2" s="45" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -3592,7 +3697,7 @@
         </is>
       </c>
       <c r="B5" s="22" t="n">
-        <v>19.5</v>
+        <v>21.35</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -3611,7 +3716,7 @@
           <t>The subject company today</t>
         </is>
       </c>
-      <c r="B6" s="49">
+      <c r="B6" s="51">
         <f>Assumptions!$C$3/('Income Statement'!D26/Assumptions!$C$4)</f>
         <v/>
       </c>
@@ -3632,8 +3737,8 @@
           <t>The subject company's own four-year mean</t>
         </is>
       </c>
-      <c r="B7" s="39">
-        <f>'Relative &amp; Normalized'!D16</f>
+      <c r="B7" s="40">
+        <f>'Relative &amp; Normalized'!D24</f>
         <v/>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -3747,7 +3852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3794,7 +3899,7 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>Terminal value 76% of core enterprise value</t>
+          <t>Terminal value 74% of core enterprise value, 62% of total</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3919,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Terminal value 75% of core enterprise value</t>
+          <t>Terminal value 75% of core enterprise value, 64% of total</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3986,7 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>WEIGHTED CENTRAL FAIR VALUE</t>
+          <t>WEIGHTED CENTRE — FRAME A</t>
         </is>
       </c>
       <c r="B7" s="9">
@@ -3899,53 +4004,62 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>Field low to field high</t>
-        </is>
-      </c>
-      <c r="B8" s="12">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>WEIGHTED CENTRE — FRAME B</t>
+        </is>
+      </c>
+      <c r="B8" s="9">
         <f>'Fundamental Valuation'!B8</f>
         <v/>
       </c>
-      <c r="C8" s="12">
-        <f>'Fundamental Valuation'!B9</f>
-        <v/>
+      <c r="C8" s="10">
+        <f>B8/Assumptions!$C$3-1</f>
+        <v/>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>TWO CENTRES, NEVER AVERAGED INTO ONE. Which one you use is a judgement about the debtor book, and it is yours to make rather than ours to bury.</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
+          <t>Field low to field high</t>
+        </is>
+      </c>
+      <c r="B9" s="12">
+        <f>'Fundamental Valuation'!B9</f>
+        <v/>
+      </c>
+      <c r="C9" s="12">
+        <f>'Fundamental Valuation'!B10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
           <t>Market price</t>
         </is>
       </c>
-      <c r="B9" s="12">
+      <c r="B10" s="12">
         <f>Assumptions!$C$3</f>
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>KEY FIGURES</t>
         </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Market capitalisation (EGP mn)</t>
-        </is>
-      </c>
-      <c r="B12" s="13">
-        <f>Assumptions!$C$96</f>
-        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Net debt (EGP mn)</t>
+          <t>Market capitalisation (EGP mn)</t>
         </is>
       </c>
       <c r="B13" s="13">
@@ -3956,131 +4070,142 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Enterprise value (EGP mn)</t>
+          <t>Net debt (EGP mn)</t>
         </is>
       </c>
       <c r="B14" s="13">
-        <f>Assumptions!$C$96+Assumptions!$C$97+Assumptions!$C$74</f>
+        <f>Assumptions!$C$98</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>FY2025 revenue (EGP mn)</t>
+          <t>Enterprise value (EGP mn)</t>
         </is>
       </c>
       <c r="B15" s="13">
-        <f>'Income Statement'!D2</f>
+        <f>Assumptions!$C$97+Assumptions!$C$98+Assumptions!$C$75</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>FY2025 EBITDA (EGP mn)</t>
+          <t>FY2025 revenue (EGP mn)</t>
         </is>
       </c>
       <c r="B16" s="13">
-        <f>'Income Statement'!D17</f>
+        <f>'Income Statement'!D2</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>FY2025 attributable profit (EGP mn)</t>
+          <t>FY2025 EBITDA (EGP mn)</t>
         </is>
       </c>
       <c r="B17" s="13">
-        <f>'Income Statement'!D26</f>
+        <f>'Income Statement'!D17</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Trailing price / earnings</t>
-        </is>
-      </c>
-      <c r="B18" s="14">
-        <f>Assumptions!$C$3/('Income Statement'!D26/Assumptions!$C$4)</f>
+          <t>FY2025 attributable profit (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B18" s="13">
+        <f>'Income Statement'!D26</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Trailing enterprise value / EBITDA</t>
+          <t>Trailing price / earnings</t>
         </is>
       </c>
       <c r="B19" s="14">
-        <f>(Assumptions!$C$96+Assumptions!$C$97+Assumptions!$C$74)/'Income Statement'!D17</f>
+        <f>Assumptions!$C$3/('Income Statement'!D26/Assumptions!$C$4)</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Cost of equity</t>
-        </is>
-      </c>
-      <c r="B20" s="15">
-        <f>Assumptions!$C$91</f>
+          <t>Trailing enterprise value / EBITDA</t>
+        </is>
+      </c>
+      <c r="B20" s="14">
+        <f>(Assumptions!$C$97+Assumptions!$C$98+Assumptions!$C$75)/'Income Statement'!D17</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Weighted average cost of capital, year one</t>
+          <t>Cost of equity</t>
         </is>
       </c>
       <c r="B21" s="15">
-        <f>Assumptions!$C$100</f>
+        <f>Assumptions!$C$92</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Terminal weighted average cost of capital</t>
+          <t>Weighted average cost of capital, year one</t>
         </is>
       </c>
       <c r="B22" s="15">
-        <f>Assumptions!$C$106</f>
+        <f>Assumptions!$C$101</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Terminal value as a percentage of enterprise value</t>
-        </is>
-      </c>
-      <c r="B23" s="6">
-        <f>DCF!B28</f>
+          <t>Terminal weighted average cost of capital</t>
+        </is>
+      </c>
+      <c r="B23" s="15">
+        <f>Assumptions!$C$107</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Dividend per share proposed for FY2025 (EGP)</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="n">
-        <v>3.5</v>
+          <t>Terminal value as a percentage of enterprise value</t>
+        </is>
+      </c>
+      <c r="B24" s="6">
+        <f>DCF!B31</f>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
+          <t>Dividend per share proposed for FY2025 (EGP)</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
           <t>Dividend yield at the market price</t>
         </is>
       </c>
-      <c r="B25" s="6">
-        <f>B24/Assumptions!$C$3</f>
+      <c r="B26" s="6">
+        <f>B25/Assumptions!$C$3</f>
         <v/>
       </c>
     </row>
@@ -4095,7 +4220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -4137,7 +4262,7 @@
         <v/>
       </c>
       <c r="C2" s="17" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
@@ -4152,11 +4277,11 @@
         </is>
       </c>
       <c r="B3" s="12">
-        <f>DCF!B37</f>
+        <f>DCF!B42</f>
         <v/>
       </c>
       <c r="C3" s="17" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
@@ -4171,7 +4296,7 @@
         </is>
       </c>
       <c r="B4" s="12">
-        <f>('Balance Sheet'!G18)*0+1.706200*'Balance Sheet'!D18</f>
+        <f>(('Relative &amp; Normalized'!B6-Assumptions!$C$58)/(Assumptions!$C$104-Assumptions!$C$58))*'Balance Sheet'!D20</f>
         <v/>
       </c>
       <c r="C4" s="17" t="n">
@@ -4179,7 +4304,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Book value per share multiplied by (sustainable return less growth) over (perpetual cost of equity less growth).</t>
+          <t>Book value per share multiplied by (sustainable return less growth) over (perpetual cost of equity less growth). EVERY term is live: the sustainable return reads the forecast return-on-equity path, and the perpetual cost of equity reads beta, the terminal risk-free rate and the terminal premium.</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4315,7 @@
         </is>
       </c>
       <c r="B5" s="12">
-        <f>'Relative &amp; Normalized'!C8</f>
+        <f>'Relative &amp; Normalized'!C16</f>
         <v/>
       </c>
       <c r="C5" s="17" t="n">
@@ -4198,7 +4323,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Three multiples triangulated ON the sheet — the multiple this model's own economics justify, the company's own four-year mean, and a cost-of-equity-adjusted regional peer median — averaged rather than asserted.</t>
+          <t>Three multiples triangulated ON the sheet, EACH APPLIED TO THE EARNINGS OF ITS OWN PERIOD — the forward multiple this model's own economics justify on forward earnings, and the company's own four-year mean and a cost-of-equity-adjusted struck peer reference on trailing earnings.</t>
         </is>
       </c>
     </row>
@@ -4209,7 +4334,7 @@
         </is>
       </c>
       <c r="B6" s="12">
-        <f>'Relative &amp; Normalized'!B25</f>
+        <f>'Relative &amp; Normalized'!B34</f>
         <v/>
       </c>
       <c r="C6" s="17" t="n">
@@ -4221,67 +4346,98 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="42" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>WEIGHTED CENTRAL FAIR VALUE</t>
+          <t>WEIGHTED CENTRE — FRAME A</t>
         </is>
       </c>
       <c r="B7" s="9">
-        <f>B2*C2+B3*C3+B4*C4+B5*C5+B6*C6</f>
+        <f>B2*C2+B4*C4+B5*C5+B6*C6</f>
         <v/>
       </c>
       <c r="C7" s="10">
-        <f>C2+C3+C4+C5+C6</f>
+        <f>C2+C4+C5+C6</f>
         <v/>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>The weights sum to one; the cell to the left proves it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>Low of the field</t>
-        </is>
-      </c>
-      <c r="B8" s="12">
-        <f>MIN(B2:B6)</f>
-        <v/>
+          <t>The discounted-cash-flow weight in full on Frame A, beside the three lenses that do not turn on the contested judgement. The weights sum to one; the cell to the left proves it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>WEIGHTED CENTRE — FRAME B</t>
+        </is>
+      </c>
+      <c r="B8" s="9">
+        <f>B3*C3+B4*C4+B5*C5+B6*C6</f>
+        <v/>
+      </c>
+      <c r="C8" s="10">
+        <f>C3+C4+C5+C6</f>
+        <v/>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>THE TWO CENTRES ARE NOT AVERAGED. Weighting both frames inside one number is a straight average of them, which is exactly what this study says it never does.</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>High of the field</t>
+          <t>Low of the field</t>
         </is>
       </c>
       <c r="B9" s="12">
-        <f>MAX(B2:B6)</f>
+        <f>MIN(B2:B6)</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
+          <t>High of the field</t>
+        </is>
+      </c>
+      <c r="B10" s="12">
+        <f>MAX(B2:B6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
           <t>Market price</t>
         </is>
       </c>
-      <c r="B10" s="12">
+      <c r="B11" s="12">
         <f>Assumptions!$C$3</f>
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Market price relative to the weighted central value</t>
-        </is>
-      </c>
-      <c r="B11" s="10">
-        <f>B10/B7-1</f>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Market price relative to the Frame A centre</t>
+        </is>
+      </c>
+      <c r="B12" s="10">
+        <f>B11/B7-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Market price relative to the Frame B centre</t>
+        </is>
+      </c>
+      <c r="B13" s="10">
+        <f>B11/B8-1</f>
         <v/>
       </c>
     </row>
@@ -5115,7 +5271,7 @@
         </is>
       </c>
       <c r="C40" s="19" t="n">
-        <v>0.2231</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="41" ht="26" customHeight="1">
@@ -5130,7 +5286,7 @@
         </is>
       </c>
       <c r="C41" s="19" t="n">
-        <v>0.0341</v>
+        <v>0.0342</v>
       </c>
     </row>
     <row r="42" ht="26" customHeight="1">
@@ -5145,7 +5301,7 @@
         </is>
       </c>
       <c r="C42" s="19" t="n">
-        <v>0.0941</v>
+        <v>0.095164</v>
       </c>
     </row>
     <row r="43" ht="26" customHeight="1">
@@ -5160,7 +5316,7 @@
         </is>
       </c>
       <c r="C43" s="19" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.059702</v>
       </c>
     </row>
     <row r="44" ht="26" customHeight="1">
@@ -5175,7 +5331,7 @@
         </is>
       </c>
       <c r="C44" s="19" t="n">
-        <v>0.1394</v>
+        <v>0.134806</v>
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
@@ -5256,12 +5412,12 @@
     <row r="50" ht="26" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Cost-of-debt path</t>
+          <t>Normalised risk-free convergence path</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>The glide fractions are DERIVED from this row</t>
+          <t>NOT a cost of debt: the first point is the normalised risk-free rate. Only the SHAPE of this row enters the model — the discount-rate glide rebases it to its own endpoints, so the levels cancel</t>
         </is>
       </c>
       <c r="C50" s="19" t="n">
@@ -5315,7 +5471,7 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>5% inflation target plus a 5.5-point real convention</t>
+          <t>A sourced 5% medium-term inflation target plus an UNSOURCED 5.5-point real convention. The real leg is an assertion, it is the widest single lever in the study, and it is an open item — see the terminal grid</t>
         </is>
       </c>
       <c r="C52" s="19" t="n">
@@ -5370,46 +5526,46 @@
     <row r="56" ht="26" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Terminal debt weight</t>
+          <t>Terminal debt weight — DERIVED, market-value basis</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>Reconciled to the model's own forecast balance sheet</t>
+          <t>Today's net debt over market capitalisation plus net debt. Not an assumption; the earlier edition's 20% was neither this nor the book reading below</t>
         </is>
       </c>
       <c r="C56" s="17" t="n">
-        <v>0.2</v>
+        <v>0.251247066000691</v>
       </c>
     </row>
     <row r="57" ht="26" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Terminal growth</t>
+          <t>Terminal debt weight — the funded forecast balance sheet at FY2030E</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>Pound-nominal, against a 5% terminal inflation rate — about zero in real terms</t>
+          <t>disclosure — the BOOK reading, published beside the market reading above rather than chosen between in silence. The valuation uses the market reading, because a weighted average cost of capital weights market values; this row drives nothing</t>
         </is>
       </c>
       <c r="C57" s="17" t="n">
-        <v>0.05</v>
+        <v>0.3953013301436529</v>
       </c>
     </row>
     <row r="58" ht="26" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Terminal return on invested capital</t>
+          <t>Terminal growth</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>Sets terminal reinvestment as growth over return</t>
+          <t>Pound-nominal, against a 5% terminal inflation rate — about zero in real terms</t>
         </is>
       </c>
       <c r="C58" s="17" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="59" ht="26" customHeight="1">
@@ -5420,7 +5576,7 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>Three disclosed years: 74.5, 147.1, 495.5</t>
+          <t>Three disclosed years, reconciled to this model's own income statement: 74.508, 151.581, 512.085 — mean 246.058. The first quarter of 2026 annualises to 52.5, but the auditor states two holdings' statements were not received, so that quarter is evidence, not a run-rate</t>
         </is>
       </c>
       <c r="C59" s="20" t="n">
@@ -5445,16 +5601,16 @@
     <row r="61" ht="26" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Regional peer median price-earnings multiple</t>
+          <t>Struck peer reference price-earnings multiple</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>MARKET DATA, cross-check layer</t>
-        </is>
-      </c>
-      <c r="C61" s="22" t="n">
-        <v>19.5</v>
+          <t>MARKET DATA, cross-check layer. The MIDPOINT of the only two disclosed observations (26.7x and 16.0x) — NOT a median of a peer set, and the peers are not named, so it cannot be rebuilt from their filings</t>
+        </is>
+      </c>
+      <c r="C61" s="23" t="n">
+        <v>21.35</v>
       </c>
     </row>
     <row r="62">
@@ -5602,202 +5758,202 @@
     <row r="72" ht="26" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>Equity attributable to the holding company</t>
+          <t>Attributable profit, FY2025 (EGP mn)</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>Audited</t>
+          <t>Audited — the trailing earnings base for every trailing multiple</t>
         </is>
       </c>
       <c r="C72" s="20" t="n">
-        <v>6243.131482</v>
+        <v>1441.6577</v>
       </c>
     </row>
     <row r="73" ht="26" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Non-controlling interests, audited 31 December 2025</t>
+          <t>Equity attributable to the holding company</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>disclosure — the audited December figure, shown so the reader can see both. It is SUPERSEDED for valuation by the March figure below, because almost all of it was the active-ingredient company and that company was deconsolidated in the first quarter of 2026. This row drives the balance sheet history only</t>
+          <t>Audited</t>
         </is>
       </c>
       <c r="C73" s="20" t="n">
-        <v>288.704605</v>
+        <v>6243.131482</v>
       </c>
     </row>
     <row r="74" ht="26" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Non-controlling interests deducted in the bridge</t>
+          <t>Non-controlling interests, audited 31 December 2025</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>Post-deconsolidation, from the reviewed 31 March 2026 interim</t>
+          <t>disclosure — the audited December figure, shown so the reader can see both. It is SUPERSEDED for valuation by the March figure below, because almost all of it was the active-ingredient company and that company was deconsolidated in the first quarter of 2026. This row drives the balance sheet history only</t>
         </is>
       </c>
       <c r="C74" s="20" t="n">
-        <v>3.999807</v>
+        <v>288.704605</v>
       </c>
     </row>
     <row r="75" ht="26" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Active-ingredient company at carrying cost (EGP mn)</t>
+          <t>Non-controlling interests deducted in the bridge</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>Pre-revenue, so cost not an earnings multiple; the Q1-2026 movement in investments in associates</t>
+          <t>Post-deconsolidation, from the reviewed 31 March 2026 interim</t>
         </is>
       </c>
       <c r="C75" s="20" t="n">
-        <v>228.4864180000001</v>
+        <v>3.999807</v>
       </c>
     </row>
     <row r="76" ht="26" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Assets held for sale</t>
+          <t>Active-ingredient company at carrying cost (EGP mn)</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>Note (8/1)</t>
+          <t>Pre-revenue, so cost not an earnings multiple; the Q1-2026 movement in investments in associates</t>
         </is>
       </c>
       <c r="C76" s="20" t="n">
-        <v>12.33</v>
+        <v>228.4864180000001</v>
       </c>
     </row>
     <row r="77" ht="26" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Intangible assets, net</t>
+          <t>Assets held for sale</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>Note (7)</t>
+          <t>Note (8/1)</t>
         </is>
       </c>
       <c r="C77" s="20" t="n">
-        <v>40.142171</v>
+        <v>12.33</v>
       </c>
     </row>
     <row r="78" ht="26" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>Right-of-use and intangible amortisation run-rate</t>
+          <t>Intangible assets, net</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>Audited FY2025 cash-flow statement</t>
-        </is>
-      </c>
-      <c r="C78" s="23" t="n">
-        <v>8.269948999999997</v>
+          <t>Note (7)</t>
+        </is>
+      </c>
+      <c r="C78" s="20" t="n">
+        <v>40.142171</v>
       </c>
     </row>
     <row r="79" ht="26" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>Share of depreciation charged to cost of sales</t>
+          <t>Right-of-use and intangible amortisation run-rate</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>Cost of sales note (26): 93.498 of 117.725</t>
-        </is>
-      </c>
-      <c r="C79" s="17" t="n">
-        <v>0.7942005773538676</v>
+          <t>Audited FY2025 cash-flow statement</t>
+        </is>
+      </c>
+      <c r="C79" s="24" t="n">
+        <v>8.269948999999997</v>
       </c>
     </row>
     <row r="80" ht="26" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>FY2025 cash cost per pack sold (EGP)</t>
+          <t>Share of depreciation charged to cost of sales</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>Cost of sales less its depreciation line, over packs sold</t>
-        </is>
-      </c>
-      <c r="C80" s="16" t="n">
-        <v>14.53600902055724</v>
+          <t>Cost of sales note (26): 93.498 of 117.725</t>
+        </is>
+      </c>
+      <c r="C80" s="17" t="n">
+        <v>0.7942005773538676</v>
       </c>
     </row>
     <row r="81" ht="26" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Consolidated-to-separate revenue factor</t>
+          <t>FY2025 cash cost per pack sold (EGP)</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>MEASURED: audited consolidated revenue over the separate-company channel total</t>
-        </is>
-      </c>
-      <c r="C81" s="24" t="n">
-        <v>1.014932591450432</v>
+          <t>Cost of sales less its depreciation line, over packs sold</t>
+        </is>
+      </c>
+      <c r="C81" s="16" t="n">
+        <v>14.53600902055724</v>
       </c>
     </row>
     <row r="82" ht="26" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>FY2025 domestic packs (million)</t>
+          <t>Consolidated-to-separate revenue factor</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>Unit build</t>
-        </is>
-      </c>
-      <c r="C82" s="16" t="n">
-        <v>291.81</v>
+          <t>MEASURED: audited consolidated revenue over the separate-company channel total</t>
+        </is>
+      </c>
+      <c r="C82" s="25" t="n">
+        <v>1.014932591450432</v>
       </c>
     </row>
     <row r="83" ht="26" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>FY2025 export packs (million)</t>
+          <t>FY2025 domestic packs (million)</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>Investor presentation</t>
+          <t>Unit build</t>
         </is>
       </c>
       <c r="C83" s="16" t="n">
-        <v>60</v>
+        <v>291.81</v>
       </c>
     </row>
     <row r="84" ht="26" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>FY2025 domestic price per pack (EGP)</t>
+          <t>FY2025 export packs (million)</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>Unit build</t>
+          <t>Investor presentation</t>
         </is>
       </c>
       <c r="C84" s="16" t="n">
-        <v>21.54012212741167</v>
+        <v>60</v>
       </c>
     </row>
     <row r="85" ht="26" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>FY2025 export price per pack (USD)</t>
+          <t>FY2025 domestic price per pack (EGP)</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
@@ -5806,81 +5962,80 @@
         </is>
       </c>
       <c r="C85" s="16" t="n">
-        <v>0.9995553449205068</v>
+        <v>21.54012212741167</v>
       </c>
     </row>
     <row r="86" ht="26" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>FY2025 contract-manufacturing packs (million)</t>
+          <t>FY2025 export price per pack (USD)</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>Board report</t>
+          <t>Unit build</t>
         </is>
       </c>
       <c r="C86" s="16" t="n">
-        <v>5.485</v>
+        <v>0.9995553449205068</v>
       </c>
     </row>
     <row r="87" ht="26" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>FY2025 contract-manufacturing revenue (EGP mn)</t>
+          <t>FY2025 contract-manufacturing packs (million)</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>Revenue note (25)</t>
-        </is>
-      </c>
-      <c r="C87" s="23" t="n">
-        <v>49.366365</v>
+          <t>Board report</t>
+        </is>
+      </c>
+      <c r="C87" s="16" t="n">
+        <v>5.485</v>
       </c>
     </row>
     <row r="88" ht="26" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
+          <t>FY2025 contract-manufacturing revenue (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>Revenue note (25)</t>
+        </is>
+      </c>
+      <c r="C88" s="24" t="n">
+        <v>49.366365</v>
+      </c>
+    </row>
+    <row r="89" ht="26" customHeight="1">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
           <t>FY2025 average exchange rate</t>
         </is>
       </c>
-      <c r="B88" s="7" t="inlineStr">
+      <c r="B89" s="7" t="inlineStr">
         <is>
           <t>Note (36)</t>
         </is>
       </c>
-      <c r="C88" s="16" t="n">
+      <c r="C89" s="16" t="n">
         <v>49.48</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="8" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="8" t="inlineStr">
         <is>
           <t>DERIVED IN THIS SHEET (formulas, not inputs)</t>
         </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="4" t="inlineStr">
-        <is>
-          <t>Normalised risk-free rate = yield less sovereign spread</t>
-        </is>
-      </c>
-      <c r="B90" s="7" t="inlineStr">
-        <is>
-          <t>calculated</t>
-        </is>
-      </c>
-      <c r="C90" s="25">
-        <f>$C$40-$C$41</f>
-        <v/>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Cost of equity = normalised risk-free + beta x premium</t>
+          <t>Normalised risk-free rate = yield less sovereign spread</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
@@ -5888,15 +6043,15 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C91" s="25">
-        <f>$C$90+$C$45*$C$42</f>
+      <c r="C91" s="26">
+        <f>$C$40-$C$41</f>
         <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>Cost of equity, rating basis (published alternative)</t>
+          <t>Cost of equity = normalised risk-free + beta x premium</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
@@ -5904,15 +6059,15 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C92" s="25">
-        <f>($C$40-$C$43)+$C$45*$C$44</f>
+      <c r="C92" s="26">
+        <f>$C$91+$C$45*$C$42</f>
         <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Hard-currency debt at LOCAL-EQUIVALENT cost</t>
+          <t>Cost of equity, rating basis (published alternative)</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
@@ -5920,15 +6075,15 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C93" s="25">
-        <f>(1+$C$47)*(1+$C$48)-1</f>
+      <c r="C93" s="26">
+        <f>($C$40-$C$43)+$C$45*$C$44</f>
         <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>Blended marginal cost of debt</t>
+          <t>Hard-currency debt at LOCAL-EQUIVALENT cost</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
@@ -5936,15 +6091,15 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C94" s="25">
-        <f>(1-$C$49)*$C$46+$C$49*$C$93</f>
+      <c r="C94" s="26">
+        <f>(1+$C$47)*(1+$C$48)-1</f>
         <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Cost of debt after tax</t>
+          <t>Blended marginal cost of debt</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
@@ -5952,15 +6107,15 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C95" s="25">
-        <f>$C$94*(1-$C$5)</f>
+      <c r="C95" s="26">
+        <f>(1-$C$49)*$C$46+$C$49*$C$94</f>
         <v/>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>Market capitalisation (EGP mn)</t>
+          <t>Cost of debt after tax</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
@@ -5969,14 +6124,14 @@
         </is>
       </c>
       <c r="C96" s="26">
-        <f>$C$3*$C$4</f>
+        <f>$C$95*(1-$C$5)</f>
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>Net debt (EGP mn)</t>
+          <t>Market capitalisation (EGP mn)</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
@@ -5984,15 +6139,15 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C97" s="26">
-        <f>$C$71-$C$70</f>
+      <c r="C97" s="27">
+        <f>$C$3*$C$4</f>
         <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>Equity weight (net basis)</t>
+          <t>Net debt (EGP mn)</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
@@ -6001,14 +6156,14 @@
         </is>
       </c>
       <c r="C98" s="27">
-        <f>$C$96/($C$96+$C$97)</f>
+        <f>$C$71-$C$70</f>
         <v/>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>Debt weight (net basis)</t>
+          <t>Equity weight (net basis)</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
@@ -6016,15 +6171,15 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C99" s="27">
-        <f>1-$C$98</f>
+      <c r="C99" s="28">
+        <f>$C$97/($C$97+$C$98)</f>
         <v/>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>Weighted average cost of capital, year one</t>
+          <t>Debt weight (net basis)</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
@@ -6032,15 +6187,15 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C100" s="25">
-        <f>$C$98*$C$91+$C$99*$C$95</f>
+      <c r="C100" s="28">
+        <f>1-$C$99</f>
         <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>Debt weight (gross basis)</t>
+          <t>Weighted average cost of capital, year one</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
@@ -6048,15 +6203,15 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C101" s="27">
-        <f>$C$71/($C$96+$C$71)</f>
+      <c r="C101" s="26">
+        <f>$C$99*$C$92+$C$100*$C$96</f>
         <v/>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>Weighted average cost of capital, gross-debt basis</t>
+          <t>Debt weight (gross basis)</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
@@ -6064,15 +6219,15 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C102" s="25">
-        <f>(1-$C$101)*$C$91+$C$101*$C$95</f>
+      <c r="C102" s="28">
+        <f>$C$71/($C$97+$C$71)</f>
         <v/>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>Terminal cost of equity</t>
+          <t>Weighted average cost of capital, gross-debt basis</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
@@ -6080,15 +6235,15 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C103" s="25">
-        <f>$C$52+$C$45*$C$53</f>
+      <c r="C103" s="26">
+        <f>(1-$C$102)*$C$92+$C$102*$C$96</f>
         <v/>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>Terminal cost of debt</t>
+          <t>Terminal cost of equity</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
@@ -6096,15 +6251,15 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C104" s="25">
-        <f>(1-$C$49)*$C$54+$C$49*((1+$C$55)*1.03-1)</f>
+      <c r="C104" s="26">
+        <f>$C$52+$C$45*$C$53</f>
         <v/>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>Terminal cost of debt after tax</t>
+          <t>Terminal cost of debt</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
@@ -6112,15 +6267,15 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C105" s="25">
-        <f>$C$104*(1-$C$5)</f>
+      <c r="C105" s="26">
+        <f>(1-$C$49)*$C$54+$C$49*((1+$C$55)*1.03-1)</f>
         <v/>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>Terminal weighted average cost of capital</t>
+          <t>Terminal cost of debt after tax</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
@@ -6128,15 +6283,15 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C106" s="25">
-        <f>(1-$C$56)*$C$103+$C$56*$C$105</f>
+      <c r="C106" s="26">
+        <f>$C$105*(1-$C$5)</f>
         <v/>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>Terminal reinvestment rate = growth / return on capital</t>
+          <t>Terminal weighted average cost of capital</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
@@ -6144,15 +6299,15 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C107" s="27">
-        <f>$C$57/$C$58</f>
+      <c r="C107" s="26">
+        <f>(1-$C$56)*$C$104+$C$56*$C$106</f>
         <v/>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>Glide fraction (derived from the cost-of-debt path)</t>
+          <t>Glide fraction (derived from the convergence path — SHAPE only)</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
@@ -6160,23 +6315,23 @@
           <t>calculated: (this year's cost of debt less the last year's) over (the first year's less the last year's)</t>
         </is>
       </c>
-      <c r="C108" s="28">
+      <c r="C108" s="29">
         <f>(C$50-$G$50)/($C$50-$G$50)</f>
         <v/>
       </c>
-      <c r="D108" s="28">
+      <c r="D108" s="29">
         <f>(D$50-$G$50)/($C$50-$G$50)</f>
         <v/>
       </c>
-      <c r="E108" s="28">
+      <c r="E108" s="29">
         <f>(E$50-$G$50)/($C$50-$G$50)</f>
         <v/>
       </c>
-      <c r="F108" s="28">
+      <c r="F108" s="29">
         <f>(F$50-$G$50)/($C$50-$G$50)</f>
         <v/>
       </c>
-      <c r="G108" s="28">
+      <c r="G108" s="29">
         <f>(G$50-$G$50)/($C$50-$G$50)</f>
         <v/>
       </c>
@@ -6193,23 +6348,23 @@
         </is>
       </c>
       <c r="C109" s="15">
-        <f>$C$106+($C$100-$C$106)*C$108</f>
+        <f>$C$107+($C$101-$C$107)*C$108</f>
         <v/>
       </c>
       <c r="D109" s="15">
-        <f>$C$106+($C$100-$C$106)*D$108</f>
+        <f>$C$107+($C$101-$C$107)*D$108</f>
         <v/>
       </c>
       <c r="E109" s="15">
-        <f>$C$106+($C$100-$C$106)*E$108</f>
+        <f>$C$107+($C$101-$C$107)*E$108</f>
         <v/>
       </c>
       <c r="F109" s="15">
-        <f>$C$106+($C$100-$C$106)*F$108</f>
+        <f>$C$107+($C$101-$C$107)*F$108</f>
         <v/>
       </c>
       <c r="G109" s="15">
-        <f>$C$106+($C$100-$C$106)*G$108</f>
+        <f>$C$107+($C$101-$C$107)*G$108</f>
         <v/>
       </c>
     </row>
@@ -6224,23 +6379,23 @@
           <t>calculated: the previous factor divided by one plus this year's rate — the factors compound</t>
         </is>
       </c>
-      <c r="C110" s="29">
+      <c r="C110" s="30">
         <f>1/(1+C$109)</f>
         <v/>
       </c>
-      <c r="D110" s="29">
+      <c r="D110" s="30">
         <f>C110/(1+D$109)</f>
         <v/>
       </c>
-      <c r="E110" s="29">
+      <c r="E110" s="30">
         <f>D110/(1+E$109)</f>
         <v/>
       </c>
-      <c r="F110" s="29">
+      <c r="F110" s="30">
         <f>E110/(1+F$109)</f>
         <v/>
       </c>
-      <c r="G110" s="29">
+      <c r="G110" s="30">
         <f>F110/(1+G$109)</f>
         <v/>
       </c>
@@ -6288,7 +6443,7 @@
         </is>
       </c>
       <c r="B2" s="13">
-        <f>DCF!B27</f>
+        <f>DCF!B30</f>
         <v/>
       </c>
       <c r="C2" s="5">
@@ -6303,7 +6458,7 @@
         </is>
       </c>
       <c r="B3" s="13">
-        <f>DCF!B24</f>
+        <f>DCF!B27</f>
         <v/>
       </c>
       <c r="C3" s="5">
@@ -6318,7 +6473,7 @@
         </is>
       </c>
       <c r="B4" s="10">
-        <f>DCF!B28</f>
+        <f>DCF!B31</f>
         <v/>
       </c>
     </row>
@@ -6344,7 +6499,7 @@
         </is>
       </c>
       <c r="B6" s="13">
-        <f>Assumptions!$C$75</f>
+        <f>Assumptions!$C$76</f>
         <v/>
       </c>
       <c r="C6" s="5">
@@ -6359,7 +6514,7 @@
         </is>
       </c>
       <c r="B7" s="13">
-        <f>Assumptions!$C$76</f>
+        <f>Assumptions!$C$77</f>
         <v/>
       </c>
       <c r="C7" s="5">
@@ -6373,7 +6528,7 @@
           <t>TOTAL ENTERPRISE VALUE</t>
         </is>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="31">
         <f>B2+B5+B6+B7</f>
         <v/>
       </c>
@@ -6389,7 +6544,7 @@
         </is>
       </c>
       <c r="B9" s="13">
-        <f>-Assumptions!$C$97</f>
+        <f>-Assumptions!$C$98</f>
         <v/>
       </c>
       <c r="C9" s="5">
@@ -6404,7 +6559,7 @@
         </is>
       </c>
       <c r="B10" s="13">
-        <f>-Assumptions!$C$74</f>
+        <f>-Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="C10" s="5">
@@ -6418,7 +6573,7 @@
           <t>EQUITY VALUE</t>
         </is>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="31">
         <f>B8+B9+B10</f>
         <v/>
       </c>
@@ -6433,7 +6588,7 @@
           <t>Value per share — Frame A</t>
         </is>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="31">
         <f>B11</f>
         <v/>
       </c>
@@ -6521,7 +6676,7 @@
         <v>291.81</v>
       </c>
       <c r="D2" s="5">
-        <f>Assumptions!$C$82*(1+Assumptions!C$8)</f>
+        <f>Assumptions!$C$83*(1+Assumptions!C$8)</f>
         <v/>
       </c>
       <c r="E2" s="5">
@@ -6554,7 +6709,7 @@
         <v>60</v>
       </c>
       <c r="D3" s="5">
-        <f>Assumptions!$C$83*(1+Assumptions!C$9)</f>
+        <f>Assumptions!$C$84*(1+Assumptions!C$9)</f>
         <v/>
       </c>
       <c r="E3" s="5">
@@ -6587,7 +6742,7 @@
         <v>21.54012212741167</v>
       </c>
       <c r="D4" s="5">
-        <f>Assumptions!$C$84*(1+Assumptions!C$10)</f>
+        <f>Assumptions!$C$85*(1+Assumptions!C$10)</f>
         <v/>
       </c>
       <c r="E4" s="5">
@@ -6620,7 +6775,7 @@
         <v>0.9995553449205068</v>
       </c>
       <c r="D5" s="5">
-        <f>Assumptions!$C$85*(1+Assumptions!C$11)</f>
+        <f>Assumptions!$C$86*(1+Assumptions!C$11)</f>
         <v/>
       </c>
       <c r="E5" s="5">
@@ -6685,23 +6840,23 @@
       <c r="C7" s="20" t="n">
         <v>6285.623038000001</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="32">
         <f>D2*D4</f>
         <v/>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="32">
         <f>E2*E4</f>
         <v/>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="32">
         <f>F2*F4</f>
         <v/>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="32">
         <f>G2*G4</f>
         <v/>
       </c>
-      <c r="H7" s="31">
+      <c r="H7" s="32">
         <f>H2*H4</f>
         <v/>
       </c>
@@ -6718,23 +6873,23 @@
       <c r="C8" s="20" t="n">
         <v>2967.479908</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="32">
         <f>D3*D5*D6</f>
         <v/>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="32">
         <f>E3*E5*E6</f>
         <v/>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="32">
         <f>F3*F5*F6</f>
         <v/>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="32">
         <f>G3*G5*G6</f>
         <v/>
       </c>
-      <c r="H8" s="31">
+      <c r="H8" s="32">
         <f>H3*H5*H6</f>
         <v/>
       </c>
@@ -6745,29 +6900,29 @@
           <t>Contract-manufacturing revenue (EGP mn)</t>
         </is>
       </c>
-      <c r="B9" s="23" t="n">
+      <c r="B9" s="24" t="n">
         <v>35.835829</v>
       </c>
-      <c r="C9" s="23" t="n">
+      <c r="C9" s="24" t="n">
         <v>49.366365</v>
       </c>
-      <c r="D9" s="32">
-        <f>Assumptions!$C$87*(1+Assumptions!C$12)</f>
-        <v/>
-      </c>
-      <c r="E9" s="32">
+      <c r="D9" s="33">
+        <f>Assumptions!$C$88*(1+Assumptions!C$12)</f>
+        <v/>
+      </c>
+      <c r="E9" s="33">
         <f>D9*(1+Assumptions!D$12)</f>
         <v/>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="33">
         <f>E9*(1+Assumptions!E$12)</f>
         <v/>
       </c>
-      <c r="G9" s="32">
+      <c r="G9" s="33">
         <f>F9*(1+Assumptions!F$12)</f>
         <v/>
       </c>
-      <c r="H9" s="32">
+      <c r="H9" s="33">
         <f>G9*(1+Assumptions!G$12)</f>
         <v/>
       </c>
@@ -6785,23 +6940,23 @@
         <v>357.295</v>
       </c>
       <c r="D10" s="5">
-        <f>D2+D3+Assumptions!$C$86</f>
+        <f>D2+D3+Assumptions!$C$87</f>
         <v/>
       </c>
       <c r="E10" s="5">
-        <f>E2+E3+Assumptions!$C$86</f>
+        <f>E2+E3+Assumptions!$C$87</f>
         <v/>
       </c>
       <c r="F10" s="5">
-        <f>F2+F3+Assumptions!$C$86</f>
+        <f>F2+F3+Assumptions!$C$87</f>
         <v/>
       </c>
       <c r="G10" s="5">
-        <f>G2+G3+Assumptions!$C$86</f>
+        <f>G2+G3+Assumptions!$C$87</f>
         <v/>
       </c>
       <c r="H10" s="5">
-        <f>H2+H3+Assumptions!$C$86</f>
+        <f>H2+H3+Assumptions!$C$87</f>
         <v/>
       </c>
     </row>
@@ -6817,24 +6972,24 @@
       <c r="C11" s="20" t="n">
         <v>9441.379305</v>
       </c>
-      <c r="D11" s="30">
-        <f>(D7+D8+D9)*Assumptions!$C$81</f>
-        <v/>
-      </c>
-      <c r="E11" s="30">
-        <f>(E7+E8+E9)*Assumptions!$C$81</f>
-        <v/>
-      </c>
-      <c r="F11" s="30">
-        <f>(F7+F8+F9)*Assumptions!$C$81</f>
-        <v/>
-      </c>
-      <c r="G11" s="30">
-        <f>(G7+G8+G9)*Assumptions!$C$81</f>
-        <v/>
-      </c>
-      <c r="H11" s="30">
-        <f>(H7+H8+H9)*Assumptions!$C$81</f>
+      <c r="D11" s="31">
+        <f>(D7+D8+D9)*Assumptions!$C$82</f>
+        <v/>
+      </c>
+      <c r="E11" s="31">
+        <f>(E7+E8+E9)*Assumptions!$C$82</f>
+        <v/>
+      </c>
+      <c r="F11" s="31">
+        <f>(F7+F8+F9)*Assumptions!$C$82</f>
+        <v/>
+      </c>
+      <c r="G11" s="31">
+        <f>(G7+G8+G9)*Assumptions!$C$82</f>
+        <v/>
+      </c>
+      <c r="H11" s="31">
+        <f>(H7+H8+H9)*Assumptions!$C$82</f>
         <v/>
       </c>
     </row>
@@ -6940,23 +7095,23 @@
           <t>Imported active ingredients</t>
         </is>
       </c>
-      <c r="D22" s="29">
-        <f>((1+Assumptions!$C$21)*(Segments!D6/Assumptions!$C$88))</f>
-        <v/>
-      </c>
-      <c r="E22" s="29">
+      <c r="D22" s="30">
+        <f>((1+Assumptions!$C$21)*(Segments!D6/Assumptions!$C$89))</f>
+        <v/>
+      </c>
+      <c r="E22" s="30">
         <f>D22*((1+Assumptions!$C$21)*(Segments!E6/Segments!D6))</f>
         <v/>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="30">
         <f>E22*((1+Assumptions!$C$21)*(Segments!F6/Segments!E6))</f>
         <v/>
       </c>
-      <c r="G22" s="29">
+      <c r="G22" s="30">
         <f>F22*((1+Assumptions!$C$21)*(Segments!G6/Segments!F6))</f>
         <v/>
       </c>
-      <c r="H22" s="29">
+      <c r="H22" s="30">
         <f>G22*((1+Assumptions!$C$21)*(Segments!H6/Segments!G6))</f>
         <v/>
       </c>
@@ -6967,23 +7122,23 @@
           <t>Packaging materials</t>
         </is>
       </c>
-      <c r="D23" s="29">
-        <f>(Assumptions!$C$22*(1+Assumptions!$C$21)*(Segments!D6/Assumptions!$C$88)+(1-Assumptions!$C$22)*(1+Assumptions!C$25))</f>
-        <v/>
-      </c>
-      <c r="E23" s="29">
+      <c r="D23" s="30">
+        <f>(Assumptions!$C$22*(1+Assumptions!$C$21)*(Segments!D6/Assumptions!$C$89)+(1-Assumptions!$C$22)*(1+Assumptions!C$25))</f>
+        <v/>
+      </c>
+      <c r="E23" s="30">
         <f>D23*(Assumptions!$C$22*(1+Assumptions!$C$21)*(Segments!E6/Segments!D6)+(1-Assumptions!$C$22)*(1+Assumptions!D$25))</f>
         <v/>
       </c>
-      <c r="F23" s="29">
+      <c r="F23" s="30">
         <f>E23*(Assumptions!$C$22*(1+Assumptions!$C$21)*(Segments!F6/Segments!E6)+(1-Assumptions!$C$22)*(1+Assumptions!E$25))</f>
         <v/>
       </c>
-      <c r="G23" s="29">
+      <c r="G23" s="30">
         <f>F23*(Assumptions!$C$22*(1+Assumptions!$C$21)*(Segments!G6/Segments!F6)+(1-Assumptions!$C$22)*(1+Assumptions!F$25))</f>
         <v/>
       </c>
-      <c r="H23" s="29">
+      <c r="H23" s="30">
         <f>G23*(Assumptions!$C$22*(1+Assumptions!$C$21)*(Segments!H6/Segments!G6)+(1-Assumptions!$C$22)*(1+Assumptions!G$25))</f>
         <v/>
       </c>
@@ -6994,23 +7149,23 @@
           <t>Labour</t>
         </is>
       </c>
-      <c r="D24" s="29">
+      <c r="D24" s="30">
         <f>(1+Assumptions!C$23)</f>
         <v/>
       </c>
-      <c r="E24" s="29">
+      <c r="E24" s="30">
         <f>D24*(1+Assumptions!D$23)</f>
         <v/>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="30">
         <f>E24*(1+Assumptions!E$23)</f>
         <v/>
       </c>
-      <c r="G24" s="29">
+      <c r="G24" s="30">
         <f>F24*(1+Assumptions!F$23)</f>
         <v/>
       </c>
-      <c r="H24" s="29">
+      <c r="H24" s="30">
         <f>G24*(1+Assumptions!G$23)</f>
         <v/>
       </c>
@@ -7021,23 +7176,23 @@
           <t>Energy and utilities</t>
         </is>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="30">
         <f>(1+Assumptions!C$24)</f>
         <v/>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="30">
         <f>D25*(1+Assumptions!D$24)</f>
         <v/>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="30">
         <f>E25*(1+Assumptions!E$24)</f>
         <v/>
       </c>
-      <c r="G25" s="29">
+      <c r="G25" s="30">
         <f>F25*(1+Assumptions!F$24)</f>
         <v/>
       </c>
-      <c r="H25" s="29">
+      <c r="H25" s="30">
         <f>G25*(1+Assumptions!G$24)</f>
         <v/>
       </c>
@@ -7048,23 +7203,23 @@
           <t>Other consumables and services</t>
         </is>
       </c>
-      <c r="D26" s="29">
+      <c r="D26" s="30">
         <f>(1+Assumptions!C$25)</f>
         <v/>
       </c>
-      <c r="E26" s="29">
+      <c r="E26" s="30">
         <f>D26*(1+Assumptions!D$25)</f>
         <v/>
       </c>
-      <c r="F26" s="29">
+      <c r="F26" s="30">
         <f>E26*(1+Assumptions!E$25)</f>
         <v/>
       </c>
-      <c r="G26" s="29">
+      <c r="G26" s="30">
         <f>F26*(1+Assumptions!F$25)</f>
         <v/>
       </c>
-      <c r="H26" s="29">
+      <c r="H26" s="30">
         <f>G26*(1+Assumptions!G$25)</f>
         <v/>
       </c>
@@ -7075,23 +7230,23 @@
           <t>Blended cash-cost index</t>
         </is>
       </c>
-      <c r="D27" s="33">
+      <c r="D27" s="34">
         <f>(Assumptions!$C$15*D22+Assumptions!$C$16*D23+Assumptions!$C$17*D24+Assumptions!$C$18*D25+Assumptions!$C$19*D26)/(Assumptions!$C$15+Assumptions!$C$16+Assumptions!$C$17+Assumptions!$C$18+Assumptions!$C$19)</f>
         <v/>
       </c>
-      <c r="E27" s="33">
+      <c r="E27" s="34">
         <f>(Assumptions!$C$15*E22+Assumptions!$C$16*E23+Assumptions!$C$17*E24+Assumptions!$C$18*E25+Assumptions!$C$19*E26)/(Assumptions!$C$15+Assumptions!$C$16+Assumptions!$C$17+Assumptions!$C$18+Assumptions!$C$19)</f>
         <v/>
       </c>
-      <c r="F27" s="33">
+      <c r="F27" s="34">
         <f>(Assumptions!$C$15*F22+Assumptions!$C$16*F23+Assumptions!$C$17*F24+Assumptions!$C$18*F25+Assumptions!$C$19*F26)/(Assumptions!$C$15+Assumptions!$C$16+Assumptions!$C$17+Assumptions!$C$18+Assumptions!$C$19)</f>
         <v/>
       </c>
-      <c r="G27" s="33">
+      <c r="G27" s="34">
         <f>(Assumptions!$C$15*G22+Assumptions!$C$16*G23+Assumptions!$C$17*G24+Assumptions!$C$18*G25+Assumptions!$C$19*G26)/(Assumptions!$C$15+Assumptions!$C$16+Assumptions!$C$17+Assumptions!$C$18+Assumptions!$C$19)</f>
         <v/>
       </c>
-      <c r="H27" s="33">
+      <c r="H27" s="34">
         <f>(Assumptions!$C$15*H22+Assumptions!$C$16*H23+Assumptions!$C$17*H24+Assumptions!$C$18*H25+Assumptions!$C$19*H26)/(Assumptions!$C$15+Assumptions!$C$16+Assumptions!$C$17+Assumptions!$C$18+Assumptions!$C$19)</f>
         <v/>
       </c>
@@ -7103,23 +7258,23 @@
         </is>
       </c>
       <c r="D28" s="12">
-        <f>Assumptions!$C$80*D27</f>
+        <f>Assumptions!$C$81*D27</f>
         <v/>
       </c>
       <c r="E28" s="12">
-        <f>Assumptions!$C$80*E27</f>
+        <f>Assumptions!$C$81*E27</f>
         <v/>
       </c>
       <c r="F28" s="12">
-        <f>Assumptions!$C$80*F27</f>
+        <f>Assumptions!$C$81*F27</f>
         <v/>
       </c>
       <c r="G28" s="12">
-        <f>Assumptions!$C$80*G27</f>
+        <f>Assumptions!$C$81*G27</f>
         <v/>
       </c>
       <c r="H28" s="12">
-        <f>Assumptions!$C$80*H27</f>
+        <f>Assumptions!$C$81*H27</f>
         <v/>
       </c>
     </row>
@@ -7217,24 +7372,24 @@
           <t>Amortisation of right-of-use and intangible assets</t>
         </is>
       </c>
-      <c r="D34" s="32">
-        <f>-Assumptions!$C$78</f>
-        <v/>
-      </c>
-      <c r="E34" s="32">
-        <f>-Assumptions!$C$78</f>
-        <v/>
-      </c>
-      <c r="F34" s="32">
-        <f>-Assumptions!$C$78</f>
-        <v/>
-      </c>
-      <c r="G34" s="32">
-        <f>-Assumptions!$C$78</f>
-        <v/>
-      </c>
-      <c r="H34" s="32">
-        <f>-Assumptions!$C$78</f>
+      <c r="D34" s="33">
+        <f>-Assumptions!$C$79</f>
+        <v/>
+      </c>
+      <c r="E34" s="33">
+        <f>-Assumptions!$C$79</f>
+        <v/>
+      </c>
+      <c r="F34" s="33">
+        <f>-Assumptions!$C$79</f>
+        <v/>
+      </c>
+      <c r="G34" s="33">
+        <f>-Assumptions!$C$79</f>
+        <v/>
+      </c>
+      <c r="H34" s="33">
+        <f>-Assumptions!$C$79</f>
         <v/>
       </c>
     </row>
@@ -7244,23 +7399,23 @@
           <t>Closing property, plant and equipment</t>
         </is>
       </c>
-      <c r="D35" s="30">
+      <c r="D35" s="31">
         <f>D31+D32+D33</f>
         <v/>
       </c>
-      <c r="E35" s="30">
+      <c r="E35" s="31">
         <f>E31+E32+E33</f>
         <v/>
       </c>
-      <c r="F35" s="30">
+      <c r="F35" s="31">
         <f>F31+F32+F33</f>
         <v/>
       </c>
-      <c r="G35" s="30">
+      <c r="G35" s="31">
         <f>G31+G32+G33</f>
         <v/>
       </c>
-      <c r="H35" s="30">
+      <c r="H35" s="31">
         <f>H31+H32+H33</f>
         <v/>
       </c>
@@ -7298,23 +7453,23 @@
           <t>Total depreciation and amortisation</t>
         </is>
       </c>
-      <c r="D37" s="26">
+      <c r="D37" s="27">
         <f>-D33-D34</f>
         <v/>
       </c>
-      <c r="E37" s="26">
+      <c r="E37" s="27">
         <f>-E33-E34</f>
         <v/>
       </c>
-      <c r="F37" s="26">
+      <c r="F37" s="27">
         <f>-F33-F34</f>
         <v/>
       </c>
-      <c r="G37" s="26">
+      <c r="G37" s="27">
         <f>-G33-G34</f>
         <v/>
       </c>
-      <c r="H37" s="26">
+      <c r="H37" s="27">
         <f>-H33-H34</f>
         <v/>
       </c>
@@ -7379,23 +7534,23 @@
           <t>Closing construction balance</t>
         </is>
       </c>
-      <c r="D40" s="30">
+      <c r="D40" s="31">
         <f>D38+D39</f>
         <v/>
       </c>
-      <c r="E40" s="30">
+      <c r="E40" s="31">
         <f>E38+E39</f>
         <v/>
       </c>
-      <c r="F40" s="30">
+      <c r="F40" s="31">
         <f>F38+F39</f>
         <v/>
       </c>
-      <c r="G40" s="30">
+      <c r="G40" s="31">
         <f>G38+G39</f>
         <v/>
       </c>
-      <c r="H40" s="30">
+      <c r="H40" s="31">
         <f>H38+H39</f>
         <v/>
       </c>
@@ -7411,7 +7566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -7443,309 +7598,421 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>FY2026E attributable earnings per share — Frame A</t>
-        </is>
-      </c>
-      <c r="B2" s="5">
-        <f>'Income Statement'!E27</f>
-        <v/>
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>SUSTAINABLE RETURN ON EQUITY — COMPUTED FROM THE FORECAST, NOT ASSERTED</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>FY2026E attributable earnings per share — Frame B</t>
-        </is>
-      </c>
-      <c r="B3" s="5">
-        <f>((DCF!B31-Assumptions!C$51)*(1-Assumptions!$C$6)+Assumptions!$C$59-18.0)/Assumptions!$C$4</f>
+          <t>Return on average equity, FY2028E</t>
+        </is>
+      </c>
+      <c r="B3" s="15">
+        <f>'Income Statement'!G26/(('Balance Sheet'!F14+'Balance Sheet'!G14)/2)</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Average of the two frames — the base for the multiples below</t>
-        </is>
-      </c>
-      <c r="B4" s="12">
-        <f>AVERAGE(B2:B3)</f>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Return on average equity, FY2029E</t>
+        </is>
+      </c>
+      <c r="B4" s="15">
+        <f>'Income Statement'!H26/(('Balance Sheet'!G14+'Balance Sheet'!H14)/2)</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Justified forward multiple from this model</t>
-        </is>
-      </c>
-      <c r="B5" s="34">
-        <f>(1-Assumptions!$C$57/0.21896499)/(Assumptions!$C$103-Assumptions!$C$57)</f>
-        <v/>
-      </c>
-      <c r="C5" s="5">
-        <f>B5*B4</f>
-        <v/>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Built from this model's own sustainable return and perpetual cost of equity</t>
-        </is>
+          <t>Return on average equity, FY2030E</t>
+        </is>
+      </c>
+      <c r="B5" s="15">
+        <f>'Income Statement'!I26/(('Balance Sheet'!H14+'Balance Sheet'!I14)/2)</f>
+        <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>The company's own four-year mean multiple</t>
-        </is>
-      </c>
-      <c r="B6" s="35" t="n">
-        <v>6.662777133225662</v>
-      </c>
-      <c r="C6" s="5">
-        <f>B6*B4</f>
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sustainable return — the mean of the last three forecast years</t>
+        </is>
+      </c>
+      <c r="B6" s="35">
+        <f>AVERAGE(B3:B5)</f>
         <v/>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Year-end closes against audited attributable profit</t>
+          <t>The forecast path RISES through the window rather than settling, so the sustainable return is the mean of its last three years — read from the path here, never typed</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Regional peer median, cost-of-equity adjusted</t>
-        </is>
-      </c>
-      <c r="B7" s="34">
-        <f>Assumptions!$C$61*(0.10-Assumptions!$C$57)/(Assumptions!$C$103-Assumptions!$C$57)</f>
-        <v/>
-      </c>
-      <c r="C7" s="5">
-        <f>B7*B4</f>
-        <v/>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>The peers face a cost of equity near 10%, not this one</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>AVERAGE OF THE THREE — the relative lens</t>
-        </is>
-      </c>
-      <c r="B8" s="36">
-        <f>AVERAGE(B5:B7)</f>
-        <v/>
-      </c>
-      <c r="C8" s="9">
-        <f>AVERAGE(C5:C7)</f>
+          <t>Payout the growth rate permits = 1 less growth over the sustainable return</t>
+        </is>
+      </c>
+      <c r="B7" s="6">
+        <f>1-Assumptions!$C$58/B6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>FY2026E attributable earnings per share — Frame A</t>
+        </is>
+      </c>
+      <c r="B9" s="5">
+        <f>'Income Statement'!E27</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>THE COMPANY'S OWN TRADED MULTIPLE HISTORY</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="37" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B11" s="38" t="inlineStr">
-        <is>
-          <t>Year-end close</t>
-        </is>
-      </c>
-      <c r="C11" s="38" t="inlineStr">
-        <is>
-          <t>Attributable EPS</t>
-        </is>
-      </c>
-      <c r="D11" s="38" t="inlineStr">
-        <is>
-          <t>Price / earnings</t>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>FY2026E attributable earnings per share — Frame B</t>
+        </is>
+      </c>
+      <c r="B10" s="5">
+        <f>((DCF!B35-Assumptions!C$51)*(1-Assumptions!$C$6)+Assumptions!$C$59-18.0)/Assumptions!$C$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Average of the two frames — the FORWARD earnings base</t>
+        </is>
+      </c>
+      <c r="B11" s="12">
+        <f>AVERAGE(B9:B10)</f>
+        <v/>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Averaging the two frames' EARNINGS is not averaging the two VALUATIONS: the frames are published as two separate centres and are never averaged into one</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="n">
-        <v>28.08</v>
-      </c>
-      <c r="C12" s="16" t="n">
-        <v>5.919508553450875</v>
-      </c>
-      <c r="D12" s="14">
-        <f>B12/C12</f>
-        <v/>
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>TRAILING attributable earnings per share, FY2025, on the count in issue today</t>
+        </is>
+      </c>
+      <c r="B12" s="12">
+        <f>Assumptions!$C$72/Assumptions!$C$4</f>
+        <v/>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>The base for the two TRAILING multiples below. A trailing multiple applied to forward earnings would mismatch the periods</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="C13" s="16" t="n">
-        <v>5.527972632990657</v>
-      </c>
-      <c r="D13" s="14">
-        <f>B13/C13</f>
-        <v/>
+          <t>Justified forward multiple from this model, on FY2026E earnings</t>
+        </is>
+      </c>
+      <c r="B13" s="36">
+        <f>B7/(Assumptions!$C$104-Assumptions!$C$58)</f>
+        <v/>
+      </c>
+      <c r="C13" s="5">
+        <f>B13*B11</f>
+        <v/>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>A FORWARD multiple, applied to FORWARD earnings — built from this model's own sustainable return and perpetual cost of equity</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n">
-        <v>45.91</v>
-      </c>
-      <c r="C14" s="16" t="n">
-        <v>7.365880505459453</v>
-      </c>
-      <c r="D14" s="14">
-        <f>B14/C14</f>
-        <v/>
+          <t>The company's own four-year mean multiple, on trailing earnings</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="n">
+        <v>6.572199327377573</v>
+      </c>
+      <c r="C14" s="5">
+        <f>B14*B12</f>
+        <v/>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>A TRAILING multiple, applied to TRAILING earnings — year-end closes against audited attributable profit, each year on its own weighted-average share count</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="C15" s="16" t="n">
-        <v>8.54286565050376</v>
-      </c>
-      <c r="D15" s="14">
-        <f>B15/C15</f>
-        <v/>
+          <t>Struck peer reference, cost-of-equity adjusted, on trailing earnings</t>
+        </is>
+      </c>
+      <c r="B15" s="36">
+        <f>Assumptions!$C$61*(0.10-Assumptions!$C$58)/(Assumptions!$C$104-Assumptions!$C$58)</f>
+        <v/>
+      </c>
+      <c r="C15" s="5">
+        <f>B15*B12</f>
+        <v/>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>A TRAILING multiple, applied to TRAILING earnings. The midpoint of the two disclosed observations, not a median of a peer set; those companies face a cost of equity near 10%, not this one</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>Four-year mean</t>
-        </is>
-      </c>
-      <c r="D16" s="39">
-        <f>AVERAGE(D12:D15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>Trailing multiple at the market price today</t>
-        </is>
-      </c>
-      <c r="B17" s="5">
-        <f>Assumptions!$C$3</f>
-        <v/>
-      </c>
-      <c r="C17" s="5">
-        <f>'Income Statement'!D27*162.016024/Assumptions!$C$4</f>
-        <v/>
-      </c>
-      <c r="D17" s="39">
-        <f>B17/C17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>NORMALISED EARNINGS POWER</t>
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>AVERAGE OF THE THREE — the relative lens</t>
+        </is>
+      </c>
+      <c r="B16" s="37">
+        <f>AVERAGE(B13:B15)</f>
+        <v/>
+      </c>
+      <c r="C16" s="9">
+        <f>AVERAGE(C13:C15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>THE COMPANY'S OWN TRADED MULTIPLE HISTORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="38" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B19" s="39" t="inlineStr">
+        <is>
+          <t>Year-end close</t>
+        </is>
+      </c>
+      <c r="C19" s="39" t="inlineStr">
+        <is>
+          <t>Attributable EPS</t>
+        </is>
+      </c>
+      <c r="D19" s="39" t="inlineStr">
+        <is>
+          <t>Price / earnings</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Three-year average operating margin</t>
-        </is>
-      </c>
-      <c r="B20" s="6">
-        <f>AVERAGE('Income Statement'!B15/'Income Statement'!B2,'Income Statement'!C15/'Income Statement'!C2,'Income Statement'!D15/'Income Statement'!D2)</f>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="n">
+        <v>28.08</v>
+      </c>
+      <c r="C20" s="16" t="n">
+        <v>5.919508553450875</v>
+      </c>
+      <c r="D20" s="14">
+        <f>B20/C20</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>FY2027E revenue</t>
-        </is>
-      </c>
-      <c r="B21" s="13">
-        <f>'Income Statement'!F2</f>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="C21" s="16" t="n">
+        <v>5.527972632990657</v>
+      </c>
+      <c r="D21" s="14">
+        <f>B21/C21</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Normalised operating profit</t>
-        </is>
-      </c>
-      <c r="B22" s="13">
-        <f>B20*B21</f>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="n">
+        <v>45.91</v>
+      </c>
+      <c r="C22" s="16" t="n">
+        <v>7.365880505459453</v>
+      </c>
+      <c r="D22" s="14">
+        <f>B22/C22</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="C23" s="16" t="n">
+        <v>8.898241448018748</v>
+      </c>
+      <c r="D23" s="14">
+        <f>B23/C23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>Four-year mean</t>
+        </is>
+      </c>
+      <c r="D24" s="40">
+        <f>AVERAGE(D20:D23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>Trailing multiple today — on the share count IN ISSUE</t>
+        </is>
+      </c>
+      <c r="B25" s="5">
+        <f>Assumptions!$C$3</f>
+        <v/>
+      </c>
+      <c r="C25" s="5">
+        <f>B12</f>
+        <v/>
+      </c>
+      <c r="D25" s="41">
+        <f>B25/C25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>Trailing multiple today — on the AUDITED WEIGHTED-AVERAGE count for FY2025</t>
+        </is>
+      </c>
+      <c r="B26" s="5">
+        <f>Assumptions!$C$3</f>
+        <v/>
+      </c>
+      <c r="C26" s="5">
+        <f>Assumptions!$C$72/162.016024</f>
+        <v/>
+      </c>
+      <c r="D26" s="41">
+        <f>B26/C26</f>
+        <v/>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>TWO SHARE COUNTS, BOTH PUBLISHED. The capital increase from 148.755750 to 168.755750 million shares completed during FY2025, so that year has a weighted-average count of 162.016024 million and a closing count of 168.755750 million. Both readings of the trailing multiple are legitimate; neither is stated alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>NORMALISED EARNINGS POWER</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Three-year average operating margin</t>
+        </is>
+      </c>
+      <c r="B29" s="6">
+        <f>AVERAGE('Income Statement'!B15/'Income Statement'!B2,'Income Statement'!C15/'Income Statement'!C2,'Income Statement'!D15/'Income Statement'!D2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>FY2027E revenue</t>
+        </is>
+      </c>
+      <c r="B30" s="13">
+        <f>'Income Statement'!F2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Normalised operating profit</t>
+        </is>
+      </c>
+      <c r="B31" s="13">
+        <f>B29*B30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
           <t>Normalised earnings per share</t>
         </is>
       </c>
-      <c r="B23" s="5">
-        <f>((B22-2.0-Assumptions!D$51)*(1-Assumptions!$C$6)+Assumptions!$C$59-18.0)/Assumptions!$C$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="B32" s="5">
+        <f>((B31-2.0-Assumptions!D$51)*(1-Assumptions!$C$6)+Assumptions!$C$59-18.0)/Assumptions!$C$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Payout the growth rate permits</t>
         </is>
       </c>
-      <c r="B24" s="6">
-        <f>1-Assumptions!$C$57/0.21896499</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="B33" s="6">
+        <f>1-Assumptions!$C$58/0.21896499</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>NORMALISED EARNINGS POWER VALUE</t>
         </is>
       </c>
-      <c r="B25" s="9">
-        <f>B23*B24/(Assumptions!$C$103-Assumptions!$C$57)</f>
+      <c r="B34" s="9">
+        <f>B32*B33/(Assumptions!$C$104-Assumptions!$C$58)</f>
         <v/>
       </c>
     </row>
@@ -7760,7 +8027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7842,23 +8109,23 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="27">
         <f>'Income Statement'!E17</f>
         <v/>
       </c>
-      <c r="C3" s="26">
+      <c r="C3" s="27">
         <f>'Income Statement'!F17</f>
         <v/>
       </c>
-      <c r="D3" s="26">
+      <c r="D3" s="27">
         <f>'Income Statement'!G17</f>
         <v/>
       </c>
-      <c r="E3" s="26">
+      <c r="E3" s="27">
         <f>'Income Statement'!H17</f>
         <v/>
       </c>
-      <c r="F3" s="26">
+      <c r="F3" s="27">
         <f>'Income Statement'!I17</f>
         <v/>
       </c>
@@ -7923,23 +8190,23 @@
           <t>EBIT = EBITDA less depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="27">
         <f>B3+B5</f>
         <v/>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="27">
         <f>C3+C5</f>
         <v/>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="27">
         <f>D3+D5</f>
         <v/>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="27">
         <f>E3+E5</f>
         <v/>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="27">
         <f>F3+F5</f>
         <v/>
       </c>
@@ -7947,27 +8214,27 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Tax rate</t>
+          <t>Tax rate — the EFFECTIVE rate the business bears, not the statutory rate</t>
         </is>
       </c>
       <c r="B7" s="15">
-        <f>Assumptions!$C$5</f>
+        <f>Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="C7" s="15">
-        <f>Assumptions!$C$5</f>
+        <f>Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="D7" s="15">
-        <f>Assumptions!$C$5</f>
+        <f>Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="E7" s="15">
-        <f>Assumptions!$C$5</f>
+        <f>Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="F7" s="15">
-        <f>Assumptions!$C$5</f>
+        <f>Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -7977,23 +8244,23 @@
           <t>NOPAT = EBIT x (1 less the tax rate)</t>
         </is>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="31">
         <f>B6*(1-B7)</f>
         <v/>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <f>C6*(1-C7)</f>
         <v/>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <f>D6*(1-D7)</f>
         <v/>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <f>E6*(1-E7)</f>
         <v/>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <f>F6*(1-F7)</f>
         <v/>
       </c>
@@ -8085,23 +8352,23 @@
           <t>FREE CASH FLOW TO THE FIRM</t>
         </is>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="31">
         <f>B8+B9+B10+B11</f>
         <v/>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="31">
         <f>C8+C9+C10+C11</f>
         <v/>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="31">
         <f>D8+D9+D10+D11</f>
         <v/>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="31">
         <f>E8+E9+E10+E11</f>
         <v/>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <f>F8+F9+F10+F11</f>
         <v/>
       </c>
@@ -8139,23 +8406,23 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B14" s="29">
+      <c r="B14" s="30">
         <f>Assumptions!C$110</f>
         <v/>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="30">
         <f>Assumptions!D$110</f>
         <v/>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <f>Assumptions!E$110</f>
         <v/>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <f>Assumptions!F$110</f>
         <v/>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <f>Assumptions!G$110</f>
         <v/>
       </c>
@@ -8166,23 +8433,23 @@
           <t>PRESENT VALUE OF FREE CASH FLOW TO THE FIRM</t>
         </is>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="31">
         <f>B12*B14</f>
         <v/>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="31">
         <f>C12*C14</f>
         <v/>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="31">
         <f>D12*D14</f>
         <v/>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="31">
         <f>E12*E14</f>
         <v/>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="31">
         <f>F12*F14</f>
         <v/>
       </c>
@@ -8197,258 +8464,323 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Terminal NOPAT = final-year NOPAT x (1 + growth)</t>
+          <t>Invested capital at FY2030E — property, construction, working capital and intangibles</t>
         </is>
       </c>
       <c r="B18" s="13">
-        <f>F8*(1+Assumptions!$C$57)</f>
+        <f>'Balance Sheet'!I2+'Balance Sheet'!I3+'Balance Sheet'!I19+Assumptions!$C$78</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Terminal reinvestment rate = growth / return on invested capital</t>
-        </is>
-      </c>
-      <c r="B19" s="6">
-        <f>Assumptions!$C$57/Assumptions!$C$58</f>
-        <v/>
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>Return on invested capital, FY2030E — the model's OWN, read from the rows above</t>
+        </is>
+      </c>
+      <c r="B19" s="26">
+        <f>F8/B18</f>
+        <v/>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>This is what sets terminal reinvestment. It is not an assumption and there is no cell to type it into.</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Terminal free cash flow = terminal NOPAT x (1 less reinvestment)</t>
+          <t>Terminal depreciation catch-up — the parked construction balance at the depreciation rate</t>
         </is>
       </c>
       <c r="B20" s="13">
-        <f>B18*(1-B19)</f>
-        <v/>
+        <f>'Balance Sheet'!I3*Assumptions!$C$34</f>
+        <v/>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Construction still parked at FY2030E has never entered the depreciable base. A perpetuity cannot capitalise profit on capital it never charges.</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Terminal discount rate</t>
-        </is>
-      </c>
-      <c r="B21" s="15">
-        <f>Assumptions!$C$106</f>
+          <t>Terminal NOPAT = final-year NOPAT x (1 + growth), less the depreciation the parked construction balance has never been charged</t>
+        </is>
+      </c>
+      <c r="B21" s="13">
+        <f>F8*(1+Assumptions!$C$58)-B20*(1-Assumptions!$C$6)</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
+          <t>Terminal reinvestment rate = growth / the return the model itself earns in FY2030E</t>
+        </is>
+      </c>
+      <c r="B22" s="6">
+        <f>Assumptions!$C$58/B19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Terminal free cash flow = terminal NOPAT x (1 less reinvestment)</t>
+        </is>
+      </c>
+      <c r="B23" s="13">
+        <f>B21*(1-B22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Terminal discount rate</t>
+        </is>
+      </c>
+      <c r="B24" s="15">
+        <f>Assumptions!$C$107</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="B22" s="6">
-        <f>Assumptions!$C$57</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>TERMINAL VALUE</t>
-        </is>
-      </c>
-      <c r="B23" s="26">
-        <f>B20/(B21-B22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>Present value of the terminal value</t>
-        </is>
-      </c>
-      <c r="B24" s="26">
-        <f>B23*F14</f>
+      <c r="B25" s="6">
+        <f>Assumptions!$C$58</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
+          <t>TERMINAL VALUE</t>
+        </is>
+      </c>
+      <c r="B26" s="27">
+        <f>B23/(B24-B25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>Present value of the terminal value</t>
+        </is>
+      </c>
+      <c r="B27" s="27">
+        <f>B26*F14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
           <t>Sum of the present values of forecast free cash flow</t>
         </is>
       </c>
-      <c r="B26" s="26">
+      <c r="B29" s="27">
         <f>SUM(B15:F15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>CORE ENTERPRISE VALUE</t>
-        </is>
-      </c>
-      <c r="B27" s="30">
-        <f>B26+B24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>Terminal value as a percentage of core enterprise value</t>
-        </is>
-      </c>
-      <c r="B28" s="10">
-        <f>B24/B27</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
+          <t>CORE ENTERPRISE VALUE</t>
+        </is>
+      </c>
+      <c r="B30" s="31">
+        <f>B29+B27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Terminal value as a percentage of CORE enterprise value</t>
+        </is>
+      </c>
+      <c r="B31" s="10">
+        <f>B27/B30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>Terminal value as a percentage of TOTAL enterprise value (both are published)</t>
+        </is>
+      </c>
+      <c r="B32" s="28">
+        <f>B27/(B30+Assumptions!$C$59*Assumptions!$C$60+Assumptions!$C$76+Assumptions!$C$77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
           <t>FRAME B — THE SAME MODEL WITH THE CONTESTED JUDGEMENT RESOLVED THE OTHER WAY</t>
         </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>EBIT on Frame B = Frame A EBIT plus the difference in the provision charge</t>
-        </is>
-      </c>
-      <c r="B31" s="13">
-        <f>B6+('Income Statement'!E12-'Income Statement'!E11)</f>
-        <v/>
-      </c>
-      <c r="C31" s="13">
-        <f>C6+('Income Statement'!F12-'Income Statement'!F11)</f>
-        <v/>
-      </c>
-      <c r="D31" s="13">
-        <f>D6+('Income Statement'!G12-'Income Statement'!G11)</f>
-        <v/>
-      </c>
-      <c r="E31" s="13">
-        <f>E6+('Income Statement'!H12-'Income Statement'!H11)</f>
-        <v/>
-      </c>
-      <c r="F31" s="13">
-        <f>F6+('Income Statement'!I12-'Income Statement'!I11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>NOPAT on Frame B</t>
-        </is>
-      </c>
-      <c r="B32" s="13">
-        <f>B31*(1-B7)</f>
-        <v/>
-      </c>
-      <c r="C32" s="13">
-        <f>C31*(1-C7)</f>
-        <v/>
-      </c>
-      <c r="D32" s="13">
-        <f>D31*(1-D7)</f>
-        <v/>
-      </c>
-      <c r="E32" s="13">
-        <f>E31*(1-E7)</f>
-        <v/>
-      </c>
-      <c r="F32" s="13">
-        <f>F31*(1-F7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>Free cash flow to the firm on Frame B</t>
-        </is>
-      </c>
-      <c r="B33" s="13">
-        <f>B32+B9+B10+B11</f>
-        <v/>
-      </c>
-      <c r="C33" s="13">
-        <f>C32+C9+C10+C11</f>
-        <v/>
-      </c>
-      <c r="D33" s="13">
-        <f>D32+D9+D10+D11</f>
-        <v/>
-      </c>
-      <c r="E33" s="13">
-        <f>E32+E9+E10+E11</f>
-        <v/>
-      </c>
-      <c r="F33" s="13">
-        <f>F32+F9+F10+F11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>Present value of free cash flow on Frame B</t>
-        </is>
-      </c>
-      <c r="B34" s="13">
-        <f>B33*B14</f>
-        <v/>
-      </c>
-      <c r="C34" s="13">
-        <f>C33*C14</f>
-        <v/>
-      </c>
-      <c r="D34" s="13">
-        <f>D33*D14</f>
-        <v/>
-      </c>
-      <c r="E34" s="13">
-        <f>E33*E14</f>
-        <v/>
-      </c>
-      <c r="F34" s="13">
-        <f>F33*F14</f>
-        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
+          <t>EBIT on Frame B = Frame A EBIT plus the difference in the provision charge</t>
+        </is>
+      </c>
+      <c r="B35" s="13">
+        <f>B6+('Income Statement'!E12-'Income Statement'!E11)</f>
+        <v/>
+      </c>
+      <c r="C35" s="13">
+        <f>C6+('Income Statement'!F12-'Income Statement'!F11)</f>
+        <v/>
+      </c>
+      <c r="D35" s="13">
+        <f>D6+('Income Statement'!G12-'Income Statement'!G11)</f>
+        <v/>
+      </c>
+      <c r="E35" s="13">
+        <f>E6+('Income Statement'!H12-'Income Statement'!H11)</f>
+        <v/>
+      </c>
+      <c r="F35" s="13">
+        <f>F6+('Income Statement'!I12-'Income Statement'!I11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>NOPAT on Frame B</t>
+        </is>
+      </c>
+      <c r="B36" s="13">
+        <f>B35*(1-B7)</f>
+        <v/>
+      </c>
+      <c r="C36" s="13">
+        <f>C35*(1-C7)</f>
+        <v/>
+      </c>
+      <c r="D36" s="13">
+        <f>D35*(1-D7)</f>
+        <v/>
+      </c>
+      <c r="E36" s="13">
+        <f>E35*(1-E7)</f>
+        <v/>
+      </c>
+      <c r="F36" s="13">
+        <f>F35*(1-F7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Free cash flow to the firm on Frame B</t>
+        </is>
+      </c>
+      <c r="B37" s="13">
+        <f>B36+B9+B10+B11</f>
+        <v/>
+      </c>
+      <c r="C37" s="13">
+        <f>C36+C9+C10+C11</f>
+        <v/>
+      </c>
+      <c r="D37" s="13">
+        <f>D36+D9+D10+D11</f>
+        <v/>
+      </c>
+      <c r="E37" s="13">
+        <f>E36+E9+E10+E11</f>
+        <v/>
+      </c>
+      <c r="F37" s="13">
+        <f>F36+F9+F10+F11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Present value of free cash flow on Frame B</t>
+        </is>
+      </c>
+      <c r="B38" s="13">
+        <f>B37*B14</f>
+        <v/>
+      </c>
+      <c r="C38" s="13">
+        <f>C37*C14</f>
+        <v/>
+      </c>
+      <c r="D38" s="13">
+        <f>D37*D14</f>
+        <v/>
+      </c>
+      <c r="E38" s="13">
+        <f>E37*E14</f>
+        <v/>
+      </c>
+      <c r="F38" s="13">
+        <f>F37*F14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Return on invested capital, FY2030E — Frame B's own</t>
+        </is>
+      </c>
+      <c r="B39" s="15">
+        <f>F36/B18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
           <t>Terminal value on Frame B</t>
         </is>
       </c>
-      <c r="B35" s="13">
-        <f>F32*(1+Assumptions!$C$57)*(1-B19)/(B21-B22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="B40" s="13">
+        <f>(F36*(1+Assumptions!$C$58)-B20*(1-Assumptions!$C$6))*(1-Assumptions!$C$58/B39)/(B24-B25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>Core enterprise value on Frame B</t>
         </is>
       </c>
-      <c r="B36" s="26">
-        <f>SUM(B34:F34)+B35*F14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="B41" s="27">
+        <f>SUM(B38:F38)+B40*F14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>VALUE PER SHARE ON FRAME B</t>
         </is>
       </c>
-      <c r="B37" s="9">
-        <f>(B36+Assumptions!$C$59*Assumptions!$C$60+Assumptions!$C$75+Assumptions!$C$76-Assumptions!$C$97-Assumptions!$C$74)/Assumptions!$C$4</f>
+      <c r="B42" s="9">
+        <f>(B41+Assumptions!$C$59*Assumptions!$C$60+Assumptions!$C$76+Assumptions!$C$77-Assumptions!$C$98-Assumptions!$C$75)/Assumptions!$C$4</f>
         <v/>
       </c>
     </row>
@@ -8530,32 +8862,32 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B2" s="40" t="n">
+      <c r="B2" s="42" t="n">
         <v>5231.665571</v>
       </c>
-      <c r="C2" s="40" t="n">
+      <c r="C2" s="42" t="n">
         <v>7590.545643</v>
       </c>
-      <c r="D2" s="40" t="n">
+      <c r="D2" s="42" t="n">
         <v>9441.379305</v>
       </c>
-      <c r="E2" s="41">
+      <c r="E2" s="43">
         <f>Segments!D11</f>
         <v/>
       </c>
-      <c r="F2" s="41">
+      <c r="F2" s="43">
         <f>Segments!E11</f>
         <v/>
       </c>
-      <c r="G2" s="41">
+      <c r="G2" s="43">
         <f>Segments!F11</f>
         <v/>
       </c>
-      <c r="H2" s="41">
+      <c r="H2" s="43">
         <f>Segments!G11</f>
         <v/>
       </c>
-      <c r="I2" s="41">
+      <c r="I2" s="43">
         <f>Segments!H11</f>
         <v/>
       </c>
@@ -8612,23 +8944,23 @@
         <v>5193.643343000001</v>
       </c>
       <c r="E4" s="13">
-        <f>Segments!D10*Assumptions!$C$80*Segments!D$27</f>
+        <f>Segments!D10*Assumptions!$C$81*Segments!D$27</f>
         <v/>
       </c>
       <c r="F4" s="13">
-        <f>Segments!E10*Assumptions!$C$80*Segments!E$27</f>
+        <f>Segments!E10*Assumptions!$C$81*Segments!E$27</f>
         <v/>
       </c>
       <c r="G4" s="13">
-        <f>Segments!F10*Assumptions!$C$80*Segments!F$27</f>
+        <f>Segments!F10*Assumptions!$C$81*Segments!F$27</f>
         <v/>
       </c>
       <c r="H4" s="13">
-        <f>Segments!G10*Assumptions!$C$80*Segments!G$27</f>
+        <f>Segments!G10*Assumptions!$C$81*Segments!G$27</f>
         <v/>
       </c>
       <c r="I4" s="13">
-        <f>Segments!H10*Assumptions!$C$80*Segments!H$27</f>
+        <f>Segments!H10*Assumptions!$C$81*Segments!H$27</f>
         <v/>
       </c>
     </row>
@@ -8648,23 +8980,23 @@
         <v>93.49755999999999</v>
       </c>
       <c r="E5" s="13">
-        <f>Segments!D$37*Assumptions!$C$79</f>
+        <f>Segments!D$37*Assumptions!$C$80</f>
         <v/>
       </c>
       <c r="F5" s="13">
-        <f>Segments!E$37*Assumptions!$C$79</f>
+        <f>Segments!E$37*Assumptions!$C$80</f>
         <v/>
       </c>
       <c r="G5" s="13">
-        <f>Segments!F$37*Assumptions!$C$79</f>
+        <f>Segments!F$37*Assumptions!$C$80</f>
         <v/>
       </c>
       <c r="H5" s="13">
-        <f>Segments!G$37*Assumptions!$C$79</f>
+        <f>Segments!G$37*Assumptions!$C$80</f>
         <v/>
       </c>
       <c r="I5" s="13">
-        <f>Segments!H$37*Assumptions!$C$79</f>
+        <f>Segments!H$37*Assumptions!$C$80</f>
         <v/>
       </c>
     </row>
@@ -8674,35 +9006,35 @@
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="31">
         <f>B2+B3</f>
         <v/>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <f>C2+C3</f>
         <v/>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <f>D2+D3</f>
         <v/>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <f>E2+E3</f>
         <v/>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <f>F2+F3</f>
         <v/>
       </c>
-      <c r="G6" s="30">
+      <c r="G6" s="31">
         <f>G2+G3</f>
         <v/>
       </c>
-      <c r="H6" s="30">
+      <c r="H6" s="31">
         <f>H2+H3</f>
         <v/>
       </c>
-      <c r="I6" s="30">
+      <c r="I6" s="31">
         <f>I2+I3</f>
         <v/>
       </c>
@@ -8932,28 +9264,28 @@
           <t>Board remuneration and attendance</t>
         </is>
       </c>
-      <c r="B13" s="23" t="n">
+      <c r="B13" s="24" t="n">
         <v>-2.02</v>
       </c>
-      <c r="C13" s="23" t="n">
+      <c r="C13" s="24" t="n">
         <v>-1.58</v>
       </c>
-      <c r="D13" s="23" t="n">
+      <c r="D13" s="24" t="n">
         <v>-1.828</v>
       </c>
-      <c r="E13" s="23" t="n">
+      <c r="E13" s="24" t="n">
         <v>-2</v>
       </c>
-      <c r="F13" s="23" t="n">
+      <c r="F13" s="24" t="n">
         <v>-2</v>
       </c>
-      <c r="G13" s="23" t="n">
+      <c r="G13" s="24" t="n">
         <v>-2</v>
       </c>
-      <c r="H13" s="23" t="n">
+      <c r="H13" s="24" t="n">
         <v>-2</v>
       </c>
-      <c r="I13" s="23" t="n">
+      <c r="I13" s="24" t="n">
         <v>-2</v>
       </c>
     </row>
@@ -8963,33 +9295,33 @@
           <t>Depreciation charged to selling and administrative expense</t>
         </is>
       </c>
-      <c r="B14" s="23" t="n">
+      <c r="B14" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="23" t="n">
+      <c r="C14" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="23" t="n">
+      <c r="D14" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="32">
-        <f>-Segments!D37*(1-Assumptions!$C$79)</f>
-        <v/>
-      </c>
-      <c r="F14" s="32">
-        <f>-Segments!E37*(1-Assumptions!$C$79)</f>
-        <v/>
-      </c>
-      <c r="G14" s="32">
-        <f>-Segments!F37*(1-Assumptions!$C$79)</f>
-        <v/>
-      </c>
-      <c r="H14" s="32">
-        <f>-Segments!G37*(1-Assumptions!$C$79)</f>
-        <v/>
-      </c>
-      <c r="I14" s="32">
-        <f>-Segments!H37*(1-Assumptions!$C$79)</f>
+      <c r="E14" s="33">
+        <f>-Segments!D37*(1-Assumptions!$C$80)</f>
+        <v/>
+      </c>
+      <c r="F14" s="33">
+        <f>-Segments!E37*(1-Assumptions!$C$80)</f>
+        <v/>
+      </c>
+      <c r="G14" s="33">
+        <f>-Segments!F37*(1-Assumptions!$C$80)</f>
+        <v/>
+      </c>
+      <c r="H14" s="33">
+        <f>-Segments!G37*(1-Assumptions!$C$80)</f>
+        <v/>
+      </c>
+      <c r="I14" s="33">
+        <f>-Segments!H37*(1-Assumptions!$C$80)</f>
         <v/>
       </c>
     </row>
@@ -8999,35 +9331,35 @@
           <t>Operating profit (EBIT)</t>
         </is>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="31">
         <f>B6+B8+B9+B10+B11+B13+B14</f>
         <v/>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="31">
         <f>C6+C8+C9+C10+C11+C13+C14</f>
         <v/>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="31">
         <f>D6+D8+D9+D10+D11+D13+D14</f>
         <v/>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="31">
         <f>E6+E8+E9+E10+E11+E13+E14</f>
         <v/>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="31">
         <f>F6+F8+F9+F10+F11+F13+F14</f>
         <v/>
       </c>
-      <c r="G15" s="30">
+      <c r="G15" s="31">
         <f>G6+G8+G9+G10+G11+G13+G14</f>
         <v/>
       </c>
-      <c r="H15" s="30">
+      <c r="H15" s="31">
         <f>H6+H8+H9+H10+H11+H13+H14</f>
         <v/>
       </c>
-      <c r="I15" s="30">
+      <c r="I15" s="31">
         <f>I6+I8+I9+I10+I11+I13+I14</f>
         <v/>
       </c>
@@ -9074,35 +9406,35 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B17" s="26">
+      <c r="B17" s="27">
         <f>B15+B16</f>
         <v/>
       </c>
-      <c r="C17" s="26">
+      <c r="C17" s="27">
         <f>C15+C16</f>
         <v/>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="27">
         <f>D15+D16</f>
         <v/>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="27">
         <f>E15+E16</f>
         <v/>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="27">
         <f>F15+F16</f>
         <v/>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="27">
         <f>G15+G16</f>
         <v/>
       </c>
-      <c r="H17" s="26">
+      <c r="H17" s="27">
         <f>H15+H16</f>
         <v/>
       </c>
-      <c r="I17" s="26">
+      <c r="I17" s="27">
         <f>I15+I16</f>
         <v/>
       </c>
@@ -9185,28 +9517,28 @@
           <t>Dividend distribution tax</t>
         </is>
       </c>
-      <c r="B20" s="23" t="n">
+      <c r="B20" s="24" t="n">
         <v>-4.123733</v>
       </c>
-      <c r="C20" s="23" t="n">
+      <c r="C20" s="24" t="n">
         <v>-4.468933</v>
       </c>
-      <c r="D20" s="23" t="n">
+      <c r="D20" s="24" t="n">
         <v>-16.58542</v>
       </c>
-      <c r="E20" s="23" t="n">
+      <c r="E20" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="F20" s="23" t="n">
+      <c r="F20" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="23" t="n">
+      <c r="G20" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="23" t="n">
+      <c r="H20" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="23" t="n">
+      <c r="I20" s="24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9247,35 +9579,35 @@
           <t>Profit before tax</t>
         </is>
       </c>
-      <c r="B22" s="30">
+      <c r="B22" s="31">
         <f>B15+B18+B19+B21+B20</f>
         <v/>
       </c>
-      <c r="C22" s="30">
+      <c r="C22" s="31">
         <f>C15+C18+C19+C21+C20</f>
         <v/>
       </c>
-      <c r="D22" s="30">
+      <c r="D22" s="31">
         <f>D15+D18+D19+D21+D20</f>
         <v/>
       </c>
-      <c r="E22" s="30">
+      <c r="E22" s="31">
         <f>E15+E18+E19+E21+E20</f>
         <v/>
       </c>
-      <c r="F22" s="30">
+      <c r="F22" s="31">
         <f>F15+F18+F19+F21+F20</f>
         <v/>
       </c>
-      <c r="G22" s="30">
+      <c r="G22" s="31">
         <f>G15+G18+G19+G21+G20</f>
         <v/>
       </c>
-      <c r="H22" s="30">
+      <c r="H22" s="31">
         <f>H15+H18+H19+H21+H20</f>
         <v/>
       </c>
-      <c r="I22" s="30">
+      <c r="I22" s="31">
         <f>I15+I18+I19+I21+I20</f>
         <v/>
       </c>
@@ -9322,35 +9654,35 @@
           <t>Profit for the year</t>
         </is>
       </c>
-      <c r="B24" s="30">
+      <c r="B24" s="31">
         <f>B22+B23</f>
         <v/>
       </c>
-      <c r="C24" s="30">
+      <c r="C24" s="31">
         <f>C22+C23</f>
         <v/>
       </c>
-      <c r="D24" s="30">
+      <c r="D24" s="31">
         <f>D22+D23</f>
         <v/>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="31">
         <f>E22+E23</f>
         <v/>
       </c>
-      <c r="F24" s="30">
+      <c r="F24" s="31">
         <f>F22+F23</f>
         <v/>
       </c>
-      <c r="G24" s="30">
+      <c r="G24" s="31">
         <f>G22+G23</f>
         <v/>
       </c>
-      <c r="H24" s="30">
+      <c r="H24" s="31">
         <f>H22+H23</f>
         <v/>
       </c>
-      <c r="I24" s="30">
+      <c r="I24" s="31">
         <f>I22+I23</f>
         <v/>
       </c>
@@ -9361,28 +9693,28 @@
           <t>Less non-controlling interests</t>
         </is>
       </c>
-      <c r="B25" s="23" t="n">
+      <c r="B25" s="24" t="n">
         <v>-0.9886149999999816</v>
       </c>
-      <c r="C25" s="23" t="n">
+      <c r="C25" s="24" t="n">
         <v>-1.206525000000056</v>
       </c>
-      <c r="D25" s="23" t="n">
+      <c r="D25" s="24" t="n">
         <v>-16.23531500000013</v>
       </c>
-      <c r="E25" s="23" t="n">
+      <c r="E25" s="24" t="n">
         <v>-18</v>
       </c>
-      <c r="F25" s="23" t="n">
+      <c r="F25" s="24" t="n">
         <v>-18</v>
       </c>
-      <c r="G25" s="23" t="n">
+      <c r="G25" s="24" t="n">
         <v>-18</v>
       </c>
-      <c r="H25" s="23" t="n">
+      <c r="H25" s="24" t="n">
         <v>-18</v>
       </c>
-      <c r="I25" s="23" t="n">
+      <c r="I25" s="24" t="n">
         <v>-18</v>
       </c>
     </row>
@@ -9392,35 +9724,35 @@
           <t>Profit attributable to the holding company</t>
         </is>
       </c>
-      <c r="B26" s="30">
+      <c r="B26" s="31">
         <f>B24+B25</f>
         <v/>
       </c>
-      <c r="C26" s="30">
+      <c r="C26" s="31">
         <f>C24+C25</f>
         <v/>
       </c>
-      <c r="D26" s="30">
+      <c r="D26" s="31">
         <f>D24+D25</f>
         <v/>
       </c>
-      <c r="E26" s="30">
+      <c r="E26" s="31">
         <f>E24+E25</f>
         <v/>
       </c>
-      <c r="F26" s="30">
+      <c r="F26" s="31">
         <f>F24+F25</f>
         <v/>
       </c>
-      <c r="G26" s="30">
+      <c r="G26" s="31">
         <f>G24+G25</f>
         <v/>
       </c>
-      <c r="H26" s="30">
+      <c r="H26" s="31">
         <f>H24+H25</f>
         <v/>
       </c>
-      <c r="I26" s="30">
+      <c r="I26" s="31">
         <f>I24+I25</f>
         <v/>
       </c>

--- a/engine/phar_study/EIPICO_Valuation_Model_09082026.xlsx
+++ b/engine/phar_study/EIPICO_Valuation_Model_09082026.xlsx
@@ -31,17 +31,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
-    <numFmt numFmtId="164" formatCode="#,##0.000000"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="0.0&quot;x&quot;"/>
-    <numFmt numFmtId="168" formatCode="0.00&quot;x&quot;"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0"/>
-    <numFmt numFmtId="170" formatCode="0.0000"/>
-    <numFmt numFmtId="171" formatCode="+0.0000;-0.0000"/>
-    <numFmt numFmtId="172" formatCode="+0&quot;bp&quot;;-0&quot;bp&quot;"/>
-    <numFmt numFmtId="173" formatCode="+0.0%;-0.0%"/>
+  <numFmts count="11">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="168" formatCode="0.0&quot;x&quot;"/>
+    <numFmt numFmtId="169" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="170" formatCode="#,##0.0"/>
+    <numFmt numFmtId="171" formatCode="0.0000"/>
+    <numFmt numFmtId="172" formatCode="+0.0000;-0.0000"/>
+    <numFmt numFmtId="173" formatCode="+0&quot;bp&quot;;-0&quot;bp&quot;"/>
+    <numFmt numFmtId="174" formatCode="+0.0%;-0.0%"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -173,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -188,7 +189,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -196,54 +197,55 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="171" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="172" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="173" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -814,34 +816,34 @@
           <t>Property, plant and equipment, net</t>
         </is>
       </c>
-      <c r="B2" s="20" t="n">
+      <c r="B2" s="19" t="n">
         <v>963.645369</v>
       </c>
-      <c r="C2" s="20" t="n">
+      <c r="C2" s="19" t="n">
         <v>1045.230507</v>
       </c>
       <c r="D2" s="13">
-        <f>Assumptions!$C$63</f>
+        <f>Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="E2" s="13">
-        <f>Segments!D35</f>
+        <f>Segments!D39</f>
         <v/>
       </c>
       <c r="F2" s="13">
-        <f>Segments!E35</f>
+        <f>Segments!E39</f>
         <v/>
       </c>
       <c r="G2" s="13">
-        <f>Segments!F35</f>
+        <f>Segments!F39</f>
         <v/>
       </c>
       <c r="H2" s="13">
-        <f>Segments!G35</f>
+        <f>Segments!G39</f>
         <v/>
       </c>
       <c r="I2" s="13">
-        <f>Segments!H35</f>
+        <f>Segments!H39</f>
         <v/>
       </c>
     </row>
@@ -851,34 +853,34 @@
           <t>Projects under construction</t>
         </is>
       </c>
-      <c r="B3" s="20" t="n">
+      <c r="B3" s="19" t="n">
         <v>3058.211677</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="C3" s="19" t="n">
         <v>5693.566382</v>
       </c>
       <c r="D3" s="13">
-        <f>Assumptions!$C$64</f>
+        <f>Assumptions!$C$68</f>
         <v/>
       </c>
       <c r="E3" s="13">
-        <f>Segments!D40</f>
+        <f>Segments!D44</f>
         <v/>
       </c>
       <c r="F3" s="13">
-        <f>Segments!E40</f>
+        <f>Segments!E44</f>
         <v/>
       </c>
       <c r="G3" s="13">
-        <f>Segments!F40</f>
+        <f>Segments!F44</f>
         <v/>
       </c>
       <c r="H3" s="13">
-        <f>Segments!G40</f>
+        <f>Segments!G44</f>
         <v/>
       </c>
       <c r="I3" s="13">
-        <f>Segments!H40</f>
+        <f>Segments!H44</f>
         <v/>
       </c>
     </row>
@@ -888,13 +890,13 @@
           <t>Associates, intangibles, right-of-use, deferred tax and assets held for sale</t>
         </is>
       </c>
-      <c r="B4" s="20" t="n">
+      <c r="B4" s="19" t="n">
         <v>483.145342</v>
       </c>
-      <c r="C4" s="20" t="n">
+      <c r="C4" s="19" t="n">
         <v>519.214192</v>
       </c>
-      <c r="D4" s="20" t="n">
+      <c r="D4" s="19" t="n">
         <v>1299.598913</v>
       </c>
       <c r="E4" s="13">
@@ -924,34 +926,34 @@
           <t>Inventories, net</t>
         </is>
       </c>
-      <c r="B5" s="20" t="n">
+      <c r="B5" s="19" t="n">
         <v>2242.39573</v>
       </c>
-      <c r="C5" s="20" t="n">
+      <c r="C5" s="19" t="n">
         <v>3584.699946</v>
       </c>
       <c r="D5" s="13">
-        <f>Assumptions!$C$65</f>
+        <f>Assumptions!$C$69</f>
         <v/>
       </c>
       <c r="E5" s="13">
-        <f>('Income Statement'!E3*-1)*Assumptions!C$35/365</f>
+        <f>('Income Statement'!E3*-1)*Assumptions!C$39/365</f>
         <v/>
       </c>
       <c r="F5" s="13">
-        <f>('Income Statement'!F3*-1)*Assumptions!D$35/365</f>
+        <f>('Income Statement'!F3*-1)*Assumptions!D$39/365</f>
         <v/>
       </c>
       <c r="G5" s="13">
-        <f>('Income Statement'!G3*-1)*Assumptions!E$35/365</f>
+        <f>('Income Statement'!G3*-1)*Assumptions!E$39/365</f>
         <v/>
       </c>
       <c r="H5" s="13">
-        <f>('Income Statement'!H3*-1)*Assumptions!F$35/365</f>
+        <f>('Income Statement'!H3*-1)*Assumptions!F$39/365</f>
         <v/>
       </c>
       <c r="I5" s="13">
-        <f>('Income Statement'!I3*-1)*Assumptions!G$35/365</f>
+        <f>('Income Statement'!I3*-1)*Assumptions!G$39/365</f>
         <v/>
       </c>
     </row>
@@ -961,34 +963,34 @@
           <t>Trade and notes receivable, net</t>
         </is>
       </c>
-      <c r="B6" s="20" t="n">
+      <c r="B6" s="19" t="n">
         <v>2357.855472</v>
       </c>
-      <c r="C6" s="20" t="n">
+      <c r="C6" s="19" t="n">
         <v>3049.275231</v>
       </c>
       <c r="D6" s="13">
-        <f>Assumptions!$C$66</f>
+        <f>Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="E6" s="13">
-        <f>'Income Statement'!E2*Assumptions!C$36/365</f>
+        <f>'Income Statement'!E2*Assumptions!C$40/365</f>
         <v/>
       </c>
       <c r="F6" s="13">
-        <f>'Income Statement'!F2*Assumptions!D$36/365</f>
+        <f>'Income Statement'!F2*Assumptions!D$40/365</f>
         <v/>
       </c>
       <c r="G6" s="13">
-        <f>'Income Statement'!G2*Assumptions!E$36/365</f>
+        <f>'Income Statement'!G2*Assumptions!E$40/365</f>
         <v/>
       </c>
       <c r="H6" s="13">
-        <f>'Income Statement'!H2*Assumptions!F$36/365</f>
+        <f>'Income Statement'!H2*Assumptions!F$40/365</f>
         <v/>
       </c>
       <c r="I6" s="13">
-        <f>'Income Statement'!I2*Assumptions!G$36/365</f>
+        <f>'Income Statement'!I2*Assumptions!G$40/365</f>
         <v/>
       </c>
     </row>
@@ -998,34 +1000,34 @@
           <t>Other debtors and debit balances</t>
         </is>
       </c>
-      <c r="B7" s="20" t="n">
+      <c r="B7" s="19" t="n">
         <v>197.731029</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="19" t="n">
         <v>185.584353</v>
       </c>
       <c r="D7" s="13">
-        <f>Assumptions!$C$67</f>
+        <f>Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="E7" s="13">
-        <f>'Income Statement'!E2/9441.379305*Assumptions!$C$67</f>
+        <f>'Income Statement'!E2/9441.379305*Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="F7" s="13">
-        <f>'Income Statement'!F2/9441.379305*Assumptions!$C$67</f>
+        <f>'Income Statement'!F2/9441.379305*Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="G7" s="13">
-        <f>'Income Statement'!G2/9441.379305*Assumptions!$C$67</f>
+        <f>'Income Statement'!G2/9441.379305*Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="H7" s="13">
-        <f>'Income Statement'!H2/9441.379305*Assumptions!$C$67</f>
+        <f>'Income Statement'!H2/9441.379305*Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="I7" s="13">
-        <f>'Income Statement'!I2/9441.379305*Assumptions!$C$67</f>
+        <f>'Income Statement'!I2/9441.379305*Assumptions!$C$71</f>
         <v/>
       </c>
     </row>
@@ -1035,34 +1037,34 @@
           <t>Cash and bank balances</t>
         </is>
       </c>
-      <c r="B8" s="20" t="n">
+      <c r="B8" s="19" t="n">
         <v>675.798245</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="19" t="n">
         <v>1295.38686</v>
       </c>
       <c r="D8" s="13">
-        <f>Assumptions!$C$70</f>
+        <f>Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="E8" s="13">
-        <f>Assumptions!$C$70</f>
+        <f>Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="F8" s="13">
-        <f>Assumptions!$C$70</f>
+        <f>Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="G8" s="13">
-        <f>Assumptions!$C$70</f>
+        <f>Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="H8" s="13">
-        <f>Assumptions!$C$70</f>
+        <f>Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="I8" s="13">
-        <f>Assumptions!$C$70</f>
+        <f>Assumptions!$C$74</f>
         <v/>
       </c>
     </row>
@@ -1072,35 +1074,35 @@
           <t>TOTAL ASSETS</t>
         </is>
       </c>
-      <c r="B9" s="31">
+      <c r="B9" s="32">
         <f>SUM(B2:B8)</f>
         <v/>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="32">
         <f>SUM(C2:C8)</f>
         <v/>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="32">
         <f>SUM(D2:D8)</f>
         <v/>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="32">
         <f>SUM(E2:E8)</f>
         <v/>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="32">
         <f>SUM(F2:F8)</f>
         <v/>
       </c>
-      <c r="G9" s="31">
+      <c r="G9" s="32">
         <f>SUM(G2:G8)</f>
         <v/>
       </c>
-      <c r="H9" s="31">
+      <c r="H9" s="32">
         <f>SUM(H2:H8)</f>
         <v/>
       </c>
-      <c r="I9" s="31">
+      <c r="I9" s="32">
         <f>SUM(I2:I8)</f>
         <v/>
       </c>
@@ -1111,34 +1113,34 @@
           <t>Trade and notes payable</t>
         </is>
       </c>
-      <c r="B10" s="20" t="n">
+      <c r="B10" s="19" t="n">
         <v>176.353891</v>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="19" t="n">
         <v>410.391619</v>
       </c>
       <c r="D10" s="13">
-        <f>Assumptions!$C$68</f>
+        <f>Assumptions!$C$72</f>
         <v/>
       </c>
       <c r="E10" s="13">
-        <f>('Income Statement'!E3*-1)*Assumptions!C$37/365</f>
+        <f>('Income Statement'!E3*-1)*Assumptions!C$41/365</f>
         <v/>
       </c>
       <c r="F10" s="13">
-        <f>('Income Statement'!F3*-1)*Assumptions!D$37/365</f>
+        <f>('Income Statement'!F3*-1)*Assumptions!D$41/365</f>
         <v/>
       </c>
       <c r="G10" s="13">
-        <f>('Income Statement'!G3*-1)*Assumptions!E$37/365</f>
+        <f>('Income Statement'!G3*-1)*Assumptions!E$41/365</f>
         <v/>
       </c>
       <c r="H10" s="13">
-        <f>('Income Statement'!H3*-1)*Assumptions!F$37/365</f>
+        <f>('Income Statement'!H3*-1)*Assumptions!F$41/365</f>
         <v/>
       </c>
       <c r="I10" s="13">
-        <f>('Income Statement'!I3*-1)*Assumptions!G$37/365</f>
+        <f>('Income Statement'!I3*-1)*Assumptions!G$41/365</f>
         <v/>
       </c>
     </row>
@@ -1148,34 +1150,34 @@
           <t>Other creditors and credit balances</t>
         </is>
       </c>
-      <c r="B11" s="20" t="n">
+      <c r="B11" s="19" t="n">
         <v>230.675384</v>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="19" t="n">
         <v>367.42118</v>
       </c>
       <c r="D11" s="13">
-        <f>Assumptions!$C$69</f>
+        <f>Assumptions!$C$73</f>
         <v/>
       </c>
       <c r="E11" s="13">
-        <f>'Income Statement'!E2/9441.379305*Assumptions!$C$69</f>
+        <f>'Income Statement'!E2/9441.379305*Assumptions!$C$73</f>
         <v/>
       </c>
       <c r="F11" s="13">
-        <f>'Income Statement'!F2/9441.379305*Assumptions!$C$69</f>
+        <f>'Income Statement'!F2/9441.379305*Assumptions!$C$73</f>
         <v/>
       </c>
       <c r="G11" s="13">
-        <f>'Income Statement'!G2/9441.379305*Assumptions!$C$69</f>
+        <f>'Income Statement'!G2/9441.379305*Assumptions!$C$73</f>
         <v/>
       </c>
       <c r="H11" s="13">
-        <f>'Income Statement'!H2/9441.379305*Assumptions!$C$69</f>
+        <f>'Income Statement'!H2/9441.379305*Assumptions!$C$73</f>
         <v/>
       </c>
       <c r="I11" s="13">
-        <f>'Income Statement'!I2/9441.379305*Assumptions!$C$69</f>
+        <f>'Income Statement'!I2/9441.379305*Assumptions!$C$73</f>
         <v/>
       </c>
     </row>
@@ -1185,13 +1187,13 @@
           <t>Provisions, income tax payable and deferred tax</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n">
+      <c r="B12" s="19" t="n">
         <v>435.0793929999999</v>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="19" t="n">
         <v>737.373915</v>
       </c>
-      <c r="D12" s="20" t="n">
+      <c r="D12" s="19" t="n">
         <v>1117.660628</v>
       </c>
       <c r="E12" s="13">
@@ -1221,14 +1223,14 @@
           <t>Gross borrowings including leases</t>
         </is>
       </c>
-      <c r="B13" s="20" t="n">
+      <c r="B13" s="19" t="n">
         <v>4879.973467999999</v>
       </c>
-      <c r="C13" s="20" t="n">
+      <c r="C13" s="19" t="n">
         <v>9200.032863</v>
       </c>
       <c r="D13" s="13">
-        <f>Assumptions!$C$71</f>
+        <f>Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="E13" s="13">
@@ -1258,34 +1260,34 @@
           <t>Equity attributable to the holding company</t>
         </is>
       </c>
-      <c r="B14" s="20" t="n">
+      <c r="B14" s="19" t="n">
         <v>4257.40809</v>
       </c>
-      <c r="C14" s="20" t="n">
+      <c r="C14" s="19" t="n">
         <v>4653.769234</v>
       </c>
       <c r="D14" s="13">
-        <f>Assumptions!$C$73</f>
-        <v/>
-      </c>
-      <c r="E14" s="27">
-        <f>Assumptions!$C$73+'Income Statement'!E26*(1-Assumptions!$C$38)</f>
-        <v/>
-      </c>
-      <c r="F14" s="27">
-        <f>E14+'Income Statement'!F26*(1-Assumptions!$C$38)</f>
-        <v/>
-      </c>
-      <c r="G14" s="27">
-        <f>F14+'Income Statement'!G26*(1-Assumptions!$C$38)</f>
-        <v/>
-      </c>
-      <c r="H14" s="27">
-        <f>G14+'Income Statement'!H26*(1-Assumptions!$C$38)</f>
-        <v/>
-      </c>
-      <c r="I14" s="27">
-        <f>H14+'Income Statement'!I26*(1-Assumptions!$C$38)</f>
+        <f>Assumptions!$C$77</f>
+        <v/>
+      </c>
+      <c r="E14" s="28">
+        <f>Assumptions!$C$77+'Income Statement'!E26*(1-Assumptions!$C$42)</f>
+        <v/>
+      </c>
+      <c r="F14" s="28">
+        <f>E14+'Income Statement'!F26*(1-Assumptions!$C$42)</f>
+        <v/>
+      </c>
+      <c r="G14" s="28">
+        <f>F14+'Income Statement'!G26*(1-Assumptions!$C$42)</f>
+        <v/>
+      </c>
+      <c r="H14" s="28">
+        <f>G14+'Income Statement'!H26*(1-Assumptions!$C$42)</f>
+        <v/>
+      </c>
+      <c r="I14" s="28">
+        <f>H14+'Income Statement'!I26*(1-Assumptions!$C$42)</f>
         <v/>
       </c>
     </row>
@@ -1295,34 +1297,34 @@
           <t>Non-controlling interests</t>
         </is>
       </c>
-      <c r="B15" s="20" t="n">
+      <c r="B15" s="19" t="n">
         <v>3.394945</v>
       </c>
-      <c r="C15" s="20" t="n">
+      <c r="C15" s="19" t="n">
         <v>3.816172</v>
       </c>
       <c r="D15" s="13">
-        <f>Assumptions!$C$74</f>
+        <f>Assumptions!$C$78</f>
         <v/>
       </c>
       <c r="E15" s="13">
-        <f>Assumptions!$C$75</f>
+        <f>Assumptions!$C$79</f>
         <v/>
       </c>
       <c r="F15" s="13">
-        <f>Assumptions!$C$75</f>
+        <f>Assumptions!$C$79</f>
         <v/>
       </c>
       <c r="G15" s="13">
-        <f>Assumptions!$C$75</f>
+        <f>Assumptions!$C$79</f>
         <v/>
       </c>
       <c r="H15" s="13">
-        <f>Assumptions!$C$75</f>
+        <f>Assumptions!$C$79</f>
         <v/>
       </c>
       <c r="I15" s="13">
-        <f>Assumptions!$C$75</f>
+        <f>Assumptions!$C$79</f>
         <v/>
       </c>
     </row>
@@ -1332,35 +1334,35 @@
           <t>TOTAL LIABILITIES AND EQUITY</t>
         </is>
       </c>
-      <c r="B16" s="31">
+      <c r="B16" s="32">
         <f>B10+B11+B12+B13+B14+B15</f>
         <v/>
       </c>
-      <c r="C16" s="31">
+      <c r="C16" s="32">
         <f>C10+C11+C12+C13+C14+C15</f>
         <v/>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="32">
         <f>D10+D11+D12+D13+D14+D15</f>
         <v/>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="32">
         <f>E10+E11+E12+E13+E14+E15</f>
         <v/>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="32">
         <f>F10+F11+F12+F13+F14+F15</f>
         <v/>
       </c>
-      <c r="G16" s="31">
+      <c r="G16" s="32">
         <f>G10+G11+G12+G13+G14+G15</f>
         <v/>
       </c>
-      <c r="H16" s="31">
+      <c r="H16" s="32">
         <f>H10+H11+H12+H13+H14+H15</f>
         <v/>
       </c>
-      <c r="I16" s="31">
+      <c r="I16" s="32">
         <f>I10+I11+I12+I13+I14+I15</f>
         <v/>
       </c>
@@ -1371,35 +1373,35 @@
           <t>BALANCE CHECK — total assets less total liabilities and equity</t>
         </is>
       </c>
-      <c r="B17" s="27">
+      <c r="B17" s="28">
         <f>B9-B16</f>
         <v/>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="28">
         <f>C9-C16</f>
         <v/>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="28">
         <f>D9-D16</f>
         <v/>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="28">
         <f>E9-E16</f>
         <v/>
       </c>
-      <c r="F17" s="27">
+      <c r="F17" s="28">
         <f>F9-F16</f>
         <v/>
       </c>
-      <c r="G17" s="27">
+      <c r="G17" s="28">
         <f>G9-G16</f>
         <v/>
       </c>
-      <c r="H17" s="27">
+      <c r="H17" s="28">
         <f>H9-H16</f>
         <v/>
       </c>
-      <c r="I17" s="27">
+      <c r="I17" s="28">
         <f>I9-I16</f>
         <v/>
       </c>
@@ -1415,35 +1417,35 @@
           <t>NET DEBT</t>
         </is>
       </c>
-      <c r="B18" s="31">
+      <c r="B18" s="32">
         <f>B13-B8</f>
         <v/>
       </c>
-      <c r="C18" s="31">
+      <c r="C18" s="32">
         <f>C13-C8</f>
         <v/>
       </c>
-      <c r="D18" s="31">
+      <c r="D18" s="32">
         <f>D13-D8</f>
         <v/>
       </c>
-      <c r="E18" s="31">
+      <c r="E18" s="32">
         <f>E13-E8</f>
         <v/>
       </c>
-      <c r="F18" s="31">
+      <c r="F18" s="32">
         <f>F13-F8</f>
         <v/>
       </c>
-      <c r="G18" s="31">
+      <c r="G18" s="32">
         <f>G13-G8</f>
         <v/>
       </c>
-      <c r="H18" s="31">
+      <c r="H18" s="32">
         <f>H13-H8</f>
         <v/>
       </c>
-      <c r="I18" s="31">
+      <c r="I18" s="32">
         <f>I13-I8</f>
         <v/>
       </c>
@@ -1454,35 +1456,35 @@
           <t>Net working capital</t>
         </is>
       </c>
-      <c r="B19" s="27">
+      <c r="B19" s="28">
         <f>B5+B6+B7-B10-B11</f>
         <v/>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="28">
         <f>C5+C6+C7-C10-C11</f>
         <v/>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="28">
         <f>D5+D6+D7-D10-D11</f>
         <v/>
       </c>
-      <c r="E19" s="27">
+      <c r="E19" s="28">
         <f>E5+E6+E7-E10-E11</f>
         <v/>
       </c>
-      <c r="F19" s="27">
+      <c r="F19" s="28">
         <f>F5+F6+F7-F10-F11</f>
         <v/>
       </c>
-      <c r="G19" s="27">
+      <c r="G19" s="28">
         <f>G5+G6+G7-G10-G11</f>
         <v/>
       </c>
-      <c r="H19" s="27">
+      <c r="H19" s="28">
         <f>H5+H6+H7-H10-H11</f>
         <v/>
       </c>
-      <c r="I19" s="27">
+      <c r="I19" s="28">
         <f>I5+I6+I7-I10-I11</f>
         <v/>
       </c>
@@ -1506,23 +1508,23 @@
         <v/>
       </c>
       <c r="E20" s="12">
-        <f>E14/Assumptions!$C$4</f>
+        <f>E14/Assumptions!$C$8</f>
         <v/>
       </c>
       <c r="F20" s="12">
-        <f>F14/Assumptions!$C$4</f>
+        <f>F14/Assumptions!$C$8</f>
         <v/>
       </c>
       <c r="G20" s="12">
-        <f>G14/Assumptions!$C$4</f>
+        <f>G14/Assumptions!$C$8</f>
         <v/>
       </c>
       <c r="H20" s="12">
-        <f>H14/Assumptions!$C$4</f>
+        <f>H14/Assumptions!$C$8</f>
         <v/>
       </c>
       <c r="I20" s="12">
-        <f>I14/Assumptions!$C$4</f>
+        <f>I14/Assumptions!$C$8</f>
         <v/>
       </c>
     </row>
@@ -1644,35 +1646,35 @@
         </is>
       </c>
       <c r="B3" s="13">
-        <f>-B2*Assumptions!$C$6</f>
+        <f>-B2*Assumptions!$C$10</f>
         <v/>
       </c>
       <c r="C3" s="13">
-        <f>-C2*Assumptions!$C$6</f>
+        <f>-C2*Assumptions!$C$10</f>
         <v/>
       </c>
       <c r="D3" s="13">
-        <f>-D2*Assumptions!$C$6</f>
+        <f>-D2*Assumptions!$C$10</f>
         <v/>
       </c>
       <c r="E3" s="13">
-        <f>-E2*Assumptions!$C$6</f>
+        <f>-E2*Assumptions!$C$10</f>
         <v/>
       </c>
       <c r="F3" s="13">
-        <f>-F2*Assumptions!$C$6</f>
+        <f>-F2*Assumptions!$C$10</f>
         <v/>
       </c>
       <c r="G3" s="13">
-        <f>-G2*Assumptions!$C$6</f>
+        <f>-G2*Assumptions!$C$10</f>
         <v/>
       </c>
       <c r="H3" s="13">
-        <f>-H2*Assumptions!$C$6</f>
+        <f>-H2*Assumptions!$C$10</f>
         <v/>
       </c>
       <c r="I3" s="13">
-        <f>-I2*Assumptions!$C$6</f>
+        <f>-I2*Assumptions!$C$10</f>
         <v/>
       </c>
     </row>
@@ -1682,35 +1684,35 @@
           <t>Operating profit after tax (NOPAT)</t>
         </is>
       </c>
-      <c r="B4" s="31">
+      <c r="B4" s="32">
         <f>B2+B3</f>
         <v/>
       </c>
-      <c r="C4" s="31">
+      <c r="C4" s="32">
         <f>C2+C3</f>
         <v/>
       </c>
-      <c r="D4" s="31">
+      <c r="D4" s="32">
         <f>D2+D3</f>
         <v/>
       </c>
-      <c r="E4" s="31">
+      <c r="E4" s="32">
         <f>E2+E3</f>
         <v/>
       </c>
-      <c r="F4" s="31">
+      <c r="F4" s="32">
         <f>F2+F3</f>
         <v/>
       </c>
-      <c r="G4" s="31">
+      <c r="G4" s="32">
         <f>G2+G3</f>
         <v/>
       </c>
-      <c r="H4" s="31">
+      <c r="H4" s="32">
         <f>H2+H3</f>
         <v/>
       </c>
-      <c r="I4" s="31">
+      <c r="I4" s="32">
         <f>I2+I3</f>
         <v/>
       </c>
@@ -1760,33 +1762,33 @@
           <t>Less capital expenditure</t>
         </is>
       </c>
-      <c r="B6" s="20" t="n">
+      <c r="B6" s="19" t="n">
         <v>-2290.194556</v>
       </c>
-      <c r="C6" s="20" t="n">
+      <c r="C6" s="19" t="n">
         <v>-2846.239746</v>
       </c>
-      <c r="D6" s="20" t="n">
+      <c r="D6" s="19" t="n">
         <v>-1354.665231</v>
       </c>
       <c r="E6" s="13">
-        <f>-Segments!D36</f>
+        <f>-Segments!D40</f>
         <v/>
       </c>
       <c r="F6" s="13">
-        <f>-Segments!E36</f>
+        <f>-Segments!E40</f>
         <v/>
       </c>
       <c r="G6" s="13">
-        <f>-Segments!F36</f>
+        <f>-Segments!F40</f>
         <v/>
       </c>
       <c r="H6" s="13">
-        <f>-Segments!G36</f>
+        <f>-Segments!G40</f>
         <v/>
       </c>
       <c r="I6" s="13">
-        <f>-Segments!H36</f>
+        <f>-Segments!H40</f>
         <v/>
       </c>
     </row>
@@ -1796,13 +1798,13 @@
           <t>Less the increase in working capital</t>
         </is>
       </c>
-      <c r="B7" s="20" t="n">
+      <c r="B7" s="19" t="n">
         <v>-835.715133</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="19" t="n">
         <v>-2426.81348</v>
       </c>
-      <c r="D7" s="20" t="n">
+      <c r="D7" s="19" t="n">
         <v>-428.2194999999999</v>
       </c>
       <c r="E7" s="13">
@@ -1832,23 +1834,23 @@
           <t>FREE CASH FLOW TO THE FIRM</t>
         </is>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="32">
         <f>E4+E5+E6+E7</f>
         <v/>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="32">
         <f>F4+F5+F6+F7</f>
         <v/>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="32">
         <f>G4+G5+G6+G7</f>
         <v/>
       </c>
-      <c r="H8" s="31">
+      <c r="H8" s="32">
         <f>H4+H5+H6+H7</f>
         <v/>
       </c>
-      <c r="I8" s="31">
+      <c r="I8" s="32">
         <f>I4+I5+I6+I7</f>
         <v/>
       </c>
@@ -1866,13 +1868,13 @@
           <t>Net cash from operating activities</t>
         </is>
       </c>
-      <c r="B11" s="20" t="n">
+      <c r="B11" s="19" t="n">
         <v>92.483752</v>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="19" t="n">
         <v>-1274.488135</v>
       </c>
-      <c r="D11" s="20" t="n">
+      <c r="D11" s="19" t="n">
         <v>1093.516116</v>
       </c>
     </row>
@@ -1882,13 +1884,13 @@
           <t>Net cash used in investing activities</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n">
+      <c r="B12" s="19" t="n">
         <v>-2329.639953</v>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="19" t="n">
         <v>-2679.028944</v>
       </c>
-      <c r="D12" s="20" t="n">
+      <c r="D12" s="19" t="n">
         <v>-1201.726573</v>
       </c>
     </row>
@@ -1898,13 +1900,13 @@
           <t>Net cash from financing activities</t>
         </is>
       </c>
-      <c r="B13" s="20" t="n">
+      <c r="B13" s="19" t="n">
         <v>2209.824906</v>
       </c>
-      <c r="C13" s="20" t="n">
+      <c r="C13" s="19" t="n">
         <v>3853.615013</v>
       </c>
-      <c r="D13" s="20" t="n">
+      <c r="D13" s="19" t="n">
         <v>262.411958</v>
       </c>
     </row>
@@ -2418,9 +2420,9 @@
           <t>THESE CELLS ARE A WHOLE-MODEL RE-RUN — 50,000 simulated price paths each. They do NOT redraw when a driver on the Assumptions sheet changes.</t>
         </is>
       </c>
-      <c r="B2" s="44" t="n"/>
-      <c r="C2" s="44" t="n"/>
-      <c r="D2" s="45" t="n"/>
+      <c r="B2" s="46" t="n"/>
+      <c r="C2" s="46" t="n"/>
+      <c r="D2" s="47" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -2446,12 +2448,12 @@
           <t>Check date</t>
         </is>
       </c>
-      <c r="B4" s="46" t="inlineStr">
+      <c r="B4" s="48" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="C4" s="46" t="inlineStr">
+      <c r="C4" s="48" t="inlineStr">
         <is>
           <t>2026-11-08</t>
         </is>
@@ -2613,22 +2615,22 @@
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="38" t="inlineStr">
+      <c r="A18" s="39" t="inlineStr">
         <is>
           <t>Window set</t>
         </is>
       </c>
-      <c r="B18" s="39" t="inlineStr">
+      <c r="B18" s="40" t="inlineStr">
         <is>
           <t>Windows</t>
         </is>
       </c>
-      <c r="C18" s="39" t="inlineStr">
+      <c r="C18" s="40" t="inlineStr">
         <is>
           <t>Skill against the benchmark</t>
         </is>
       </c>
-      <c r="D18" s="39" t="inlineStr">
+      <c r="D18" s="40" t="inlineStr">
         <is>
           <t>Probability-transform uniformity</t>
         </is>
@@ -2640,10 +2642,10 @@
           <t>Full cleaned history (2012-05-23 to 2026-03-24)</t>
         </is>
       </c>
-      <c r="B19" s="20" t="n">
+      <c r="B19" s="19" t="n">
         <v>56</v>
       </c>
-      <c r="C19" s="47" t="n">
+      <c r="C19" s="49" t="n">
         <v>-0.01771436655010961</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -2658,10 +2660,10 @@
           <t>Last five years of origins (2021-09-19 to 2026-03-24)</t>
         </is>
       </c>
-      <c r="B20" s="20" t="n">
+      <c r="B20" s="19" t="n">
         <v>19</v>
       </c>
-      <c r="C20" s="47" t="n">
+      <c r="C20" s="49" t="n">
         <v>0.002147922911274858</v>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -2676,10 +2678,10 @@
           <t>Post-break window set (2022-06-20 to 2026-03-24)</t>
         </is>
       </c>
-      <c r="B21" s="20" t="n">
+      <c r="B21" s="19" t="n">
         <v>16</v>
       </c>
-      <c r="C21" s="47" t="n">
+      <c r="C21" s="49" t="n">
         <v>-0.01085817085606799</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -2731,11 +2733,11 @@
           <t>THESE GRIDS ARE WHOLE-MODEL RE-RUNS. Each cell re-runs the entire model at a different input. They do NOT redraw when a driver on the Assumptions sheet changes.</t>
         </is>
       </c>
-      <c r="B2" s="44" t="n"/>
-      <c r="C2" s="44" t="n"/>
-      <c r="D2" s="44" t="n"/>
-      <c r="E2" s="44" t="n"/>
-      <c r="F2" s="45" t="n"/>
+      <c r="B2" s="46" t="n"/>
+      <c r="C2" s="46" t="n"/>
+      <c r="D2" s="46" t="n"/>
+      <c r="E2" s="46" t="n"/>
+      <c r="F2" s="47" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -2743,19 +2745,19 @@
           <t>Shift in the cost of equity (basis points)</t>
         </is>
       </c>
-      <c r="B4" s="48" t="n">
+      <c r="B4" s="50" t="n">
         <v>-200</v>
       </c>
-      <c r="C4" s="48" t="n">
+      <c r="C4" s="50" t="n">
         <v>-100</v>
       </c>
-      <c r="D4" s="48" t="n">
+      <c r="D4" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="48" t="n">
+      <c r="E4" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="F4" s="48" t="n">
+      <c r="F4" s="50" t="n">
         <v>200</v>
       </c>
     </row>
@@ -2766,19 +2768,19 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>78.31243222697051</v>
+        <v>77.29589290051553</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>67.66927140208438</v>
+        <v>66.74301308250047</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>58.89505972579192</v>
+        <v>58.04356316438152</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>51.53879625116383</v>
+        <v>50.75027515072584</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>45.28376888412894</v>
+        <v>44.54905891123189</v>
       </c>
     </row>
     <row r="7">
@@ -2810,19 +2812,19 @@
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>54.91909695306187</v>
+        <v>54.19932760616772</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>56.7496401224546</v>
+        <v>55.97105249260597</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>58.89505972579192</v>
+        <v>58.04356316438152</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>61.48029305778895</v>
+        <v>60.53620600076448</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>64.70644908483796</v>
+        <v>63.64109038776664</v>
       </c>
     </row>
     <row r="10">
@@ -2831,19 +2833,19 @@
           <t>Beta</t>
         </is>
       </c>
-      <c r="B10" s="49" t="n">
+      <c r="B10" s="51" t="n">
         <v>0.45</v>
       </c>
-      <c r="C10" s="49" t="n">
+      <c r="C10" s="51" t="n">
         <v>0.55</v>
       </c>
-      <c r="D10" s="49" t="n">
+      <c r="D10" s="51" t="n">
         <v>0.629</v>
       </c>
-      <c r="E10" s="49" t="n">
+      <c r="E10" s="51" t="n">
         <v>0.75</v>
       </c>
-      <c r="F10" s="49" t="n">
+      <c r="F10" s="51" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -2854,19 +2856,19 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>70.79426033337107</v>
+        <v>69.84088801144183</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>63.80394773089595</v>
+        <v>62.91034125538415</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>58.89505972579192</v>
+        <v>58.04356316438152</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>52.24641505345505</v>
+        <v>51.4521683412368</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>45.19664792628173</v>
+        <v>44.46342676007655</v>
       </c>
     </row>
     <row r="13">
@@ -2875,19 +2877,19 @@
           <t>Provision charge as a share of revenue</t>
         </is>
       </c>
-      <c r="B13" s="19" t="n">
+      <c r="B13" s="21" t="n">
         <v>0.025</v>
       </c>
-      <c r="C13" s="19" t="n">
+      <c r="C13" s="21" t="n">
         <v>0.035</v>
       </c>
-      <c r="D13" s="19" t="n">
+      <c r="D13" s="21" t="n">
         <v>0.0525</v>
       </c>
-      <c r="E13" s="19" t="n">
+      <c r="E13" s="21" t="n">
         <v>0.065</v>
       </c>
-      <c r="F13" s="19" t="n">
+      <c r="F13" s="21" t="n">
         <v>0.08</v>
       </c>
     </row>
@@ -2898,19 +2900,19 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>75.44108799206906</v>
+        <v>74.64279440856899</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>69.42057921447211</v>
+        <v>68.60284325666746</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>58.89505972579192</v>
+        <v>58.04356316438152</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>51.38643553893024</v>
+        <v>50.51108196144131</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>42.38906083457892</v>
+        <v>41.48545024215522</v>
       </c>
     </row>
     <row r="16">
@@ -2919,19 +2921,19 @@
           <t>Exchange-rate path, scaled</t>
         </is>
       </c>
-      <c r="B16" s="23" t="n">
+      <c r="B16" s="24" t="n">
         <v>0.9</v>
       </c>
-      <c r="C16" s="23" t="n">
+      <c r="C16" s="24" t="n">
         <v>0.95</v>
       </c>
-      <c r="D16" s="23" t="n">
+      <c r="D16" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="23" t="n">
+      <c r="E16" s="24" t="n">
         <v>1.05</v>
       </c>
-      <c r="F16" s="23" t="n">
+      <c r="F16" s="24" t="n">
         <v>1.1</v>
       </c>
     </row>
@@ -2942,19 +2944,19 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>69.63797562069173</v>
+        <v>68.94051402078955</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>64.26420965733911</v>
+        <v>63.48963636605803</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>58.89505972579192</v>
+        <v>58.04356316438152</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>53.53091600504677</v>
+        <v>52.60271140089909</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>48.17221392319875</v>
+        <v>47.16754775265088</v>
       </c>
     </row>
     <row r="19">
@@ -2963,19 +2965,19 @@
           <t>Shift in domestic volume growth</t>
         </is>
       </c>
-      <c r="B19" s="50" t="n">
+      <c r="B19" s="52" t="n">
         <v>-0.04</v>
       </c>
-      <c r="C19" s="50" t="n">
+      <c r="C19" s="52" t="n">
         <v>-0.02</v>
       </c>
-      <c r="D19" s="50" t="n">
+      <c r="D19" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="E19" s="50" t="n">
+      <c r="E19" s="52" t="n">
         <v>0.02</v>
       </c>
-      <c r="F19" s="50" t="n">
+      <c r="F19" s="52" t="n">
         <v>0.04</v>
       </c>
     </row>
@@ -2986,19 +2988,19 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>56.64350538610749</v>
+        <v>56.50638310547686</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>57.7177306936283</v>
+        <v>57.23625199428405</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>58.89505972579192</v>
+        <v>58.04356316438152</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>60.18174317376977</v>
+        <v>58.93310192687731</v>
       </c>
       <c r="F20" s="16" t="n">
-        <v>61.58427576254385</v>
+        <v>59.90984223453741</v>
       </c>
     </row>
     <row r="22">
@@ -3007,19 +3009,19 @@
           <t>Depreciation rate</t>
         </is>
       </c>
-      <c r="B22" s="19" t="n">
+      <c r="B22" s="21" t="n">
         <v>0.045</v>
       </c>
-      <c r="C22" s="19" t="n">
+      <c r="C22" s="21" t="n">
         <v>0.055</v>
       </c>
-      <c r="D22" s="19" t="n">
+      <c r="D22" s="21" t="n">
         <v>0.062</v>
       </c>
-      <c r="E22" s="19" t="n">
+      <c r="E22" s="21" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="F22" s="19" t="n">
+      <c r="F22" s="21" t="n">
         <v>0.08</v>
       </c>
     </row>
@@ -3030,19 +3032,19 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>61.06862787034969</v>
+        <v>60.21623559180343</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>59.75834853177898</v>
+        <v>58.90647160099854</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>58.89505972579192</v>
+        <v>58.04356316438152</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>57.96049310852472</v>
+        <v>57.10944765905171</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>56.86697608562417</v>
+        <v>56.01651400062947</v>
       </c>
     </row>
     <row r="25">
@@ -3074,19 +3076,19 @@
         </is>
       </c>
       <c r="B26" s="16" t="n">
-        <v>70.22746456102367</v>
+        <v>69.40058103952305</v>
       </c>
       <c r="C26" s="16" t="n">
-        <v>73.83242923979699</v>
+        <v>72.92267594034055</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>78.31243222697051</v>
+        <v>77.29589290051553</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>84.10042351180795</v>
+        <v>82.94134866765025</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>91.97138153249236</v>
+        <v>90.61284023318153</v>
       </c>
     </row>
     <row r="27">
@@ -3096,19 +3098,19 @@
         </is>
       </c>
       <c r="B27" s="16" t="n">
-        <v>61.97903730199961</v>
+        <v>61.20967522657672</v>
       </c>
       <c r="C27" s="16" t="n">
-        <v>64.55784487355071</v>
+        <v>63.71911223049474</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>67.66927140208438</v>
+        <v>66.74301308250047</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>71.54787934213813</v>
+        <v>70.5079448271878</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>76.58966229449742</v>
+        <v>75.39640303480886</v>
       </c>
     </row>
     <row r="28">
@@ -3118,19 +3120,19 @@
         </is>
       </c>
       <c r="B28" s="16" t="n">
-        <v>54.91909695306187</v>
+        <v>54.19932760616772</v>
       </c>
       <c r="C28" s="16" t="n">
-        <v>56.7496401224546</v>
+        <v>55.97105249260597</v>
       </c>
       <c r="D28" s="16" t="n">
-        <v>58.89505972579192</v>
+        <v>58.04356316438152</v>
       </c>
       <c r="E28" s="16" t="n">
-        <v>61.48029305778895</v>
+        <v>60.53620600076448</v>
       </c>
       <c r="F28" s="16" t="n">
-        <v>64.70644908483796</v>
+        <v>63.64109038776664</v>
       </c>
     </row>
     <row r="29">
@@ -3140,19 +3142,19 @@
         </is>
       </c>
       <c r="B29" s="16" t="n">
-        <v>48.81103139736771</v>
+        <v>48.13449081209406</v>
       </c>
       <c r="C29" s="16" t="n">
-        <v>50.08798575638645</v>
+        <v>49.36102634801223</v>
       </c>
       <c r="D29" s="16" t="n">
-        <v>51.53879625116383</v>
+        <v>50.75027515072584</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>53.22623000061837</v>
+        <v>52.36098143954015</v>
       </c>
       <c r="F29" s="16" t="n">
-        <v>55.24740198900633</v>
+        <v>54.28403585960935</v>
       </c>
     </row>
     <row r="30">
@@ -3162,19 +3164,19 @@
         </is>
       </c>
       <c r="B30" s="16" t="n">
-        <v>43.47701854793333</v>
+        <v>42.83851934755974</v>
       </c>
       <c r="C30" s="16" t="n">
-        <v>44.33968449095657</v>
+        <v>43.65755701531543</v>
       </c>
       <c r="D30" s="16" t="n">
-        <v>45.28376888412894</v>
+        <v>44.54905891123189</v>
       </c>
       <c r="E30" s="16" t="n">
-        <v>46.33623644020645</v>
+        <v>45.53702422829129</v>
       </c>
       <c r="F30" s="16" t="n">
-        <v>47.53743663148617</v>
+        <v>46.65736489261532</v>
       </c>
     </row>
     <row r="32">
@@ -3190,8 +3192,8 @@
           <t>Additional FY2030E revenue required to reach the market price (EGP mn)</t>
         </is>
       </c>
-      <c r="B33" s="20" t="n">
-        <v>6848.505570056388</v>
+      <c r="B33" s="19" t="n">
+        <v>6930.883371175429</v>
       </c>
     </row>
     <row r="34">
@@ -3201,7 +3203,7 @@
         </is>
       </c>
       <c r="B34" s="17" t="n">
-        <v>0.2823794219690113</v>
+        <v>0.2840609235494332</v>
       </c>
     </row>
     <row r="35">
@@ -3210,8 +3212,8 @@
           <t xml:space="preserve">   in US dollars a year (mn)</t>
         </is>
       </c>
-      <c r="B35" s="20" t="n">
-        <v>118.6916043337329</v>
+      <c r="B35" s="19" t="n">
+        <v>120.119295860926</v>
       </c>
     </row>
     <row r="36">
@@ -3220,8 +3222,8 @@
           <t xml:space="preserve">   as a multiple of the plant's stated USD 100 million cost</t>
         </is>
       </c>
-      <c r="B36" s="23" t="n">
-        <v>1.186916043337329</v>
+      <c r="B36" s="24" t="n">
+        <v>1.20119295860926</v>
       </c>
     </row>
   </sheetData>
@@ -3389,23 +3391,23 @@
         <v>3.5</v>
       </c>
       <c r="E4" s="5">
-        <f>'Income Statement'!E27*Assumptions!$C$38</f>
+        <f>'Income Statement'!E27*Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="F4" s="5">
-        <f>'Income Statement'!F27*Assumptions!$C$38</f>
+        <f>'Income Statement'!F27*Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="G4" s="5">
-        <f>'Income Statement'!G27*Assumptions!$C$38</f>
+        <f>'Income Statement'!G27*Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="H4" s="5">
-        <f>'Income Statement'!H27*Assumptions!$C$38</f>
+        <f>'Income Statement'!H27*Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="I4" s="5">
-        <f>'Income Statement'!I27*Assumptions!$C$38</f>
+        <f>'Income Statement'!I27*Assumptions!$C$42</f>
         <v/>
       </c>
     </row>
@@ -3442,24 +3444,24 @@
           <t>Net debt / EBITDA</t>
         </is>
       </c>
-      <c r="E6" s="36">
-        <f>('Balance Sheet'!E13-Assumptions!$C$70)/'Income Statement'!E17</f>
-        <v/>
-      </c>
-      <c r="F6" s="36">
-        <f>('Balance Sheet'!F13-Assumptions!$C$70)/'Income Statement'!F17</f>
-        <v/>
-      </c>
-      <c r="G6" s="36">
-        <f>('Balance Sheet'!G13-Assumptions!$C$70)/'Income Statement'!G17</f>
-        <v/>
-      </c>
-      <c r="H6" s="36">
-        <f>('Balance Sheet'!H13-Assumptions!$C$70)/'Income Statement'!H17</f>
-        <v/>
-      </c>
-      <c r="I6" s="36">
-        <f>('Balance Sheet'!I13-Assumptions!$C$70)/'Income Statement'!I17</f>
+      <c r="E6" s="41">
+        <f>('Balance Sheet'!E13-Assumptions!$C$74)/'Income Statement'!E17</f>
+        <v/>
+      </c>
+      <c r="F6" s="41">
+        <f>('Balance Sheet'!F13-Assumptions!$C$74)/'Income Statement'!F17</f>
+        <v/>
+      </c>
+      <c r="G6" s="41">
+        <f>('Balance Sheet'!G13-Assumptions!$C$74)/'Income Statement'!G17</f>
+        <v/>
+      </c>
+      <c r="H6" s="41">
+        <f>('Balance Sheet'!H13-Assumptions!$C$74)/'Income Statement'!H17</f>
+        <v/>
+      </c>
+      <c r="I6" s="41">
+        <f>('Balance Sheet'!I13-Assumptions!$C$74)/'Income Statement'!I17</f>
         <v/>
       </c>
     </row>
@@ -3470,23 +3472,23 @@
         </is>
       </c>
       <c r="E7" s="13">
-        <f>Assumptions!C$35</f>
+        <f>Assumptions!C$39</f>
         <v/>
       </c>
       <c r="F7" s="13">
-        <f>Assumptions!D$35</f>
+        <f>Assumptions!D$39</f>
         <v/>
       </c>
       <c r="G7" s="13">
-        <f>Assumptions!E$35</f>
+        <f>Assumptions!E$39</f>
         <v/>
       </c>
       <c r="H7" s="13">
-        <f>Assumptions!F$35</f>
+        <f>Assumptions!F$39</f>
         <v/>
       </c>
       <c r="I7" s="13">
-        <f>Assumptions!G$35</f>
+        <f>Assumptions!G$39</f>
         <v/>
       </c>
     </row>
@@ -3497,23 +3499,23 @@
         </is>
       </c>
       <c r="E8" s="13">
-        <f>Assumptions!C$36</f>
+        <f>Assumptions!C$40</f>
         <v/>
       </c>
       <c r="F8" s="13">
-        <f>Assumptions!D$36</f>
+        <f>Assumptions!D$40</f>
         <v/>
       </c>
       <c r="G8" s="13">
-        <f>Assumptions!E$36</f>
+        <f>Assumptions!E$40</f>
         <v/>
       </c>
       <c r="H8" s="13">
-        <f>Assumptions!F$36</f>
+        <f>Assumptions!F$40</f>
         <v/>
       </c>
       <c r="I8" s="13">
-        <f>Assumptions!G$36</f>
+        <f>Assumptions!G$40</f>
         <v/>
       </c>
     </row>
@@ -3524,23 +3526,23 @@
         </is>
       </c>
       <c r="E9" s="13">
-        <f>Assumptions!C$37</f>
+        <f>Assumptions!C$41</f>
         <v/>
       </c>
       <c r="F9" s="13">
-        <f>Assumptions!D$37</f>
+        <f>Assumptions!D$41</f>
         <v/>
       </c>
       <c r="G9" s="13">
-        <f>Assumptions!E$37</f>
+        <f>Assumptions!E$41</f>
         <v/>
       </c>
       <c r="H9" s="13">
-        <f>Assumptions!F$37</f>
+        <f>Assumptions!F$41</f>
         <v/>
       </c>
       <c r="I9" s="13">
-        <f>Assumptions!G$37</f>
+        <f>Assumptions!G$41</f>
         <v/>
       </c>
     </row>
@@ -3550,23 +3552,23 @@
           <t>Cash conversion cycle (days)</t>
         </is>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="28">
         <f>E7+E8-E9</f>
         <v/>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="28">
         <f>F7+F8-F9</f>
         <v/>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="28">
         <f>G7+G8-G9</f>
         <v/>
       </c>
-      <c r="H10" s="27">
+      <c r="H10" s="28">
         <f>H7+H8-H9</f>
         <v/>
       </c>
-      <c r="I10" s="27">
+      <c r="I10" s="28">
         <f>I7+I8-I9</f>
         <v/>
       </c>
@@ -3578,23 +3580,23 @@
         </is>
       </c>
       <c r="E11" s="6">
-        <f>('Income Statement'!E15*(1-Assumptions!$C$6))/('Balance Sheet'!E2+'Balance Sheet'!E3+'Balance Sheet'!E19+Assumptions!$C$78)</f>
+        <f>('Income Statement'!E15*(1-Assumptions!$C$10))/('Balance Sheet'!E2+'Balance Sheet'!E3+'Balance Sheet'!E19+Assumptions!$C$82)</f>
         <v/>
       </c>
       <c r="F11" s="6">
-        <f>('Income Statement'!F15*(1-Assumptions!$C$6))/('Balance Sheet'!F2+'Balance Sheet'!F3+'Balance Sheet'!F19+Assumptions!$C$78)</f>
+        <f>('Income Statement'!F15*(1-Assumptions!$C$10))/('Balance Sheet'!F2+'Balance Sheet'!F3+'Balance Sheet'!F19+Assumptions!$C$82)</f>
         <v/>
       </c>
       <c r="G11" s="6">
-        <f>('Income Statement'!G15*(1-Assumptions!$C$6))/('Balance Sheet'!G2+'Balance Sheet'!G3+'Balance Sheet'!G19+Assumptions!$C$78)</f>
+        <f>('Income Statement'!G15*(1-Assumptions!$C$10))/('Balance Sheet'!G2+'Balance Sheet'!G3+'Balance Sheet'!G19+Assumptions!$C$82)</f>
         <v/>
       </c>
       <c r="H11" s="6">
-        <f>('Income Statement'!H15*(1-Assumptions!$C$6))/('Balance Sheet'!H2+'Balance Sheet'!H3+'Balance Sheet'!H19+Assumptions!$C$78)</f>
+        <f>('Income Statement'!H15*(1-Assumptions!$C$10))/('Balance Sheet'!H2+'Balance Sheet'!H3+'Balance Sheet'!H19+Assumptions!$C$82)</f>
         <v/>
       </c>
       <c r="I11" s="6">
-        <f>('Income Statement'!I15*(1-Assumptions!$C$6))/('Balance Sheet'!I2+'Balance Sheet'!I3+'Balance Sheet'!I19+Assumptions!$C$78)</f>
+        <f>('Income Statement'!I15*(1-Assumptions!$C$10))/('Balance Sheet'!I2+'Balance Sheet'!I3+'Balance Sheet'!I19+Assumptions!$C$82)</f>
         <v/>
       </c>
     </row>
@@ -3646,9 +3648,9 @@
           <t>Peer multiples are MARKET DATA and sit in the cross-check layer. No peer figure is used to build any historical number for the subject company.</t>
         </is>
       </c>
-      <c r="B2" s="44" t="n"/>
-      <c r="C2" s="44" t="n"/>
-      <c r="D2" s="45" t="n"/>
+      <c r="B2" s="46" t="n"/>
+      <c r="C2" s="46" t="n"/>
+      <c r="D2" s="47" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -3656,7 +3658,7 @@
           <t>Listed Saudi Arabian generics manufacturer</t>
         </is>
       </c>
-      <c r="B3" s="22" t="n">
+      <c r="B3" s="24" t="n">
         <v>26.7</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -3666,7 +3668,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Public-comparables service, 2025 basis — cross-check only</t>
+          <t>Public-comparables service, 2025 basis — cross-check only. This company is not named and its financial statements are not published here, so this multiple cannot be rebuilt from its filings</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3678,7 @@
           <t>Regional and international generic manufacturers, mid-cap</t>
         </is>
       </c>
-      <c r="B4" s="22" t="n">
+      <c r="B4" s="24" t="n">
         <v>16</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -3693,11 +3695,12 @@
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>PEER MEDIAN USED</t>
-        </is>
-      </c>
-      <c r="B5" s="22" t="n">
-        <v>21.35</v>
+          <t>STRUCK REFERENCE USED — the midpoint of the two above</t>
+        </is>
+      </c>
+      <c r="B5" s="42">
+        <f>AVERAGE(B3:B4)</f>
+        <v/>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -3706,7 +3709,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Struck between the two above; the lens runs a 13-26 times band</t>
+          <t>NOT a median of a disclosed peer set: two observations have a midpoint, and this cell computes it. The lens runs a 13-26 times band around it</t>
         </is>
       </c>
     </row>
@@ -3716,8 +3719,8 @@
           <t>The subject company today</t>
         </is>
       </c>
-      <c r="B6" s="51">
-        <f>Assumptions!$C$3/('Income Statement'!D26/Assumptions!$C$4)</f>
+      <c r="B6" s="43">
+        <f>Assumptions!$C$3/('Income Statement'!D26/Assumptions!$C$8)</f>
         <v/>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -3737,8 +3740,8 @@
           <t>The subject company's own four-year mean</t>
         </is>
       </c>
-      <c r="B7" s="40">
-        <f>'Relative &amp; Normalized'!D24</f>
+      <c r="B7" s="42">
+        <f>'Relative &amp; Normalized'!D21</f>
         <v/>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -3755,7 +3758,7 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Discount of the subject to the peer median</t>
+          <t>Discount of the subject to the struck reference</t>
         </is>
       </c>
       <c r="B8" s="10">
@@ -3803,8 +3806,9 @@
           <t>Return on average equity, FY2025</t>
         </is>
       </c>
-      <c r="B13" s="17" t="n">
-        <v>0.264599584335609</v>
+      <c r="B13" s="6">
+        <f>'Income Statement'!D26/(('Balance Sheet'!C14+'Balance Sheet'!D14)/2)</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -3814,7 +3818,7 @@
         </is>
       </c>
       <c r="B14" s="6">
-        <f>Segments!C16</f>
+        <f>Segments!C20</f>
         <v/>
       </c>
     </row>
@@ -3824,7 +3828,7 @@
           <t>Cash conversion cycle, FY2025 (days)</t>
         </is>
       </c>
-      <c r="B15" s="20" t="n">
+      <c r="B15" s="19" t="n">
         <v>343.0145217463265</v>
       </c>
     </row>
@@ -3939,7 +3943,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Justified 1.71 times book</t>
+          <t>Justified 1.70 times book</t>
         </is>
       </c>
     </row>
@@ -4063,7 +4067,7 @@
         </is>
       </c>
       <c r="B13" s="13">
-        <f>Assumptions!$C$97</f>
+        <f>Assumptions!$C$102</f>
         <v/>
       </c>
     </row>
@@ -4074,7 +4078,7 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>Assumptions!$C$98</f>
+        <f>Assumptions!$C$103</f>
         <v/>
       </c>
     </row>
@@ -4085,7 +4089,7 @@
         </is>
       </c>
       <c r="B15" s="13">
-        <f>Assumptions!$C$97+Assumptions!$C$98+Assumptions!$C$75</f>
+        <f>Assumptions!$C$102+Assumptions!$C$103+Assumptions!$C$79</f>
         <v/>
       </c>
     </row>
@@ -4129,7 +4133,7 @@
         </is>
       </c>
       <c r="B19" s="14">
-        <f>Assumptions!$C$3/('Income Statement'!D26/Assumptions!$C$4)</f>
+        <f>Assumptions!$C$3/('Income Statement'!D26/Assumptions!$C$8)</f>
         <v/>
       </c>
     </row>
@@ -4140,7 +4144,7 @@
         </is>
       </c>
       <c r="B20" s="14">
-        <f>(Assumptions!$C$97+Assumptions!$C$98+Assumptions!$C$75)/'Income Statement'!D17</f>
+        <f>(Assumptions!$C$102+Assumptions!$C$103+Assumptions!$C$79)/'Income Statement'!D17</f>
         <v/>
       </c>
     </row>
@@ -4151,7 +4155,7 @@
         </is>
       </c>
       <c r="B21" s="15">
-        <f>Assumptions!$C$92</f>
+        <f>Assumptions!$C$97</f>
         <v/>
       </c>
     </row>
@@ -4162,7 +4166,7 @@
         </is>
       </c>
       <c r="B22" s="15">
-        <f>Assumptions!$C$101</f>
+        <f>Assumptions!$C$106</f>
         <v/>
       </c>
     </row>
@@ -4173,7 +4177,7 @@
         </is>
       </c>
       <c r="B23" s="15">
-        <f>Assumptions!$C$107</f>
+        <f>Assumptions!$C$112</f>
         <v/>
       </c>
     </row>
@@ -4258,7 +4262,7 @@
         </is>
       </c>
       <c r="B2" s="12">
-        <f>('SOTP Bridge'!B11)/Assumptions!$C$4</f>
+        <f>('SOTP Bridge'!B11)/Assumptions!$C$8</f>
         <v/>
       </c>
       <c r="C2" s="17" t="n">
@@ -4296,7 +4300,7 @@
         </is>
       </c>
       <c r="B4" s="12">
-        <f>(('Relative &amp; Normalized'!B6-Assumptions!$C$58)/(Assumptions!$C$104-Assumptions!$C$58))*'Balance Sheet'!D20</f>
+        <f>(('Relative &amp; Normalized'!B6-Assumptions!$C$62)/(Assumptions!$C$109-Assumptions!$C$62))*'Balance Sheet'!D20</f>
         <v/>
       </c>
       <c r="C4" s="17" t="n">
@@ -4315,7 +4319,7 @@
         </is>
       </c>
       <c r="B5" s="12">
-        <f>'Relative &amp; Normalized'!C16</f>
+        <f>'Relative &amp; Normalized'!C29</f>
         <v/>
       </c>
       <c r="C5" s="17" t="n">
@@ -4334,7 +4338,7 @@
         </is>
       </c>
       <c r="B6" s="12">
-        <f>'Relative &amp; Normalized'!B34</f>
+        <f>'Relative &amp; Normalized'!B37</f>
         <v/>
       </c>
       <c r="C6" s="17" t="n">
@@ -4452,7 +4456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -4526,288 +4530,288 @@
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Shares in issue (million)</t>
+          <t>Shares in issue at 31 December 2022 (million)</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Capital note (13): issued capital of EGP 1,687,557,500 at EGP 10 nominal a share</t>
+          <t>Board report, capital and shareholders table</t>
         </is>
       </c>
       <c r="C4" s="18" t="n">
-        <v>168.75575</v>
+        <v>99.1705</v>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Corporate income tax rate</t>
+          <t>Shares in issue, FY2023 and FY2024 (million)</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Egyptian statutory rate</t>
-        </is>
-      </c>
-      <c r="C5" s="19" t="n">
-        <v>0.225</v>
+          <t>Board report</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="n">
+        <v>148.75575</v>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Effective tax rate on forecast pre-tax profit</t>
+          <t>Weighted-average shares, FY2025 (million)</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Above statutory to allow for the solidarity contribution and disallowed items</t>
-        </is>
-      </c>
-      <c r="C6" s="19" t="n">
-        <v>0.235</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>VOLUME AND PRICE</t>
-        </is>
+          <t>Audited — the capital increase completed during the year</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="n">
+        <v>162.016024</v>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Attributable profit, FY2022 (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Board report, eleven-year profit table</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>587.040623</v>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Domestic pack volume growth</t>
+          <t>Shares in issue (million)</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Not capacity-constrained at 65% utilisation</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="D8" s="17" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E8" s="17" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="F8" s="17" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="G8" s="17" t="n">
-        <v>0.055</v>
+          <t>Capital note (13): issued capital of EGP 1,687,557,500 at EGP 10 nominal a share</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="n">
+        <v>168.75575</v>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Export pack volume growth</t>
+          <t>Corporate income tax rate</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Hard-currency export growth was 10% in FY2025</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D9" s="17" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E9" s="17" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="F9" s="17" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G9" s="17" t="n">
-        <v>0.07000000000000001</v>
+          <t>Egyptian statutory rate</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="n">
+        <v>0.225</v>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Domestic price per pack growth</t>
+          <t>Effective tax rate on forecast pre-tax profit</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Administered prices track inflation, no real gain</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D10" s="17" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E10" s="17" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="F10" s="17" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="G10" s="17" t="n">
-        <v>0.055</v>
-      </c>
-    </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Export price per pack growth (USD)</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Competitive generic export pricing</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D11" s="17" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E11" s="17" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F11" s="17" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G11" s="17" t="n">
-        <v>0.01</v>
+          <t>Above statutory to allow for the solidarity contribution and disallowed items</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="n">
+        <v>0.235</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>VOLUME AND PRICE</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Contract-manufacturing revenue growth</t>
+          <t>Domestic pack volume growth</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Small line, idle-capacity utilisation</t>
+          <t>Not capacity-constrained at 65% utilisation</t>
         </is>
       </c>
       <c r="C12" s="17" t="n">
-        <v>0.15</v>
+        <v>0.055</v>
       </c>
       <c r="D12" s="17" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>0.1</v>
+        <v>0.075</v>
       </c>
       <c r="F12" s="17" t="n">
-        <v>0.08</v>
+        <v>0.065</v>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Exchange rate (EGP per USD, period average)</t>
+          <t>Export pack volume growth</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Partial real-rate reversal as domestic inflation converges</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="D13" s="16" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>54.3</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <v>56</v>
-      </c>
-      <c r="G13" s="16" t="n">
-        <v>57.7</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>COST STACK — ONE ESCALATOR PER DRIVER CLASS</t>
-        </is>
+          <t>Hard-currency export growth was 10% in FY2025</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G13" s="17" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Domestic price per pack growth</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Administered prices track inflation, no real gain</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="G14" s="17" t="n">
+        <v>0.055</v>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Cost share: imported active ingredients</t>
+          <t>Export price per pack growth (USD)</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Cost of sales note (26)</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="n">
-        <v>0.5488</v>
+          <t>Competitive generic export pricing</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G15" s="17" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Cost share: packaging materials</t>
+          <t>Contract-manufacturing revenue growth</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Cost of sales note (26)</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="n">
-        <v>0.2456</v>
+          <t>Small line, idle-capacity utilisation</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D16" s="17" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G16" s="17" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Cost share: labour</t>
+          <t>Exchange rate (EGP per USD, period average)</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Cost of sales note (26), wages plus benefits plus social insurance</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="n">
-        <v>0.0977</v>
-      </c>
-    </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Cost share: energy and utilities</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Cost of sales note (26)</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="n">
-        <v>0.0342</v>
+          <t>Partial real-rate reversal as domestic inflation converges</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="D17" s="16" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="F17" s="16" t="n">
+        <v>56</v>
+      </c>
+      <c r="G17" s="16" t="n">
+        <v>57.7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>COST STACK — ONE ESCALATOR PER DRIVER CLASS</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Cost share: other consumables and services</t>
+          <t>Cost share: imported active ingredients</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -4815,1307 +4819,1302 @@
           <t>Cost of sales note (26)</t>
         </is>
       </c>
-      <c r="C19" s="19" t="n">
-        <v>0.0571</v>
+      <c r="C19" s="21" t="n">
+        <v>0.5488</v>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Cost share: depreciation</t>
+          <t>Cost share: packaging materials</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>disclosure — the audited split is shown for completeness, but depreciation is EXCLUDED from the escalated unit cost by design and enters exactly once, from the property roll-forward. This row drives nothing and is meant to drive nothing</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="n">
-        <v>0.0166</v>
+          <t>Cost of sales note (26)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="n">
+        <v>0.2456</v>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Escalator: hard-currency ingredient price</t>
+          <t>Cost share: labour</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Applied THROUGH the exchange-rate path, never a domestic index</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="n">
-        <v>0.02</v>
+          <t>Cost of sales note (26), wages plus benefits plus social insurance</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="n">
+        <v>0.0977</v>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Imported share of the packaging line</t>
+          <t>Cost share: energy and utilities</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>The balance is made in-house</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="n">
-        <v>0.55</v>
+          <t>Cost of sales note (26)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="n">
+        <v>0.0342</v>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Escalator: Egyptian wages</t>
+          <t>Cost share: other consumables and services</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Minimum-wage resets run above consumer prices</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="D23" s="17" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E23" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F23" s="17" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="G23" s="17" t="n">
-        <v>0.075</v>
+          <t>Cost of sales note (26)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="n">
+        <v>0.0571</v>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Escalator: regulated energy tariffs</t>
+          <t>Cost share: depreciation</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Subsidy reform, ABOVE consumer prices</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D24" s="17" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E24" s="17" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="F24" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G24" s="17" t="n">
-        <v>0.08</v>
+          <t>disclosure — the audited split is shown for completeness, but depreciation is EXCLUDED from the escalated unit cost by design and enters exactly once, from the property roll-forward. This row drives nothing and is meant to drive nothing</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="n">
+        <v>0.0166</v>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Escalator: domestic consumer prices</t>
+          <t>Escalator: hard-currency ingredient price</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Applied only to genuinely domestic lines</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="D25" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E25" s="17" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="F25" s="17" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G25" s="17" t="n">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>OPERATING EXPENSE, CAPITAL AND WORKING CAPITAL</t>
-        </is>
+          <t>Applied THROUGH the exchange-rate path, never a domestic index</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Imported share of the packaging line</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>The balance is made in-house</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="n">
+        <v>0.55</v>
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Selling and marketing / revenue</t>
+          <t>Escalator: Egyptian wages</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Disclosed 12.9% -&gt; 12.4% -&gt; 10.7%</t>
+          <t>Minimum-wage resets run above consumer prices</t>
         </is>
       </c>
       <c r="C27" s="17" t="n">
-        <v>0.104</v>
+        <v>0.14</v>
       </c>
       <c r="D27" s="17" t="n">
-        <v>0.102</v>
+        <v>0.12</v>
       </c>
       <c r="E27" s="17" t="n">
         <v>0.1</v>
       </c>
       <c r="F27" s="17" t="n">
-        <v>0.099</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.098</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Research and development / revenue</t>
+          <t>Escalator: regulated energy tariffs</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Rising with the biosimilar pipeline</t>
-        </is>
-      </c>
-      <c r="C28" s="19" t="n">
-        <v>0.008500000000000001</v>
-      </c>
-      <c r="D28" s="19" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="E28" s="19" t="n">
-        <v>0.0095</v>
-      </c>
-      <c r="F28" s="19" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G28" s="19" t="n">
-        <v>0.01</v>
+          <t>Subsidy reform, ABOVE consumer prices</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D28" s="17" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F28" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G28" s="17" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>General and administrative / revenue</t>
+          <t>Escalator: domestic consumer prices</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Held near the FY2025 level</t>
-        </is>
-      </c>
-      <c r="C29" s="19" t="n">
-        <v>0.0235</v>
-      </c>
-      <c r="D29" s="19" t="n">
-        <v>0.0235</v>
-      </c>
-      <c r="E29" s="19" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="F29" s="19" t="n">
-        <v>0.0228</v>
-      </c>
-      <c r="G29" s="19" t="n">
-        <v>0.0225</v>
-      </c>
-    </row>
-    <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>FRAME A — provision charge / revenue</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Permanent, at the three-year average</t>
-        </is>
-      </c>
-      <c r="C30" s="19" t="n">
-        <v>0.0525</v>
-      </c>
-      <c r="D30" s="19" t="n">
-        <v>0.0525</v>
-      </c>
-      <c r="E30" s="19" t="n">
-        <v>0.0525</v>
-      </c>
-      <c r="F30" s="19" t="n">
-        <v>0.0525</v>
-      </c>
-      <c r="G30" s="19" t="n">
-        <v>0.0525</v>
+          <t>Applied only to genuinely domestic lines</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D29" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="F29" s="17" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G29" s="17" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSE, CAPITAL AND WORKING CAPITAL</t>
+        </is>
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>FRAME B — provision charge / revenue</t>
+          <t>Selling and marketing / revenue</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Normalising as the book seasons</t>
-        </is>
-      </c>
-      <c r="C31" s="19" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="D31" s="19" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="E31" s="19" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="F31" s="19" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="G31" s="19" t="n">
-        <v>0.025</v>
+          <t>Disclosed 12.9% -&gt; 12.4% -&gt; 10.7%</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="D31" s="17" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F31" s="17" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="G31" s="17" t="n">
+        <v>0.098</v>
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Capital expenditure / revenue</t>
+          <t>Research and development / revenue</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Falls as the construction cycle completes</t>
-        </is>
-      </c>
-      <c r="C32" s="17" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="D32" s="17" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="E32" s="17" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="F32" s="17" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="G32" s="17" t="n">
-        <v>0.03</v>
+          <t>Rising with the biosimilar pipeline</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="D32" s="21" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="E32" s="21" t="n">
+        <v>0.0095</v>
+      </c>
+      <c r="F32" s="21" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G32" s="21" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="33" ht="26" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Transfers out of construction (EGP mn)</t>
+          <t>General and administrative / revenue</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>The plant was licensed in December 2025 and enters service</t>
-        </is>
-      </c>
-      <c r="C33" s="20" t="n">
-        <v>3400</v>
-      </c>
-      <c r="D33" s="20" t="n">
-        <v>1100</v>
-      </c>
-      <c r="E33" s="20" t="n">
-        <v>400</v>
-      </c>
-      <c r="F33" s="20" t="n">
-        <v>200</v>
-      </c>
-      <c r="G33" s="20" t="n">
-        <v>200</v>
+          <t>Held near the FY2025 level</t>
+        </is>
+      </c>
+      <c r="C33" s="21" t="n">
+        <v>0.0235</v>
+      </c>
+      <c r="D33" s="21" t="n">
+        <v>0.0235</v>
+      </c>
+      <c r="E33" s="21" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="F33" s="21" t="n">
+        <v>0.0228</v>
+      </c>
+      <c r="G33" s="21" t="n">
+        <v>0.0225</v>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Depreciation rate on the property base</t>
+          <t>FRAME A — provision charge / revenue</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>About a sixteen-year blended life</t>
-        </is>
-      </c>
-      <c r="C34" s="19" t="n">
-        <v>0.062</v>
+          <t>Permanent, at the three-year average</t>
+        </is>
+      </c>
+      <c r="C34" s="21" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="D34" s="21" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="E34" s="21" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="F34" s="21" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="G34" s="21" t="n">
+        <v>0.0525</v>
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Inventory days</t>
+          <t>FRAME B — provision charge / revenue</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>An eight-month strategic stockpile, stated policy</t>
-        </is>
-      </c>
-      <c r="C35" s="20" t="n">
-        <v>265</v>
-      </c>
-      <c r="D35" s="20" t="n">
-        <v>258</v>
-      </c>
-      <c r="E35" s="20" t="n">
-        <v>250</v>
-      </c>
-      <c r="F35" s="20" t="n">
-        <v>245</v>
-      </c>
-      <c r="G35" s="20" t="n">
-        <v>240</v>
+          <t>Normalising as the book seasons</t>
+        </is>
+      </c>
+      <c r="C35" s="21" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="D35" s="21" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="E35" s="21" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="F35" s="21" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="G35" s="21" t="n">
+        <v>0.025</v>
       </c>
     </row>
     <row r="36" ht="26" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Receivable days</t>
+          <t>Capital expenditure / revenue</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>Distributor-concentrated book plus export terms</t>
-        </is>
-      </c>
-      <c r="C36" s="20" t="n">
-        <v>126</v>
-      </c>
-      <c r="D36" s="20" t="n">
-        <v>122</v>
-      </c>
-      <c r="E36" s="20" t="n">
-        <v>118</v>
-      </c>
-      <c r="F36" s="20" t="n">
-        <v>115</v>
-      </c>
-      <c r="G36" s="20" t="n">
-        <v>112</v>
+          <t>Falls as the construction cycle completes</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="D36" s="17" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="F36" s="17" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="G36" s="17" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="37" ht="26" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Payable days</t>
+          <t>Transfers out of construction (EGP mn)</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Audited FY2025 implies 54 days</t>
-        </is>
-      </c>
-      <c r="C37" s="20" t="n">
-        <v>55</v>
-      </c>
-      <c r="D37" s="20" t="n">
-        <v>56</v>
-      </c>
-      <c r="E37" s="20" t="n">
-        <v>57</v>
-      </c>
-      <c r="F37" s="20" t="n">
-        <v>58</v>
-      </c>
-      <c r="G37" s="20" t="n">
-        <v>58</v>
+          <t>The plant was licensed in December 2025 and enters service</t>
+        </is>
+      </c>
+      <c r="C37" s="19" t="n">
+        <v>3400</v>
+      </c>
+      <c r="D37" s="19" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E37" s="19" t="n">
+        <v>400</v>
+      </c>
+      <c r="F37" s="19" t="n">
+        <v>200</v>
+      </c>
+      <c r="G37" s="19" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="38" ht="26" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Dividend payout ratio</t>
+          <t>Depreciation rate on the property base</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>EGP 3.50 a share proposed for FY2025 on attributable profit</t>
-        </is>
-      </c>
-      <c r="C38" s="17" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>COST OF CAPITAL</t>
-        </is>
+          <t>About a sixteen-year blended life</t>
+        </is>
+      </c>
+      <c r="C38" s="21" t="n">
+        <v>0.062</v>
+      </c>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Inventory days</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>An eight-month strategic stockpile, stated policy</t>
+        </is>
+      </c>
+      <c r="C39" s="19" t="n">
+        <v>265</v>
+      </c>
+      <c r="D39" s="19" t="n">
+        <v>258</v>
+      </c>
+      <c r="E39" s="19" t="n">
+        <v>250</v>
+      </c>
+      <c r="F39" s="19" t="n">
+        <v>245</v>
+      </c>
+      <c r="G39" s="19" t="n">
+        <v>240</v>
       </c>
     </row>
     <row r="40" ht="26" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Ten-year local-currency government yield</t>
+          <t>Receivable days</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>House cost-of-capital reference print</t>
+          <t>Distributor-concentrated book plus export terms</t>
         </is>
       </c>
       <c r="C40" s="19" t="n">
-        <v>0.23</v>
+        <v>126</v>
+      </c>
+      <c r="D40" s="19" t="n">
+        <v>122</v>
+      </c>
+      <c r="E40" s="19" t="n">
+        <v>118</v>
+      </c>
+      <c r="F40" s="19" t="n">
+        <v>115</v>
+      </c>
+      <c r="G40" s="19" t="n">
+        <v>112</v>
       </c>
     </row>
     <row r="41" ht="26" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Sovereign credit-default-swap spread</t>
+          <t>Payable days</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Country risk-premium file, Egypt row, read live</t>
+          <t>Audited FY2025 implies 54 days</t>
         </is>
       </c>
       <c r="C41" s="19" t="n">
-        <v>0.0342</v>
+        <v>55</v>
+      </c>
+      <c r="D41" s="19" t="n">
+        <v>56</v>
+      </c>
+      <c r="E41" s="19" t="n">
+        <v>57</v>
+      </c>
+      <c r="F41" s="19" t="n">
+        <v>58</v>
+      </c>
+      <c r="G41" s="19" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="42" ht="26" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Country equity risk premium (swap basis)</t>
+          <t>Dividend payout ratio</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Same file, same row</t>
-        </is>
-      </c>
-      <c r="C42" s="19" t="n">
-        <v>0.095164</v>
-      </c>
-    </row>
-    <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>Adjusted default spread (rating basis)</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>Same file — the alternative</t>
-        </is>
-      </c>
-      <c r="C43" s="19" t="n">
-        <v>0.059702</v>
+          <t>EGP 3.50 a share proposed for FY2025 on attributable profit</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>COST OF CAPITAL</t>
+        </is>
       </c>
     </row>
     <row r="44" ht="26" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Country equity risk premium (rating basis)</t>
+          <t>Ten-year local-currency government yield</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Same file — the alternative</t>
-        </is>
-      </c>
-      <c r="C44" s="19" t="n">
-        <v>0.134806</v>
+          <t>House cost-of-capital reference print</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n">
+        <v>0.23</v>
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Beta</t>
+          <t>Sovereign credit-default-swap spread</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Own-stock weekly regression against a 36-name local composite, five years; R-squared 0.235, n = 257</t>
+          <t>Country risk-premium file, Egypt row, read live</t>
         </is>
       </c>
       <c r="C45" s="21" t="n">
-        <v>0.629</v>
+        <v>0.0342</v>
       </c>
     </row>
     <row r="46" ht="26" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Cost of local-currency debt</t>
+          <t>Country equity risk premium (swap basis)</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Sovereign yield plus 250 basis points</t>
-        </is>
-      </c>
-      <c r="C46" s="19" t="n">
-        <v>0.2481</v>
+          <t>Same file, same row</t>
+        </is>
+      </c>
+      <c r="C46" s="21" t="n">
+        <v>0.095164</v>
       </c>
     </row>
     <row r="47" ht="26" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Hard-currency coupon</t>
+          <t>Adjusted default spread (rating basis)</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Dollar and euro term loans</t>
-        </is>
-      </c>
-      <c r="C47" s="19" t="n">
-        <v>0.075</v>
+          <t>Same file — the alternative</t>
+        </is>
+      </c>
+      <c r="C47" s="21" t="n">
+        <v>0.059702</v>
       </c>
     </row>
     <row r="48" ht="26" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Expected currency depreciation for the debt charge</t>
+          <t>Country equity risk premium (rating basis)</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>Carries foreign-currency debt at its LOCAL-EQUIVALENT cost</t>
-        </is>
-      </c>
-      <c r="C48" s="19" t="n">
-        <v>0.045</v>
+          <t>Same file — the alternative</t>
+        </is>
+      </c>
+      <c r="C48" s="21" t="n">
+        <v>0.134806</v>
       </c>
     </row>
     <row r="49" ht="26" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Hard-currency share of the term-loan book</t>
+          <t>Beta</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Borrowings note (17), by lender and currency</t>
-        </is>
-      </c>
-      <c r="C49" s="17" t="n">
-        <v>0.5020324090046201</v>
+          <t>Own-stock weekly regression against a 36-name local composite, five years; R-squared 0.235, n = 257</t>
+        </is>
+      </c>
+      <c r="C49" s="22" t="n">
+        <v>0.629</v>
       </c>
     </row>
     <row r="50" ht="26" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Normalised risk-free convergence path</t>
+          <t>Cost of local-currency debt</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>NOT a cost of debt: the first point is the normalised risk-free rate. Only the SHAPE of this row enters the model — the discount-rate glide rebases it to its own endpoints, so the levels cancel</t>
-        </is>
-      </c>
-      <c r="C50" s="19" t="n">
-        <v>0.189</v>
-      </c>
-      <c r="D50" s="19" t="n">
-        <v>0.178</v>
-      </c>
-      <c r="E50" s="19" t="n">
-        <v>0.166</v>
-      </c>
-      <c r="F50" s="19" t="n">
-        <v>0.156</v>
-      </c>
-      <c r="G50" s="19" t="n">
-        <v>0.148</v>
+          <t>Sovereign yield plus 250 basis points</t>
+        </is>
+      </c>
+      <c r="C50" s="21" t="n">
+        <v>0.2481</v>
       </c>
     </row>
     <row r="51" ht="26" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Finance cost charged to profit (EGP mn)</t>
+          <t>Hard-currency coupon</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>What the profit and loss account actually bears — NOT the marginal cost of debt above. Calibrated to the first quarter of 2026</t>
-        </is>
-      </c>
-      <c r="C51" s="20" t="n">
-        <v>1250</v>
-      </c>
-      <c r="D51" s="20" t="n">
-        <v>1210</v>
-      </c>
-      <c r="E51" s="20" t="n">
-        <v>1150</v>
-      </c>
-      <c r="F51" s="20" t="n">
-        <v>1090</v>
-      </c>
-      <c r="G51" s="20" t="n">
-        <v>1030</v>
+          <t>Dollar and euro term loans</t>
+        </is>
+      </c>
+      <c r="C51" s="21" t="n">
+        <v>0.075</v>
       </c>
     </row>
     <row r="52" ht="26" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Terminal risk-free rate</t>
+          <t>Expected currency depreciation for the debt charge</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>A sourced 5% medium-term inflation target plus an UNSOURCED 5.5-point real convention. The real leg is an assertion, it is the widest single lever in the study, and it is an open item — see the terminal grid</t>
-        </is>
-      </c>
-      <c r="C52" s="19" t="n">
-        <v>0.105</v>
+          <t>Carries foreign-currency debt at its LOCAL-EQUIVALENT cost</t>
+        </is>
+      </c>
+      <c r="C52" s="21" t="n">
+        <v>0.045</v>
       </c>
     </row>
     <row r="53" ht="26" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Terminal equity risk premium</t>
+          <t>Hard-currency share of the term-loan book</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Normalised toward the rating-class norm</t>
-        </is>
-      </c>
-      <c r="C53" s="19" t="n">
-        <v>0.07000000000000001</v>
+          <t>Borrowings note (17), by lender and currency</t>
+        </is>
+      </c>
+      <c r="C53" s="17" t="n">
+        <v>0.5020324090046201</v>
       </c>
     </row>
     <row r="54" ht="26" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Terminal local-currency borrowing rate</t>
+          <t>Normalised risk-free convergence path</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>Long-run Egyptian norm</t>
-        </is>
-      </c>
-      <c r="C54" s="19" t="n">
-        <v>0.15</v>
+          <t>NOT a cost of debt: the first point is the normalised risk-free rate. Only the SHAPE of this row enters the model — the discount-rate glide rebases it to its own endpoints, so the levels cancel</t>
+        </is>
+      </c>
+      <c r="C54" s="21" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="D54" s="21" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="E54" s="21" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="F54" s="21" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="G54" s="21" t="n">
+        <v>0.148</v>
       </c>
     </row>
     <row r="55" ht="26" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Terminal hard-currency coupon</t>
+          <t>Finance cost charged to profit (EGP mn)</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>Long-run norm</t>
+          <t>What the profit and loss account actually bears — NOT the marginal cost of debt above. Calibrated to the first quarter of 2026</t>
         </is>
       </c>
       <c r="C55" s="19" t="n">
-        <v>0.065</v>
+        <v>1250</v>
+      </c>
+      <c r="D55" s="19" t="n">
+        <v>1210</v>
+      </c>
+      <c r="E55" s="19" t="n">
+        <v>1150</v>
+      </c>
+      <c r="F55" s="19" t="n">
+        <v>1090</v>
+      </c>
+      <c r="G55" s="19" t="n">
+        <v>1030</v>
       </c>
     </row>
     <row r="56" ht="26" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Terminal debt weight — DERIVED, market-value basis</t>
+          <t>Terminal risk-free rate</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>Today's net debt over market capitalisation plus net debt. Not an assumption; the earlier edition's 20% was neither this nor the book reading below</t>
-        </is>
-      </c>
-      <c r="C56" s="17" t="n">
-        <v>0.251247066000691</v>
+          <t>A sourced 5% medium-term inflation target plus an UNSOURCED 5.5-point real convention. The real leg is an assertion, it is the widest single lever in the study, and it is an open item — see the terminal grid</t>
+        </is>
+      </c>
+      <c r="C56" s="21" t="n">
+        <v>0.105</v>
       </c>
     </row>
     <row r="57" ht="26" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Terminal debt weight — the funded forecast balance sheet at FY2030E</t>
+          <t>Terminal equity risk premium</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>disclosure — the BOOK reading, published beside the market reading above rather than chosen between in silence. The valuation uses the market reading, because a weighted average cost of capital weights market values; this row drives nothing</t>
-        </is>
-      </c>
-      <c r="C57" s="17" t="n">
-        <v>0.3953013301436529</v>
+          <t>Normalised toward the rating-class norm</t>
+        </is>
+      </c>
+      <c r="C57" s="21" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="58" ht="26" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Terminal growth</t>
+          <t>Terminal local-currency borrowing rate</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>Pound-nominal, against a 5% terminal inflation rate — about zero in real terms</t>
-        </is>
-      </c>
-      <c r="C58" s="17" t="n">
-        <v>0.05</v>
+          <t>Long-run Egyptian norm</t>
+        </is>
+      </c>
+      <c r="C58" s="21" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="59" ht="26" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Normalised associate contribution (EGP mn)</t>
+          <t>Terminal hard-currency coupon</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>Three disclosed years, reconciled to this model's own income statement: 74.508, 151.581, 512.085 — mean 246.058. The first quarter of 2026 annualises to 52.5, but the auditor states two holdings' statements were not received, so that quarter is evidence, not a run-rate</t>
-        </is>
-      </c>
-      <c r="C59" s="20" t="n">
-        <v>250</v>
+          <t>Long-run norm</t>
+        </is>
+      </c>
+      <c r="C59" s="21" t="n">
+        <v>0.065</v>
       </c>
     </row>
     <row r="60" ht="26" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Associate earnings multiple</t>
+          <t>Terminal debt weight — DERIVED, market-value basis</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Below the Gulf listed range for a minority, unlisted, non-controlled stake</t>
-        </is>
-      </c>
-      <c r="C60" s="22" t="n">
-        <v>11</v>
+          <t>Today's net debt over market capitalisation plus net debt. Not an assumption; the earlier edition's 20% was neither this nor the book reading below</t>
+        </is>
+      </c>
+      <c r="C60" s="17" t="n">
+        <v>0.251247066000691</v>
       </c>
     </row>
     <row r="61" ht="26" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Struck peer reference price-earnings multiple</t>
+          <t>Terminal debt weight — the funded forecast balance sheet at FY2030E</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>MARKET DATA, cross-check layer. The MIDPOINT of the only two disclosed observations (26.7x and 16.0x) — NOT a median of a peer set, and the peers are not named, so it cannot be rebuilt from their filings</t>
-        </is>
-      </c>
-      <c r="C61" s="23" t="n">
-        <v>21.35</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="8" t="inlineStr">
-        <is>
-          <t>OPENING BALANCE SHEET (AUDITED, 31 DECEMBER 2025)</t>
-        </is>
+          <t>disclosure — the BOOK reading, published beside the market reading above rather than chosen between in silence. The valuation uses the market reading, because a weighted average cost of capital weights market values; this row drives nothing</t>
+        </is>
+      </c>
+      <c r="C61" s="17" t="n">
+        <v>0.398408806312907</v>
+      </c>
+    </row>
+    <row r="62" ht="26" customHeight="1">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>Terminal growth</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>Pound-nominal, against a 5% terminal inflation rate — about zero in real terms</t>
+        </is>
+      </c>
+      <c r="C62" s="17" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="63" ht="26" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Property, plant and equipment, net</t>
+          <t>Normalised associate contribution (EGP mn)</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>Note (4)</t>
-        </is>
-      </c>
-      <c r="C63" s="20" t="n">
-        <v>3069.747924</v>
+          <t>Three disclosed years, reconciled to this model's own income statement: 74.508, 151.581, 512.085 — mean 246.058. The first quarter of 2026 annualises to 52.5, but the auditor states two holdings' statements were not received, so that quarter is evidence, not a run-rate</t>
+        </is>
+      </c>
+      <c r="C63" s="19" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="64" ht="26" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Projects under construction</t>
+          <t>Associate earnings multiple</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>Note (6)</t>
-        </is>
-      </c>
-      <c r="C64" s="20" t="n">
-        <v>4901.223806</v>
+          <t>Below the Gulf listed range for a minority, unlisted, non-controlled stake</t>
+        </is>
+      </c>
+      <c r="C64" s="23" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="65" ht="26" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Inventories, net</t>
+          <t>Struck peer reference price-earnings multiple</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>Note (9)</t>
-        </is>
-      </c>
-      <c r="C65" s="20" t="n">
-        <v>3887.077629</v>
-      </c>
-    </row>
-    <row r="66" ht="26" customHeight="1">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>Trade and notes receivable, net</t>
-        </is>
-      </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>Note (10)</t>
-        </is>
-      </c>
-      <c r="C66" s="20" t="n">
-        <v>3325.044117</v>
+          <t>MARKET DATA, cross-check layer. The MIDPOINT of the only two disclosed observations (26.7x and 16.0x) — NOT a median of a peer set, and the peers are not named, so it cannot be rebuilt from their filings</t>
+        </is>
+      </c>
+      <c r="C65" s="24" t="n">
+        <v>21.35</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE SHEET (AUDITED, 31 DECEMBER 2025)</t>
+        </is>
       </c>
     </row>
     <row r="67" ht="26" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Other debtors</t>
+          <t>Property, plant and equipment, net</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>Note (11)</t>
-        </is>
-      </c>
-      <c r="C67" s="20" t="n">
-        <v>356.786958</v>
+          <t>Note (4)</t>
+        </is>
+      </c>
+      <c r="C67" s="19" t="n">
+        <v>3069.747924</v>
       </c>
     </row>
     <row r="68" ht="26" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>Trade and notes payable</t>
+          <t>Projects under construction</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>Note (22)</t>
-        </is>
-      </c>
-      <c r="C68" s="20" t="n">
-        <v>780.416969</v>
+          <t>Note (6)</t>
+        </is>
+      </c>
+      <c r="C68" s="19" t="n">
+        <v>4901.223806</v>
       </c>
     </row>
     <row r="69" ht="26" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Other creditors</t>
+          <t>Inventories, net</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Note (23)</t>
-        </is>
-      </c>
-      <c r="C69" s="20" t="n">
-        <v>1044.832275</v>
+          <t>Note (9)</t>
+        </is>
+      </c>
+      <c r="C69" s="19" t="n">
+        <v>3887.077629</v>
       </c>
     </row>
     <row r="70" ht="26" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Cash and bank balances</t>
+          <t>Trade and notes receivable, net</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Note (12)</t>
-        </is>
-      </c>
-      <c r="C70" s="20" t="n">
-        <v>1433.426902</v>
+          <t>Note (10)</t>
+        </is>
+      </c>
+      <c r="C70" s="19" t="n">
+        <v>3325.044117</v>
       </c>
     </row>
     <row r="71" ht="26" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Gross borrowings including leases</t>
+          <t>Other debtors</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>Notes (17), (18) and (21)</t>
-        </is>
-      </c>
-      <c r="C71" s="20" t="n">
-        <v>8797.725640000001</v>
+          <t>Note (11)</t>
+        </is>
+      </c>
+      <c r="C71" s="19" t="n">
+        <v>356.786958</v>
       </c>
     </row>
     <row r="72" ht="26" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>Attributable profit, FY2025 (EGP mn)</t>
+          <t>Trade and notes payable</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>Audited — the trailing earnings base for every trailing multiple</t>
-        </is>
-      </c>
-      <c r="C72" s="20" t="n">
-        <v>1441.6577</v>
+          <t>Note (22)</t>
+        </is>
+      </c>
+      <c r="C72" s="19" t="n">
+        <v>780.416969</v>
       </c>
     </row>
     <row r="73" ht="26" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Equity attributable to the holding company</t>
+          <t>Other creditors</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>Audited</t>
-        </is>
-      </c>
-      <c r="C73" s="20" t="n">
-        <v>6243.131482</v>
+          <t>Note (23)</t>
+        </is>
+      </c>
+      <c r="C73" s="19" t="n">
+        <v>1044.832275</v>
       </c>
     </row>
     <row r="74" ht="26" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Non-controlling interests, audited 31 December 2025</t>
+          <t>Cash and bank balances</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>disclosure — the audited December figure, shown so the reader can see both. It is SUPERSEDED for valuation by the March figure below, because almost all of it was the active-ingredient company and that company was deconsolidated in the first quarter of 2026. This row drives the balance sheet history only</t>
-        </is>
-      </c>
-      <c r="C74" s="20" t="n">
-        <v>288.704605</v>
+          <t>Note (12)</t>
+        </is>
+      </c>
+      <c r="C74" s="19" t="n">
+        <v>1433.426902</v>
       </c>
     </row>
     <row r="75" ht="26" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Non-controlling interests deducted in the bridge</t>
+          <t>Gross borrowings including leases</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>Post-deconsolidation, from the reviewed 31 March 2026 interim</t>
-        </is>
-      </c>
-      <c r="C75" s="20" t="n">
-        <v>3.999807</v>
+          <t>Notes (17), (18) and (21)</t>
+        </is>
+      </c>
+      <c r="C75" s="19" t="n">
+        <v>8797.725640000001</v>
       </c>
     </row>
     <row r="76" ht="26" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Active-ingredient company at carrying cost (EGP mn)</t>
+          <t>Attributable profit, FY2025 (EGP mn)</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>Pre-revenue, so cost not an earnings multiple; the Q1-2026 movement in investments in associates</t>
-        </is>
-      </c>
-      <c r="C76" s="20" t="n">
-        <v>228.4864180000001</v>
+          <t>Audited — the trailing earnings base for every trailing multiple</t>
+        </is>
+      </c>
+      <c r="C76" s="19" t="n">
+        <v>1441.6577</v>
       </c>
     </row>
     <row r="77" ht="26" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Assets held for sale</t>
+          <t>Equity attributable to the holding company</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>Note (8/1)</t>
-        </is>
-      </c>
-      <c r="C77" s="20" t="n">
-        <v>12.33</v>
+          <t>Audited</t>
+        </is>
+      </c>
+      <c r="C77" s="19" t="n">
+        <v>6243.131482</v>
       </c>
     </row>
     <row r="78" ht="26" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>Intangible assets, net</t>
+          <t>Non-controlling interests, audited 31 December 2025</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>Note (7)</t>
-        </is>
-      </c>
-      <c r="C78" s="20" t="n">
-        <v>40.142171</v>
+          <t>disclosure — the audited December figure, shown so the reader can see both. It is SUPERSEDED for valuation by the March figure below, because almost all of it was the active-ingredient company and that company was deconsolidated in the first quarter of 2026. This row drives the balance sheet history only</t>
+        </is>
+      </c>
+      <c r="C78" s="19" t="n">
+        <v>288.704605</v>
       </c>
     </row>
     <row r="79" ht="26" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>Right-of-use and intangible amortisation run-rate</t>
+          <t>Non-controlling interests deducted in the bridge</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>Audited FY2025 cash-flow statement</t>
-        </is>
-      </c>
-      <c r="C79" s="24" t="n">
-        <v>8.269948999999997</v>
+          <t>Post-deconsolidation, from the reviewed 31 March 2026 interim</t>
+        </is>
+      </c>
+      <c r="C79" s="19" t="n">
+        <v>3.999807</v>
       </c>
     </row>
     <row r="80" ht="26" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>Share of depreciation charged to cost of sales</t>
+          <t>Active-ingredient company at carrying cost (EGP mn)</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>Cost of sales note (26): 93.498 of 117.725</t>
-        </is>
-      </c>
-      <c r="C80" s="17" t="n">
-        <v>0.7942005773538676</v>
+          <t>Pre-revenue, so cost not an earnings multiple; the Q1-2026 movement in investments in associates</t>
+        </is>
+      </c>
+      <c r="C80" s="19" t="n">
+        <v>228.4864180000001</v>
       </c>
     </row>
     <row r="81" ht="26" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>FY2025 cash cost per pack sold (EGP)</t>
+          <t>Assets held for sale</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>Cost of sales less its depreciation line, over packs sold</t>
-        </is>
-      </c>
-      <c r="C81" s="16" t="n">
-        <v>14.53600902055724</v>
+          <t>Note (8/1)</t>
+        </is>
+      </c>
+      <c r="C81" s="19" t="n">
+        <v>12.33</v>
       </c>
     </row>
     <row r="82" ht="26" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>Consolidated-to-separate revenue factor</t>
+          <t>Intangible assets, net</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>MEASURED: audited consolidated revenue over the separate-company channel total</t>
-        </is>
-      </c>
-      <c r="C82" s="25" t="n">
-        <v>1.014932591450432</v>
+          <t>Note (7)</t>
+        </is>
+      </c>
+      <c r="C82" s="19" t="n">
+        <v>40.142171</v>
       </c>
     </row>
     <row r="83" ht="26" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>FY2025 domestic packs (million)</t>
+          <t>Right-of-use and intangible amortisation run-rate</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>Unit build</t>
-        </is>
-      </c>
-      <c r="C83" s="16" t="n">
-        <v>291.81</v>
+          <t>Audited FY2025 cash-flow statement</t>
+        </is>
+      </c>
+      <c r="C83" s="25" t="n">
+        <v>8.269948999999997</v>
       </c>
     </row>
     <row r="84" ht="26" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>FY2025 export packs (million)</t>
+          <t>Share of depreciation charged to cost of sales</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>Investor presentation</t>
-        </is>
-      </c>
-      <c r="C84" s="16" t="n">
-        <v>60</v>
+          <t>Cost of sales note (26): 93.498 of 117.725</t>
+        </is>
+      </c>
+      <c r="C84" s="17" t="n">
+        <v>0.7942005773538676</v>
       </c>
     </row>
     <row r="85" ht="26" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>FY2025 domestic price per pack (EGP)</t>
+          <t>FY2025 cash cost per pack sold (EGP)</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>Unit build</t>
+          <t>Cost of sales less its depreciation line, over packs sold</t>
         </is>
       </c>
       <c r="C85" s="16" t="n">
-        <v>21.54012212741167</v>
+        <v>14.53600902055724</v>
       </c>
     </row>
     <row r="86" ht="26" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>FY2025 export price per pack (USD)</t>
+          <t>Consolidated-to-separate revenue factor</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>Unit build</t>
-        </is>
-      </c>
-      <c r="C86" s="16" t="n">
-        <v>0.9995553449205068</v>
+          <t>MEASURED: audited consolidated revenue over the separate-company channel total</t>
+        </is>
+      </c>
+      <c r="C86" s="26" t="n">
+        <v>1.014932591450432</v>
       </c>
     </row>
     <row r="87" ht="26" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>FY2025 contract-manufacturing packs (million)</t>
+          <t>FY2025 packs sold of the company's OWN preparations (million)</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>Board report</t>
-        </is>
-      </c>
-      <c r="C87" s="16" t="n">
-        <v>5.485</v>
+          <t>Board report, sales-indicators table</t>
+        </is>
+      </c>
+      <c r="C87" s="18" t="n">
+        <v>351.81</v>
       </c>
     </row>
     <row r="88" ht="26" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>FY2025 contract-manufacturing revenue (EGP mn)</t>
+          <t>FY2025 export packs (million)</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>Revenue note (25)</t>
-        </is>
-      </c>
-      <c r="C88" s="24" t="n">
-        <v>49.366365</v>
+          <t>Investor presentation</t>
+        </is>
+      </c>
+      <c r="C88" s="18" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="89" ht="26" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
+          <t>FY2025 export revenue (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>Revenue note (25)</t>
+        </is>
+      </c>
+      <c r="C89" s="19" t="n">
+        <v>2967.479908</v>
+      </c>
+    </row>
+    <row r="90" ht="26" customHeight="1">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 sales value of the company's OWN preparations (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>Board report, sales-indicators table</t>
+        </is>
+      </c>
+      <c r="C90" s="19" t="n">
+        <v>9160.147999999999</v>
+      </c>
+    </row>
+    <row r="91" ht="26" customHeight="1">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 sales value of CONTRACT-MANUFACTURED preparations (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>Board report, sales-indicators table — product value, not the fee the company books</t>
+        </is>
+      </c>
+      <c r="C91" s="19" t="n">
+        <v>142.321</v>
+      </c>
+    </row>
+    <row r="92" ht="26" customHeight="1">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 contract-manufactured packs (million)</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>Board report</t>
+        </is>
+      </c>
+      <c r="C92" s="18" t="n">
+        <v>5.485</v>
+      </c>
+    </row>
+    <row r="93" ht="26" customHeight="1">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 contract-manufacturing FEE revenue (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>disclosure — this row SPLITS the contract-manufacturing line in two and cannot move the valuation by construction: the fee per pack rises by exactly what the resale price per pack falls, so the product value above is what reaches revenue either way. It is carried because the two halves are disclosed separately and a reader should see both. Revenue note (25)</t>
+        </is>
+      </c>
+      <c r="C93" s="25" t="n">
+        <v>49.366365</v>
+      </c>
+    </row>
+    <row r="94" ht="26" customHeight="1">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
           <t>FY2025 average exchange rate</t>
         </is>
       </c>
-      <c r="B89" s="7" t="inlineStr">
+      <c r="B94" s="7" t="inlineStr">
         <is>
           <t>Note (36)</t>
         </is>
       </c>
-      <c r="C89" s="16" t="n">
+      <c r="C94" s="16" t="n">
         <v>49.48</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="8" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="8" t="inlineStr">
         <is>
           <t>DERIVED IN THIS SHEET (formulas, not inputs)</t>
         </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="4" t="inlineStr">
-        <is>
-          <t>Normalised risk-free rate = yield less sovereign spread</t>
-        </is>
-      </c>
-      <c r="B91" s="7" t="inlineStr">
-        <is>
-          <t>calculated</t>
-        </is>
-      </c>
-      <c r="C91" s="26">
-        <f>$C$40-$C$41</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="4" t="inlineStr">
-        <is>
-          <t>Cost of equity = normalised risk-free + beta x premium</t>
-        </is>
-      </c>
-      <c r="B92" s="7" t="inlineStr">
-        <is>
-          <t>calculated</t>
-        </is>
-      </c>
-      <c r="C92" s="26">
-        <f>$C$91+$C$45*$C$42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="4" t="inlineStr">
-        <is>
-          <t>Cost of equity, rating basis (published alternative)</t>
-        </is>
-      </c>
-      <c r="B93" s="7" t="inlineStr">
-        <is>
-          <t>calculated</t>
-        </is>
-      </c>
-      <c r="C93" s="26">
-        <f>($C$40-$C$43)+$C$45*$C$44</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="4" t="inlineStr">
-        <is>
-          <t>Hard-currency debt at LOCAL-EQUIVALENT cost</t>
-        </is>
-      </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>calculated</t>
-        </is>
-      </c>
-      <c r="C94" s="26">
-        <f>(1+$C$47)*(1+$C$48)-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t>Blended marginal cost of debt</t>
-        </is>
-      </c>
-      <c r="B95" s="7" t="inlineStr">
-        <is>
-          <t>calculated</t>
-        </is>
-      </c>
-      <c r="C95" s="26">
-        <f>(1-$C$49)*$C$46+$C$49*$C$94</f>
-        <v/>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>Cost of debt after tax</t>
+          <t>Normalised risk-free rate = yield less sovereign spread</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
@@ -6123,15 +6122,15 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C96" s="26">
-        <f>$C$95*(1-$C$5)</f>
+      <c r="C96" s="27">
+        <f>$C$44-$C$45</f>
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>Market capitalisation (EGP mn)</t>
+          <t>Cost of equity = normalised risk-free + beta x premium</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
@@ -6140,14 +6139,14 @@
         </is>
       </c>
       <c r="C97" s="27">
-        <f>$C$3*$C$4</f>
+        <f>$C$96+$C$49*$C$46</f>
         <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>Net debt (EGP mn)</t>
+          <t>Cost of equity, rating basis (published alternative)</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
@@ -6156,14 +6155,14 @@
         </is>
       </c>
       <c r="C98" s="27">
-        <f>$C$71-$C$70</f>
+        <f>($C$44-$C$47)+$C$49*$C$48</f>
         <v/>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>Equity weight (net basis)</t>
+          <t>Hard-currency debt at LOCAL-EQUIVALENT cost</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
@@ -6171,15 +6170,15 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C99" s="28">
-        <f>$C$97/($C$97+$C$98)</f>
+      <c r="C99" s="27">
+        <f>(1+$C$51)*(1+$C$52)-1</f>
         <v/>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>Debt weight (net basis)</t>
+          <t>Blended marginal cost of debt</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
@@ -6187,15 +6186,15 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C100" s="28">
-        <f>1-$C$99</f>
+      <c r="C100" s="27">
+        <f>(1-$C$53)*$C$50+$C$53*$C$99</f>
         <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>Weighted average cost of capital, year one</t>
+          <t>Cost of debt after tax</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
@@ -6203,15 +6202,15 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C101" s="26">
-        <f>$C$99*$C$92+$C$100*$C$96</f>
+      <c r="C101" s="27">
+        <f>$C$100*(1-$C$9)</f>
         <v/>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>Debt weight (gross basis)</t>
+          <t>Market capitalisation (EGP mn)</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
@@ -6220,14 +6219,14 @@
         </is>
       </c>
       <c r="C102" s="28">
-        <f>$C$71/($C$97+$C$71)</f>
+        <f>$C$3*$C$8</f>
         <v/>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>Weighted average cost of capital, gross-debt basis</t>
+          <t>Net debt (EGP mn)</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
@@ -6235,15 +6234,15 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C103" s="26">
-        <f>(1-$C$102)*$C$92+$C$102*$C$96</f>
+      <c r="C103" s="28">
+        <f>$C$75-$C$74</f>
         <v/>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>Terminal cost of equity</t>
+          <t>Equity weight (net basis)</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
@@ -6251,15 +6250,15 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C104" s="26">
-        <f>$C$52+$C$45*$C$53</f>
+      <c r="C104" s="29">
+        <f>$C$102/($C$102+$C$103)</f>
         <v/>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>Terminal cost of debt</t>
+          <t>Debt weight (net basis)</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
@@ -6267,15 +6266,15 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C105" s="26">
-        <f>(1-$C$49)*$C$54+$C$49*((1+$C$55)*1.03-1)</f>
+      <c r="C105" s="29">
+        <f>1-$C$104</f>
         <v/>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>Terminal cost of debt after tax</t>
+          <t>Weighted average cost of capital, year one</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
@@ -6283,120 +6282,200 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C106" s="26">
-        <f>$C$105*(1-$C$5)</f>
+      <c r="C106" s="27">
+        <f>$C$104*$C$97+$C$105*$C$101</f>
         <v/>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
+          <t>Debt weight (gross basis)</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="C107" s="29">
+        <f>$C$75/($C$102+$C$75)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>Weighted average cost of capital, gross-debt basis</t>
+        </is>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="C108" s="27">
+        <f>(1-$C$107)*$C$97+$C$107*$C$101</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>Terminal cost of equity</t>
+        </is>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="C109" s="27">
+        <f>$C$56+$C$49*$C$57</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>Terminal cost of debt</t>
+        </is>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="C110" s="27">
+        <f>(1-$C$53)*$C$58+$C$53*((1+$C$59)*1.03-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>Terminal cost of debt after tax</t>
+        </is>
+      </c>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="C111" s="27">
+        <f>$C$110*(1-$C$9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
           <t>Terminal weighted average cost of capital</t>
         </is>
       </c>
-      <c r="B107" s="7" t="inlineStr">
+      <c r="B112" s="7" t="inlineStr">
         <is>
           <t>calculated</t>
         </is>
       </c>
-      <c r="C107" s="26">
-        <f>(1-$C$56)*$C$104+$C$56*$C$106</f>
-        <v/>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="11" t="inlineStr">
+      <c r="C112" s="27">
+        <f>(1-$C$60)*$C$109+$C$60*$C$111</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="11" t="inlineStr">
         <is>
           <t>Glide fraction (derived from the convergence path — SHAPE only)</t>
         </is>
       </c>
-      <c r="B108" s="7" t="inlineStr">
+      <c r="B113" s="7" t="inlineStr">
         <is>
           <t>calculated: (this year's cost of debt less the last year's) over (the first year's less the last year's)</t>
         </is>
       </c>
-      <c r="C108" s="29">
-        <f>(C$50-$G$50)/($C$50-$G$50)</f>
-        <v/>
-      </c>
-      <c r="D108" s="29">
-        <f>(D$50-$G$50)/($C$50-$G$50)</f>
-        <v/>
-      </c>
-      <c r="E108" s="29">
-        <f>(E$50-$G$50)/($C$50-$G$50)</f>
-        <v/>
-      </c>
-      <c r="F108" s="29">
-        <f>(F$50-$G$50)/($C$50-$G$50)</f>
-        <v/>
-      </c>
-      <c r="G108" s="29">
-        <f>(G$50-$G$50)/($C$50-$G$50)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="11" t="inlineStr">
+      <c r="C113" s="30">
+        <f>(C$54-$G$54)/($C$54-$G$54)</f>
+        <v/>
+      </c>
+      <c r="D113" s="30">
+        <f>(D$54-$G$54)/($C$54-$G$54)</f>
+        <v/>
+      </c>
+      <c r="E113" s="30">
+        <f>(E$54-$G$54)/($C$54-$G$54)</f>
+        <v/>
+      </c>
+      <c r="F113" s="30">
+        <f>(F$54-$G$54)/($C$54-$G$54)</f>
+        <v/>
+      </c>
+      <c r="G113" s="30">
+        <f>(G$54-$G$54)/($C$54-$G$54)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="11" t="inlineStr">
         <is>
           <t>Discount rate</t>
         </is>
       </c>
-      <c r="B109" s="7" t="inlineStr">
+      <c r="B114" s="7" t="inlineStr">
         <is>
           <t>calculated: terminal rate plus the glide fraction of the gap to year one</t>
         </is>
       </c>
-      <c r="C109" s="15">
-        <f>$C$107+($C$101-$C$107)*C$108</f>
-        <v/>
-      </c>
-      <c r="D109" s="15">
-        <f>$C$107+($C$101-$C$107)*D$108</f>
-        <v/>
-      </c>
-      <c r="E109" s="15">
-        <f>$C$107+($C$101-$C$107)*E$108</f>
-        <v/>
-      </c>
-      <c r="F109" s="15">
-        <f>$C$107+($C$101-$C$107)*F$108</f>
-        <v/>
-      </c>
-      <c r="G109" s="15">
-        <f>$C$107+($C$101-$C$107)*G$108</f>
-        <v/>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="11" t="inlineStr">
+      <c r="C114" s="15">
+        <f>$C$112+($C$106-$C$112)*C$113</f>
+        <v/>
+      </c>
+      <c r="D114" s="15">
+        <f>$C$112+($C$106-$C$112)*D$113</f>
+        <v/>
+      </c>
+      <c r="E114" s="15">
+        <f>$C$112+($C$106-$C$112)*E$113</f>
+        <v/>
+      </c>
+      <c r="F114" s="15">
+        <f>$C$112+($C$106-$C$112)*F$113</f>
+        <v/>
+      </c>
+      <c r="G114" s="15">
+        <f>$C$112+($C$106-$C$112)*G$113</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="11" t="inlineStr">
         <is>
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B110" s="7" t="inlineStr">
+      <c r="B115" s="7" t="inlineStr">
         <is>
           <t>calculated: the previous factor divided by one plus this year's rate — the factors compound</t>
         </is>
       </c>
-      <c r="C110" s="30">
-        <f>1/(1+C$109)</f>
-        <v/>
-      </c>
-      <c r="D110" s="30">
-        <f>C110/(1+D$109)</f>
-        <v/>
-      </c>
-      <c r="E110" s="30">
-        <f>D110/(1+E$109)</f>
-        <v/>
-      </c>
-      <c r="F110" s="30">
-        <f>E110/(1+F$109)</f>
-        <v/>
-      </c>
-      <c r="G110" s="30">
-        <f>F110/(1+G$109)</f>
+      <c r="C115" s="31">
+        <f>1/(1+C$114)</f>
+        <v/>
+      </c>
+      <c r="D115" s="31">
+        <f>C115/(1+D$114)</f>
+        <v/>
+      </c>
+      <c r="E115" s="31">
+        <f>D115/(1+E$114)</f>
+        <v/>
+      </c>
+      <c r="F115" s="31">
+        <f>E115/(1+F$114)</f>
+        <v/>
+      </c>
+      <c r="G115" s="31">
+        <f>F115/(1+G$114)</f>
         <v/>
       </c>
     </row>
@@ -6447,7 +6526,7 @@
         <v/>
       </c>
       <c r="C2" s="5">
-        <f>B2/Assumptions!$C$4</f>
+        <f>B2/Assumptions!$C$8</f>
         <v/>
       </c>
     </row>
@@ -6462,7 +6541,7 @@
         <v/>
       </c>
       <c r="C3" s="5">
-        <f>B3/Assumptions!$C$4</f>
+        <f>B3/Assumptions!$C$8</f>
         <v/>
       </c>
     </row>
@@ -6484,11 +6563,11 @@
         </is>
       </c>
       <c r="B5" s="13">
-        <f>Assumptions!$C$59*Assumptions!$C$60</f>
+        <f>Assumptions!$C$63*Assumptions!$C$64</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>B5/Assumptions!$C$4</f>
+        <f>B5/Assumptions!$C$8</f>
         <v/>
       </c>
     </row>
@@ -6499,11 +6578,11 @@
         </is>
       </c>
       <c r="B6" s="13">
-        <f>Assumptions!$C$76</f>
+        <f>Assumptions!$C$80</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>B6/Assumptions!$C$4</f>
+        <f>B6/Assumptions!$C$8</f>
         <v/>
       </c>
     </row>
@@ -6514,11 +6593,11 @@
         </is>
       </c>
       <c r="B7" s="13">
-        <f>Assumptions!$C$77</f>
+        <f>Assumptions!$C$81</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>B7/Assumptions!$C$4</f>
+        <f>B7/Assumptions!$C$8</f>
         <v/>
       </c>
     </row>
@@ -6528,12 +6607,12 @@
           <t>TOTAL ENTERPRISE VALUE</t>
         </is>
       </c>
-      <c r="B8" s="31">
+      <c r="B8" s="32">
         <f>B2+B5+B6+B7</f>
         <v/>
       </c>
       <c r="C8" s="9">
-        <f>B8/Assumptions!$C$4</f>
+        <f>B8/Assumptions!$C$8</f>
         <v/>
       </c>
     </row>
@@ -6544,11 +6623,11 @@
         </is>
       </c>
       <c r="B9" s="13">
-        <f>-Assumptions!$C$98</f>
+        <f>-Assumptions!$C$103</f>
         <v/>
       </c>
       <c r="C9" s="5">
-        <f>B9/Assumptions!$C$4</f>
+        <f>B9/Assumptions!$C$8</f>
         <v/>
       </c>
     </row>
@@ -6559,11 +6638,11 @@
         </is>
       </c>
       <c r="B10" s="13">
-        <f>-Assumptions!$C$75</f>
+        <f>-Assumptions!$C$79</f>
         <v/>
       </c>
       <c r="C10" s="5">
-        <f>B10/Assumptions!$C$4</f>
+        <f>B10/Assumptions!$C$8</f>
         <v/>
       </c>
     </row>
@@ -6573,12 +6652,12 @@
           <t>EQUITY VALUE</t>
         </is>
       </c>
-      <c r="B11" s="31">
+      <c r="B11" s="32">
         <f>B8+B9+B10</f>
         <v/>
       </c>
       <c r="C11" s="9">
-        <f>B11/Assumptions!$C$4</f>
+        <f>B11/Assumptions!$C$8</f>
         <v/>
       </c>
     </row>
@@ -6588,12 +6667,12 @@
           <t>Value per share — Frame A</t>
         </is>
       </c>
-      <c r="B13" s="31">
+      <c r="B13" s="32">
         <f>B11</f>
         <v/>
       </c>
       <c r="C13" s="9">
-        <f>B13/Assumptions!$C$4</f>
+        <f>B13/Assumptions!$C$8</f>
         <v/>
       </c>
     </row>
@@ -6608,7 +6687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6672,27 +6751,28 @@
       <c r="B2" s="16" t="n">
         <v>244.272</v>
       </c>
-      <c r="C2" s="16" t="n">
-        <v>291.81</v>
+      <c r="C2" s="33">
+        <f>Assumptions!$C$87-Assumptions!$C$88</f>
+        <v/>
       </c>
       <c r="D2" s="5">
-        <f>Assumptions!$C$83*(1+Assumptions!C$8)</f>
+        <f>C2*(1+Assumptions!C$12)</f>
         <v/>
       </c>
       <c r="E2" s="5">
-        <f>D2*(1+Assumptions!D$8)</f>
+        <f>D2*(1+Assumptions!D$12)</f>
         <v/>
       </c>
       <c r="F2" s="5">
-        <f>E2*(1+Assumptions!E$8)</f>
+        <f>E2*(1+Assumptions!E$12)</f>
         <v/>
       </c>
       <c r="G2" s="5">
-        <f>F2*(1+Assumptions!F$8)</f>
+        <f>F2*(1+Assumptions!F$12)</f>
         <v/>
       </c>
       <c r="H2" s="5">
-        <f>G2*(1+Assumptions!G$8)</f>
+        <f>G2*(1+Assumptions!G$12)</f>
         <v/>
       </c>
     </row>
@@ -6705,60 +6785,63 @@
       <c r="B3" s="16" t="n">
         <v>54.7</v>
       </c>
-      <c r="C3" s="16" t="n">
-        <v>60</v>
+      <c r="C3" s="33">
+        <f>Assumptions!$C$88</f>
+        <v/>
       </c>
       <c r="D3" s="5">
-        <f>Assumptions!$C$84*(1+Assumptions!C$9)</f>
+        <f>C3*(1+Assumptions!C$13)</f>
         <v/>
       </c>
       <c r="E3" s="5">
-        <f>D3*(1+Assumptions!D$9)</f>
+        <f>D3*(1+Assumptions!D$13)</f>
         <v/>
       </c>
       <c r="F3" s="5">
-        <f>E3*(1+Assumptions!E$9)</f>
+        <f>E3*(1+Assumptions!E$13)</f>
         <v/>
       </c>
       <c r="G3" s="5">
-        <f>F3*(1+Assumptions!F$9)</f>
+        <f>F3*(1+Assumptions!F$13)</f>
         <v/>
       </c>
       <c r="H3" s="5">
-        <f>G3*(1+Assumptions!G$9)</f>
+        <f>G3*(1+Assumptions!G$13)</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Domestic realised price per pack (EGP)</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="n">
-        <v>19.76517940246938</v>
-      </c>
-      <c r="C4" s="16" t="n">
-        <v>21.54012212741167</v>
+          <t>Domestic realised price per pack (EGP) — own preparations only</t>
+        </is>
+      </c>
+      <c r="B4" s="5">
+        <f>B7/B2</f>
+        <v/>
+      </c>
+      <c r="C4" s="5">
+        <f>C7/C2</f>
+        <v/>
       </c>
       <c r="D4" s="5">
-        <f>Assumptions!$C$85*(1+Assumptions!C$10)</f>
+        <f>C4*(1+Assumptions!C$14)</f>
         <v/>
       </c>
       <c r="E4" s="5">
-        <f>D4*(1+Assumptions!D$10)</f>
+        <f>D4*(1+Assumptions!D$14)</f>
         <v/>
       </c>
       <c r="F4" s="5">
-        <f>E4*(1+Assumptions!E$10)</f>
+        <f>E4*(1+Assumptions!E$14)</f>
         <v/>
       </c>
       <c r="G4" s="5">
-        <f>F4*(1+Assumptions!F$10)</f>
+        <f>F4*(1+Assumptions!F$14)</f>
         <v/>
       </c>
       <c r="H4" s="5">
-        <f>G4*(1+Assumptions!G$10)</f>
+        <f>G4*(1+Assumptions!G$14)</f>
         <v/>
       </c>
     </row>
@@ -6768,30 +6851,32 @@
           <t>Export realised price per pack (USD)</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>0.9574086731220066</v>
-      </c>
-      <c r="C5" s="16" t="n">
-        <v>0.9995553449205068</v>
+      <c r="B5" s="5">
+        <f>B8/B3/B6</f>
+        <v/>
+      </c>
+      <c r="C5" s="5">
+        <f>C8/C3/C6</f>
+        <v/>
       </c>
       <c r="D5" s="5">
-        <f>Assumptions!$C$86*(1+Assumptions!C$11)</f>
+        <f>C5*(1+Assumptions!C$15)</f>
         <v/>
       </c>
       <c r="E5" s="5">
-        <f>D5*(1+Assumptions!D$11)</f>
+        <f>D5*(1+Assumptions!D$15)</f>
         <v/>
       </c>
       <c r="F5" s="5">
-        <f>E5*(1+Assumptions!E$11)</f>
+        <f>E5*(1+Assumptions!E$15)</f>
         <v/>
       </c>
       <c r="G5" s="5">
-        <f>F5*(1+Assumptions!F$11)</f>
+        <f>F5*(1+Assumptions!F$15)</f>
         <v/>
       </c>
       <c r="H5" s="5">
-        <f>G5*(1+Assumptions!G$11)</f>
+        <f>G5*(1+Assumptions!G$15)</f>
         <v/>
       </c>
     </row>
@@ -6808,55 +6893,57 @@
         <v>49.48</v>
       </c>
       <c r="D6" s="5">
-        <f>Assumptions!C$13</f>
+        <f>Assumptions!C$17</f>
         <v/>
       </c>
       <c r="E6" s="5">
-        <f>Assumptions!D$13</f>
+        <f>Assumptions!D$17</f>
         <v/>
       </c>
       <c r="F6" s="5">
-        <f>Assumptions!E$13</f>
+        <f>Assumptions!E$17</f>
         <v/>
       </c>
       <c r="G6" s="5">
-        <f>Assumptions!F$13</f>
+        <f>Assumptions!F$17</f>
         <v/>
       </c>
       <c r="H6" s="5">
-        <f>Assumptions!G$13</f>
+        <f>Assumptions!G$17</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Domestic revenue (EGP mn)</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="n">
-        <v>4828.079903</v>
-      </c>
-      <c r="C7" s="20" t="n">
-        <v>6285.623038000001</v>
-      </c>
-      <c r="D7" s="32">
+          <t>Domestic revenue, own preparations (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B7" s="13">
+        <f>7104.16-B8</f>
+        <v/>
+      </c>
+      <c r="C7" s="13">
+        <f>Assumptions!$C$90-C8</f>
+        <v/>
+      </c>
+      <c r="D7" s="34">
         <f>D2*D4</f>
         <v/>
       </c>
-      <c r="E7" s="32">
+      <c r="E7" s="34">
         <f>E2*E4</f>
         <v/>
       </c>
-      <c r="F7" s="32">
+      <c r="F7" s="34">
         <f>F2*F4</f>
         <v/>
       </c>
-      <c r="G7" s="32">
+      <c r="G7" s="34">
         <f>G2*G4</f>
         <v/>
       </c>
-      <c r="H7" s="32">
+      <c r="H7" s="34">
         <f>H2*H4</f>
         <v/>
       </c>
@@ -6867,29 +6954,30 @@
           <t>Export revenue (EGP mn)</t>
         </is>
       </c>
-      <c r="B8" s="20" t="n">
+      <c r="B8" s="19" t="n">
         <v>2500.155946</v>
       </c>
-      <c r="C8" s="20" t="n">
-        <v>2967.479908</v>
-      </c>
-      <c r="D8" s="32">
+      <c r="C8" s="13">
+        <f>Assumptions!$C$89</f>
+        <v/>
+      </c>
+      <c r="D8" s="34">
         <f>D3*D5*D6</f>
         <v/>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="34">
         <f>E3*E5*E6</f>
         <v/>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="34">
         <f>F3*F5*F6</f>
         <v/>
       </c>
-      <c r="G8" s="32">
+      <c r="G8" s="34">
         <f>G3*G5*G6</f>
         <v/>
       </c>
-      <c r="H8" s="32">
+      <c r="H8" s="34">
         <f>H3*H5*H6</f>
         <v/>
       </c>
@@ -6897,661 +6985,802 @@
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>Contract-manufacturing revenue (EGP mn)</t>
-        </is>
-      </c>
-      <c r="B9" s="24" t="n">
-        <v>35.835829</v>
-      </c>
-      <c r="C9" s="24" t="n">
-        <v>49.366365</v>
+          <t>Contract-manufactured packs (million)</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="n">
+        <v>8.874000000000001</v>
+      </c>
+      <c r="C9" s="33">
+        <f>Assumptions!$C$92</f>
+        <v/>
       </c>
       <c r="D9" s="33">
-        <f>Assumptions!$C$88*(1+Assumptions!C$12)</f>
+        <f>C9*(1+Assumptions!C$16)</f>
         <v/>
       </c>
       <c r="E9" s="33">
-        <f>D9*(1+Assumptions!D$12)</f>
+        <f>D9*(1+Assumptions!D$16)</f>
         <v/>
       </c>
       <c r="F9" s="33">
-        <f>E9*(1+Assumptions!E$12)</f>
+        <f>E9*(1+Assumptions!E$16)</f>
         <v/>
       </c>
       <c r="G9" s="33">
-        <f>F9*(1+Assumptions!F$12)</f>
+        <f>F9*(1+Assumptions!F$16)</f>
         <v/>
       </c>
       <c r="H9" s="33">
-        <f>G9*(1+Assumptions!G$12)</f>
+        <f>G9*(1+Assumptions!G$16)</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
+          <t>Contract-manufacturing FEE per pack (EGP)</t>
+        </is>
+      </c>
+      <c r="B10" s="5">
+        <f>35.835829/B9</f>
+        <v/>
+      </c>
+      <c r="C10" s="5">
+        <f>Assumptions!$C$93/C9</f>
+        <v/>
+      </c>
+      <c r="D10" s="5">
+        <f>C10*(1+Assumptions!C$14)</f>
+        <v/>
+      </c>
+      <c r="E10" s="5">
+        <f>D10*(1+Assumptions!D$14)</f>
+        <v/>
+      </c>
+      <c r="F10" s="5">
+        <f>E10*(1+Assumptions!E$14)</f>
+        <v/>
+      </c>
+      <c r="G10" s="5">
+        <f>F10*(1+Assumptions!F$14)</f>
+        <v/>
+      </c>
+      <c r="H10" s="5">
+        <f>G10*(1+Assumptions!G$14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Contract product resold through own channels, per pack (EGP)</t>
+        </is>
+      </c>
+      <c r="B11" s="5">
+        <f>(259.912-35.835829)/B9</f>
+        <v/>
+      </c>
+      <c r="C11" s="5">
+        <f>(Assumptions!$C$91-Assumptions!$C$93)/C9</f>
+        <v/>
+      </c>
+      <c r="D11" s="5">
+        <f>C11*(1+Assumptions!C$14)</f>
+        <v/>
+      </c>
+      <c r="E11" s="5">
+        <f>D11*(1+Assumptions!D$14)</f>
+        <v/>
+      </c>
+      <c r="F11" s="5">
+        <f>E11*(1+Assumptions!E$14)</f>
+        <v/>
+      </c>
+      <c r="G11" s="5">
+        <f>F11*(1+Assumptions!F$14)</f>
+        <v/>
+      </c>
+      <c r="H11" s="5">
+        <f>G11*(1+Assumptions!G$14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Contract-manufacturing revenue — fee (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B12" s="35">
+        <f>B9*B10</f>
+        <v/>
+      </c>
+      <c r="C12" s="35">
+        <f>C9*C10</f>
+        <v/>
+      </c>
+      <c r="D12" s="36">
+        <f>D9*D10</f>
+        <v/>
+      </c>
+      <c r="E12" s="36">
+        <f>E9*E10</f>
+        <v/>
+      </c>
+      <c r="F12" s="36">
+        <f>F9*F10</f>
+        <v/>
+      </c>
+      <c r="G12" s="36">
+        <f>G9*G10</f>
+        <v/>
+      </c>
+      <c r="H12" s="36">
+        <f>H9*H10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Contract product resold through own channels (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B13" s="35">
+        <f>B9*B11</f>
+        <v/>
+      </c>
+      <c r="C13" s="35">
+        <f>C9*C11</f>
+        <v/>
+      </c>
+      <c r="D13" s="36">
+        <f>D9*D11</f>
+        <v/>
+      </c>
+      <c r="E13" s="36">
+        <f>E9*E11</f>
+        <v/>
+      </c>
+      <c r="F13" s="36">
+        <f>F9*F11</f>
+        <v/>
+      </c>
+      <c r="G13" s="36">
+        <f>G9*G11</f>
+        <v/>
+      </c>
+      <c r="H13" s="36">
+        <f>H9*H11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
           <t>Total packs sold (million)</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B14" s="16" t="n">
         <v>307.846</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C14" s="16" t="n">
         <v>357.295</v>
       </c>
-      <c r="D10" s="5">
-        <f>D2+D3+Assumptions!$C$87</f>
-        <v/>
-      </c>
-      <c r="E10" s="5">
-        <f>E2+E3+Assumptions!$C$87</f>
-        <v/>
-      </c>
-      <c r="F10" s="5">
-        <f>F2+F3+Assumptions!$C$87</f>
-        <v/>
-      </c>
-      <c r="G10" s="5">
-        <f>G2+G3+Assumptions!$C$87</f>
-        <v/>
-      </c>
-      <c r="H10" s="5">
-        <f>H2+H3+Assumptions!$C$87</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="D14" s="5">
+        <f>D2+D3+D9</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>E2+E3+E9</f>
+        <v/>
+      </c>
+      <c r="F14" s="5">
+        <f>F2+F3+F9</f>
+        <v/>
+      </c>
+      <c r="G14" s="5">
+        <f>G2+G3+G9</f>
+        <v/>
+      </c>
+      <c r="H14" s="5">
+        <f>H2+H3+H9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>REVENUE, consolidated (EGP mn)</t>
         </is>
       </c>
-      <c r="B11" s="20" t="n">
+      <c r="B15" s="19" t="n">
         <v>7590.545643</v>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C15" s="19" t="n">
         <v>9441.379305</v>
       </c>
-      <c r="D11" s="31">
-        <f>(D7+D8+D9)*Assumptions!$C$82</f>
-        <v/>
-      </c>
-      <c r="E11" s="31">
-        <f>(E7+E8+E9)*Assumptions!$C$82</f>
-        <v/>
-      </c>
-      <c r="F11" s="31">
-        <f>(F7+F8+F9)*Assumptions!$C$82</f>
-        <v/>
-      </c>
-      <c r="G11" s="31">
-        <f>(G7+G8+G9)*Assumptions!$C$82</f>
-        <v/>
-      </c>
-      <c r="H11" s="31">
-        <f>(H7+H8+H9)*Assumptions!$C$82</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="D15" s="32">
+        <f>(D7+D8+D12+D13)*Assumptions!$C$86</f>
+        <v/>
+      </c>
+      <c r="E15" s="32">
+        <f>(E7+E8+E12+E13)*Assumptions!$C$86</f>
+        <v/>
+      </c>
+      <c r="F15" s="32">
+        <f>(F7+F8+F12+F13)*Assumptions!$C$86</f>
+        <v/>
+      </c>
+      <c r="G15" s="32">
+        <f>(G7+G8+G12+G13)*Assumptions!$C$86</f>
+        <v/>
+      </c>
+      <c r="H15" s="32">
+        <f>(H7+H8+H12+H13)*Assumptions!$C$86</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>DISCLOSED CAPACITY AND UTILISATION</t>
         </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Units produced (million)</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="n">
-        <v>2143.68</v>
-      </c>
-      <c r="C14" s="20" t="n">
-        <v>2207.95</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Available capacity (million units)</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="n">
-        <v>3383.06</v>
-      </c>
-      <c r="C15" s="20" t="n">
-        <v>3383.06</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>Capacity utilisation</t>
-        </is>
-      </c>
-      <c r="B16" s="6">
-        <f>B14/B15</f>
-        <v/>
-      </c>
-      <c r="C16" s="6">
-        <f>C14/C15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Registered preparations produced</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="n">
-        <v>401</v>
-      </c>
-      <c r="C17" s="20" t="n">
-        <v>414</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Average headcount</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="n">
-        <v>4880</v>
-      </c>
-      <c r="C18" s="20" t="n">
-        <v>4981</v>
+          <t>Units produced (million)</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="n">
+        <v>2143.68</v>
+      </c>
+      <c r="C18" s="19" t="n">
+        <v>2207.95</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>Revenue per employee (EGP)</t>
-        </is>
-      </c>
-      <c r="B19" s="13">
-        <f>B11*1000000/B18</f>
-        <v/>
-      </c>
-      <c r="C19" s="13">
-        <f>C11*1000000/C18</f>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Available capacity (million units)</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="n">
+        <v>3383.06</v>
+      </c>
+      <c r="C19" s="19" t="n">
+        <v>3383.06</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>Capacity utilisation</t>
+        </is>
+      </c>
+      <c r="B20" s="6">
+        <f>B18/B19</f>
+        <v/>
+      </c>
+      <c r="C20" s="6">
+        <f>C18/C19</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>COST ESCALATOR INDEX (base FY2025 = 1.000)</t>
-        </is>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Registered preparations produced</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="n">
+        <v>401</v>
+      </c>
+      <c r="C21" s="19" t="n">
+        <v>414</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Imported active ingredients</t>
-        </is>
-      </c>
-      <c r="D22" s="30">
-        <f>((1+Assumptions!$C$21)*(Segments!D6/Assumptions!$C$89))</f>
-        <v/>
-      </c>
-      <c r="E22" s="30">
-        <f>D22*((1+Assumptions!$C$21)*(Segments!E6/Segments!D6))</f>
-        <v/>
-      </c>
-      <c r="F22" s="30">
-        <f>E22*((1+Assumptions!$C$21)*(Segments!F6/Segments!E6))</f>
-        <v/>
-      </c>
-      <c r="G22" s="30">
-        <f>F22*((1+Assumptions!$C$21)*(Segments!G6/Segments!F6))</f>
-        <v/>
-      </c>
-      <c r="H22" s="30">
-        <f>G22*((1+Assumptions!$C$21)*(Segments!H6/Segments!G6))</f>
-        <v/>
+          <t>Average headcount</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="n">
+        <v>4880</v>
+      </c>
+      <c r="C22" s="19" t="n">
+        <v>4981</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Packaging materials</t>
-        </is>
-      </c>
-      <c r="D23" s="30">
-        <f>(Assumptions!$C$22*(1+Assumptions!$C$21)*(Segments!D6/Assumptions!$C$89)+(1-Assumptions!$C$22)*(1+Assumptions!C$25))</f>
-        <v/>
-      </c>
-      <c r="E23" s="30">
-        <f>D23*(Assumptions!$C$22*(1+Assumptions!$C$21)*(Segments!E6/Segments!D6)+(1-Assumptions!$C$22)*(1+Assumptions!D$25))</f>
-        <v/>
-      </c>
-      <c r="F23" s="30">
-        <f>E23*(Assumptions!$C$22*(1+Assumptions!$C$21)*(Segments!F6/Segments!E6)+(1-Assumptions!$C$22)*(1+Assumptions!E$25))</f>
-        <v/>
-      </c>
-      <c r="G23" s="30">
-        <f>F23*(Assumptions!$C$22*(1+Assumptions!$C$21)*(Segments!G6/Segments!F6)+(1-Assumptions!$C$22)*(1+Assumptions!F$25))</f>
-        <v/>
-      </c>
-      <c r="H23" s="30">
-        <f>G23*(Assumptions!$C$22*(1+Assumptions!$C$21)*(Segments!H6/Segments!G6)+(1-Assumptions!$C$22)*(1+Assumptions!G$25))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Labour</t>
-        </is>
-      </c>
-      <c r="D24" s="30">
-        <f>(1+Assumptions!C$23)</f>
-        <v/>
-      </c>
-      <c r="E24" s="30">
-        <f>D24*(1+Assumptions!D$23)</f>
-        <v/>
-      </c>
-      <c r="F24" s="30">
-        <f>E24*(1+Assumptions!E$23)</f>
-        <v/>
-      </c>
-      <c r="G24" s="30">
-        <f>F24*(1+Assumptions!F$23)</f>
-        <v/>
-      </c>
-      <c r="H24" s="30">
-        <f>G24*(1+Assumptions!G$23)</f>
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Revenue per employee (EGP)</t>
+        </is>
+      </c>
+      <c r="B23" s="13">
+        <f>B15*1000000/B22</f>
+        <v/>
+      </c>
+      <c r="C23" s="13">
+        <f>C15*1000000/C22</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>Energy and utilities</t>
-        </is>
-      </c>
-      <c r="D25" s="30">
-        <f>(1+Assumptions!C$24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="30">
-        <f>D25*(1+Assumptions!D$24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="30">
-        <f>E25*(1+Assumptions!E$24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="30">
-        <f>F25*(1+Assumptions!F$24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="30">
-        <f>G25*(1+Assumptions!G$24)</f>
-        <v/>
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>COST ESCALATOR INDEX (base FY2025 = 1.000)</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
+          <t>Imported active ingredients</t>
+        </is>
+      </c>
+      <c r="D26" s="31">
+        <f>((1+Assumptions!$C$25)*(Segments!D6/Assumptions!$C$94))</f>
+        <v/>
+      </c>
+      <c r="E26" s="31">
+        <f>D26*((1+Assumptions!$C$25)*(Segments!E6/Segments!D6))</f>
+        <v/>
+      </c>
+      <c r="F26" s="31">
+        <f>E26*((1+Assumptions!$C$25)*(Segments!F6/Segments!E6))</f>
+        <v/>
+      </c>
+      <c r="G26" s="31">
+        <f>F26*((1+Assumptions!$C$25)*(Segments!G6/Segments!F6))</f>
+        <v/>
+      </c>
+      <c r="H26" s="31">
+        <f>G26*((1+Assumptions!$C$25)*(Segments!H6/Segments!G6))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Packaging materials</t>
+        </is>
+      </c>
+      <c r="D27" s="31">
+        <f>(Assumptions!$C$26*(1+Assumptions!$C$25)*(Segments!D6/Assumptions!$C$94)+(1-Assumptions!$C$26)*(1+Assumptions!C$29))</f>
+        <v/>
+      </c>
+      <c r="E27" s="31">
+        <f>D27*(Assumptions!$C$26*(1+Assumptions!$C$25)*(Segments!E6/Segments!D6)+(1-Assumptions!$C$26)*(1+Assumptions!D$29))</f>
+        <v/>
+      </c>
+      <c r="F27" s="31">
+        <f>E27*(Assumptions!$C$26*(1+Assumptions!$C$25)*(Segments!F6/Segments!E6)+(1-Assumptions!$C$26)*(1+Assumptions!E$29))</f>
+        <v/>
+      </c>
+      <c r="G27" s="31">
+        <f>F27*(Assumptions!$C$26*(1+Assumptions!$C$25)*(Segments!G6/Segments!F6)+(1-Assumptions!$C$26)*(1+Assumptions!F$29))</f>
+        <v/>
+      </c>
+      <c r="H27" s="31">
+        <f>G27*(Assumptions!$C$26*(1+Assumptions!$C$25)*(Segments!H6/Segments!G6)+(1-Assumptions!$C$26)*(1+Assumptions!G$29))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Labour</t>
+        </is>
+      </c>
+      <c r="D28" s="31">
+        <f>(1+Assumptions!C$27)</f>
+        <v/>
+      </c>
+      <c r="E28" s="31">
+        <f>D28*(1+Assumptions!D$27)</f>
+        <v/>
+      </c>
+      <c r="F28" s="31">
+        <f>E28*(1+Assumptions!E$27)</f>
+        <v/>
+      </c>
+      <c r="G28" s="31">
+        <f>F28*(1+Assumptions!F$27)</f>
+        <v/>
+      </c>
+      <c r="H28" s="31">
+        <f>G28*(1+Assumptions!G$27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Energy and utilities</t>
+        </is>
+      </c>
+      <c r="D29" s="31">
+        <f>(1+Assumptions!C$28)</f>
+        <v/>
+      </c>
+      <c r="E29" s="31">
+        <f>D29*(1+Assumptions!D$28)</f>
+        <v/>
+      </c>
+      <c r="F29" s="31">
+        <f>E29*(1+Assumptions!E$28)</f>
+        <v/>
+      </c>
+      <c r="G29" s="31">
+        <f>F29*(1+Assumptions!F$28)</f>
+        <v/>
+      </c>
+      <c r="H29" s="31">
+        <f>G29*(1+Assumptions!G$28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
           <t>Other consumables and services</t>
         </is>
       </c>
-      <c r="D26" s="30">
-        <f>(1+Assumptions!C$25)</f>
-        <v/>
-      </c>
-      <c r="E26" s="30">
-        <f>D26*(1+Assumptions!D$25)</f>
-        <v/>
-      </c>
-      <c r="F26" s="30">
-        <f>E26*(1+Assumptions!E$25)</f>
-        <v/>
-      </c>
-      <c r="G26" s="30">
-        <f>F26*(1+Assumptions!F$25)</f>
-        <v/>
-      </c>
-      <c r="H26" s="30">
-        <f>G26*(1+Assumptions!G$25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="D30" s="31">
+        <f>(1+Assumptions!C$29)</f>
+        <v/>
+      </c>
+      <c r="E30" s="31">
+        <f>D30*(1+Assumptions!D$29)</f>
+        <v/>
+      </c>
+      <c r="F30" s="31">
+        <f>E30*(1+Assumptions!E$29)</f>
+        <v/>
+      </c>
+      <c r="G30" s="31">
+        <f>F30*(1+Assumptions!F$29)</f>
+        <v/>
+      </c>
+      <c r="H30" s="31">
+        <f>G30*(1+Assumptions!G$29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>Blended cash-cost index</t>
         </is>
       </c>
-      <c r="D27" s="34">
-        <f>(Assumptions!$C$15*D22+Assumptions!$C$16*D23+Assumptions!$C$17*D24+Assumptions!$C$18*D25+Assumptions!$C$19*D26)/(Assumptions!$C$15+Assumptions!$C$16+Assumptions!$C$17+Assumptions!$C$18+Assumptions!$C$19)</f>
-        <v/>
-      </c>
-      <c r="E27" s="34">
-        <f>(Assumptions!$C$15*E22+Assumptions!$C$16*E23+Assumptions!$C$17*E24+Assumptions!$C$18*E25+Assumptions!$C$19*E26)/(Assumptions!$C$15+Assumptions!$C$16+Assumptions!$C$17+Assumptions!$C$18+Assumptions!$C$19)</f>
-        <v/>
-      </c>
-      <c r="F27" s="34">
-        <f>(Assumptions!$C$15*F22+Assumptions!$C$16*F23+Assumptions!$C$17*F24+Assumptions!$C$18*F25+Assumptions!$C$19*F26)/(Assumptions!$C$15+Assumptions!$C$16+Assumptions!$C$17+Assumptions!$C$18+Assumptions!$C$19)</f>
-        <v/>
-      </c>
-      <c r="G27" s="34">
-        <f>(Assumptions!$C$15*G22+Assumptions!$C$16*G23+Assumptions!$C$17*G24+Assumptions!$C$18*G25+Assumptions!$C$19*G26)/(Assumptions!$C$15+Assumptions!$C$16+Assumptions!$C$17+Assumptions!$C$18+Assumptions!$C$19)</f>
-        <v/>
-      </c>
-      <c r="H27" s="34">
-        <f>(Assumptions!$C$15*H22+Assumptions!$C$16*H23+Assumptions!$C$17*H24+Assumptions!$C$18*H25+Assumptions!$C$19*H26)/(Assumptions!$C$15+Assumptions!$C$16+Assumptions!$C$17+Assumptions!$C$18+Assumptions!$C$19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="D31" s="37">
+        <f>(Assumptions!$C$19*D26+Assumptions!$C$20*D27+Assumptions!$C$21*D28+Assumptions!$C$22*D29+Assumptions!$C$23*D30)/(Assumptions!$C$19+Assumptions!$C$20+Assumptions!$C$21+Assumptions!$C$22+Assumptions!$C$23)</f>
+        <v/>
+      </c>
+      <c r="E31" s="37">
+        <f>(Assumptions!$C$19*E26+Assumptions!$C$20*E27+Assumptions!$C$21*E28+Assumptions!$C$22*E29+Assumptions!$C$23*E30)/(Assumptions!$C$19+Assumptions!$C$20+Assumptions!$C$21+Assumptions!$C$22+Assumptions!$C$23)</f>
+        <v/>
+      </c>
+      <c r="F31" s="37">
+        <f>(Assumptions!$C$19*F26+Assumptions!$C$20*F27+Assumptions!$C$21*F28+Assumptions!$C$22*F29+Assumptions!$C$23*F30)/(Assumptions!$C$19+Assumptions!$C$20+Assumptions!$C$21+Assumptions!$C$22+Assumptions!$C$23)</f>
+        <v/>
+      </c>
+      <c r="G31" s="37">
+        <f>(Assumptions!$C$19*G26+Assumptions!$C$20*G27+Assumptions!$C$21*G28+Assumptions!$C$22*G29+Assumptions!$C$23*G30)/(Assumptions!$C$19+Assumptions!$C$20+Assumptions!$C$21+Assumptions!$C$22+Assumptions!$C$23)</f>
+        <v/>
+      </c>
+      <c r="H31" s="37">
+        <f>(Assumptions!$C$19*H26+Assumptions!$C$20*H27+Assumptions!$C$21*H28+Assumptions!$C$22*H29+Assumptions!$C$23*H30)/(Assumptions!$C$19+Assumptions!$C$20+Assumptions!$C$21+Assumptions!$C$22+Assumptions!$C$23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>Cash cost per pack (EGP)</t>
         </is>
       </c>
-      <c r="D28" s="12">
-        <f>Assumptions!$C$81*D27</f>
-        <v/>
-      </c>
-      <c r="E28" s="12">
-        <f>Assumptions!$C$81*E27</f>
-        <v/>
-      </c>
-      <c r="F28" s="12">
-        <f>Assumptions!$C$81*F27</f>
-        <v/>
-      </c>
-      <c r="G28" s="12">
-        <f>Assumptions!$C$81*G27</f>
-        <v/>
-      </c>
-      <c r="H28" s="12">
-        <f>Assumptions!$C$81*H27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="D32" s="12">
+        <f>Assumptions!$C$85*D31</f>
+        <v/>
+      </c>
+      <c r="E32" s="12">
+        <f>Assumptions!$C$85*E31</f>
+        <v/>
+      </c>
+      <c r="F32" s="12">
+        <f>Assumptions!$C$85*F31</f>
+        <v/>
+      </c>
+      <c r="G32" s="12">
+        <f>Assumptions!$C$85*G31</f>
+        <v/>
+      </c>
+      <c r="H32" s="12">
+        <f>Assumptions!$C$85*H31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>PROPERTY ROLL-FORWARD (EGP mn)</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Opening property, plant and equipment</t>
         </is>
       </c>
-      <c r="D31" s="13">
-        <f>Assumptions!$C$63</f>
-        <v/>
-      </c>
-      <c r="E31" s="13">
-        <f>D35</f>
-        <v/>
-      </c>
-      <c r="F31" s="13">
-        <f>E35</f>
-        <v/>
-      </c>
-      <c r="G31" s="13">
-        <f>F35</f>
-        <v/>
-      </c>
-      <c r="H31" s="13">
-        <f>G35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>Transfers in from construction</t>
-        </is>
-      </c>
-      <c r="D32" s="13">
-        <f>Assumptions!C$33</f>
-        <v/>
-      </c>
-      <c r="E32" s="13">
-        <f>Assumptions!D$33</f>
-        <v/>
-      </c>
-      <c r="F32" s="13">
-        <f>Assumptions!E$33</f>
-        <v/>
-      </c>
-      <c r="G32" s="13">
-        <f>Assumptions!F$33</f>
-        <v/>
-      </c>
-      <c r="H32" s="13">
-        <f>Assumptions!G$33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>Depreciation charge</t>
-        </is>
-      </c>
-      <c r="D33" s="13">
-        <f>-Assumptions!$C$34*(D31+D32/2)</f>
-        <v/>
-      </c>
-      <c r="E33" s="13">
-        <f>-Assumptions!$C$34*(E31+E32/2)</f>
-        <v/>
-      </c>
-      <c r="F33" s="13">
-        <f>-Assumptions!$C$34*(F31+F32/2)</f>
-        <v/>
-      </c>
-      <c r="G33" s="13">
-        <f>-Assumptions!$C$34*(G31+G32/2)</f>
-        <v/>
-      </c>
-      <c r="H33" s="13">
-        <f>-Assumptions!$C$34*(H31+H32/2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>Amortisation of right-of-use and intangible assets</t>
-        </is>
-      </c>
-      <c r="D34" s="33">
-        <f>-Assumptions!$C$79</f>
-        <v/>
-      </c>
-      <c r="E34" s="33">
-        <f>-Assumptions!$C$79</f>
-        <v/>
-      </c>
-      <c r="F34" s="33">
-        <f>-Assumptions!$C$79</f>
-        <v/>
-      </c>
-      <c r="G34" s="33">
-        <f>-Assumptions!$C$79</f>
-        <v/>
-      </c>
-      <c r="H34" s="33">
-        <f>-Assumptions!$C$79</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>Closing property, plant and equipment</t>
-        </is>
-      </c>
-      <c r="D35" s="31">
-        <f>D31+D32+D33</f>
-        <v/>
-      </c>
-      <c r="E35" s="31">
-        <f>E31+E32+E33</f>
-        <v/>
-      </c>
-      <c r="F35" s="31">
-        <f>F31+F32+F33</f>
-        <v/>
-      </c>
-      <c r="G35" s="31">
-        <f>G31+G32+G33</f>
-        <v/>
-      </c>
-      <c r="H35" s="31">
-        <f>H31+H32+H33</f>
+      <c r="D35" s="13">
+        <f>Assumptions!$C$67</f>
+        <v/>
+      </c>
+      <c r="E35" s="13">
+        <f>D39</f>
+        <v/>
+      </c>
+      <c r="F35" s="13">
+        <f>E39</f>
+        <v/>
+      </c>
+      <c r="G35" s="13">
+        <f>F39</f>
+        <v/>
+      </c>
+      <c r="H35" s="13">
+        <f>G39</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Capital expenditure</t>
+          <t>Transfers in from construction</t>
         </is>
       </c>
       <c r="D36" s="13">
-        <f>D11*Assumptions!C$32</f>
+        <f>Assumptions!C$37</f>
         <v/>
       </c>
       <c r="E36" s="13">
-        <f>E11*Assumptions!D$32</f>
+        <f>Assumptions!D$37</f>
         <v/>
       </c>
       <c r="F36" s="13">
-        <f>F11*Assumptions!E$32</f>
+        <f>Assumptions!E$37</f>
         <v/>
       </c>
       <c r="G36" s="13">
-        <f>G11*Assumptions!F$32</f>
+        <f>Assumptions!F$37</f>
         <v/>
       </c>
       <c r="H36" s="13">
-        <f>H11*Assumptions!G$32</f>
+        <f>Assumptions!G$37</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>Total depreciation and amortisation</t>
-        </is>
-      </c>
-      <c r="D37" s="27">
-        <f>-D33-D34</f>
-        <v/>
-      </c>
-      <c r="E37" s="27">
-        <f>-E33-E34</f>
-        <v/>
-      </c>
-      <c r="F37" s="27">
-        <f>-F33-F34</f>
-        <v/>
-      </c>
-      <c r="G37" s="27">
-        <f>-G33-G34</f>
-        <v/>
-      </c>
-      <c r="H37" s="27">
-        <f>-H33-H34</f>
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Depreciation charge</t>
+        </is>
+      </c>
+      <c r="D37" s="13">
+        <f>-Assumptions!$C$38*(D35+D36/2)</f>
+        <v/>
+      </c>
+      <c r="E37" s="13">
+        <f>-Assumptions!$C$38*(E35+E36/2)</f>
+        <v/>
+      </c>
+      <c r="F37" s="13">
+        <f>-Assumptions!$C$38*(F35+F36/2)</f>
+        <v/>
+      </c>
+      <c r="G37" s="13">
+        <f>-Assumptions!$C$38*(G35+G36/2)</f>
+        <v/>
+      </c>
+      <c r="H37" s="13">
+        <f>-Assumptions!$C$38*(H35+H36/2)</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
+          <t>Amortisation of right-of-use and intangible assets</t>
+        </is>
+      </c>
+      <c r="D38" s="35">
+        <f>-Assumptions!$C$83</f>
+        <v/>
+      </c>
+      <c r="E38" s="35">
+        <f>-Assumptions!$C$83</f>
+        <v/>
+      </c>
+      <c r="F38" s="35">
+        <f>-Assumptions!$C$83</f>
+        <v/>
+      </c>
+      <c r="G38" s="35">
+        <f>-Assumptions!$C$83</f>
+        <v/>
+      </c>
+      <c r="H38" s="35">
+        <f>-Assumptions!$C$83</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Closing property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="D39" s="32">
+        <f>D35+D36+D37</f>
+        <v/>
+      </c>
+      <c r="E39" s="32">
+        <f>E35+E36+E37</f>
+        <v/>
+      </c>
+      <c r="F39" s="32">
+        <f>F35+F36+F37</f>
+        <v/>
+      </c>
+      <c r="G39" s="32">
+        <f>G35+G36+G37</f>
+        <v/>
+      </c>
+      <c r="H39" s="32">
+        <f>H35+H36+H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Capital expenditure</t>
+        </is>
+      </c>
+      <c r="D40" s="13">
+        <f>D15*Assumptions!C$36</f>
+        <v/>
+      </c>
+      <c r="E40" s="13">
+        <f>E15*Assumptions!D$36</f>
+        <v/>
+      </c>
+      <c r="F40" s="13">
+        <f>F15*Assumptions!E$36</f>
+        <v/>
+      </c>
+      <c r="G40" s="13">
+        <f>G15*Assumptions!F$36</f>
+        <v/>
+      </c>
+      <c r="H40" s="13">
+        <f>H15*Assumptions!G$36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>Total depreciation and amortisation</t>
+        </is>
+      </c>
+      <c r="D41" s="28">
+        <f>-D37-D38</f>
+        <v/>
+      </c>
+      <c r="E41" s="28">
+        <f>-E37-E38</f>
+        <v/>
+      </c>
+      <c r="F41" s="28">
+        <f>-F37-F38</f>
+        <v/>
+      </c>
+      <c r="G41" s="28">
+        <f>-G37-G38</f>
+        <v/>
+      </c>
+      <c r="H41" s="28">
+        <f>-H37-H38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
           <t>Opening construction balance</t>
         </is>
       </c>
-      <c r="D38" s="13">
-        <f>Assumptions!$C$64</f>
-        <v/>
-      </c>
-      <c r="E38" s="13">
-        <f>D40</f>
-        <v/>
-      </c>
-      <c r="F38" s="13">
-        <f>E40</f>
-        <v/>
-      </c>
-      <c r="G38" s="13">
-        <f>F40</f>
-        <v/>
-      </c>
-      <c r="H38" s="13">
-        <f>G40</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="D42" s="13">
+        <f>Assumptions!$C$68</f>
+        <v/>
+      </c>
+      <c r="E42" s="13">
+        <f>D44</f>
+        <v/>
+      </c>
+      <c r="F42" s="13">
+        <f>E44</f>
+        <v/>
+      </c>
+      <c r="G42" s="13">
+        <f>F44</f>
+        <v/>
+      </c>
+      <c r="H42" s="13">
+        <f>G44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>Additions less transfers out</t>
         </is>
       </c>
-      <c r="D39" s="13">
-        <f>D36-D32</f>
-        <v/>
-      </c>
-      <c r="E39" s="13">
-        <f>E36-E32</f>
-        <v/>
-      </c>
-      <c r="F39" s="13">
-        <f>F36-F32</f>
-        <v/>
-      </c>
-      <c r="G39" s="13">
-        <f>G36-G32</f>
-        <v/>
-      </c>
-      <c r="H39" s="13">
-        <f>H36-H32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="D43" s="13">
+        <f>D40-D36</f>
+        <v/>
+      </c>
+      <c r="E43" s="13">
+        <f>E40-E36</f>
+        <v/>
+      </c>
+      <c r="F43" s="13">
+        <f>F40-F36</f>
+        <v/>
+      </c>
+      <c r="G43" s="13">
+        <f>G40-G36</f>
+        <v/>
+      </c>
+      <c r="H43" s="13">
+        <f>H40-H36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>Closing construction balance</t>
         </is>
       </c>
-      <c r="D40" s="31">
-        <f>D38+D39</f>
-        <v/>
-      </c>
-      <c r="E40" s="31">
-        <f>E38+E39</f>
-        <v/>
-      </c>
-      <c r="F40" s="31">
-        <f>F38+F39</f>
-        <v/>
-      </c>
-      <c r="G40" s="31">
-        <f>G38+G39</f>
-        <v/>
-      </c>
-      <c r="H40" s="31">
-        <f>H38+H39</f>
+      <c r="D44" s="32">
+        <f>D42+D43</f>
+        <v/>
+      </c>
+      <c r="E44" s="32">
+        <f>E42+E43</f>
+        <v/>
+      </c>
+      <c r="F44" s="32">
+        <f>F42+F43</f>
+        <v/>
+      </c>
+      <c r="G44" s="32">
+        <f>G42+G43</f>
+        <v/>
+      </c>
+      <c r="H44" s="32">
+        <f>H42+H43</f>
         <v/>
       </c>
     </row>
@@ -7566,7 +7795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -7643,7 +7872,7 @@
           <t>Sustainable return — the mean of the last three forecast years</t>
         </is>
       </c>
-      <c r="B6" s="35">
+      <c r="B6" s="38">
         <f>AVERAGE(B3:B5)</f>
         <v/>
       </c>
@@ -7660,7 +7889,7 @@
         </is>
       </c>
       <c r="B7" s="6">
-        <f>1-Assumptions!$C$58/B6</f>
+        <f>1-Assumptions!$C$62/B6</f>
         <v/>
       </c>
     </row>
@@ -7682,7 +7911,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>((DCF!B35-Assumptions!C$51)*(1-Assumptions!$C$6)+Assumptions!$C$59-18.0)/Assumptions!$C$4</f>
+        <f>((DCF!B35-Assumptions!C$55)*(1-Assumptions!$C$10)+Assumptions!$C$63-18.0)/Assumptions!$C$8</f>
         <v/>
       </c>
     </row>
@@ -7709,7 +7938,7 @@
         </is>
       </c>
       <c r="B12" s="12">
-        <f>Assumptions!$C$72/Assumptions!$C$4</f>
+        <f>Assumptions!$C$76/Assumptions!$C$8</f>
         <v/>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -7718,301 +7947,313 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Justified forward multiple from this model, on FY2026E earnings</t>
-        </is>
-      </c>
-      <c r="B13" s="36">
-        <f>B7/(Assumptions!$C$104-Assumptions!$C$58)</f>
-        <v/>
-      </c>
-      <c r="C13" s="5">
-        <f>B13*B11</f>
-        <v/>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>A FORWARD multiple, applied to FORWARD earnings — built from this model's own sustainable return and perpetual cost of equity</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>The company's own four-year mean multiple, on trailing earnings</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="n">
-        <v>6.572199327377573</v>
-      </c>
-      <c r="C14" s="5">
-        <f>B14*B12</f>
-        <v/>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>A TRAILING multiple, applied to TRAILING earnings — year-end closes against audited attributable profit, each year on its own weighted-average share count</t>
-        </is>
-      </c>
-    </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Struck peer reference, cost-of-equity adjusted, on trailing earnings</t>
-        </is>
-      </c>
-      <c r="B15" s="36">
-        <f>Assumptions!$C$61*(0.10-Assumptions!$C$58)/(Assumptions!$C$104-Assumptions!$C$58)</f>
-        <v/>
-      </c>
-      <c r="C15" s="5">
-        <f>B15*B12</f>
-        <v/>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>A TRAILING multiple, applied to TRAILING earnings. The midpoint of the two disclosed observations, not a median of a peer set; those companies face a cost of equity near 10%, not this one</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>AVERAGE OF THE THREE — the relative lens</t>
-        </is>
-      </c>
-      <c r="B16" s="37">
-        <f>AVERAGE(B13:B15)</f>
-        <v/>
-      </c>
-      <c r="C16" s="9">
-        <f>AVERAGE(C13:C15)</f>
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>THE COMPANY'S OWN TRADED MULTIPLE HISTORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="39" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B16" s="40" t="inlineStr">
+        <is>
+          <t>Year-end close</t>
+        </is>
+      </c>
+      <c r="C16" s="40" t="inlineStr">
+        <is>
+          <t>Attributable EPS</t>
+        </is>
+      </c>
+      <c r="D16" s="40" t="inlineStr">
+        <is>
+          <t>Price / earnings</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="n">
+        <v>28.08</v>
+      </c>
+      <c r="C17" s="5">
+        <f>Assumptions!$C$7/Assumptions!$C$4</f>
+        <v/>
+      </c>
+      <c r="D17" s="41">
+        <f>B17/C17</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>THE COMPANY'S OWN TRADED MULTIPLE HISTORY</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="38" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B19" s="39" t="inlineStr">
-        <is>
-          <t>Year-end close</t>
-        </is>
-      </c>
-      <c r="C19" s="39" t="inlineStr">
-        <is>
-          <t>Attributable EPS</t>
-        </is>
-      </c>
-      <c r="D19" s="39" t="inlineStr">
-        <is>
-          <t>Price / earnings</t>
-        </is>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="C18" s="5">
+        <f>'Income Statement'!B26/Assumptions!$C$5</f>
+        <v/>
+      </c>
+      <c r="D18" s="41">
+        <f>B18/C18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="n">
+        <v>45.91</v>
+      </c>
+      <c r="C19" s="5">
+        <f>'Income Statement'!C26/Assumptions!$C$5</f>
+        <v/>
+      </c>
+      <c r="D19" s="41">
+        <f>B19/C19</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>28.08</v>
-      </c>
-      <c r="C20" s="16" t="n">
-        <v>5.919508553450875</v>
-      </c>
-      <c r="D20" s="14">
+        <v>77.5</v>
+      </c>
+      <c r="C20" s="5">
+        <f>'Income Statement'!D26/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="D20" s="41">
         <f>B20/C20</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="C21" s="16" t="n">
-        <v>5.527972632990657</v>
-      </c>
-      <c r="D21" s="14">
-        <f>B21/C21</f>
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>Four-year mean</t>
+        </is>
+      </c>
+      <c r="D21" s="42">
+        <f>AVERAGE(D17:D20)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="n">
-        <v>45.91</v>
-      </c>
-      <c r="C22" s="16" t="n">
-        <v>7.365880505459453</v>
-      </c>
-      <c r="D22" s="14">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>Trailing multiple today — on the share count IN ISSUE</t>
+        </is>
+      </c>
+      <c r="B22" s="5">
+        <f>Assumptions!$C$3</f>
+        <v/>
+      </c>
+      <c r="C22" s="5">
+        <f>B12</f>
+        <v/>
+      </c>
+      <c r="D22" s="42">
         <f>B22/C22</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="C23" s="16" t="n">
-        <v>8.898241448018748</v>
-      </c>
-      <c r="D23" s="14">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Trailing multiple today — on the AUDITED WEIGHTED-AVERAGE count for FY2025</t>
+        </is>
+      </c>
+      <c r="B23" s="5">
+        <f>Assumptions!$C$3</f>
+        <v/>
+      </c>
+      <c r="C23" s="5">
+        <f>Assumptions!$C$76/162.016024</f>
+        <v/>
+      </c>
+      <c r="D23" s="42">
         <f>B23/C23</f>
         <v/>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>Four-year mean</t>
-        </is>
-      </c>
-      <c r="D24" s="40">
-        <f>AVERAGE(D20:D23)</f>
-        <v/>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>TWO SHARE COUNTS, BOTH PUBLISHED. The capital increase from 148.755750 to 168.755750 million shares completed during FY2025, so that year has a weighted-average count of 162.016024 million and a closing count of 168.755750 million. Both readings of the trailing multiple are legitimate; neither is stated alone.</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>Trailing multiple today — on the share count IN ISSUE</t>
-        </is>
-      </c>
-      <c r="B25" s="5">
-        <f>Assumptions!$C$3</f>
-        <v/>
-      </c>
-      <c r="C25" s="5">
-        <f>B12</f>
-        <v/>
-      </c>
-      <c r="D25" s="41">
-        <f>B25/C25</f>
-        <v/>
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>THE THREE MULTIPLES, EACH ON THE EARNINGS OF ITS OWN PERIOD</t>
+        </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>Trailing multiple today — on the AUDITED WEIGHTED-AVERAGE count for FY2025</t>
-        </is>
-      </c>
-      <c r="B26" s="5">
-        <f>Assumptions!$C$3</f>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Justified forward multiple from this model, on FY2026E earnings</t>
+        </is>
+      </c>
+      <c r="B26" s="41">
+        <f>B7/(Assumptions!$C$109-Assumptions!$C$62)</f>
         <v/>
       </c>
       <c r="C26" s="5">
-        <f>Assumptions!$C$72/162.016024</f>
-        <v/>
-      </c>
-      <c r="D26" s="41">
-        <f>B26/C26</f>
-        <v/>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>TWO SHARE COUNTS, BOTH PUBLISHED. The capital increase from 148.755750 to 168.755750 million shares completed during FY2025, so that year has a weighted-average count of 162.016024 million and a closing count of 168.755750 million. Both readings of the trailing multiple are legitimate; neither is stated alone.</t>
+        <f>B26*B11</f>
+        <v/>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>A FORWARD multiple, applied to FORWARD earnings — built from this model's own sustainable return and perpetual cost of equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>The company's own four-year mean multiple, on trailing earnings</t>
+        </is>
+      </c>
+      <c r="B27" s="41">
+        <f>D21</f>
+        <v/>
+      </c>
+      <c r="C27" s="5">
+        <f>B27*B12</f>
+        <v/>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>A TRAILING multiple, applied to TRAILING earnings — year-end closes against audited attributable profit, each year on its own weighted-average share count</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Struck peer reference, cost-of-equity adjusted, on trailing earnings</t>
+        </is>
+      </c>
+      <c r="B28" s="41">
+        <f>Assumptions!$C$65*(0.10-Assumptions!$C$62)/(Assumptions!$C$109-Assumptions!$C$62)</f>
+        <v/>
+      </c>
+      <c r="C28" s="5">
+        <f>B28*B12</f>
+        <v/>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>A TRAILING multiple, applied to TRAILING earnings. The midpoint of the two disclosed observations, not a median of a peer set; those companies face a cost of equity near 10%, not this one</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>AVERAGE OF THE THREE — the relative lens</t>
+        </is>
+      </c>
+      <c r="B29" s="43">
+        <f>AVERAGE(B26:B28)</f>
+        <v/>
+      </c>
+      <c r="C29" s="9">
+        <f>AVERAGE(C26:C28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>NORMALISED EARNINGS POWER</t>
         </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Three-year average operating margin</t>
-        </is>
-      </c>
-      <c r="B29" s="6">
-        <f>AVERAGE('Income Statement'!B15/'Income Statement'!B2,'Income Statement'!C15/'Income Statement'!C2,'Income Statement'!D15/'Income Statement'!D2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>FY2027E revenue</t>
-        </is>
-      </c>
-      <c r="B30" s="13">
-        <f>'Income Statement'!F2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>Normalised operating profit</t>
-        </is>
-      </c>
-      <c r="B31" s="13">
-        <f>B29*B30</f>
-        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Normalised earnings per share</t>
-        </is>
-      </c>
-      <c r="B32" s="5">
-        <f>((B31-2.0-Assumptions!D$51)*(1-Assumptions!$C$6)+Assumptions!$C$59-18.0)/Assumptions!$C$4</f>
+          <t>Three-year average operating margin</t>
+        </is>
+      </c>
+      <c r="B32" s="6">
+        <f>AVERAGE('Income Statement'!B15/'Income Statement'!B2,'Income Statement'!C15/'Income Statement'!C2,'Income Statement'!D15/'Income Statement'!D2)</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
+          <t>FY2027E revenue</t>
+        </is>
+      </c>
+      <c r="B33" s="13">
+        <f>'Income Statement'!F2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Normalised operating profit</t>
+        </is>
+      </c>
+      <c r="B34" s="13">
+        <f>B32*B33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Normalised earnings per share</t>
+        </is>
+      </c>
+      <c r="B35" s="5">
+        <f>((B34-2.0-Assumptions!D$55)*(1-Assumptions!$C$10)+Assumptions!$C$63-18.0)/Assumptions!$C$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
           <t>Payout the growth rate permits</t>
         </is>
       </c>
-      <c r="B33" s="6">
-        <f>1-Assumptions!$C$58/0.21896499</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="B36" s="6">
+        <f>1-Assumptions!$C$62/0.21812391</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>NORMALISED EARNINGS POWER VALUE</t>
         </is>
       </c>
-      <c r="B34" s="9">
-        <f>B32*B33/(Assumptions!$C$104-Assumptions!$C$58)</f>
+      <c r="B37" s="9">
+        <f>B35*B36/(Assumptions!$C$109-Assumptions!$C$62)</f>
         <v/>
       </c>
     </row>
@@ -8109,23 +8350,23 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B3" s="27">
+      <c r="B3" s="28">
         <f>'Income Statement'!E17</f>
         <v/>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="28">
         <f>'Income Statement'!F17</f>
         <v/>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="28">
         <f>'Income Statement'!G17</f>
         <v/>
       </c>
-      <c r="E3" s="27">
+      <c r="E3" s="28">
         <f>'Income Statement'!H17</f>
         <v/>
       </c>
-      <c r="F3" s="27">
+      <c r="F3" s="28">
         <f>'Income Statement'!I17</f>
         <v/>
       </c>
@@ -8164,23 +8405,23 @@
         </is>
       </c>
       <c r="B5" s="13">
-        <f>-Segments!D37</f>
+        <f>-Segments!D41</f>
         <v/>
       </c>
       <c r="C5" s="13">
-        <f>-Segments!E37</f>
+        <f>-Segments!E41</f>
         <v/>
       </c>
       <c r="D5" s="13">
-        <f>-Segments!F37</f>
+        <f>-Segments!F41</f>
         <v/>
       </c>
       <c r="E5" s="13">
-        <f>-Segments!G37</f>
+        <f>-Segments!G41</f>
         <v/>
       </c>
       <c r="F5" s="13">
-        <f>-Segments!H37</f>
+        <f>-Segments!H41</f>
         <v/>
       </c>
     </row>
@@ -8190,23 +8431,23 @@
           <t>EBIT = EBITDA less depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="28">
         <f>B3+B5</f>
         <v/>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="28">
         <f>C3+C5</f>
         <v/>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="28">
         <f>D3+D5</f>
         <v/>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="28">
         <f>E3+E5</f>
         <v/>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="28">
         <f>F3+F5</f>
         <v/>
       </c>
@@ -8218,23 +8459,23 @@
         </is>
       </c>
       <c r="B7" s="15">
-        <f>Assumptions!$C$6</f>
+        <f>Assumptions!$C$10</f>
         <v/>
       </c>
       <c r="C7" s="15">
-        <f>Assumptions!$C$6</f>
+        <f>Assumptions!$C$10</f>
         <v/>
       </c>
       <c r="D7" s="15">
-        <f>Assumptions!$C$6</f>
+        <f>Assumptions!$C$10</f>
         <v/>
       </c>
       <c r="E7" s="15">
-        <f>Assumptions!$C$6</f>
+        <f>Assumptions!$C$10</f>
         <v/>
       </c>
       <c r="F7" s="15">
-        <f>Assumptions!$C$6</f>
+        <f>Assumptions!$C$10</f>
         <v/>
       </c>
     </row>
@@ -8244,23 +8485,23 @@
           <t>NOPAT = EBIT x (1 less the tax rate)</t>
         </is>
       </c>
-      <c r="B8" s="31">
+      <c r="B8" s="32">
         <f>B6*(1-B7)</f>
         <v/>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="32">
         <f>C6*(1-C7)</f>
         <v/>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="32">
         <f>D6*(1-D7)</f>
         <v/>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="32">
         <f>E6*(1-E7)</f>
         <v/>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="32">
         <f>F6*(1-F7)</f>
         <v/>
       </c>
@@ -8272,23 +8513,23 @@
         </is>
       </c>
       <c r="B9" s="13">
-        <f>Segments!D37</f>
+        <f>Segments!D41</f>
         <v/>
       </c>
       <c r="C9" s="13">
-        <f>Segments!E37</f>
+        <f>Segments!E41</f>
         <v/>
       </c>
       <c r="D9" s="13">
-        <f>Segments!F37</f>
+        <f>Segments!F41</f>
         <v/>
       </c>
       <c r="E9" s="13">
-        <f>Segments!G37</f>
+        <f>Segments!G41</f>
         <v/>
       </c>
       <c r="F9" s="13">
-        <f>Segments!H37</f>
+        <f>Segments!H41</f>
         <v/>
       </c>
     </row>
@@ -8299,23 +8540,23 @@
         </is>
       </c>
       <c r="B10" s="13">
-        <f>-Segments!D36</f>
+        <f>-Segments!D40</f>
         <v/>
       </c>
       <c r="C10" s="13">
-        <f>-Segments!E36</f>
+        <f>-Segments!E40</f>
         <v/>
       </c>
       <c r="D10" s="13">
-        <f>-Segments!F36</f>
+        <f>-Segments!F40</f>
         <v/>
       </c>
       <c r="E10" s="13">
-        <f>-Segments!G36</f>
+        <f>-Segments!G40</f>
         <v/>
       </c>
       <c r="F10" s="13">
-        <f>-Segments!H36</f>
+        <f>-Segments!H40</f>
         <v/>
       </c>
     </row>
@@ -8352,23 +8593,23 @@
           <t>FREE CASH FLOW TO THE FIRM</t>
         </is>
       </c>
-      <c r="B12" s="31">
+      <c r="B12" s="32">
         <f>B8+B9+B10+B11</f>
         <v/>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="32">
         <f>C8+C9+C10+C11</f>
         <v/>
       </c>
-      <c r="D12" s="31">
+      <c r="D12" s="32">
         <f>D8+D9+D10+D11</f>
         <v/>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="32">
         <f>E8+E9+E10+E11</f>
         <v/>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="32">
         <f>F8+F9+F10+F11</f>
         <v/>
       </c>
@@ -8380,23 +8621,23 @@
         </is>
       </c>
       <c r="B13" s="15">
-        <f>Assumptions!C$109</f>
+        <f>Assumptions!C$114</f>
         <v/>
       </c>
       <c r="C13" s="15">
-        <f>Assumptions!D$109</f>
+        <f>Assumptions!D$114</f>
         <v/>
       </c>
       <c r="D13" s="15">
-        <f>Assumptions!E$109</f>
+        <f>Assumptions!E$114</f>
         <v/>
       </c>
       <c r="E13" s="15">
-        <f>Assumptions!F$109</f>
+        <f>Assumptions!F$114</f>
         <v/>
       </c>
       <c r="F13" s="15">
-        <f>Assumptions!G$109</f>
+        <f>Assumptions!G$114</f>
         <v/>
       </c>
     </row>
@@ -8406,24 +8647,24 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B14" s="30">
-        <f>Assumptions!C$110</f>
-        <v/>
-      </c>
-      <c r="C14" s="30">
-        <f>Assumptions!D$110</f>
-        <v/>
-      </c>
-      <c r="D14" s="30">
-        <f>Assumptions!E$110</f>
-        <v/>
-      </c>
-      <c r="E14" s="30">
-        <f>Assumptions!F$110</f>
-        <v/>
-      </c>
-      <c r="F14" s="30">
-        <f>Assumptions!G$110</f>
+      <c r="B14" s="31">
+        <f>Assumptions!C$115</f>
+        <v/>
+      </c>
+      <c r="C14" s="31">
+        <f>Assumptions!D$115</f>
+        <v/>
+      </c>
+      <c r="D14" s="31">
+        <f>Assumptions!E$115</f>
+        <v/>
+      </c>
+      <c r="E14" s="31">
+        <f>Assumptions!F$115</f>
+        <v/>
+      </c>
+      <c r="F14" s="31">
+        <f>Assumptions!G$115</f>
         <v/>
       </c>
     </row>
@@ -8433,23 +8674,23 @@
           <t>PRESENT VALUE OF FREE CASH FLOW TO THE FIRM</t>
         </is>
       </c>
-      <c r="B15" s="31">
+      <c r="B15" s="32">
         <f>B12*B14</f>
         <v/>
       </c>
-      <c r="C15" s="31">
+      <c r="C15" s="32">
         <f>C12*C14</f>
         <v/>
       </c>
-      <c r="D15" s="31">
+      <c r="D15" s="32">
         <f>D12*D14</f>
         <v/>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="32">
         <f>E12*E14</f>
         <v/>
       </c>
-      <c r="F15" s="31">
+      <c r="F15" s="32">
         <f>F12*F14</f>
         <v/>
       </c>
@@ -8468,7 +8709,7 @@
         </is>
       </c>
       <c r="B18" s="13">
-        <f>'Balance Sheet'!I2+'Balance Sheet'!I3+'Balance Sheet'!I19+Assumptions!$C$78</f>
+        <f>'Balance Sheet'!I2+'Balance Sheet'!I3+'Balance Sheet'!I19+Assumptions!$C$82</f>
         <v/>
       </c>
     </row>
@@ -8478,7 +8719,7 @@
           <t>Return on invested capital, FY2030E — the model's OWN, read from the rows above</t>
         </is>
       </c>
-      <c r="B19" s="26">
+      <c r="B19" s="27">
         <f>F8/B18</f>
         <v/>
       </c>
@@ -8495,7 +8736,7 @@
         </is>
       </c>
       <c r="B20" s="13">
-        <f>'Balance Sheet'!I3*Assumptions!$C$34</f>
+        <f>'Balance Sheet'!I3*Assumptions!$C$38</f>
         <v/>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -8511,7 +8752,7 @@
         </is>
       </c>
       <c r="B21" s="13">
-        <f>F8*(1+Assumptions!$C$58)-B20*(1-Assumptions!$C$6)</f>
+        <f>F8*(1+Assumptions!$C$62)-B20*(1-Assumptions!$C$10)</f>
         <v/>
       </c>
     </row>
@@ -8522,7 +8763,7 @@
         </is>
       </c>
       <c r="B22" s="6">
-        <f>Assumptions!$C$58/B19</f>
+        <f>Assumptions!$C$62/B19</f>
         <v/>
       </c>
     </row>
@@ -8544,7 +8785,7 @@
         </is>
       </c>
       <c r="B24" s="15">
-        <f>Assumptions!$C$107</f>
+        <f>Assumptions!$C$112</f>
         <v/>
       </c>
     </row>
@@ -8555,7 +8796,7 @@
         </is>
       </c>
       <c r="B25" s="6">
-        <f>Assumptions!$C$58</f>
+        <f>Assumptions!$C$62</f>
         <v/>
       </c>
     </row>
@@ -8565,7 +8806,7 @@
           <t>TERMINAL VALUE</t>
         </is>
       </c>
-      <c r="B26" s="27">
+      <c r="B26" s="28">
         <f>B23/(B24-B25)</f>
         <v/>
       </c>
@@ -8576,7 +8817,7 @@
           <t>Present value of the terminal value</t>
         </is>
       </c>
-      <c r="B27" s="27">
+      <c r="B27" s="28">
         <f>B26*F14</f>
         <v/>
       </c>
@@ -8587,7 +8828,7 @@
           <t>Sum of the present values of forecast free cash flow</t>
         </is>
       </c>
-      <c r="B29" s="27">
+      <c r="B29" s="28">
         <f>SUM(B15:F15)</f>
         <v/>
       </c>
@@ -8598,7 +8839,7 @@
           <t>CORE ENTERPRISE VALUE</t>
         </is>
       </c>
-      <c r="B30" s="31">
+      <c r="B30" s="32">
         <f>B29+B27</f>
         <v/>
       </c>
@@ -8620,8 +8861,8 @@
           <t>Terminal value as a percentage of TOTAL enterprise value (both are published)</t>
         </is>
       </c>
-      <c r="B32" s="28">
-        <f>B27/(B30+Assumptions!$C$59*Assumptions!$C$60+Assumptions!$C$76+Assumptions!$C$77)</f>
+      <c r="B32" s="29">
+        <f>B27/(B30+Assumptions!$C$63*Assumptions!$C$64+Assumptions!$C$80+Assumptions!$C$81)</f>
         <v/>
       </c>
     </row>
@@ -8758,7 +8999,7 @@
         </is>
       </c>
       <c r="B40" s="13">
-        <f>(F36*(1+Assumptions!$C$58)-B20*(1-Assumptions!$C$6))*(1-Assumptions!$C$58/B39)/(B24-B25)</f>
+        <f>(F36*(1+Assumptions!$C$62)-B20*(1-Assumptions!$C$10))*(1-Assumptions!$C$62/B39)/(B24-B25)</f>
         <v/>
       </c>
     </row>
@@ -8768,7 +9009,7 @@
           <t>Core enterprise value on Frame B</t>
         </is>
       </c>
-      <c r="B41" s="27">
+      <c r="B41" s="28">
         <f>SUM(B38:F38)+B40*F14</f>
         <v/>
       </c>
@@ -8780,7 +9021,7 @@
         </is>
       </c>
       <c r="B42" s="9">
-        <f>(B41+Assumptions!$C$59*Assumptions!$C$60+Assumptions!$C$76+Assumptions!$C$77-Assumptions!$C$98-Assumptions!$C$75)/Assumptions!$C$4</f>
+        <f>(B41+Assumptions!$C$63*Assumptions!$C$64+Assumptions!$C$80+Assumptions!$C$81-Assumptions!$C$103-Assumptions!$C$79)/Assumptions!$C$8</f>
         <v/>
       </c>
     </row>
@@ -8862,33 +9103,33 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B2" s="42" t="n">
+      <c r="B2" s="44" t="n">
         <v>5231.665571</v>
       </c>
-      <c r="C2" s="42" t="n">
+      <c r="C2" s="44" t="n">
         <v>7590.545643</v>
       </c>
-      <c r="D2" s="42" t="n">
+      <c r="D2" s="44" t="n">
         <v>9441.379305</v>
       </c>
-      <c r="E2" s="43">
-        <f>Segments!D11</f>
-        <v/>
-      </c>
-      <c r="F2" s="43">
-        <f>Segments!E11</f>
-        <v/>
-      </c>
-      <c r="G2" s="43">
-        <f>Segments!F11</f>
-        <v/>
-      </c>
-      <c r="H2" s="43">
-        <f>Segments!G11</f>
-        <v/>
-      </c>
-      <c r="I2" s="43">
-        <f>Segments!H11</f>
+      <c r="E2" s="45">
+        <f>Segments!D15</f>
+        <v/>
+      </c>
+      <c r="F2" s="45">
+        <f>Segments!E15</f>
+        <v/>
+      </c>
+      <c r="G2" s="45">
+        <f>Segments!F15</f>
+        <v/>
+      </c>
+      <c r="H2" s="45">
+        <f>Segments!G15</f>
+        <v/>
+      </c>
+      <c r="I2" s="45">
+        <f>Segments!H15</f>
         <v/>
       </c>
     </row>
@@ -8898,13 +9139,13 @@
           <t>Cost of sales</t>
         </is>
       </c>
-      <c r="B3" s="20" t="n">
+      <c r="B3" s="19" t="n">
         <v>-2896.343413</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="C3" s="19" t="n">
         <v>-4184.382863</v>
       </c>
-      <c r="D3" s="20" t="n">
+      <c r="D3" s="19" t="n">
         <v>-5287.140903</v>
       </c>
       <c r="E3" s="13">
@@ -8934,33 +9175,33 @@
           <t xml:space="preserve">   of which cash cost (packs x cash cost per pack, escalated)</t>
         </is>
       </c>
-      <c r="B4" s="20" t="n">
+      <c r="B4" s="19" t="n">
         <v>2896.343413</v>
       </c>
-      <c r="C4" s="20" t="n">
+      <c r="C4" s="19" t="n">
         <v>4184.382863</v>
       </c>
-      <c r="D4" s="20" t="n">
+      <c r="D4" s="19" t="n">
         <v>5193.643343000001</v>
       </c>
       <c r="E4" s="13">
-        <f>Segments!D10*Assumptions!$C$81*Segments!D$27</f>
+        <f>Segments!D14*Assumptions!$C$85*Segments!D$31</f>
         <v/>
       </c>
       <c r="F4" s="13">
-        <f>Segments!E10*Assumptions!$C$81*Segments!E$27</f>
+        <f>Segments!E14*Assumptions!$C$85*Segments!E$31</f>
         <v/>
       </c>
       <c r="G4" s="13">
-        <f>Segments!F10*Assumptions!$C$81*Segments!F$27</f>
+        <f>Segments!F14*Assumptions!$C$85*Segments!F$31</f>
         <v/>
       </c>
       <c r="H4" s="13">
-        <f>Segments!G10*Assumptions!$C$81*Segments!G$27</f>
+        <f>Segments!G14*Assumptions!$C$85*Segments!G$31</f>
         <v/>
       </c>
       <c r="I4" s="13">
-        <f>Segments!H10*Assumptions!$C$81*Segments!H$27</f>
+        <f>Segments!H14*Assumptions!$C$85*Segments!H$31</f>
         <v/>
       </c>
     </row>
@@ -8970,33 +9211,33 @@
           <t xml:space="preserve">   of which depreciation charged to production</t>
         </is>
       </c>
-      <c r="B5" s="20" t="n">
+      <c r="B5" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="20" t="n">
+      <c r="C5" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="20" t="n">
+      <c r="D5" s="19" t="n">
         <v>93.49755999999999</v>
       </c>
       <c r="E5" s="13">
-        <f>Segments!D$37*Assumptions!$C$80</f>
+        <f>Segments!D$41*Assumptions!$C$84</f>
         <v/>
       </c>
       <c r="F5" s="13">
-        <f>Segments!E$37*Assumptions!$C$80</f>
+        <f>Segments!E$41*Assumptions!$C$84</f>
         <v/>
       </c>
       <c r="G5" s="13">
-        <f>Segments!F$37*Assumptions!$C$80</f>
+        <f>Segments!F$41*Assumptions!$C$84</f>
         <v/>
       </c>
       <c r="H5" s="13">
-        <f>Segments!G$37*Assumptions!$C$80</f>
+        <f>Segments!G$41*Assumptions!$C$84</f>
         <v/>
       </c>
       <c r="I5" s="13">
-        <f>Segments!H$37*Assumptions!$C$80</f>
+        <f>Segments!H$41*Assumptions!$C$84</f>
         <v/>
       </c>
     </row>
@@ -9006,35 +9247,35 @@
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="B6" s="31">
+      <c r="B6" s="32">
         <f>B2+B3</f>
         <v/>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="32">
         <f>C2+C3</f>
         <v/>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="32">
         <f>D2+D3</f>
         <v/>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="32">
         <f>E2+E3</f>
         <v/>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="32">
         <f>F2+F3</f>
         <v/>
       </c>
-      <c r="G6" s="31">
+      <c r="G6" s="32">
         <f>G2+G3</f>
         <v/>
       </c>
-      <c r="H6" s="31">
+      <c r="H6" s="32">
         <f>H2+H3</f>
         <v/>
       </c>
-      <c r="I6" s="31">
+      <c r="I6" s="32">
         <f>I2+I3</f>
         <v/>
       </c>
@@ -9084,33 +9325,33 @@
           <t>Selling and marketing</t>
         </is>
       </c>
-      <c r="B8" s="20" t="n">
+      <c r="B8" s="19" t="n">
         <v>-648.291681</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="19" t="n">
         <v>-915.021183</v>
       </c>
-      <c r="D8" s="20" t="n">
+      <c r="D8" s="19" t="n">
         <v>-1000.128922</v>
       </c>
       <c r="E8" s="13">
-        <f>-E2*Assumptions!C$27</f>
+        <f>-E2*Assumptions!C$31</f>
         <v/>
       </c>
       <c r="F8" s="13">
-        <f>-F2*Assumptions!D$27</f>
+        <f>-F2*Assumptions!D$31</f>
         <v/>
       </c>
       <c r="G8" s="13">
-        <f>-G2*Assumptions!E$27</f>
+        <f>-G2*Assumptions!E$31</f>
         <v/>
       </c>
       <c r="H8" s="13">
-        <f>-H2*Assumptions!F$27</f>
+        <f>-H2*Assumptions!F$31</f>
         <v/>
       </c>
       <c r="I8" s="13">
-        <f>-I2*Assumptions!G$27</f>
+        <f>-I2*Assumptions!G$31</f>
         <v/>
       </c>
     </row>
@@ -9120,33 +9361,33 @@
           <t>Research and development</t>
         </is>
       </c>
-      <c r="B9" s="20" t="n">
+      <c r="B9" s="19" t="n">
         <v>-43.227785</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="19" t="n">
         <v>-70.460824</v>
       </c>
-      <c r="D9" s="20" t="n">
+      <c r="D9" s="19" t="n">
         <v>-70.935883</v>
       </c>
       <c r="E9" s="13">
-        <f>-E2*Assumptions!C$28</f>
+        <f>-E2*Assumptions!C$32</f>
         <v/>
       </c>
       <c r="F9" s="13">
-        <f>-F2*Assumptions!D$28</f>
+        <f>-F2*Assumptions!D$32</f>
         <v/>
       </c>
       <c r="G9" s="13">
-        <f>-G2*Assumptions!E$28</f>
+        <f>-G2*Assumptions!E$32</f>
         <v/>
       </c>
       <c r="H9" s="13">
-        <f>-H2*Assumptions!F$28</f>
+        <f>-H2*Assumptions!F$32</f>
         <v/>
       </c>
       <c r="I9" s="13">
-        <f>-I2*Assumptions!G$28</f>
+        <f>-I2*Assumptions!G$32</f>
         <v/>
       </c>
     </row>
@@ -9156,33 +9397,33 @@
           <t>General and administrative</t>
         </is>
       </c>
-      <c r="B10" s="20" t="n">
+      <c r="B10" s="19" t="n">
         <v>-147.460991</v>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="19" t="n">
         <v>-188.492929</v>
       </c>
-      <c r="D10" s="20" t="n">
+      <c r="D10" s="19" t="n">
         <v>-221.13686</v>
       </c>
       <c r="E10" s="13">
-        <f>-E2*Assumptions!C$29</f>
+        <f>-E2*Assumptions!C$33</f>
         <v/>
       </c>
       <c r="F10" s="13">
-        <f>-F2*Assumptions!D$29</f>
+        <f>-F2*Assumptions!D$33</f>
         <v/>
       </c>
       <c r="G10" s="13">
-        <f>-G2*Assumptions!E$29</f>
+        <f>-G2*Assumptions!E$33</f>
         <v/>
       </c>
       <c r="H10" s="13">
-        <f>-H2*Assumptions!F$29</f>
+        <f>-H2*Assumptions!F$33</f>
         <v/>
       </c>
       <c r="I10" s="13">
-        <f>-I2*Assumptions!G$29</f>
+        <f>-I2*Assumptions!G$33</f>
         <v/>
       </c>
     </row>
@@ -9192,33 +9433,33 @@
           <t>Credit losses, inventory write-downs and provisions — FRAME A</t>
         </is>
       </c>
-      <c r="B11" s="20" t="n">
+      <c r="B11" s="19" t="n">
         <v>-265</v>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="19" t="n">
         <v>-702</v>
       </c>
-      <c r="D11" s="20" t="n">
+      <c r="D11" s="19" t="n">
         <v>-494.218374</v>
       </c>
       <c r="E11" s="13">
-        <f>-E2*Assumptions!C$30</f>
+        <f>-E2*Assumptions!C$34</f>
         <v/>
       </c>
       <c r="F11" s="13">
-        <f>-F2*Assumptions!D$30</f>
+        <f>-F2*Assumptions!D$34</f>
         <v/>
       </c>
       <c r="G11" s="13">
-        <f>-G2*Assumptions!E$30</f>
+        <f>-G2*Assumptions!E$34</f>
         <v/>
       </c>
       <c r="H11" s="13">
-        <f>-H2*Assumptions!F$30</f>
+        <f>-H2*Assumptions!F$34</f>
         <v/>
       </c>
       <c r="I11" s="13">
-        <f>-I2*Assumptions!G$30</f>
+        <f>-I2*Assumptions!G$34</f>
         <v/>
       </c>
     </row>
@@ -9228,33 +9469,33 @@
           <t>The same charge on FRAME B (memorandum)</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n">
+      <c r="B12" s="19" t="n">
         <v>-265</v>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="19" t="n">
         <v>-702</v>
       </c>
-      <c r="D12" s="20" t="n">
+      <c r="D12" s="19" t="n">
         <v>-494.218374</v>
       </c>
       <c r="E12" s="13">
-        <f>-E2*Assumptions!C$31</f>
+        <f>-E2*Assumptions!C$35</f>
         <v/>
       </c>
       <c r="F12" s="13">
-        <f>-F2*Assumptions!D$31</f>
+        <f>-F2*Assumptions!D$35</f>
         <v/>
       </c>
       <c r="G12" s="13">
-        <f>-G2*Assumptions!E$31</f>
+        <f>-G2*Assumptions!E$35</f>
         <v/>
       </c>
       <c r="H12" s="13">
-        <f>-H2*Assumptions!F$31</f>
+        <f>-H2*Assumptions!F$35</f>
         <v/>
       </c>
       <c r="I12" s="13">
-        <f>-I2*Assumptions!G$31</f>
+        <f>-I2*Assumptions!G$35</f>
         <v/>
       </c>
     </row>
@@ -9264,28 +9505,28 @@
           <t>Board remuneration and attendance</t>
         </is>
       </c>
-      <c r="B13" s="24" t="n">
+      <c r="B13" s="25" t="n">
         <v>-2.02</v>
       </c>
-      <c r="C13" s="24" t="n">
+      <c r="C13" s="25" t="n">
         <v>-1.58</v>
       </c>
-      <c r="D13" s="24" t="n">
+      <c r="D13" s="25" t="n">
         <v>-1.828</v>
       </c>
-      <c r="E13" s="24" t="n">
+      <c r="E13" s="25" t="n">
         <v>-2</v>
       </c>
-      <c r="F13" s="24" t="n">
+      <c r="F13" s="25" t="n">
         <v>-2</v>
       </c>
-      <c r="G13" s="24" t="n">
+      <c r="G13" s="25" t="n">
         <v>-2</v>
       </c>
-      <c r="H13" s="24" t="n">
+      <c r="H13" s="25" t="n">
         <v>-2</v>
       </c>
-      <c r="I13" s="24" t="n">
+      <c r="I13" s="25" t="n">
         <v>-2</v>
       </c>
     </row>
@@ -9295,33 +9536,33 @@
           <t>Depreciation charged to selling and administrative expense</t>
         </is>
       </c>
-      <c r="B14" s="24" t="n">
+      <c r="B14" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="24" t="n">
+      <c r="C14" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="24" t="n">
+      <c r="D14" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="33">
-        <f>-Segments!D37*(1-Assumptions!$C$80)</f>
-        <v/>
-      </c>
-      <c r="F14" s="33">
-        <f>-Segments!E37*(1-Assumptions!$C$80)</f>
-        <v/>
-      </c>
-      <c r="G14" s="33">
-        <f>-Segments!F37*(1-Assumptions!$C$80)</f>
-        <v/>
-      </c>
-      <c r="H14" s="33">
-        <f>-Segments!G37*(1-Assumptions!$C$80)</f>
-        <v/>
-      </c>
-      <c r="I14" s="33">
-        <f>-Segments!H37*(1-Assumptions!$C$80)</f>
+      <c r="E14" s="35">
+        <f>-Segments!D41*(1-Assumptions!$C$84)</f>
+        <v/>
+      </c>
+      <c r="F14" s="35">
+        <f>-Segments!E41*(1-Assumptions!$C$84)</f>
+        <v/>
+      </c>
+      <c r="G14" s="35">
+        <f>-Segments!F41*(1-Assumptions!$C$84)</f>
+        <v/>
+      </c>
+      <c r="H14" s="35">
+        <f>-Segments!G41*(1-Assumptions!$C$84)</f>
+        <v/>
+      </c>
+      <c r="I14" s="35">
+        <f>-Segments!H41*(1-Assumptions!$C$84)</f>
         <v/>
       </c>
     </row>
@@ -9331,35 +9572,35 @@
           <t>Operating profit (EBIT)</t>
         </is>
       </c>
-      <c r="B15" s="31">
+      <c r="B15" s="32">
         <f>B6+B8+B9+B10+B11+B13+B14</f>
         <v/>
       </c>
-      <c r="C15" s="31">
+      <c r="C15" s="32">
         <f>C6+C8+C9+C10+C11+C13+C14</f>
         <v/>
       </c>
-      <c r="D15" s="31">
+      <c r="D15" s="32">
         <f>D6+D8+D9+D10+D11+D13+D14</f>
         <v/>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="32">
         <f>E6+E8+E9+E10+E11+E13+E14</f>
         <v/>
       </c>
-      <c r="F15" s="31">
+      <c r="F15" s="32">
         <f>F6+F8+F9+F10+F11+F13+F14</f>
         <v/>
       </c>
-      <c r="G15" s="31">
+      <c r="G15" s="32">
         <f>G6+G8+G9+G10+G11+G13+G14</f>
         <v/>
       </c>
-      <c r="H15" s="31">
+      <c r="H15" s="32">
         <f>H6+H8+H9+H10+H11+H13+H14</f>
         <v/>
       </c>
-      <c r="I15" s="31">
+      <c r="I15" s="32">
         <f>I6+I8+I9+I10+I11+I13+I14</f>
         <v/>
       </c>
@@ -9370,33 +9611,33 @@
           <t>Depreciation and amortisation (memorandum)</t>
         </is>
       </c>
-      <c r="B16" s="20" t="n">
+      <c r="B16" s="19" t="n">
         <v>105.249745</v>
       </c>
-      <c r="C16" s="20" t="n">
+      <c r="C16" s="19" t="n">
         <v>102.811854</v>
       </c>
-      <c r="D16" s="20" t="n">
+      <c r="D16" s="19" t="n">
         <v>117.725374</v>
       </c>
       <c r="E16" s="13">
-        <f>Segments!D$37</f>
+        <f>Segments!D$41</f>
         <v/>
       </c>
       <c r="F16" s="13">
-        <f>Segments!E$37</f>
+        <f>Segments!E$41</f>
         <v/>
       </c>
       <c r="G16" s="13">
-        <f>Segments!F$37</f>
+        <f>Segments!F$41</f>
         <v/>
       </c>
       <c r="H16" s="13">
-        <f>Segments!G$37</f>
+        <f>Segments!G$41</f>
         <v/>
       </c>
       <c r="I16" s="13">
-        <f>Segments!H$37</f>
+        <f>Segments!H$41</f>
         <v/>
       </c>
     </row>
@@ -9406,35 +9647,35 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B17" s="27">
+      <c r="B17" s="28">
         <f>B15+B16</f>
         <v/>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="28">
         <f>C15+C16</f>
         <v/>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="28">
         <f>D15+D16</f>
         <v/>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="28">
         <f>E15+E16</f>
         <v/>
       </c>
-      <c r="F17" s="27">
+      <c r="F17" s="28">
         <f>F15+F16</f>
         <v/>
       </c>
-      <c r="G17" s="27">
+      <c r="G17" s="28">
         <f>G15+G16</f>
         <v/>
       </c>
-      <c r="H17" s="27">
+      <c r="H17" s="28">
         <f>H15+H16</f>
         <v/>
       </c>
-      <c r="I17" s="27">
+      <c r="I17" s="28">
         <f>I15+I16</f>
         <v/>
       </c>
@@ -9445,33 +9686,33 @@
           <t>Finance costs</t>
         </is>
       </c>
-      <c r="B18" s="20" t="n">
+      <c r="B18" s="19" t="n">
         <v>-407.7052</v>
       </c>
-      <c r="C18" s="20" t="n">
+      <c r="C18" s="19" t="n">
         <v>-960.131966</v>
       </c>
-      <c r="D18" s="20" t="n">
+      <c r="D18" s="19" t="n">
         <v>-1332.946559</v>
       </c>
       <c r="E18" s="13">
-        <f>-Assumptions!C$51</f>
+        <f>-Assumptions!C$55</f>
         <v/>
       </c>
       <c r="F18" s="13">
-        <f>-Assumptions!D$51</f>
+        <f>-Assumptions!D$55</f>
         <v/>
       </c>
       <c r="G18" s="13">
-        <f>-Assumptions!E$51</f>
+        <f>-Assumptions!E$55</f>
         <v/>
       </c>
       <c r="H18" s="13">
-        <f>-Assumptions!F$51</f>
+        <f>-Assumptions!F$55</f>
         <v/>
       </c>
       <c r="I18" s="13">
-        <f>-Assumptions!G$51</f>
+        <f>-Assumptions!G$55</f>
         <v/>
       </c>
     </row>
@@ -9481,33 +9722,33 @@
           <t>Share of results of associates</t>
         </is>
       </c>
-      <c r="B19" s="20" t="n">
+      <c r="B19" s="19" t="n">
         <v>74.508447</v>
       </c>
-      <c r="C19" s="20" t="n">
+      <c r="C19" s="19" t="n">
         <v>151.580926</v>
       </c>
-      <c r="D19" s="20" t="n">
+      <c r="D19" s="19" t="n">
         <v>512.084638</v>
       </c>
       <c r="E19" s="13">
-        <f>Assumptions!$C$59</f>
+        <f>Assumptions!$C$63</f>
         <v/>
       </c>
       <c r="F19" s="13">
-        <f>Assumptions!$C$59</f>
+        <f>Assumptions!$C$63</f>
         <v/>
       </c>
       <c r="G19" s="13">
-        <f>Assumptions!$C$59</f>
+        <f>Assumptions!$C$63</f>
         <v/>
       </c>
       <c r="H19" s="13">
-        <f>Assumptions!$C$59</f>
+        <f>Assumptions!$C$63</f>
         <v/>
       </c>
       <c r="I19" s="13">
-        <f>Assumptions!$C$59</f>
+        <f>Assumptions!$C$63</f>
         <v/>
       </c>
     </row>
@@ -9517,28 +9758,28 @@
           <t>Dividend distribution tax</t>
         </is>
       </c>
-      <c r="B20" s="24" t="n">
+      <c r="B20" s="25" t="n">
         <v>-4.123733</v>
       </c>
-      <c r="C20" s="24" t="n">
+      <c r="C20" s="25" t="n">
         <v>-4.468933</v>
       </c>
-      <c r="D20" s="24" t="n">
+      <c r="D20" s="25" t="n">
         <v>-16.58542</v>
       </c>
-      <c r="E20" s="24" t="n">
+      <c r="E20" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F20" s="24" t="n">
+      <c r="F20" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="24" t="n">
+      <c r="G20" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="24" t="n">
+      <c r="H20" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="24" t="n">
+      <c r="I20" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9548,28 +9789,28 @@
           <t>Interest income, exchange differences and other income</t>
         </is>
       </c>
-      <c r="B21" s="20" t="n">
+      <c r="B21" s="19" t="n">
         <v>191.254269</v>
       </c>
-      <c r="C21" s="20" t="n">
+      <c r="C21" s="19" t="n">
         <v>814.782229</v>
       </c>
-      <c r="D21" s="20" t="n">
+      <c r="D21" s="19" t="n">
         <v>267.358836</v>
       </c>
-      <c r="E21" s="20" t="n">
+      <c r="E21" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="F21" s="20" t="n">
+      <c r="F21" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="20" t="n">
+      <c r="G21" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="20" t="n">
+      <c r="H21" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I21" s="20" t="n">
+      <c r="I21" s="19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9579,35 +9820,35 @@
           <t>Profit before tax</t>
         </is>
       </c>
-      <c r="B22" s="31">
+      <c r="B22" s="32">
         <f>B15+B18+B19+B21+B20</f>
         <v/>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="32">
         <f>C15+C18+C19+C21+C20</f>
         <v/>
       </c>
-      <c r="D22" s="31">
+      <c r="D22" s="32">
         <f>D15+D18+D19+D21+D20</f>
         <v/>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="32">
         <f>E15+E18+E19+E21+E20</f>
         <v/>
       </c>
-      <c r="F22" s="31">
+      <c r="F22" s="32">
         <f>F15+F18+F19+F21+F20</f>
         <v/>
       </c>
-      <c r="G22" s="31">
+      <c r="G22" s="32">
         <f>G15+G18+G19+G21+G20</f>
         <v/>
       </c>
-      <c r="H22" s="31">
+      <c r="H22" s="32">
         <f>H15+H18+H19+H21+H20</f>
         <v/>
       </c>
-      <c r="I22" s="31">
+      <c r="I22" s="32">
         <f>I15+I18+I19+I21+I20</f>
         <v/>
       </c>
@@ -9618,33 +9859,33 @@
           <t>Income tax and the statutory solidarity contribution</t>
         </is>
       </c>
-      <c r="B23" s="20" t="n">
+      <c r="B23" s="19" t="n">
         <v>-259.949154</v>
       </c>
-      <c r="C23" s="20" t="n">
+      <c r="C23" s="19" t="n">
         <v>-433.446496</v>
       </c>
-      <c r="D23" s="20" t="n">
+      <c r="D23" s="19" t="n">
         <v>-338.008843</v>
       </c>
       <c r="E23" s="13">
-        <f>-(E22-E19)*Assumptions!$C$6</f>
+        <f>-(E22-E19)*Assumptions!$C$10</f>
         <v/>
       </c>
       <c r="F23" s="13">
-        <f>-(F22-F19)*Assumptions!$C$6</f>
+        <f>-(F22-F19)*Assumptions!$C$10</f>
         <v/>
       </c>
       <c r="G23" s="13">
-        <f>-(G22-G19)*Assumptions!$C$6</f>
+        <f>-(G22-G19)*Assumptions!$C$10</f>
         <v/>
       </c>
       <c r="H23" s="13">
-        <f>-(H22-H19)*Assumptions!$C$6</f>
+        <f>-(H22-H19)*Assumptions!$C$10</f>
         <v/>
       </c>
       <c r="I23" s="13">
-        <f>-(I22-I19)*Assumptions!$C$6</f>
+        <f>-(I22-I19)*Assumptions!$C$10</f>
         <v/>
       </c>
     </row>
@@ -9654,35 +9895,35 @@
           <t>Profit for the year</t>
         </is>
       </c>
-      <c r="B24" s="31">
+      <c r="B24" s="32">
         <f>B22+B23</f>
         <v/>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="32">
         <f>C22+C23</f>
         <v/>
       </c>
-      <c r="D24" s="31">
+      <c r="D24" s="32">
         <f>D22+D23</f>
         <v/>
       </c>
-      <c r="E24" s="31">
+      <c r="E24" s="32">
         <f>E22+E23</f>
         <v/>
       </c>
-      <c r="F24" s="31">
+      <c r="F24" s="32">
         <f>F22+F23</f>
         <v/>
       </c>
-      <c r="G24" s="31">
+      <c r="G24" s="32">
         <f>G22+G23</f>
         <v/>
       </c>
-      <c r="H24" s="31">
+      <c r="H24" s="32">
         <f>H22+H23</f>
         <v/>
       </c>
-      <c r="I24" s="31">
+      <c r="I24" s="32">
         <f>I22+I23</f>
         <v/>
       </c>
@@ -9693,28 +9934,28 @@
           <t>Less non-controlling interests</t>
         </is>
       </c>
-      <c r="B25" s="24" t="n">
+      <c r="B25" s="25" t="n">
         <v>-0.9886149999999816</v>
       </c>
-      <c r="C25" s="24" t="n">
+      <c r="C25" s="25" t="n">
         <v>-1.206525000000056</v>
       </c>
-      <c r="D25" s="24" t="n">
+      <c r="D25" s="25" t="n">
         <v>-16.23531500000013</v>
       </c>
-      <c r="E25" s="24" t="n">
+      <c r="E25" s="25" t="n">
         <v>-18</v>
       </c>
-      <c r="F25" s="24" t="n">
+      <c r="F25" s="25" t="n">
         <v>-18</v>
       </c>
-      <c r="G25" s="24" t="n">
+      <c r="G25" s="25" t="n">
         <v>-18</v>
       </c>
-      <c r="H25" s="24" t="n">
+      <c r="H25" s="25" t="n">
         <v>-18</v>
       </c>
-      <c r="I25" s="24" t="n">
+      <c r="I25" s="25" t="n">
         <v>-18</v>
       </c>
     </row>
@@ -9724,35 +9965,35 @@
           <t>Profit attributable to the holding company</t>
         </is>
       </c>
-      <c r="B26" s="31">
+      <c r="B26" s="32">
         <f>B24+B25</f>
         <v/>
       </c>
-      <c r="C26" s="31">
+      <c r="C26" s="32">
         <f>C24+C25</f>
         <v/>
       </c>
-      <c r="D26" s="31">
+      <c r="D26" s="32">
         <f>D24+D25</f>
         <v/>
       </c>
-      <c r="E26" s="31">
+      <c r="E26" s="32">
         <f>E24+E25</f>
         <v/>
       </c>
-      <c r="F26" s="31">
+      <c r="F26" s="32">
         <f>F24+F25</f>
         <v/>
       </c>
-      <c r="G26" s="31">
+      <c r="G26" s="32">
         <f>G24+G25</f>
         <v/>
       </c>
-      <c r="H26" s="31">
+      <c r="H26" s="32">
         <f>H24+H25</f>
         <v/>
       </c>
-      <c r="I26" s="31">
+      <c r="I26" s="32">
         <f>I24+I25</f>
         <v/>
       </c>
@@ -9776,23 +10017,23 @@
         <v/>
       </c>
       <c r="E27" s="12">
-        <f>E26/Assumptions!$C$4</f>
+        <f>E26/Assumptions!$C$8</f>
         <v/>
       </c>
       <c r="F27" s="12">
-        <f>F26/Assumptions!$C$4</f>
+        <f>F26/Assumptions!$C$8</f>
         <v/>
       </c>
       <c r="G27" s="12">
-        <f>G26/Assumptions!$C$4</f>
+        <f>G26/Assumptions!$C$8</f>
         <v/>
       </c>
       <c r="H27" s="12">
-        <f>H26/Assumptions!$C$4</f>
+        <f>H26/Assumptions!$C$8</f>
         <v/>
       </c>
       <c r="I27" s="12">
-        <f>I26/Assumptions!$C$4</f>
+        <f>I26/Assumptions!$C$8</f>
         <v/>
       </c>
     </row>

--- a/engine/phar_study/EIPICO_Valuation_Model_09082026.xlsx
+++ b/engine/phar_study/EIPICO_Valuation_Model_09082026.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Audited CONSOLIDATED financial statements. Share price 130.05 at 2026-08-06; 168.755750 million shares in issue. Fiscal year ends 31 December.</t>
+          <t>Audited CONSOLIDATED financial statements. Share price 127.30 at 2026-08-06; 168.755750 million shares in issue. Fiscal year ends 31 December.</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
         <v>1045.230507</v>
       </c>
       <c r="D2" s="13">
-        <f>Assumptions!$C$67</f>
+        <f>Assumptions!$C$68</f>
         <v/>
       </c>
       <c r="E2" s="13">
@@ -860,7 +860,7 @@
         <v>5693.566382</v>
       </c>
       <c r="D3" s="13">
-        <f>Assumptions!$C$68</f>
+        <f>Assumptions!$C$69</f>
         <v/>
       </c>
       <c r="E3" s="13">
@@ -933,7 +933,7 @@
         <v>3584.699946</v>
       </c>
       <c r="D5" s="13">
-        <f>Assumptions!$C$69</f>
+        <f>Assumptions!$C$70</f>
         <v/>
       </c>
       <c r="E5" s="13">
@@ -970,7 +970,7 @@
         <v>3049.275231</v>
       </c>
       <c r="D6" s="13">
-        <f>Assumptions!$C$70</f>
+        <f>Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="E6" s="13">
@@ -1007,27 +1007,27 @@
         <v>185.584353</v>
       </c>
       <c r="D7" s="13">
-        <f>Assumptions!$C$71</f>
+        <f>Assumptions!$C$72</f>
         <v/>
       </c>
       <c r="E7" s="13">
-        <f>'Income Statement'!E2/9441.379305*Assumptions!$C$71</f>
+        <f>'Income Statement'!E2/9441.379305*Assumptions!$C$72</f>
         <v/>
       </c>
       <c r="F7" s="13">
-        <f>'Income Statement'!F2/9441.379305*Assumptions!$C$71</f>
+        <f>'Income Statement'!F2/9441.379305*Assumptions!$C$72</f>
         <v/>
       </c>
       <c r="G7" s="13">
-        <f>'Income Statement'!G2/9441.379305*Assumptions!$C$71</f>
+        <f>'Income Statement'!G2/9441.379305*Assumptions!$C$72</f>
         <v/>
       </c>
       <c r="H7" s="13">
-        <f>'Income Statement'!H2/9441.379305*Assumptions!$C$71</f>
+        <f>'Income Statement'!H2/9441.379305*Assumptions!$C$72</f>
         <v/>
       </c>
       <c r="I7" s="13">
-        <f>'Income Statement'!I2/9441.379305*Assumptions!$C$71</f>
+        <f>'Income Statement'!I2/9441.379305*Assumptions!$C$72</f>
         <v/>
       </c>
     </row>
@@ -1044,27 +1044,27 @@
         <v>1295.38686</v>
       </c>
       <c r="D8" s="13">
-        <f>Assumptions!$C$74</f>
+        <f>Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="E8" s="13">
-        <f>Assumptions!$C$74</f>
+        <f>Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="F8" s="13">
-        <f>Assumptions!$C$74</f>
+        <f>Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="G8" s="13">
-        <f>Assumptions!$C$74</f>
+        <f>Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="H8" s="13">
-        <f>Assumptions!$C$74</f>
+        <f>Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="I8" s="13">
-        <f>Assumptions!$C$74</f>
+        <f>Assumptions!$C$75</f>
         <v/>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
         <v>410.391619</v>
       </c>
       <c r="D10" s="13">
-        <f>Assumptions!$C$72</f>
+        <f>Assumptions!$C$73</f>
         <v/>
       </c>
       <c r="E10" s="13">
@@ -1157,27 +1157,27 @@
         <v>367.42118</v>
       </c>
       <c r="D11" s="13">
-        <f>Assumptions!$C$73</f>
+        <f>Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="E11" s="13">
-        <f>'Income Statement'!E2/9441.379305*Assumptions!$C$73</f>
+        <f>'Income Statement'!E2/9441.379305*Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="F11" s="13">
-        <f>'Income Statement'!F2/9441.379305*Assumptions!$C$73</f>
+        <f>'Income Statement'!F2/9441.379305*Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="G11" s="13">
-        <f>'Income Statement'!G2/9441.379305*Assumptions!$C$73</f>
+        <f>'Income Statement'!G2/9441.379305*Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="H11" s="13">
-        <f>'Income Statement'!H2/9441.379305*Assumptions!$C$73</f>
+        <f>'Income Statement'!H2/9441.379305*Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="I11" s="13">
-        <f>'Income Statement'!I2/9441.379305*Assumptions!$C$73</f>
+        <f>'Income Statement'!I2/9441.379305*Assumptions!$C$74</f>
         <v/>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
         <v>9200.032863</v>
       </c>
       <c r="D13" s="13">
-        <f>Assumptions!$C$75</f>
+        <f>Assumptions!$C$76</f>
         <v/>
       </c>
       <c r="E13" s="13">
@@ -1267,11 +1267,11 @@
         <v>4653.769234</v>
       </c>
       <c r="D14" s="13">
-        <f>Assumptions!$C$77</f>
+        <f>Assumptions!$C$78</f>
         <v/>
       </c>
       <c r="E14" s="28">
-        <f>Assumptions!$C$77+'Income Statement'!E26*(1-Assumptions!$C$42)</f>
+        <f>Assumptions!$C$78+'Income Statement'!E26*(1-Assumptions!$C$42)</f>
         <v/>
       </c>
       <c r="F14" s="28">
@@ -1304,27 +1304,27 @@
         <v>3.816172</v>
       </c>
       <c r="D15" s="13">
-        <f>Assumptions!$C$78</f>
+        <f>Assumptions!$C$79</f>
         <v/>
       </c>
       <c r="E15" s="13">
-        <f>Assumptions!$C$79</f>
+        <f>Assumptions!$C$80</f>
         <v/>
       </c>
       <c r="F15" s="13">
-        <f>Assumptions!$C$79</f>
+        <f>Assumptions!$C$80</f>
         <v/>
       </c>
       <c r="G15" s="13">
-        <f>Assumptions!$C$79</f>
+        <f>Assumptions!$C$80</f>
         <v/>
       </c>
       <c r="H15" s="13">
-        <f>Assumptions!$C$79</f>
+        <f>Assumptions!$C$80</f>
         <v/>
       </c>
       <c r="I15" s="13">
-        <f>Assumptions!$C$79</f>
+        <f>Assumptions!$C$80</f>
         <v/>
       </c>
     </row>
@@ -2768,19 +2768,19 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>77.29589290051553</v>
+        <v>52.87174617751678</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>66.74301308250047</v>
+        <v>43.91794786985742</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>58.04356316438152</v>
+        <v>36.63949773388239</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>50.75027515072584</v>
+        <v>30.60944067360987</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>44.54905891123189</v>
+        <v>25.53445407113366</v>
       </c>
     </row>
     <row r="7">
@@ -2812,19 +2812,19 @@
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>54.19932760616772</v>
+        <v>24.89238838802118</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>55.97105249260597</v>
+        <v>27.08100396297257</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>58.04356316438152</v>
+        <v>29.6689241928033</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>60.53620600076448</v>
+        <v>32.78882816716791</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>63.64109038776664</v>
+        <v>36.63949773388239</v>
       </c>
     </row>
     <row r="10">
@@ -2856,19 +2856,19 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>69.84088801144183</v>
+        <v>46.48276755483419</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>62.91034125538415</v>
+        <v>40.68048040441269</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>58.04356316438152</v>
+        <v>36.63949773388239</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>51.4521683412368</v>
+        <v>31.21093776529835</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>44.46342676007655</v>
+        <v>25.51161940550458</v>
       </c>
     </row>
     <row r="13">
@@ -2900,19 +2900,19 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>74.64279440856899</v>
+        <v>55.90961031827637</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>68.60284325666746</v>
+        <v>48.90229665122401</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>58.04356316438152</v>
+        <v>36.63949773388239</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>50.51108196144131</v>
+        <v>27.88035565006691</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>41.48545024215522</v>
+        <v>17.3693851494884</v>
       </c>
     </row>
     <row r="16">
@@ -2944,19 +2944,19 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>68.94051402078955</v>
+        <v>50.75521953556864</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>63.48963636605803</v>
+        <v>43.69735863472546</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>58.04356316438152</v>
+        <v>36.63949773388239</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>52.60271140089909</v>
+        <v>29.5816368330391</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>47.16754775265088</v>
+        <v>22.52377593219603</v>
       </c>
     </row>
     <row r="19">
@@ -2988,19 +2988,19 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>56.50638310547686</v>
+        <v>42.79873970509544</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>57.23625199428405</v>
+        <v>39.82120218385909</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>58.04356316438152</v>
+        <v>36.63949773388239</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>58.93310192687731</v>
+        <v>33.24239702293765</v>
       </c>
       <c r="F20" s="16" t="n">
-        <v>59.90984223453741</v>
+        <v>29.61825605669214</v>
       </c>
     </row>
     <row r="22">
@@ -3032,19 +3032,19 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>60.21623559180343</v>
+        <v>42.54294576364056</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>58.90647160099854</v>
+        <v>38.99364180915672</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>58.04356316438152</v>
+        <v>36.63949773388239</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>57.10944765905171</v>
+        <v>34.07581530837081</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>56.01651400062947</v>
+        <v>31.05447660436835</v>
       </c>
     </row>
     <row r="25">
@@ -3076,19 +3076,19 @@
         </is>
       </c>
       <c r="B26" s="16" t="n">
-        <v>69.40058103952305</v>
+        <v>33.91980523946785</v>
       </c>
       <c r="C26" s="16" t="n">
-        <v>72.92267594034055</v>
+        <v>37.23017363970158</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>77.29589290051553</v>
+        <v>41.26937562789497</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>82.94134866765025</v>
+        <v>46.32742747255725</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>90.61284023318153</v>
+        <v>52.87174617751678</v>
       </c>
     </row>
     <row r="27">
@@ -3098,19 +3098,19 @@
         </is>
       </c>
       <c r="B27" s="16" t="n">
-        <v>61.20967522657672</v>
+        <v>29.09798312781783</v>
       </c>
       <c r="C27" s="16" t="n">
-        <v>63.71911223049474</v>
+        <v>31.778273158147</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>66.74301308250047</v>
+        <v>34.99453268848002</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>70.5079448271878</v>
+        <v>38.94086106863173</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>75.39640303480886</v>
+        <v>43.91794786985742</v>
       </c>
     </row>
     <row r="28">
@@ -3120,19 +3120,19 @@
         </is>
       </c>
       <c r="B28" s="16" t="n">
-        <v>54.19932760616772</v>
+        <v>24.89238838802118</v>
       </c>
       <c r="C28" s="16" t="n">
-        <v>55.97105249260597</v>
+        <v>27.08100396297257</v>
       </c>
       <c r="D28" s="16" t="n">
-        <v>58.04356316438152</v>
+        <v>29.6689241928033</v>
       </c>
       <c r="E28" s="16" t="n">
-        <v>60.53620600076448</v>
+        <v>32.78882816716791</v>
       </c>
       <c r="F28" s="16" t="n">
-        <v>63.64109038776664</v>
+        <v>36.63949773388239</v>
       </c>
     </row>
     <row r="29">
@@ -3142,19 +3142,19 @@
         </is>
       </c>
       <c r="B29" s="16" t="n">
-        <v>48.13449081209406</v>
+        <v>21.19463710773727</v>
       </c>
       <c r="C29" s="16" t="n">
-        <v>49.36102634801223</v>
+        <v>22.99461214749164</v>
       </c>
       <c r="D29" s="16" t="n">
-        <v>50.75027515072584</v>
+        <v>25.09520754686392</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>52.36098143954015</v>
+        <v>27.5887007173728</v>
       </c>
       <c r="F29" s="16" t="n">
-        <v>54.28403585960935</v>
+        <v>30.60944067360987</v>
       </c>
     </row>
     <row r="30">
@@ -3164,19 +3164,19 @@
         </is>
       </c>
       <c r="B30" s="16" t="n">
-        <v>42.83851934755974</v>
+        <v>17.92025263747544</v>
       </c>
       <c r="C30" s="16" t="n">
-        <v>43.65755701531543</v>
+        <v>19.40957317966708</v>
       </c>
       <c r="D30" s="16" t="n">
-        <v>44.54905891123189</v>
+        <v>21.12709566972723</v>
       </c>
       <c r="E30" s="16" t="n">
-        <v>45.53702422829129</v>
+        <v>23.13790859590948</v>
       </c>
       <c r="F30" s="16" t="n">
-        <v>46.65736489261532</v>
+        <v>25.53445407113366</v>
       </c>
     </row>
     <row r="32">
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="B33" s="19" t="n">
-        <v>6930.883371175429</v>
+        <v>7982.760359839642</v>
       </c>
     </row>
     <row r="34">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="B34" s="17" t="n">
-        <v>0.2840609235494332</v>
+        <v>0.3002077087568915</v>
       </c>
     </row>
     <row r="35">
@@ -3213,7 +3213,7 @@
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>120.119295860926</v>
+        <v>113.854176701619</v>
       </c>
     </row>
     <row r="36">
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="B36" s="24" t="n">
-        <v>1.20119295860926</v>
+        <v>1.138541767016189</v>
       </c>
     </row>
   </sheetData>
@@ -3445,23 +3445,23 @@
         </is>
       </c>
       <c r="E6" s="41">
-        <f>('Balance Sheet'!E13-Assumptions!$C$74)/'Income Statement'!E17</f>
+        <f>('Balance Sheet'!E13-Assumptions!$C$75)/'Income Statement'!E17</f>
         <v/>
       </c>
       <c r="F6" s="41">
-        <f>('Balance Sheet'!F13-Assumptions!$C$74)/'Income Statement'!F17</f>
+        <f>('Balance Sheet'!F13-Assumptions!$C$75)/'Income Statement'!F17</f>
         <v/>
       </c>
       <c r="G6" s="41">
-        <f>('Balance Sheet'!G13-Assumptions!$C$74)/'Income Statement'!G17</f>
+        <f>('Balance Sheet'!G13-Assumptions!$C$75)/'Income Statement'!G17</f>
         <v/>
       </c>
       <c r="H6" s="41">
-        <f>('Balance Sheet'!H13-Assumptions!$C$74)/'Income Statement'!H17</f>
+        <f>('Balance Sheet'!H13-Assumptions!$C$75)/'Income Statement'!H17</f>
         <v/>
       </c>
       <c r="I6" s="41">
-        <f>('Balance Sheet'!I13-Assumptions!$C$74)/'Income Statement'!I17</f>
+        <f>('Balance Sheet'!I13-Assumptions!$C$75)/'Income Statement'!I17</f>
         <v/>
       </c>
     </row>
@@ -3580,23 +3580,23 @@
         </is>
       </c>
       <c r="E11" s="6">
-        <f>('Income Statement'!E15*(1-Assumptions!$C$10))/('Balance Sheet'!E2+'Balance Sheet'!E3+'Balance Sheet'!E19+Assumptions!$C$82)</f>
+        <f>('Income Statement'!E15*(1-Assumptions!$C$10))/('Balance Sheet'!E2+'Balance Sheet'!E3+'Balance Sheet'!E19+Assumptions!$C$83)</f>
         <v/>
       </c>
       <c r="F11" s="6">
-        <f>('Income Statement'!F15*(1-Assumptions!$C$10))/('Balance Sheet'!F2+'Balance Sheet'!F3+'Balance Sheet'!F19+Assumptions!$C$82)</f>
+        <f>('Income Statement'!F15*(1-Assumptions!$C$10))/('Balance Sheet'!F2+'Balance Sheet'!F3+'Balance Sheet'!F19+Assumptions!$C$83)</f>
         <v/>
       </c>
       <c r="G11" s="6">
-        <f>('Income Statement'!G15*(1-Assumptions!$C$10))/('Balance Sheet'!G2+'Balance Sheet'!G3+'Balance Sheet'!G19+Assumptions!$C$82)</f>
+        <f>('Income Statement'!G15*(1-Assumptions!$C$10))/('Balance Sheet'!G2+'Balance Sheet'!G3+'Balance Sheet'!G19+Assumptions!$C$83)</f>
         <v/>
       </c>
       <c r="H11" s="6">
-        <f>('Income Statement'!H15*(1-Assumptions!$C$10))/('Balance Sheet'!H2+'Balance Sheet'!H3+'Balance Sheet'!H19+Assumptions!$C$82)</f>
+        <f>('Income Statement'!H15*(1-Assumptions!$C$10))/('Balance Sheet'!H2+'Balance Sheet'!H3+'Balance Sheet'!H19+Assumptions!$C$83)</f>
         <v/>
       </c>
       <c r="I11" s="6">
-        <f>('Income Statement'!I15*(1-Assumptions!$C$10))/('Balance Sheet'!I2+'Balance Sheet'!I3+'Balance Sheet'!I19+Assumptions!$C$82)</f>
+        <f>('Income Statement'!I15*(1-Assumptions!$C$10))/('Balance Sheet'!I2+'Balance Sheet'!I3+'Balance Sheet'!I19+Assumptions!$C$83)</f>
         <v/>
       </c>
     </row>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>Terminal value 74% of core enterprise value, 62% of total</t>
+          <t>Terminal value 81% of core enterprise value, 63% of total</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Terminal value 75% of core enterprise value, 64% of total</t>
+          <t>Terminal value 81% of core enterprise value, 66% of total</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Justified 1.70 times book</t>
+          <t>Justified 1.19 times book</t>
         </is>
       </c>
     </row>
@@ -3990,7 +3990,7 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>WEIGHTED CENTRE — FRAME A</t>
+          <t>CENTRE — FRAME A (the cash-flow lens, unweighted)</t>
         </is>
       </c>
       <c r="B7" s="9">
@@ -4010,7 +4010,7 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>WEIGHTED CENTRE — FRAME B</t>
+          <t>CENTRE — FRAME B (the cash-flow lens, unweighted)</t>
         </is>
       </c>
       <c r="B8" s="9">
@@ -4034,11 +4034,11 @@
         </is>
       </c>
       <c r="B9" s="12">
-        <f>'Fundamental Valuation'!B9</f>
+        <f>'Fundamental Valuation'!B10</f>
         <v/>
       </c>
       <c r="C9" s="12">
-        <f>'Fundamental Valuation'!B10</f>
+        <f>'Fundamental Valuation'!B11</f>
         <v/>
       </c>
     </row>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="B13" s="13">
-        <f>Assumptions!$C$102</f>
+        <f>Assumptions!$C$103</f>
         <v/>
       </c>
     </row>
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>Assumptions!$C$103</f>
+        <f>Assumptions!$C$104</f>
         <v/>
       </c>
     </row>
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="B15" s="13">
-        <f>Assumptions!$C$102+Assumptions!$C$103+Assumptions!$C$79</f>
+        <f>Assumptions!$C$103+Assumptions!$C$104+Assumptions!$C$80</f>
         <v/>
       </c>
     </row>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="B20" s="14">
-        <f>(Assumptions!$C$102+Assumptions!$C$103+Assumptions!$C$79)/'Income Statement'!D17</f>
+        <f>(Assumptions!$C$103+Assumptions!$C$104+Assumptions!$C$80)/'Income Statement'!D17</f>
         <v/>
       </c>
     </row>
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="B21" s="15">
-        <f>Assumptions!$C$97</f>
+        <f>Assumptions!$C$98</f>
         <v/>
       </c>
     </row>
@@ -4166,7 +4166,7 @@
         </is>
       </c>
       <c r="B22" s="15">
-        <f>Assumptions!$C$106</f>
+        <f>Assumptions!$C$107</f>
         <v/>
       </c>
     </row>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="B23" s="15">
-        <f>Assumptions!$C$112</f>
+        <f>Assumptions!$C$113</f>
         <v/>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
         </is>
       </c>
       <c r="B24" s="6">
-        <f>DCF!B31</f>
+        <f>DCF!B34</f>
         <v/>
       </c>
     </row>
@@ -4224,7 +4224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="B3" s="12">
-        <f>DCF!B42</f>
+        <f>DCF!B47</f>
         <v/>
       </c>
       <c r="C3" s="17" t="n">
@@ -4300,7 +4300,7 @@
         </is>
       </c>
       <c r="B4" s="12">
-        <f>(('Relative &amp; Normalized'!B6-Assumptions!$C$62)/(Assumptions!$C$109-Assumptions!$C$62))*'Balance Sheet'!D20</f>
+        <f>(('Relative &amp; Normalized'!B6-Assumptions!$C$62)/(Assumptions!$C$110-Assumptions!$C$62))*'Balance Sheet'!D20</f>
         <v/>
       </c>
       <c r="C4" s="17" t="n">
@@ -4353,95 +4353,103 @@
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>WEIGHTED CENTRE — FRAME A</t>
+          <t>CENTRE — FRAME A (the cash-flow lens, unweighted)</t>
         </is>
       </c>
       <c r="B7" s="9">
-        <f>B2*C2+B4*C4+B5*C5+B6*C6</f>
-        <v/>
-      </c>
-      <c r="C7" s="10">
-        <f>C2+C4+C5+C6</f>
+        <f>B2</f>
         <v/>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>The discounted-cash-flow weight in full on Frame A, beside the three lenses that do not turn on the contested judgement. The weights sum to one; the cell to the left proves it.</t>
+          <t>The centre of each frame IS its own cash-flow read. The three lenses that do not turn on the contested judgement are published beside it and averaged into neither.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>WEIGHTED CENTRE — FRAME B</t>
+          <t>CENTRE — FRAME B (the cash-flow lens, unweighted)</t>
         </is>
       </c>
       <c r="B8" s="9">
-        <f>B3*C3+B4*C4+B5*C5+B6*C6</f>
-        <v/>
-      </c>
-      <c r="C8" s="10">
-        <f>C3+C4+C5+C6</f>
+        <f>B3</f>
         <v/>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>THE TWO CENTRES ARE NOT AVERAGED. Weighting both frames inside one number is a straight average of them, which is exactly what this study says it never does.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>Low of the field</t>
-        </is>
-      </c>
-      <c r="B9" s="12">
-        <f>MIN(B2:B6)</f>
-        <v/>
+          <t>THE TWO CENTRES ARE NOT AVERAGED. One number covering both frames is a straight average of them, which is exactly what this study says it never does.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Memo — the retired weighted blend this edition replaced, on Frame A</t>
+        </is>
+      </c>
+      <c r="B9" s="5">
+        <f>B2*C2+B4*C4+B5*C5+B6*C6</f>
+        <v/>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Printed so the change is visible rather than only described. Its weights had never been tested out of sample, and one of the four readings it carried is not a lens this class uses at all.</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>High of the field</t>
+          <t>Low of the field</t>
         </is>
       </c>
       <c r="B10" s="12">
-        <f>MAX(B2:B6)</f>
+        <f>MIN(B2:B6)</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
+          <t>High of the field</t>
+        </is>
+      </c>
+      <c r="B11" s="12">
+        <f>MAX(B2:B6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
           <t>Market price</t>
         </is>
       </c>
-      <c r="B11" s="12">
+      <c r="B12" s="12">
         <f>Assumptions!$C$3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>Market price relative to the Frame A centre</t>
-        </is>
-      </c>
-      <c r="B12" s="10">
-        <f>B11/B7-1</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
+          <t>Market price relative to the Frame A centre</t>
+        </is>
+      </c>
+      <c r="B13" s="10">
+        <f>B12/B7-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
           <t>Market price relative to the Frame B centre</t>
         </is>
       </c>
-      <c r="B13" s="10">
-        <f>B11/B8-1</f>
+      <c r="B14" s="10">
+        <f>B12/B8-1</f>
         <v/>
       </c>
     </row>
@@ -4456,7 +4464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -4524,7 +4532,7 @@
         </is>
       </c>
       <c r="C3" s="16" t="n">
-        <v>130.05</v>
+        <v>127.3</v>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
@@ -4786,19 +4794,19 @@
         </is>
       </c>
       <c r="C17" s="16" t="n">
-        <v>50.5</v>
+        <v>55.1141</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>52.5</v>
+        <v>60.2223</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>54.3</v>
+        <v>64.04130000000001</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>56</v>
+        <v>67.1652</v>
       </c>
       <c r="G17" s="16" t="n">
-        <v>57.7</v>
+        <v>70.1139</v>
       </c>
     </row>
     <row r="18">
@@ -4994,19 +5002,19 @@
         </is>
       </c>
       <c r="C29" s="17" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D29" s="17" t="n">
         <v>0.12</v>
       </c>
-      <c r="D29" s="17" t="n">
-        <v>0.1</v>
-      </c>
       <c r="E29" s="17" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="F29" s="17" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="G29" s="17" t="n">
         <v>0.07000000000000001</v>
-      </c>
-      <c r="G29" s="17" t="n">
-        <v>0.06</v>
       </c>
     </row>
     <row r="30">
@@ -5539,7 +5547,7 @@
         </is>
       </c>
       <c r="C56" s="21" t="n">
-        <v>0.105</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="57" ht="26" customHeight="1">
@@ -5599,7 +5607,7 @@
         </is>
       </c>
       <c r="C60" s="17" t="n">
-        <v>0.251247066000691</v>
+        <v>0.2552890355474502</v>
       </c>
     </row>
     <row r="61" ht="26" customHeight="1">
@@ -5614,7 +5622,7 @@
         </is>
       </c>
       <c r="C61" s="17" t="n">
-        <v>0.398408806312907</v>
+        <v>0.4792091017585894</v>
       </c>
     </row>
     <row r="62" ht="26" customHeight="1">
@@ -5629,7 +5637,7 @@
         </is>
       </c>
       <c r="C62" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000006</v>
       </c>
     </row>
     <row r="63" ht="26" customHeight="1">
@@ -5677,460 +5685,459 @@
         <v>21.35</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="8" t="inlineStr">
+    <row r="66" ht="26" customHeight="1">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Cost of equity faced by the struck reference companies</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>The ONE difference the peer multiple is adjusted for, registered here rather than typed inside the adjustment so a reader can see what the adjustment is made of</t>
+        </is>
+      </c>
+      <c r="C66" s="17" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
         <is>
           <t>OPENING BALANCE SHEET (AUDITED, 31 DECEMBER 2025)</t>
         </is>
-      </c>
-    </row>
-    <row r="67" ht="26" customHeight="1">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>Property, plant and equipment, net</t>
-        </is>
-      </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>Note (4)</t>
-        </is>
-      </c>
-      <c r="C67" s="19" t="n">
-        <v>3069.747924</v>
       </c>
     </row>
     <row r="68" ht="26" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>Projects under construction</t>
+          <t>Property, plant and equipment, net</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>Note (6)</t>
+          <t>Note (4)</t>
         </is>
       </c>
       <c r="C68" s="19" t="n">
-        <v>4901.223806</v>
+        <v>3069.747924</v>
       </c>
     </row>
     <row r="69" ht="26" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Inventories, net</t>
+          <t>Projects under construction</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Note (9)</t>
+          <t>Note (6)</t>
         </is>
       </c>
       <c r="C69" s="19" t="n">
-        <v>3887.077629</v>
+        <v>4901.223806</v>
       </c>
     </row>
     <row r="70" ht="26" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Trade and notes receivable, net</t>
+          <t>Inventories, net</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Note (10)</t>
+          <t>Note (9)</t>
         </is>
       </c>
       <c r="C70" s="19" t="n">
-        <v>3325.044117</v>
+        <v>3887.077629</v>
       </c>
     </row>
     <row r="71" ht="26" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Other debtors</t>
+          <t>Trade and notes receivable, net</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>Note (11)</t>
+          <t>Note (10)</t>
         </is>
       </c>
       <c r="C71" s="19" t="n">
-        <v>356.786958</v>
+        <v>3325.044117</v>
       </c>
     </row>
     <row r="72" ht="26" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>Trade and notes payable</t>
+          <t>Other debtors</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>Note (22)</t>
+          <t>Note (11)</t>
         </is>
       </c>
       <c r="C72" s="19" t="n">
-        <v>780.416969</v>
+        <v>356.786958</v>
       </c>
     </row>
     <row r="73" ht="26" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Other creditors</t>
+          <t>Trade and notes payable</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>Note (23)</t>
+          <t>Note (22)</t>
         </is>
       </c>
       <c r="C73" s="19" t="n">
-        <v>1044.832275</v>
+        <v>780.416969</v>
       </c>
     </row>
     <row r="74" ht="26" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Cash and bank balances</t>
+          <t>Other creditors</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>Note (12)</t>
+          <t>Note (23)</t>
         </is>
       </c>
       <c r="C74" s="19" t="n">
-        <v>1433.426902</v>
+        <v>1044.832275</v>
       </c>
     </row>
     <row r="75" ht="26" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Gross borrowings including leases</t>
+          <t>Cash and bank balances</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>Notes (17), (18) and (21)</t>
+          <t>Note (12)</t>
         </is>
       </c>
       <c r="C75" s="19" t="n">
-        <v>8797.725640000001</v>
+        <v>1433.426902</v>
       </c>
     </row>
     <row r="76" ht="26" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Attributable profit, FY2025 (EGP mn)</t>
+          <t>Gross borrowings including leases</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>Audited — the trailing earnings base for every trailing multiple</t>
+          <t>Notes (17), (18) and (21)</t>
         </is>
       </c>
       <c r="C76" s="19" t="n">
-        <v>1441.6577</v>
+        <v>8797.725640000001</v>
       </c>
     </row>
     <row r="77" ht="26" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Equity attributable to the holding company</t>
+          <t>Attributable profit, FY2025 (EGP mn)</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>Audited</t>
+          <t>Audited — the trailing earnings base for every trailing multiple</t>
         </is>
       </c>
       <c r="C77" s="19" t="n">
-        <v>6243.131482</v>
+        <v>1441.6577</v>
       </c>
     </row>
     <row r="78" ht="26" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>Non-controlling interests, audited 31 December 2025</t>
+          <t>Equity attributable to the holding company</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>disclosure — the audited December figure, shown so the reader can see both. It is SUPERSEDED for valuation by the March figure below, because almost all of it was the active-ingredient company and that company was deconsolidated in the first quarter of 2026. This row drives the balance sheet history only</t>
+          <t>Audited</t>
         </is>
       </c>
       <c r="C78" s="19" t="n">
-        <v>288.704605</v>
+        <v>6243.131482</v>
       </c>
     </row>
     <row r="79" ht="26" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>Non-controlling interests deducted in the bridge</t>
+          <t>Non-controlling interests, audited 31 December 2025</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>Post-deconsolidation, from the reviewed 31 March 2026 interim</t>
+          <t>disclosure — the audited December figure, shown so the reader can see both. It is SUPERSEDED for valuation by the March figure below, because almost all of it was the active-ingredient company and that company was deconsolidated in the first quarter of 2026. This row drives the balance sheet history only</t>
         </is>
       </c>
       <c r="C79" s="19" t="n">
-        <v>3.999807</v>
+        <v>288.704605</v>
       </c>
     </row>
     <row r="80" ht="26" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>Active-ingredient company at carrying cost (EGP mn)</t>
+          <t>Non-controlling interests deducted in the bridge</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>Pre-revenue, so cost not an earnings multiple; the Q1-2026 movement in investments in associates</t>
+          <t>Post-deconsolidation, from the reviewed 31 March 2026 interim</t>
         </is>
       </c>
       <c r="C80" s="19" t="n">
-        <v>228.4864180000001</v>
+        <v>3.999807</v>
       </c>
     </row>
     <row r="81" ht="26" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Assets held for sale</t>
+          <t>Active-ingredient company at carrying cost (EGP mn)</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>Note (8/1)</t>
+          <t>Pre-revenue, so cost not an earnings multiple; the Q1-2026 movement in investments in associates</t>
         </is>
       </c>
       <c r="C81" s="19" t="n">
-        <v>12.33</v>
+        <v>228.4864180000001</v>
       </c>
     </row>
     <row r="82" ht="26" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>Intangible assets, net</t>
+          <t>Assets held for sale</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>Note (7)</t>
+          <t>Note (8/1)</t>
         </is>
       </c>
       <c r="C82" s="19" t="n">
-        <v>40.142171</v>
+        <v>12.33</v>
       </c>
     </row>
     <row r="83" ht="26" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>Right-of-use and intangible amortisation run-rate</t>
+          <t>Intangible assets, net</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>Audited FY2025 cash-flow statement</t>
-        </is>
-      </c>
-      <c r="C83" s="25" t="n">
-        <v>8.269948999999997</v>
+          <t>Note (7)</t>
+        </is>
+      </c>
+      <c r="C83" s="19" t="n">
+        <v>40.142171</v>
       </c>
     </row>
     <row r="84" ht="26" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>Share of depreciation charged to cost of sales</t>
+          <t>Right-of-use and intangible amortisation run-rate</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>Cost of sales note (26): 93.498 of 117.725</t>
-        </is>
-      </c>
-      <c r="C84" s="17" t="n">
-        <v>0.7942005773538676</v>
+          <t>Audited FY2025 cash-flow statement</t>
+        </is>
+      </c>
+      <c r="C84" s="25" t="n">
+        <v>8.269948999999997</v>
       </c>
     </row>
     <row r="85" ht="26" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>FY2025 cash cost per pack sold (EGP)</t>
+          <t>Share of depreciation charged to cost of sales</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>Cost of sales less its depreciation line, over packs sold</t>
-        </is>
-      </c>
-      <c r="C85" s="16" t="n">
-        <v>14.53600902055724</v>
+          <t>Cost of sales note (26): 93.498 of 117.725</t>
+        </is>
+      </c>
+      <c r="C85" s="17" t="n">
+        <v>0.7942005773538676</v>
       </c>
     </row>
     <row r="86" ht="26" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>Consolidated-to-separate revenue factor</t>
+          <t>FY2025 cash cost per pack sold (EGP)</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>MEASURED: audited consolidated revenue over the separate-company channel total</t>
-        </is>
-      </c>
-      <c r="C86" s="26" t="n">
-        <v>1.014932591450432</v>
+          <t>Cost of sales less its depreciation line, over packs sold</t>
+        </is>
+      </c>
+      <c r="C86" s="16" t="n">
+        <v>14.53600902055724</v>
       </c>
     </row>
     <row r="87" ht="26" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>FY2025 packs sold of the company's OWN preparations (million)</t>
+          <t>Consolidated-to-separate revenue factor</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>Board report, sales-indicators table</t>
-        </is>
-      </c>
-      <c r="C87" s="18" t="n">
-        <v>351.81</v>
+          <t>MEASURED: audited consolidated revenue over the separate-company channel total</t>
+        </is>
+      </c>
+      <c r="C87" s="26" t="n">
+        <v>1.014932591450432</v>
       </c>
     </row>
     <row r="88" ht="26" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>FY2025 export packs (million)</t>
+          <t>FY2025 packs sold of the company's OWN preparations (million)</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>Investor presentation</t>
+          <t>Board report, sales-indicators table</t>
         </is>
       </c>
       <c r="C88" s="18" t="n">
-        <v>60</v>
+        <v>351.81</v>
       </c>
     </row>
     <row r="89" ht="26" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>FY2025 export revenue (EGP mn)</t>
+          <t>FY2025 export packs (million)</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>Revenue note (25)</t>
-        </is>
-      </c>
-      <c r="C89" s="19" t="n">
-        <v>2967.479908</v>
+          <t>Investor presentation</t>
+        </is>
+      </c>
+      <c r="C89" s="18" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="90" ht="26" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>FY2025 sales value of the company's OWN preparations (EGP mn)</t>
+          <t>FY2025 export revenue (EGP mn)</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>Board report, sales-indicators table</t>
+          <t>Revenue note (25)</t>
         </is>
       </c>
       <c r="C90" s="19" t="n">
-        <v>9160.147999999999</v>
+        <v>2967.479908</v>
       </c>
     </row>
     <row r="91" ht="26" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>FY2025 sales value of CONTRACT-MANUFACTURED preparations (EGP mn)</t>
+          <t>FY2025 sales value of the company's OWN preparations (EGP mn)</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>Board report, sales-indicators table — product value, not the fee the company books</t>
+          <t>Board report, sales-indicators table</t>
         </is>
       </c>
       <c r="C91" s="19" t="n">
-        <v>142.321</v>
+        <v>9160.147999999999</v>
       </c>
     </row>
     <row r="92" ht="26" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>FY2025 contract-manufactured packs (million)</t>
+          <t>FY2025 sales value of CONTRACT-MANUFACTURED preparations (EGP mn)</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>Board report</t>
-        </is>
-      </c>
-      <c r="C92" s="18" t="n">
-        <v>5.485</v>
+          <t>Board report, sales-indicators table — product value, not the fee the company books</t>
+        </is>
+      </c>
+      <c r="C92" s="19" t="n">
+        <v>142.321</v>
       </c>
     </row>
     <row r="93" ht="26" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>FY2025 contract-manufacturing FEE revenue (EGP mn)</t>
+          <t>FY2025 contract-manufactured packs (million)</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>disclosure — this row SPLITS the contract-manufacturing line in two and cannot move the valuation by construction: the fee per pack rises by exactly what the resale price per pack falls, so the product value above is what reaches revenue either way. It is carried because the two halves are disclosed separately and a reader should see both. Revenue note (25)</t>
-        </is>
-      </c>
-      <c r="C93" s="25" t="n">
-        <v>49.366365</v>
+          <t>Board report</t>
+        </is>
+      </c>
+      <c r="C93" s="18" t="n">
+        <v>5.485</v>
       </c>
     </row>
     <row r="94" ht="26" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
         <is>
+          <t>FY2025 contract-manufacturing FEE revenue (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>disclosure — this row SPLITS the contract-manufacturing line in two and cannot move the valuation by construction: the fee per pack rises by exactly what the resale price per pack falls, so the product value above is what reaches revenue either way. It is carried because the two halves are disclosed separately and a reader should see both. Revenue note (25)</t>
+        </is>
+      </c>
+      <c r="C94" s="25" t="n">
+        <v>49.366365</v>
+      </c>
+    </row>
+    <row r="95" ht="26" customHeight="1">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
           <t>FY2025 average exchange rate</t>
         </is>
       </c>
-      <c r="B94" s="7" t="inlineStr">
+      <c r="B95" s="7" t="inlineStr">
         <is>
           <t>Note (36)</t>
         </is>
       </c>
-      <c r="C94" s="16" t="n">
+      <c r="C95" s="16" t="n">
         <v>49.48</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="8" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="8" t="inlineStr">
         <is>
           <t>DERIVED IN THIS SHEET (formulas, not inputs)</t>
         </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="4" t="inlineStr">
-        <is>
-          <t>Normalised risk-free rate = yield less sovereign spread</t>
-        </is>
-      </c>
-      <c r="B96" s="7" t="inlineStr">
-        <is>
-          <t>calculated</t>
-        </is>
-      </c>
-      <c r="C96" s="27">
-        <f>$C$44-$C$45</f>
-        <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>Cost of equity = normalised risk-free + beta x premium</t>
+          <t>Normalised risk-free rate = yield less sovereign spread</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
@@ -6139,14 +6146,14 @@
         </is>
       </c>
       <c r="C97" s="27">
-        <f>$C$96+$C$49*$C$46</f>
+        <f>$C$44-$C$45</f>
         <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>Cost of equity, rating basis (published alternative)</t>
+          <t>Cost of equity = normalised risk-free + beta x premium</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
@@ -6155,14 +6162,14 @@
         </is>
       </c>
       <c r="C98" s="27">
-        <f>($C$44-$C$47)+$C$49*$C$48</f>
+        <f>$C$97+$C$49*$C$46</f>
         <v/>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>Hard-currency debt at LOCAL-EQUIVALENT cost</t>
+          <t>Cost of equity, rating basis (published alternative)</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
@@ -6171,14 +6178,14 @@
         </is>
       </c>
       <c r="C99" s="27">
-        <f>(1+$C$51)*(1+$C$52)-1</f>
+        <f>($C$44-$C$47)+$C$49*$C$48</f>
         <v/>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>Blended marginal cost of debt</t>
+          <t>Hard-currency debt at LOCAL-EQUIVALENT cost</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
@@ -6187,14 +6194,14 @@
         </is>
       </c>
       <c r="C100" s="27">
-        <f>(1-$C$53)*$C$50+$C$53*$C$99</f>
+        <f>(1+$C$51)*(1+$C$52)-1</f>
         <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>Cost of debt after tax</t>
+          <t>Blended marginal cost of debt</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
@@ -6203,14 +6210,14 @@
         </is>
       </c>
       <c r="C101" s="27">
-        <f>$C$100*(1-$C$9)</f>
+        <f>(1-$C$53)*$C$50+$C$53*$C$100</f>
         <v/>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>Market capitalisation (EGP mn)</t>
+          <t>Cost of debt after tax</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
@@ -6218,15 +6225,15 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C102" s="28">
-        <f>$C$3*$C$8</f>
+      <c r="C102" s="27">
+        <f>$C$101*(1-$C$9)</f>
         <v/>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>Net debt (EGP mn)</t>
+          <t>Market capitalisation (EGP mn)</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
@@ -6235,14 +6242,14 @@
         </is>
       </c>
       <c r="C103" s="28">
-        <f>$C$75-$C$74</f>
+        <f>$C$3*$C$8</f>
         <v/>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>Equity weight (net basis)</t>
+          <t>Net debt (EGP mn)</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
@@ -6250,15 +6257,15 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C104" s="29">
-        <f>$C$102/($C$102+$C$103)</f>
+      <c r="C104" s="28">
+        <f>$C$76-$C$75</f>
         <v/>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>Debt weight (net basis)</t>
+          <t>Equity weight (net basis)</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
@@ -6267,14 +6274,14 @@
         </is>
       </c>
       <c r="C105" s="29">
-        <f>1-$C$104</f>
+        <f>$C$103/($C$103+$C$104)</f>
         <v/>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>Weighted average cost of capital, year one</t>
+          <t>Debt weight (net basis)</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
@@ -6282,15 +6289,15 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C106" s="27">
-        <f>$C$104*$C$97+$C$105*$C$101</f>
+      <c r="C106" s="29">
+        <f>1-$C$105</f>
         <v/>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>Debt weight (gross basis)</t>
+          <t>Weighted average cost of capital, year one</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
@@ -6298,15 +6305,15 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C107" s="29">
-        <f>$C$75/($C$102+$C$75)</f>
+      <c r="C107" s="27">
+        <f>$C$105*$C$98+$C$106*$C$102</f>
         <v/>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>Weighted average cost of capital, gross-debt basis</t>
+          <t>Debt weight (gross basis)</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
@@ -6314,15 +6321,15 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C108" s="27">
-        <f>(1-$C$107)*$C$97+$C$107*$C$101</f>
+      <c r="C108" s="29">
+        <f>$C$76/($C$103+$C$76)</f>
         <v/>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>Terminal cost of equity</t>
+          <t>Weighted average cost of capital, gross-debt basis</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
@@ -6331,14 +6338,14 @@
         </is>
       </c>
       <c r="C109" s="27">
-        <f>$C$56+$C$49*$C$57</f>
+        <f>(1-$C$108)*$C$98+$C$108*$C$102</f>
         <v/>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>Terminal cost of debt</t>
+          <t>Terminal cost of equity</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
@@ -6347,14 +6354,14 @@
         </is>
       </c>
       <c r="C110" s="27">
-        <f>(1-$C$53)*$C$58+$C$53*((1+$C$59)*1.03-1)</f>
+        <f>$C$56+$C$49*$C$57</f>
         <v/>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>Terminal cost of debt after tax</t>
+          <t>Terminal cost of debt</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
@@ -6363,119 +6370,135 @@
         </is>
       </c>
       <c r="C111" s="27">
-        <f>$C$110*(1-$C$9)</f>
+        <f>(1-$C$53)*$C$58+$C$53*((1+$C$59)*1.03-1)</f>
         <v/>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
+          <t>Terminal cost of debt after tax</t>
+        </is>
+      </c>
+      <c r="B112" s="7" t="inlineStr">
+        <is>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="C112" s="27">
+        <f>$C$111*(1-$C$9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
           <t>Terminal weighted average cost of capital</t>
         </is>
       </c>
-      <c r="B112" s="7" t="inlineStr">
+      <c r="B113" s="7" t="inlineStr">
         <is>
           <t>calculated</t>
         </is>
       </c>
-      <c r="C112" s="27">
-        <f>(1-$C$60)*$C$109+$C$60*$C$111</f>
-        <v/>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="11" t="inlineStr">
-        <is>
-          <t>Glide fraction (derived from the convergence path — SHAPE only)</t>
-        </is>
-      </c>
-      <c r="B113" s="7" t="inlineStr">
-        <is>
-          <t>calculated: (this year's cost of debt less the last year's) over (the first year's less the last year's)</t>
-        </is>
-      </c>
-      <c r="C113" s="30">
-        <f>(C$54-$G$54)/($C$54-$G$54)</f>
-        <v/>
-      </c>
-      <c r="D113" s="30">
-        <f>(D$54-$G$54)/($C$54-$G$54)</f>
-        <v/>
-      </c>
-      <c r="E113" s="30">
-        <f>(E$54-$G$54)/($C$54-$G$54)</f>
-        <v/>
-      </c>
-      <c r="F113" s="30">
-        <f>(F$54-$G$54)/($C$54-$G$54)</f>
-        <v/>
-      </c>
-      <c r="G113" s="30">
-        <f>(G$54-$G$54)/($C$54-$G$54)</f>
+      <c r="C113" s="27">
+        <f>(1-$C$60)*$C$110+$C$60*$C$112</f>
         <v/>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>Discount rate</t>
+          <t>Glide fraction (derived from the convergence path — SHAPE only)</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
         <is>
-          <t>calculated: terminal rate plus the glide fraction of the gap to year one</t>
-        </is>
-      </c>
-      <c r="C114" s="15">
-        <f>$C$112+($C$106-$C$112)*C$113</f>
-        <v/>
-      </c>
-      <c r="D114" s="15">
-        <f>$C$112+($C$106-$C$112)*D$113</f>
-        <v/>
-      </c>
-      <c r="E114" s="15">
-        <f>$C$112+($C$106-$C$112)*E$113</f>
-        <v/>
-      </c>
-      <c r="F114" s="15">
-        <f>$C$112+($C$106-$C$112)*F$113</f>
-        <v/>
-      </c>
-      <c r="G114" s="15">
-        <f>$C$112+($C$106-$C$112)*G$113</f>
+          <t>calculated: (this year's cost of debt less the last year's) over (the first year's less the last year's)</t>
+        </is>
+      </c>
+      <c r="C114" s="30">
+        <f>(C$54-$G$54)/($C$54-$G$54)</f>
+        <v/>
+      </c>
+      <c r="D114" s="30">
+        <f>(D$54-$G$54)/($C$54-$G$54)</f>
+        <v/>
+      </c>
+      <c r="E114" s="30">
+        <f>(E$54-$G$54)/($C$54-$G$54)</f>
+        <v/>
+      </c>
+      <c r="F114" s="30">
+        <f>(F$54-$G$54)/($C$54-$G$54)</f>
+        <v/>
+      </c>
+      <c r="G114" s="30">
+        <f>(G$54-$G$54)/($C$54-$G$54)</f>
         <v/>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
         <is>
+          <t>Discount rate</t>
+        </is>
+      </c>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>calculated: terminal rate plus the glide fraction of the gap to year one</t>
+        </is>
+      </c>
+      <c r="C115" s="15">
+        <f>$C$113+($C$107-$C$113)*C$114</f>
+        <v/>
+      </c>
+      <c r="D115" s="15">
+        <f>$C$113+($C$107-$C$113)*D$114</f>
+        <v/>
+      </c>
+      <c r="E115" s="15">
+        <f>$C$113+($C$107-$C$113)*E$114</f>
+        <v/>
+      </c>
+      <c r="F115" s="15">
+        <f>$C$113+($C$107-$C$113)*F$114</f>
+        <v/>
+      </c>
+      <c r="G115" s="15">
+        <f>$C$113+($C$107-$C$113)*G$114</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="11" t="inlineStr">
+        <is>
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B115" s="7" t="inlineStr">
+      <c r="B116" s="7" t="inlineStr">
         <is>
           <t>calculated: the previous factor divided by one plus this year's rate — the factors compound</t>
         </is>
       </c>
-      <c r="C115" s="31">
-        <f>1/(1+C$114)</f>
-        <v/>
-      </c>
-      <c r="D115" s="31">
-        <f>C115/(1+D$114)</f>
-        <v/>
-      </c>
-      <c r="E115" s="31">
-        <f>D115/(1+E$114)</f>
-        <v/>
-      </c>
-      <c r="F115" s="31">
-        <f>E115/(1+F$114)</f>
-        <v/>
-      </c>
-      <c r="G115" s="31">
-        <f>F115/(1+G$114)</f>
+      <c r="C116" s="31">
+        <f>1/(1+C$115)</f>
+        <v/>
+      </c>
+      <c r="D116" s="31">
+        <f>C116/(1+D$115)</f>
+        <v/>
+      </c>
+      <c r="E116" s="31">
+        <f>D116/(1+E$115)</f>
+        <v/>
+      </c>
+      <c r="F116" s="31">
+        <f>E116/(1+F$115)</f>
+        <v/>
+      </c>
+      <c r="G116" s="31">
+        <f>F116/(1+G$115)</f>
         <v/>
       </c>
     </row>
@@ -6522,7 +6545,7 @@
         </is>
       </c>
       <c r="B2" s="13">
-        <f>DCF!B30</f>
+        <f>DCF!B33</f>
         <v/>
       </c>
       <c r="C2" s="5">
@@ -6537,7 +6560,7 @@
         </is>
       </c>
       <c r="B3" s="13">
-        <f>DCF!B27</f>
+        <f>DCF!B30</f>
         <v/>
       </c>
       <c r="C3" s="5">
@@ -6552,7 +6575,7 @@
         </is>
       </c>
       <c r="B4" s="10">
-        <f>DCF!B31</f>
+        <f>DCF!B34</f>
         <v/>
       </c>
     </row>
@@ -6578,7 +6601,7 @@
         </is>
       </c>
       <c r="B6" s="13">
-        <f>Assumptions!$C$80</f>
+        <f>Assumptions!$C$81</f>
         <v/>
       </c>
       <c r="C6" s="5">
@@ -6593,7 +6616,7 @@
         </is>
       </c>
       <c r="B7" s="13">
-        <f>Assumptions!$C$81</f>
+        <f>Assumptions!$C$82</f>
         <v/>
       </c>
       <c r="C7" s="5">
@@ -6623,7 +6646,7 @@
         </is>
       </c>
       <c r="B9" s="13">
-        <f>-Assumptions!$C$103</f>
+        <f>-Assumptions!$C$104</f>
         <v/>
       </c>
       <c r="C9" s="5">
@@ -6638,7 +6661,7 @@
         </is>
       </c>
       <c r="B10" s="13">
-        <f>-Assumptions!$C$79</f>
+        <f>-Assumptions!$C$80</f>
         <v/>
       </c>
       <c r="C10" s="5">
@@ -6752,7 +6775,7 @@
         <v>244.272</v>
       </c>
       <c r="C2" s="33">
-        <f>Assumptions!$C$87-Assumptions!$C$88</f>
+        <f>Assumptions!$C$88-Assumptions!$C$89</f>
         <v/>
       </c>
       <c r="D2" s="5">
@@ -6786,7 +6809,7 @@
         <v>54.7</v>
       </c>
       <c r="C3" s="33">
-        <f>Assumptions!$C$88</f>
+        <f>Assumptions!$C$89</f>
         <v/>
       </c>
       <c r="D3" s="5">
@@ -6924,7 +6947,7 @@
         <v/>
       </c>
       <c r="C7" s="13">
-        <f>Assumptions!$C$90-C8</f>
+        <f>Assumptions!$C$91-C8</f>
         <v/>
       </c>
       <c r="D7" s="34">
@@ -6958,7 +6981,7 @@
         <v>2500.155946</v>
       </c>
       <c r="C8" s="13">
-        <f>Assumptions!$C$89</f>
+        <f>Assumptions!$C$90</f>
         <v/>
       </c>
       <c r="D8" s="34">
@@ -6992,7 +7015,7 @@
         <v>8.874000000000001</v>
       </c>
       <c r="C9" s="33">
-        <f>Assumptions!$C$92</f>
+        <f>Assumptions!$C$93</f>
         <v/>
       </c>
       <c r="D9" s="33">
@@ -7027,7 +7050,7 @@
         <v/>
       </c>
       <c r="C10" s="5">
-        <f>Assumptions!$C$93/C9</f>
+        <f>Assumptions!$C$94/C9</f>
         <v/>
       </c>
       <c r="D10" s="5">
@@ -7062,7 +7085,7 @@
         <v/>
       </c>
       <c r="C11" s="5">
-        <f>(Assumptions!$C$91-Assumptions!$C$93)/C9</f>
+        <f>(Assumptions!$C$92-Assumptions!$C$94)/C9</f>
         <v/>
       </c>
       <c r="D11" s="5">
@@ -7202,23 +7225,23 @@
         <v>9441.379305</v>
       </c>
       <c r="D15" s="32">
-        <f>(D7+D8+D12+D13)*Assumptions!$C$86</f>
+        <f>(D7+D8+D12+D13)*Assumptions!$C$87</f>
         <v/>
       </c>
       <c r="E15" s="32">
-        <f>(E7+E8+E12+E13)*Assumptions!$C$86</f>
+        <f>(E7+E8+E12+E13)*Assumptions!$C$87</f>
         <v/>
       </c>
       <c r="F15" s="32">
-        <f>(F7+F8+F12+F13)*Assumptions!$C$86</f>
+        <f>(F7+F8+F12+F13)*Assumptions!$C$87</f>
         <v/>
       </c>
       <c r="G15" s="32">
-        <f>(G7+G8+G12+G13)*Assumptions!$C$86</f>
+        <f>(G7+G8+G12+G13)*Assumptions!$C$87</f>
         <v/>
       </c>
       <c r="H15" s="32">
-        <f>(H7+H8+H12+H13)*Assumptions!$C$86</f>
+        <f>(H7+H8+H12+H13)*Assumptions!$C$87</f>
         <v/>
       </c>
     </row>
@@ -7325,7 +7348,7 @@
         </is>
       </c>
       <c r="D26" s="31">
-        <f>((1+Assumptions!$C$25)*(Segments!D6/Assumptions!$C$94))</f>
+        <f>((1+Assumptions!$C$25)*(Segments!D6/Assumptions!$C$95))</f>
         <v/>
       </c>
       <c r="E26" s="31">
@@ -7352,7 +7375,7 @@
         </is>
       </c>
       <c r="D27" s="31">
-        <f>(Assumptions!$C$26*(1+Assumptions!$C$25)*(Segments!D6/Assumptions!$C$94)+(1-Assumptions!$C$26)*(1+Assumptions!C$29))</f>
+        <f>(Assumptions!$C$26*(1+Assumptions!$C$25)*(Segments!D6/Assumptions!$C$95)+(1-Assumptions!$C$26)*(1+Assumptions!C$29))</f>
         <v/>
       </c>
       <c r="E27" s="31">
@@ -7487,23 +7510,23 @@
         </is>
       </c>
       <c r="D32" s="12">
-        <f>Assumptions!$C$85*D31</f>
+        <f>Assumptions!$C$86*D31</f>
         <v/>
       </c>
       <c r="E32" s="12">
-        <f>Assumptions!$C$85*E31</f>
+        <f>Assumptions!$C$86*E31</f>
         <v/>
       </c>
       <c r="F32" s="12">
-        <f>Assumptions!$C$85*F31</f>
+        <f>Assumptions!$C$86*F31</f>
         <v/>
       </c>
       <c r="G32" s="12">
-        <f>Assumptions!$C$85*G31</f>
+        <f>Assumptions!$C$86*G31</f>
         <v/>
       </c>
       <c r="H32" s="12">
-        <f>Assumptions!$C$85*H31</f>
+        <f>Assumptions!$C$86*H31</f>
         <v/>
       </c>
     </row>
@@ -7521,7 +7544,7 @@
         </is>
       </c>
       <c r="D35" s="13">
-        <f>Assumptions!$C$67</f>
+        <f>Assumptions!$C$68</f>
         <v/>
       </c>
       <c r="E35" s="13">
@@ -7602,23 +7625,23 @@
         </is>
       </c>
       <c r="D38" s="35">
-        <f>-Assumptions!$C$83</f>
+        <f>-Assumptions!$C$84</f>
         <v/>
       </c>
       <c r="E38" s="35">
-        <f>-Assumptions!$C$83</f>
+        <f>-Assumptions!$C$84</f>
         <v/>
       </c>
       <c r="F38" s="35">
-        <f>-Assumptions!$C$83</f>
+        <f>-Assumptions!$C$84</f>
         <v/>
       </c>
       <c r="G38" s="35">
-        <f>-Assumptions!$C$83</f>
+        <f>-Assumptions!$C$84</f>
         <v/>
       </c>
       <c r="H38" s="35">
-        <f>-Assumptions!$C$83</f>
+        <f>-Assumptions!$C$84</f>
         <v/>
       </c>
     </row>
@@ -7710,7 +7733,7 @@
         </is>
       </c>
       <c r="D42" s="13">
-        <f>Assumptions!$C$68</f>
+        <f>Assumptions!$C$69</f>
         <v/>
       </c>
       <c r="E42" s="13">
@@ -7911,7 +7934,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>((DCF!B35-Assumptions!C$55)*(1-Assumptions!$C$10)+Assumptions!$C$63-18.0)/Assumptions!$C$8</f>
+        <f>((DCF!B38-Assumptions!C$55)*(1-Assumptions!$C$10)+Assumptions!$C$63-18.0)/Assumptions!$C$8</f>
         <v/>
       </c>
     </row>
@@ -7938,7 +7961,7 @@
         </is>
       </c>
       <c r="B12" s="12">
-        <f>Assumptions!$C$76/Assumptions!$C$8</f>
+        <f>Assumptions!$C$77/Assumptions!$C$8</f>
         <v/>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -8089,7 +8112,7 @@
         <v/>
       </c>
       <c r="C23" s="5">
-        <f>Assumptions!$C$76/162.016024</f>
+        <f>Assumptions!$C$77/162.016024</f>
         <v/>
       </c>
       <c r="D23" s="42">
@@ -8116,7 +8139,7 @@
         </is>
       </c>
       <c r="B26" s="41">
-        <f>B7/(Assumptions!$C$109-Assumptions!$C$62)</f>
+        <f>B7/(Assumptions!$C$110-Assumptions!$C$62)</f>
         <v/>
       </c>
       <c r="C26" s="5">
@@ -8156,7 +8179,7 @@
         </is>
       </c>
       <c r="B28" s="41">
-        <f>Assumptions!$C$65*(0.10-Assumptions!$C$62)/(Assumptions!$C$109-Assumptions!$C$62)</f>
+        <f>Assumptions!$C$65*(Assumptions!$C$66-Assumptions!$C$62)/(Assumptions!$C$110-Assumptions!$C$62)</f>
         <v/>
       </c>
       <c r="C28" s="5">
@@ -8242,7 +8265,7 @@
         </is>
       </c>
       <c r="B36" s="6">
-        <f>1-Assumptions!$C$62/0.21812391</f>
+        <f>1-Assumptions!$C$62/0.18754717</f>
         <v/>
       </c>
     </row>
@@ -8253,7 +8276,7 @@
         </is>
       </c>
       <c r="B37" s="9">
-        <f>B35*B36/(Assumptions!$C$109-Assumptions!$C$62)</f>
+        <f>B35*B36/(Assumptions!$C$110-Assumptions!$C$62)</f>
         <v/>
       </c>
     </row>
@@ -8268,7 +8291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8621,23 +8644,23 @@
         </is>
       </c>
       <c r="B13" s="15">
-        <f>Assumptions!C$114</f>
+        <f>Assumptions!C$115</f>
         <v/>
       </c>
       <c r="C13" s="15">
-        <f>Assumptions!D$114</f>
+        <f>Assumptions!D$115</f>
         <v/>
       </c>
       <c r="D13" s="15">
-        <f>Assumptions!E$114</f>
+        <f>Assumptions!E$115</f>
         <v/>
       </c>
       <c r="E13" s="15">
-        <f>Assumptions!F$114</f>
+        <f>Assumptions!F$115</f>
         <v/>
       </c>
       <c r="F13" s="15">
-        <f>Assumptions!G$114</f>
+        <f>Assumptions!G$115</f>
         <v/>
       </c>
     </row>
@@ -8648,23 +8671,23 @@
         </is>
       </c>
       <c r="B14" s="31">
-        <f>Assumptions!C$115</f>
+        <f>Assumptions!C$116</f>
         <v/>
       </c>
       <c r="C14" s="31">
-        <f>Assumptions!D$115</f>
+        <f>Assumptions!D$116</f>
         <v/>
       </c>
       <c r="D14" s="31">
-        <f>Assumptions!E$115</f>
+        <f>Assumptions!E$116</f>
         <v/>
       </c>
       <c r="E14" s="31">
-        <f>Assumptions!F$115</f>
+        <f>Assumptions!F$116</f>
         <v/>
       </c>
       <c r="F14" s="31">
-        <f>Assumptions!G$115</f>
+        <f>Assumptions!G$116</f>
         <v/>
       </c>
     </row>
@@ -8709,7 +8732,7 @@
         </is>
       </c>
       <c r="B18" s="13">
-        <f>'Balance Sheet'!I2+'Balance Sheet'!I3+'Balance Sheet'!I19+Assumptions!$C$82</f>
+        <f>'Balance Sheet'!I2+'Balance Sheet'!I3+'Balance Sheet'!I19+Assumptions!$C$83</f>
         <v/>
       </c>
     </row>
@@ -8759,269 +8782,324 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Terminal reinvestment rate = growth / the return the model itself earns in FY2030E</t>
-        </is>
-      </c>
-      <c r="B22" s="6">
-        <f>Assumptions!$C$62/B19</f>
+          <t>Plus book depreciation (terminal NOPAT is already net of it)</t>
+        </is>
+      </c>
+      <c r="B22" s="13">
+        <f>452.701729</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Terminal free cash flow = terminal NOPAT x (1 less reinvestment)</t>
+          <t>Less maintenance at current cost — book depreciation escalated over half the useful life the company itself discloses</t>
         </is>
       </c>
       <c r="B23" s="13">
-        <f>B21*(1-B22)</f>
+        <f>-722.038275</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Terminal discount rate</t>
-        </is>
-      </c>
-      <c r="B24" s="15">
-        <f>Assumptions!$C$112</f>
+          <t>Less the capital behind real growth</t>
+        </is>
+      </c>
+      <c r="B24" s="13">
+        <f>-0.000000</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
+          <t>Less inflation on working capital</t>
+        </is>
+      </c>
+      <c r="B25" s="13">
+        <f>-767.671686</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Terminal free cash flow to the firm</t>
+        </is>
+      </c>
+      <c r="B26" s="13">
+        <f>B21+B22+B23+B24+B25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Terminal discount rate</t>
+        </is>
+      </c>
+      <c r="B27" s="15">
+        <f>Assumptions!$C$113</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="B25" s="6">
+      <c r="B28" s="6">
         <f>Assumptions!$C$62</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>TERMINAL VALUE</t>
-        </is>
-      </c>
-      <c r="B26" s="28">
-        <f>B23/(B24-B25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>Present value of the terminal value</t>
-        </is>
-      </c>
-      <c r="B27" s="28">
-        <f>B26*F14</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>Sum of the present values of forecast free cash flow</t>
+          <t>TERMINAL VALUE — the free cash flow above, grown one year and capitalised</t>
         </is>
       </c>
       <c r="B29" s="28">
-        <f>SUM(B15:F15)</f>
+        <f>B26*(1+B28)/(B27-B28)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>CORE ENTERPRISE VALUE</t>
-        </is>
-      </c>
-      <c r="B30" s="32">
-        <f>B29+B27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>Terminal value as a percentage of CORE enterprise value</t>
-        </is>
-      </c>
-      <c r="B31" s="10">
-        <f>B27/B30</f>
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>Present value of the terminal value</t>
+        </is>
+      </c>
+      <c r="B30" s="28">
+        <f>B29*F14</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>Terminal value as a percentage of TOTAL enterprise value (both are published)</t>
-        </is>
-      </c>
-      <c r="B32" s="29">
-        <f>B27/(B30+Assumptions!$C$63*Assumptions!$C$64+Assumptions!$C$80+Assumptions!$C$81)</f>
+          <t>Sum of the present values of forecast free cash flow</t>
+        </is>
+      </c>
+      <c r="B32" s="28">
+        <f>SUM(B15:F15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>CORE ENTERPRISE VALUE</t>
+        </is>
+      </c>
+      <c r="B33" s="32">
+        <f>B32+B30</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
+          <t>Terminal value as a percentage of CORE enterprise value</t>
+        </is>
+      </c>
+      <c r="B34" s="10">
+        <f>B30/B33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>Terminal value as a percentage of TOTAL enterprise value (both are published)</t>
+        </is>
+      </c>
+      <c r="B35" s="29">
+        <f>B30/(B33+Assumptions!$C$63*Assumptions!$C$64+Assumptions!$C$81+Assumptions!$C$82)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
           <t>FRAME B — THE SAME MODEL WITH THE CONTESTED JUDGEMENT RESOLVED THE OTHER WAY</t>
         </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>EBIT on Frame B = Frame A EBIT plus the difference in the provision charge</t>
-        </is>
-      </c>
-      <c r="B35" s="13">
-        <f>B6+('Income Statement'!E12-'Income Statement'!E11)</f>
-        <v/>
-      </c>
-      <c r="C35" s="13">
-        <f>C6+('Income Statement'!F12-'Income Statement'!F11)</f>
-        <v/>
-      </c>
-      <c r="D35" s="13">
-        <f>D6+('Income Statement'!G12-'Income Statement'!G11)</f>
-        <v/>
-      </c>
-      <c r="E35" s="13">
-        <f>E6+('Income Statement'!H12-'Income Statement'!H11)</f>
-        <v/>
-      </c>
-      <c r="F35" s="13">
-        <f>F6+('Income Statement'!I12-'Income Statement'!I11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>NOPAT on Frame B</t>
-        </is>
-      </c>
-      <c r="B36" s="13">
-        <f>B35*(1-B7)</f>
-        <v/>
-      </c>
-      <c r="C36" s="13">
-        <f>C35*(1-C7)</f>
-        <v/>
-      </c>
-      <c r="D36" s="13">
-        <f>D35*(1-D7)</f>
-        <v/>
-      </c>
-      <c r="E36" s="13">
-        <f>E35*(1-E7)</f>
-        <v/>
-      </c>
-      <c r="F36" s="13">
-        <f>F35*(1-F7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>Free cash flow to the firm on Frame B</t>
-        </is>
-      </c>
-      <c r="B37" s="13">
-        <f>B36+B9+B10+B11</f>
-        <v/>
-      </c>
-      <c r="C37" s="13">
-        <f>C36+C9+C10+C11</f>
-        <v/>
-      </c>
-      <c r="D37" s="13">
-        <f>D36+D9+D10+D11</f>
-        <v/>
-      </c>
-      <c r="E37" s="13">
-        <f>E36+E9+E10+E11</f>
-        <v/>
-      </c>
-      <c r="F37" s="13">
-        <f>F36+F9+F10+F11</f>
-        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Present value of free cash flow on Frame B</t>
+          <t>EBIT on Frame B = Frame A EBIT plus the difference in the provision charge</t>
         </is>
       </c>
       <c r="B38" s="13">
-        <f>B37*B14</f>
+        <f>B6+('Income Statement'!E12-'Income Statement'!E11)</f>
         <v/>
       </c>
       <c r="C38" s="13">
-        <f>C37*C14</f>
+        <f>C6+('Income Statement'!F12-'Income Statement'!F11)</f>
         <v/>
       </c>
       <c r="D38" s="13">
-        <f>D37*D14</f>
+        <f>D6+('Income Statement'!G12-'Income Statement'!G11)</f>
         <v/>
       </c>
       <c r="E38" s="13">
-        <f>E37*E14</f>
+        <f>E6+('Income Statement'!H12-'Income Statement'!H11)</f>
         <v/>
       </c>
       <c r="F38" s="13">
-        <f>F37*F14</f>
+        <f>F6+('Income Statement'!I12-'Income Statement'!I11)</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Return on invested capital, FY2030E — Frame B's own</t>
-        </is>
-      </c>
-      <c r="B39" s="15">
-        <f>F36/B18</f>
+          <t>NOPAT on Frame B</t>
+        </is>
+      </c>
+      <c r="B39" s="13">
+        <f>B38*(1-B7)</f>
+        <v/>
+      </c>
+      <c r="C39" s="13">
+        <f>C38*(1-C7)</f>
+        <v/>
+      </c>
+      <c r="D39" s="13">
+        <f>D38*(1-D7)</f>
+        <v/>
+      </c>
+      <c r="E39" s="13">
+        <f>E38*(1-E7)</f>
+        <v/>
+      </c>
+      <c r="F39" s="13">
+        <f>F38*(1-F7)</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
+          <t>Free cash flow to the firm on Frame B</t>
+        </is>
+      </c>
+      <c r="B40" s="13">
+        <f>B39+B9+B10+B11</f>
+        <v/>
+      </c>
+      <c r="C40" s="13">
+        <f>C39+C9+C10+C11</f>
+        <v/>
+      </c>
+      <c r="D40" s="13">
+        <f>D39+D9+D10+D11</f>
+        <v/>
+      </c>
+      <c r="E40" s="13">
+        <f>E39+E9+E10+E11</f>
+        <v/>
+      </c>
+      <c r="F40" s="13">
+        <f>F39+F9+F10+F11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Present value of free cash flow on Frame B</t>
+        </is>
+      </c>
+      <c r="B41" s="13">
+        <f>B40*B14</f>
+        <v/>
+      </c>
+      <c r="C41" s="13">
+        <f>C40*C14</f>
+        <v/>
+      </c>
+      <c r="D41" s="13">
+        <f>D40*D14</f>
+        <v/>
+      </c>
+      <c r="E41" s="13">
+        <f>E40*E14</f>
+        <v/>
+      </c>
+      <c r="F41" s="13">
+        <f>F40*F14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Return on invested capital, FY2030E — Frame B's own</t>
+        </is>
+      </c>
+      <c r="B42" s="15">
+        <f>F39/B18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Terminal NOPAT on Frame B, less the parked construction depreciation</t>
+        </is>
+      </c>
+      <c r="B43" s="13">
+        <f>F39*(1+Assumptions!$C$62)-B20*(1-Assumptions!$C$10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Terminal free cash flow on Frame B — the same construction as Frame A: NOPAT plus book depreciation, less maintenance at current cost, less growth capital, less inflation on working capital</t>
+        </is>
+      </c>
+      <c r="B44" s="13">
+        <f>B43+-1037.008231</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
           <t>Terminal value on Frame B</t>
         </is>
       </c>
-      <c r="B40" s="13">
-        <f>(F36*(1+Assumptions!$C$62)-B20*(1-Assumptions!$C$10))*(1-Assumptions!$C$62/B39)/(B24-B25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="11" t="inlineStr">
+      <c r="B45" s="13">
+        <f>B44*(1+B28)/(B27-B28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>Core enterprise value on Frame B</t>
         </is>
       </c>
-      <c r="B41" s="28">
-        <f>SUM(B38:F38)+B40*F14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="B46" s="28">
+        <f>SUM(B41:F41)+B45*F14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>VALUE PER SHARE ON FRAME B</t>
         </is>
       </c>
-      <c r="B42" s="9">
-        <f>(B41+Assumptions!$C$63*Assumptions!$C$64+Assumptions!$C$80+Assumptions!$C$81-Assumptions!$C$103-Assumptions!$C$79)/Assumptions!$C$8</f>
+      <c r="B47" s="9">
+        <f>(B46+Assumptions!$C$63*Assumptions!$C$64+Assumptions!$C$81+Assumptions!$C$82-Assumptions!$C$104-Assumptions!$C$80)/Assumptions!$C$8</f>
         <v/>
       </c>
     </row>
@@ -9185,23 +9263,23 @@
         <v>5193.643343000001</v>
       </c>
       <c r="E4" s="13">
-        <f>Segments!D14*Assumptions!$C$85*Segments!D$31</f>
+        <f>Segments!D14*Assumptions!$C$86*Segments!D$31</f>
         <v/>
       </c>
       <c r="F4" s="13">
-        <f>Segments!E14*Assumptions!$C$85*Segments!E$31</f>
+        <f>Segments!E14*Assumptions!$C$86*Segments!E$31</f>
         <v/>
       </c>
       <c r="G4" s="13">
-        <f>Segments!F14*Assumptions!$C$85*Segments!F$31</f>
+        <f>Segments!F14*Assumptions!$C$86*Segments!F$31</f>
         <v/>
       </c>
       <c r="H4" s="13">
-        <f>Segments!G14*Assumptions!$C$85*Segments!G$31</f>
+        <f>Segments!G14*Assumptions!$C$86*Segments!G$31</f>
         <v/>
       </c>
       <c r="I4" s="13">
-        <f>Segments!H14*Assumptions!$C$85*Segments!H$31</f>
+        <f>Segments!H14*Assumptions!$C$86*Segments!H$31</f>
         <v/>
       </c>
     </row>
@@ -9221,23 +9299,23 @@
         <v>93.49755999999999</v>
       </c>
       <c r="E5" s="13">
-        <f>Segments!D$41*Assumptions!$C$84</f>
+        <f>Segments!D$41*Assumptions!$C$85</f>
         <v/>
       </c>
       <c r="F5" s="13">
-        <f>Segments!E$41*Assumptions!$C$84</f>
+        <f>Segments!E$41*Assumptions!$C$85</f>
         <v/>
       </c>
       <c r="G5" s="13">
-        <f>Segments!F$41*Assumptions!$C$84</f>
+        <f>Segments!F$41*Assumptions!$C$85</f>
         <v/>
       </c>
       <c r="H5" s="13">
-        <f>Segments!G$41*Assumptions!$C$84</f>
+        <f>Segments!G$41*Assumptions!$C$85</f>
         <v/>
       </c>
       <c r="I5" s="13">
-        <f>Segments!H$41*Assumptions!$C$84</f>
+        <f>Segments!H$41*Assumptions!$C$85</f>
         <v/>
       </c>
     </row>
@@ -9546,23 +9624,23 @@
         <v>0</v>
       </c>
       <c r="E14" s="35">
-        <f>-Segments!D41*(1-Assumptions!$C$84)</f>
+        <f>-Segments!D41*(1-Assumptions!$C$85)</f>
         <v/>
       </c>
       <c r="F14" s="35">
-        <f>-Segments!E41*(1-Assumptions!$C$84)</f>
+        <f>-Segments!E41*(1-Assumptions!$C$85)</f>
         <v/>
       </c>
       <c r="G14" s="35">
-        <f>-Segments!F41*(1-Assumptions!$C$84)</f>
+        <f>-Segments!F41*(1-Assumptions!$C$85)</f>
         <v/>
       </c>
       <c r="H14" s="35">
-        <f>-Segments!G41*(1-Assumptions!$C$84)</f>
+        <f>-Segments!G41*(1-Assumptions!$C$85)</f>
         <v/>
       </c>
       <c r="I14" s="35">
-        <f>-Segments!H41*(1-Assumptions!$C$84)</f>
+        <f>-Segments!H41*(1-Assumptions!$C$85)</f>
         <v/>
       </c>
     </row>

--- a/engine/phar_study/EIPICO_Valuation_Model_09082026.xlsx
+++ b/engine/phar_study/EIPICO_Valuation_Model_09082026.xlsx
@@ -611,7 +611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -657,7 +657,7 @@
     <row r="4" ht="46" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Pasted cell class 1 of 3 — audited and disclosed history</t>
+          <t>Pasted cell class 1 of 4 — audited and disclosed history</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -669,7 +669,7 @@
     <row r="5" ht="46" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Pasted cell class 2 of 3 — the unit build's output</t>
+          <t>Pasted cell class 2 of 4 — the unit build's output</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -681,7 +681,7 @@
     <row r="6" ht="46" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Pasted cell class 3 of 3 — whole-model re-runs</t>
+          <t>Pasted cell class 3 of 4 — whole-model re-runs</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -693,46 +693,58 @@
     <row r="7" ht="46" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Blue means input, black means formula</t>
+          <t>Pasted cell class 4 of 4 — the measured-error multipliers</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Blue type is a pasted number. Black type is calculated in the sheet.</t>
+          <t>The factors behind the far-year ranges at the foot of the Income Statement sheet. They are a measurement of how far this method's own projections have landed from what the company later reported, so they are an observation and not something the model can derive. The ranges they produce ARE formulas and move with the projection above them.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="46" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>The contested judgement is carried both ways</t>
+          <t>Blue means input, black means formula</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>The credit-loss and provision charge is the study's single most consequential contested judgement. Frame A treats it as a permanent cost of doing business; Frame B treats it as normalising. Both run all the way through to a value per share and both are published. They are never averaged into one number.</t>
+          <t>Blue type is a pasted number. Black type is calculated in the sheet.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="46" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Currency and units</t>
+          <t>The contested judgement is carried both ways</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Egyptian pounds. Money in millions unless a row says otherwise; per-share figures in pounds; packs and units in millions.</t>
+          <t>The credit-loss and provision charge is the study's single most consequential contested judgement. Frame A treats it as a permanent cost of doing business; Frame B treats it as normalising. Both run all the way through to a value per share and both are published. They are never averaged into one number.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="46" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
+          <t>Currency and units</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Egyptian pounds. Money in millions unless a row says otherwise; per-share figures in pounds; packs and units in millions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
           <t>Basis and date</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Audited CONSOLIDATED financial statements. Share price 127.30 at 2026-08-06; 168.755750 million shares in issue. Fiscal year ends 31 December.</t>
         </is>
@@ -9114,7 +9126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -10115,6 +10127,307 @@
         <v/>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>YEARS THREE TO FIVE AS RANGES — the method replayed on this company's own past, year by year, and scored against what was later reported</t>
+        </is>
+      </c>
+      <c r="K29" s="8" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>Readings</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>MULTIPLY the projection by the factor: above one means the outturn came in ABOVE the projection. The basis is a SPAN — the widest and the narrowest of the readings behind it, never a percentile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Revenue — low of the range</t>
+        </is>
+      </c>
+      <c r="G31" s="13">
+        <f>G2*K31</f>
+        <v/>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="K31" s="16" t="n">
+        <v>1.731530386298975</v>
+      </c>
+      <c r="L31" s="19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Revenue — high of the range</t>
+        </is>
+      </c>
+      <c r="G32" s="13">
+        <f>G2*K32</f>
+        <v/>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="K32" s="16" t="n">
+        <v>2.023455302609483</v>
+      </c>
+      <c r="L32" s="19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Cost of sales — low of the range</t>
+        </is>
+      </c>
+      <c r="G33" s="13">
+        <f>G3*K33</f>
+        <v/>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="K33" s="16" t="n">
+        <v>1.646500820627678</v>
+      </c>
+      <c r="L33" s="19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Cost of sales — high of the range</t>
+        </is>
+      </c>
+      <c r="G34" s="13">
+        <f>G3*K34</f>
+        <v/>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="K34" s="16" t="n">
+        <v>1.946898481956563</v>
+      </c>
+      <c r="L34" s="19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Gross profit — low of the range</t>
+        </is>
+      </c>
+      <c r="G35" s="13">
+        <f>G6*K35</f>
+        <v/>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="K35" s="16" t="n">
+        <v>1.830389697781688</v>
+      </c>
+      <c r="L35" s="19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Gross profit — high of the range</t>
+        </is>
+      </c>
+      <c r="G36" s="13">
+        <f>G6*K36</f>
+        <v/>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="K36" s="16" t="n">
+        <v>2.130056265290247</v>
+      </c>
+      <c r="L36" s="19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Profit for the year — low of the range</t>
+        </is>
+      </c>
+      <c r="G37" s="13">
+        <f>G24*K37</f>
+        <v/>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="K37" s="16" t="n">
+        <v>1.719212803624718</v>
+      </c>
+      <c r="L37" s="19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Profit for the year — high of the range</t>
+        </is>
+      </c>
+      <c r="G38" s="13">
+        <f>G24*K38</f>
+        <v/>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="K38" s="16" t="n">
+        <v>3.405013586428177</v>
+      </c>
+      <c r="L38" s="19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Depreciation and amortisation — low of the range</t>
+        </is>
+      </c>
+      <c r="G39" s="13">
+        <f>G16*K39</f>
+        <v/>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="K39" s="16" t="n">
+        <v>0.56170003273404</v>
+      </c>
+      <c r="L39" s="19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Depreciation and amortisation — high of the range</t>
+        </is>
+      </c>
+      <c r="G40" s="13">
+        <f>G16*K40</f>
+        <v/>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>no measured range</t>
+        </is>
+      </c>
+      <c r="K40" s="16" t="n">
+        <v>0.6032344004250967</v>
+      </c>
+      <c r="L40" s="19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>The fourth and fifth forecast years carry no measured range: the replay covers three years ahead and no further, and none is invented for them.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/engine/phar_study/EIPICO_Valuation_Model_09082026.xlsx
+++ b/engine/phar_study/EIPICO_Valuation_Model_09082026.xlsx
@@ -2780,19 +2780,19 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>52.87174617751678</v>
+        <v>48.10850731158106</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>43.91794786985742</v>
+        <v>39.77511325126461</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>36.63949773388239</v>
+        <v>32.99747064299516</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>30.60944067360987</v>
+        <v>27.37925743745052</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>25.53445407113366</v>
+        <v>22.64818890004397</v>
       </c>
     </row>
     <row r="7">
@@ -2824,19 +2824,19 @@
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>24.89238838802118</v>
+        <v>23.88951618644536</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>27.08100396297257</v>
+        <v>25.60843732759319</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>29.6689241928033</v>
+        <v>27.62520707737693</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>32.78882816716791</v>
+        <v>30.03879318326904</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>36.63949773388239</v>
+        <v>32.99747064299516</v>
       </c>
     </row>
     <row r="10">
@@ -2868,19 +2868,19 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>46.48276755483419</v>
+        <v>42.16724285094727</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>40.68048040441269</v>
+        <v>36.76279124931227</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>36.63949773388239</v>
+        <v>32.99747064299516</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>31.21093776529835</v>
+        <v>27.93707835693304</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>25.51161940550458</v>
+        <v>22.62112480563719</v>
       </c>
     </row>
     <row r="13">
@@ -2912,19 +2912,19 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>55.90961031827637</v>
+        <v>51.3465182256518</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>48.90229665122401</v>
+        <v>44.67413728650396</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>36.63949773388239</v>
+        <v>32.99747064299516</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>27.88035565006691</v>
+        <v>24.65699446906032</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>17.3693851494884</v>
+        <v>14.64842306033853</v>
       </c>
     </row>
     <row r="16">
@@ -2956,19 +2956,19 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>50.75521953556864</v>
+        <v>46.55399859968628</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>43.69735863472546</v>
+        <v>39.77573462134068</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>36.63949773388239</v>
+        <v>32.99747064299516</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>29.5816368330391</v>
+        <v>26.21920666464951</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>22.52377593219603</v>
+        <v>19.440942686304</v>
       </c>
     </row>
     <row r="19">
@@ -3000,19 +3000,19 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>42.79873970509544</v>
+        <v>39.06699370892114</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>39.82120218385909</v>
+        <v>36.13260099179308</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>36.63949773388239</v>
+        <v>32.99747064299516</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>33.24239702293765</v>
+        <v>29.65057380959478</v>
       </c>
       <c r="F20" s="16" t="n">
-        <v>29.61825605669214</v>
+        <v>26.08047464187032</v>
       </c>
     </row>
     <row r="22">
@@ -3044,19 +3044,19 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>42.54294576364056</v>
+        <v>38.5893686066067</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>38.99364180915672</v>
+        <v>35.22839062070677</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>36.63949773388239</v>
+        <v>32.99747064299516</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>34.07581530837081</v>
+        <v>30.56624626531026</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>31.05447660436835</v>
+        <v>27.69837601691766</v>
       </c>
     </row>
     <row r="25">
@@ -3088,19 +3088,19 @@
         </is>
       </c>
       <c r="B26" s="16" t="n">
-        <v>33.91980523946785</v>
+        <v>32.70054369639525</v>
       </c>
       <c r="C26" s="16" t="n">
-        <v>37.23017363970158</v>
+        <v>35.41663310005087</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>41.26937562789497</v>
+        <v>38.71262822213044</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>46.32742747255725</v>
+        <v>42.81928419703347</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>52.87174617751678</v>
+        <v>48.10850731158106</v>
       </c>
     </row>
     <row r="27">
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="B27" s="16" t="n">
-        <v>29.09798312781783</v>
+        <v>27.99471779162108</v>
       </c>
       <c r="C27" s="16" t="n">
-        <v>31.778273158147</v>
+        <v>30.14854174524684</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>34.99453268848002</v>
+        <v>32.71624170205939</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>38.94086106863173</v>
+        <v>35.84770130865045</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>43.91794786985742</v>
+        <v>39.77511325126461</v>
       </c>
     </row>
     <row r="28">
@@ -3132,19 +3132,19 @@
         </is>
       </c>
       <c r="B28" s="16" t="n">
-        <v>24.89238838802118</v>
+        <v>23.88951618644536</v>
       </c>
       <c r="C28" s="16" t="n">
-        <v>27.08100396297257</v>
+        <v>25.60843732759319</v>
       </c>
       <c r="D28" s="16" t="n">
-        <v>29.6689241928033</v>
+        <v>27.62520707737693</v>
       </c>
       <c r="E28" s="16" t="n">
-        <v>32.78882816716791</v>
+        <v>30.03879318326904</v>
       </c>
       <c r="F28" s="16" t="n">
-        <v>36.63949773388239</v>
+        <v>32.99747064299516</v>
       </c>
     </row>
     <row r="29">
@@ -3154,19 +3154,19 @@
         </is>
       </c>
       <c r="B29" s="16" t="n">
-        <v>21.19463710773727</v>
+        <v>20.27933441741304</v>
       </c>
       <c r="C29" s="16" t="n">
-        <v>22.99461214749164</v>
+        <v>21.65769560796352</v>
       </c>
       <c r="D29" s="16" t="n">
-        <v>25.09520754686392</v>
+        <v>23.25138341859161</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>27.5887007173728</v>
+        <v>25.12649378224442</v>
       </c>
       <c r="F29" s="16" t="n">
-        <v>30.60944067360987</v>
+        <v>27.37925743745052</v>
       </c>
     </row>
     <row r="30">
@@ -3176,19 +3176,19 @@
         </is>
       </c>
       <c r="B30" s="16" t="n">
-        <v>17.92025263747544</v>
+        <v>17.08186047120632</v>
       </c>
       <c r="C30" s="16" t="n">
-        <v>19.40957317966708</v>
+        <v>18.19069765675845</v>
       </c>
       <c r="D30" s="16" t="n">
-        <v>21.12709566972723</v>
+        <v>19.45530089136148</v>
       </c>
       <c r="E30" s="16" t="n">
-        <v>23.13790859590948</v>
+        <v>20.9200982649097</v>
       </c>
       <c r="F30" s="16" t="n">
-        <v>25.53445407113366</v>
+        <v>22.64818890004397</v>
       </c>
     </row>
     <row r="32">
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="B33" s="19" t="n">
-        <v>7982.760359839642</v>
+        <v>8870.715521684808</v>
       </c>
     </row>
     <row r="34">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="B34" s="17" t="n">
-        <v>0.3002077087568915</v>
+        <v>0.3228209742828306</v>
       </c>
     </row>
     <row r="35">
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>113.854176701619</v>
+        <v>126.5186435454996</v>
       </c>
     </row>
     <row r="36">
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="B36" s="24" t="n">
-        <v>1.138541767016189</v>
+        <v>1.265186435454996</v>
       </c>
     </row>
   </sheetData>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>Terminal value 81% of core enterprise value, 63% of total</t>
+          <t>Terminal value 80% of core enterprise value, 61% of total</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Terminal value 81% of core enterprise value, 66% of total</t>
+          <t>Terminal value 80% of core enterprise value, 65% of total</t>
         </is>
       </c>
     </row>
@@ -8783,11 +8783,11 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Terminal NOPAT = final-year NOPAT x (1 + growth), less the depreciation the parked construction balance has never been charged</t>
+          <t>Terminal NOPAT, on FY2030E money = final-year NOPAT less the depreciation the parked construction balance has never been charged. It is NOT grown here: the terminal value row below grows the whole free cash flow one year</t>
         </is>
       </c>
       <c r="B21" s="13">
-        <f>F8*(1+Assumptions!$C$62)-B20*(1-Assumptions!$C$10)</f>
+        <f>F8-B20*(1-Assumptions!$C$10)</f>
         <v/>
       </c>
     </row>
@@ -8798,7 +8798,7 @@
         </is>
       </c>
       <c r="B22" s="13">
-        <f>452.701729</f>
+        <f>423.085728</f>
         <v/>
       </c>
     </row>
@@ -8809,7 +8809,7 @@
         </is>
       </c>
       <c r="B23" s="13">
-        <f>-722.038275</f>
+        <f>-674.802126</f>
         <v/>
       </c>
     </row>
@@ -8831,7 +8831,7 @@
         </is>
       </c>
       <c r="B25" s="13">
-        <f>-767.671686</f>
+        <f>-717.450174</f>
         <v/>
       </c>
     </row>
@@ -9063,11 +9063,11 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Terminal NOPAT on Frame B, less the parked construction depreciation</t>
+          <t>Terminal NOPAT on Frame B, on FY2030E money, less the parked construction depreciation — not grown here, for the same reason as Frame A</t>
         </is>
       </c>
       <c r="B43" s="13">
-        <f>F39*(1+Assumptions!$C$62)-B20*(1-Assumptions!$C$10)</f>
+        <f>F39-B20*(1-Assumptions!$C$10)</f>
         <v/>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
         </is>
       </c>
       <c r="B44" s="13">
-        <f>B43+-1037.008231</f>
+        <f>B43+-969.166571</f>
         <v/>
       </c>
     </row>

--- a/engine/phar_study/EIPICO_Valuation_Model_09082026.xlsx
+++ b/engine/phar_study/EIPICO_Valuation_Model_09082026.xlsx
@@ -2780,19 +2780,19 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>48.10850731158106</v>
+        <v>45.68528385393408</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>39.77511325126461</v>
+        <v>37.81150099018128</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>32.99747064299516</v>
+        <v>31.37379902733586</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>27.37925743745052</v>
+        <v>26.01416352323024</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>22.64818890004397</v>
+        <v>21.4844134990437</v>
       </c>
     </row>
     <row r="7">
@@ -2824,19 +2824,19 @@
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>23.88951618644536</v>
+        <v>22.8494533223467</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>25.60843732759319</v>
+        <v>24.47046167069734</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>27.62520707737693</v>
+        <v>26.3649795393194</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>30.03879318326904</v>
+        <v>28.621995629933</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>32.99747064299516</v>
+        <v>31.37379902733586</v>
       </c>
     </row>
     <row r="10">
@@ -2852,7 +2852,7 @@
         <v>0.55</v>
       </c>
       <c r="D10" s="51" t="n">
-        <v>0.629</v>
+        <v>0.6658188407423365</v>
       </c>
       <c r="E10" s="51" t="n">
         <v>0.75</v>
@@ -2874,7 +2874,7 @@
         <v>36.76279124931227</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>32.99747064299516</v>
+        <v>31.37379902733586</v>
       </c>
       <c r="E11" s="16" t="n">
         <v>27.93707835693304</v>
@@ -2912,19 +2912,19 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>51.3465182256518</v>
+        <v>49.26491319840814</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>44.67413728650396</v>
+        <v>42.7590534998364</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>32.99747064299516</v>
+        <v>31.37379902733586</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>24.65699446906032</v>
+        <v>23.24147440412117</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>14.64842306033853</v>
+        <v>13.4826848562636</v>
       </c>
     </row>
     <row r="16">
@@ -2956,19 +2956,19 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>46.55399859968628</v>
+        <v>44.63956596764732</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>39.77573462134068</v>
+        <v>38.00668249749155</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>32.99747064299516</v>
+        <v>31.37379902733586</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>26.21920666464951</v>
+        <v>24.74091555718003</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>19.440942686304</v>
+        <v>18.10803208702435</v>
       </c>
     </row>
     <row r="19">
@@ -3000,19 +3000,19 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>39.06699370892114</v>
+        <v>37.36532565503385</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>36.13260099179308</v>
+        <v>34.4684633681824</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>32.99747064299516</v>
+        <v>31.37379902733586</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>29.65057380959478</v>
+        <v>28.0704744073638</v>
       </c>
       <c r="F20" s="16" t="n">
-        <v>26.08047464187032</v>
+        <v>24.54723077671931</v>
       </c>
     </row>
     <row r="22">
@@ -3044,19 +3044,19 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>38.5893686066067</v>
+        <v>36.77869012904124</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>35.22839062070677</v>
+        <v>33.53006026952217</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>32.99747064299516</v>
+        <v>31.37379902733586</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>30.56624626531026</v>
+        <v>29.02402305899556</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>27.69837601691766</v>
+        <v>26.252358655231</v>
       </c>
     </row>
     <row r="25">
@@ -3088,19 +3088,19 @@
         </is>
       </c>
       <c r="B26" s="16" t="n">
-        <v>32.70054369639525</v>
+        <v>31.34494284548571</v>
       </c>
       <c r="C26" s="16" t="n">
-        <v>35.41663310005087</v>
+        <v>33.89811072289919</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>38.71262822213044</v>
+        <v>36.98163985573206</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>42.81928419703347</v>
+        <v>40.80133138880694</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>48.10850731158106</v>
+        <v>45.68528385393408</v>
       </c>
     </row>
     <row r="27">
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="B27" s="16" t="n">
-        <v>27.99471779162108</v>
+        <v>26.81224996276908</v>
       </c>
       <c r="C27" s="16" t="n">
-        <v>30.14854174524684</v>
+        <v>28.8405802906386</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>32.71624170205939</v>
+        <v>31.24838047980015</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>35.84770130865045</v>
+        <v>34.1699621733944</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>39.77511325126461</v>
+        <v>37.81150099018128</v>
       </c>
     </row>
     <row r="28">
@@ -3132,19 +3132,19 @@
         </is>
       </c>
       <c r="B28" s="16" t="n">
-        <v>23.88951618644536</v>
+        <v>22.8494533223467</v>
       </c>
       <c r="C28" s="16" t="n">
-        <v>25.60843732759319</v>
+        <v>24.47046167069734</v>
       </c>
       <c r="D28" s="16" t="n">
-        <v>27.62520707737693</v>
+        <v>26.3649795393194</v>
       </c>
       <c r="E28" s="16" t="n">
-        <v>30.03879318326904</v>
+        <v>28.621995629933</v>
       </c>
       <c r="F28" s="16" t="n">
-        <v>32.99747064299516</v>
+        <v>31.37379902733586</v>
       </c>
     </row>
     <row r="29">
@@ -3154,19 +3154,19 @@
         </is>
       </c>
       <c r="B29" s="16" t="n">
-        <v>20.27933441741304</v>
+        <v>19.35781412337375</v>
       </c>
       <c r="C29" s="16" t="n">
-        <v>21.65769560796352</v>
+        <v>20.65893665542676</v>
       </c>
       <c r="D29" s="16" t="n">
-        <v>23.25138341859161</v>
+        <v>22.15790078568526</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>25.12649378224442</v>
+        <v>23.9142656428088</v>
       </c>
       <c r="F29" s="16" t="n">
-        <v>27.37925743745052</v>
+        <v>26.01416352323024</v>
       </c>
     </row>
     <row r="30">
@@ -3176,19 +3176,19 @@
         </is>
       </c>
       <c r="B30" s="16" t="n">
-        <v>17.08186047120632</v>
+        <v>16.26006785654848</v>
       </c>
       <c r="C30" s="16" t="n">
-        <v>18.19069765675845</v>
+        <v>17.3073954172165</v>
       </c>
       <c r="D30" s="16" t="n">
-        <v>19.45530089136148</v>
+        <v>18.49776590833174</v>
       </c>
       <c r="E30" s="16" t="n">
-        <v>20.9200982649097</v>
+        <v>19.87124732344099</v>
       </c>
       <c r="F30" s="16" t="n">
-        <v>22.64818890004397</v>
+        <v>21.4844134990437</v>
       </c>
     </row>
     <row r="32">
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="B33" s="19" t="n">
-        <v>8870.715521684808</v>
+        <v>9321.885127781243</v>
       </c>
     </row>
     <row r="34">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="B34" s="17" t="n">
-        <v>0.3228209742828306</v>
+        <v>0.3337598757730512</v>
       </c>
     </row>
     <row r="35">
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>126.5186435454996</v>
+        <v>132.9534532778984</v>
       </c>
     </row>
     <row r="36">
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="B36" s="24" t="n">
-        <v>1.265186435454996</v>
+        <v>1.329534532778984</v>
       </c>
     </row>
   </sheetData>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>Terminal value 80% of core enterprise value, 61% of total</t>
+          <t>Terminal value 79% of core enterprise value, 61% of total</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Terminal value 80% of core enterprise value, 65% of total</t>
+          <t>Terminal value 79% of core enterprise value, 64% of total</t>
         </is>
       </c>
     </row>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Justified 1.19 times book</t>
+          <t>Justified 1.16 times book</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
         </is>
       </c>
       <c r="C49" s="22" t="n">
-        <v>0.629</v>
+        <v>0.6658188407423365</v>
       </c>
     </row>
     <row r="50" ht="26" customHeight="1">
